--- a/Översikt HYLTE.xlsx
+++ b/Översikt HYLTE.xlsx
@@ -601,7 +601,7 @@
         <v>46090</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -718,7 +718,7 @@
         <v>45265</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -834,7 +834,7 @@
         <v>46066</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -945,7 +945,7 @@
         <v>44873</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1054,7 +1054,7 @@
         <v>45348</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1166,7 +1166,7 @@
         <v>45719</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1274,7 +1274,7 @@
         <v>45245</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1385,7 +1385,7 @@
         <v>46268</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1492,7 +1492,7 @@
         <v>45230</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1599,7 +1599,7 @@
         <v>45737</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1706,7 +1706,7 @@
         <v>46141</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1813,7 +1813,7 @@
         <v>46161</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1920,7 +1920,7 @@
         <v>44839</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2030,7 +2030,7 @@
         <v>46048</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2136,7 +2136,7 @@
         <v>45904</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2246,7 +2246,7 @@
         <v>45841</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2356,7 +2356,7 @@
         <v>45099</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2466,7 +2466,7 @@
         <v>46130</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2572,7 +2572,7 @@
         <v>44648</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2677,7 +2677,7 @@
         <v>44651</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2782,7 +2782,7 @@
         <v>44876</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2887,7 +2887,7 @@
         <v>45245</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2992,7 +2992,7 @@
         <v>45343</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3097,7 +3097,7 @@
         <v>45476</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3207,7 +3207,7 @@
         <v>45163</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3312,7 +3312,7 @@
         <v>45299</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3421,7 +3421,7 @@
         <v>45245</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3526,7 +3526,7 @@
         <v>45593</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3631,7 +3631,7 @@
         <v>45153</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3745,7 +3745,7 @@
         <v>45186</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3850,7 +3850,7 @@
         <v>45085</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3959,7 +3959,7 @@
         <v>45617</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4064,7 +4064,7 @@
         <v>45253</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4169,7 +4169,7 @@
         <v>45754</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4274,7 +4274,7 @@
         <v>46253</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4384,7 +4384,7 @@
         <v>44481</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4457,7 +4457,7 @@
         <v>44810</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4530,7 +4530,7 @@
         <v>44600</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4603,7 +4603,7 @@
         <v>44529</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4676,7 +4676,7 @@
         <v>44557</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4749,7 +4749,7 @@
         <v>44483</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4822,7 +4822,7 @@
         <v>44705</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4895,7 +4895,7 @@
         <v>44778</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4968,7 +4968,7 @@
         <v>44488</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5041,7 +5041,7 @@
         <v>44475</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5114,7 +5114,7 @@
         <v>44624</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5187,7 +5187,7 @@
         <v>44812</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5260,7 +5260,7 @@
         <v>44638</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5333,7 +5333,7 @@
         <v>44498</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5406,7 +5406,7 @@
         <v>44845</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5479,7 +5479,7 @@
         <v>44559</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5552,7 +5552,7 @@
         <v>44659</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5630,7 +5630,7 @@
         <v>44578</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5703,7 +5703,7 @@
         <v>44756</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5776,7 +5776,7 @@
         <v>44501</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5849,7 +5849,7 @@
         <v>44651</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5922,7 +5922,7 @@
         <v>44711</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5995,7 +5995,7 @@
         <v>44487</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6073,7 +6073,7 @@
         <v>44735</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6146,7 +6146,7 @@
         <v>44477</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6219,7 +6219,7 @@
         <v>44489</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6292,7 +6292,7 @@
         <v>44834</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6365,7 +6365,7 @@
         <v>44469</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6438,7 +6438,7 @@
         <v>44796</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6511,7 +6511,7 @@
         <v>44502</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6584,7 +6584,7 @@
         <v>44631</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6657,7 +6657,7 @@
         <v>44876</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6730,7 +6730,7 @@
         <v>44659</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6803,7 +6803,7 @@
         <v>44644</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6876,7 +6876,7 @@
         <v>44515</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6954,7 +6954,7 @@
         <v>44778</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7027,7 +7027,7 @@
         <v>44482</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7100,7 +7100,7 @@
         <v>44482</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7173,7 +7173,7 @@
         <v>44867</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7246,7 +7246,7 @@
         <v>44634</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7319,7 +7319,7 @@
         <v>44505</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7392,7 +7392,7 @@
         <v>44728</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7465,7 +7465,7 @@
         <v>44714</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7538,7 +7538,7 @@
         <v>44795</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7611,7 +7611,7 @@
         <v>44818</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7684,7 +7684,7 @@
         <v>44801</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7757,7 +7757,7 @@
         <v>44596</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7835,7 +7835,7 @@
         <v>44644</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7908,7 +7908,7 @@
         <v>44523</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7981,7 +7981,7 @@
         <v>44500</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8054,7 +8054,7 @@
         <v>44727</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8127,7 +8127,7 @@
         <v>44705</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8200,7 +8200,7 @@
         <v>44659</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8278,7 +8278,7 @@
         <v>44659</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8356,7 +8356,7 @@
         <v>44494</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8429,7 +8429,7 @@
         <v>44757</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8502,7 +8502,7 @@
         <v>44495</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8575,7 +8575,7 @@
         <v>45460</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8648,7 +8648,7 @@
         <v>45132</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8721,7 +8721,7 @@
         <v>44487</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8799,7 +8799,7 @@
         <v>44851</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8872,7 +8872,7 @@
         <v>44851</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8945,7 +8945,7 @@
         <v>45062</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -9018,7 +9018,7 @@
         <v>45002</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9091,7 +9091,7 @@
         <v>45568</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9164,7 +9164,7 @@
         <v>44900</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9242,7 +9242,7 @@
         <v>44476</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9315,7 +9315,7 @@
         <v>44958</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9388,7 +9388,7 @@
         <v>44899</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9461,7 +9461,7 @@
         <v>45107</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9534,7 +9534,7 @@
         <v>44559</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9607,7 +9607,7 @@
         <v>45211</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9680,7 +9680,7 @@
         <v>45548</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9753,7 +9753,7 @@
         <v>45254</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9826,7 +9826,7 @@
         <v>45254</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9899,7 +9899,7 @@
         <v>45589</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9972,7 +9972,7 @@
         <v>45254</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -10045,7 +10045,7 @@
         <v>45254</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10118,7 +10118,7 @@
         <v>45258</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10191,7 +10191,7 @@
         <v>45229</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10264,7 +10264,7 @@
         <v>45098</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10342,7 +10342,7 @@
         <v>44868</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10415,7 +10415,7 @@
         <v>45715</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10488,7 +10488,7 @@
         <v>44714</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10566,7 +10566,7 @@
         <v>44910</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10639,7 +10639,7 @@
         <v>44823</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10712,7 +10712,7 @@
         <v>45104</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -10785,7 +10785,7 @@
         <v>45684</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10858,7 +10858,7 @@
         <v>45600</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10931,7 +10931,7 @@
         <v>45352</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -11004,7 +11004,7 @@
         <v>45352</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -11077,7 +11077,7 @@
         <v>44719</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11150,7 +11150,7 @@
         <v>45638</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11223,7 +11223,7 @@
         <v>44896</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11296,7 +11296,7 @@
         <v>45539</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11369,7 +11369,7 @@
         <v>45434</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11442,7 +11442,7 @@
         <v>45538</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11515,7 +11515,7 @@
         <v>45163</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11588,7 +11588,7 @@
         <v>45145</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11661,7 +11661,7 @@
         <v>45089</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -11734,7 +11734,7 @@
         <v>45194</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -11807,7 +11807,7 @@
         <v>44482</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -11880,7 +11880,7 @@
         <v>44701</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -11958,7 +11958,7 @@
         <v>45252</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -12031,7 +12031,7 @@
         <v>44901</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -12104,7 +12104,7 @@
         <v>45182</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12177,7 +12177,7 @@
         <v>45181</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12250,7 +12250,7 @@
         <v>44495</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12323,7 +12323,7 @@
         <v>45694</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12396,7 +12396,7 @@
         <v>45441</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -12474,7 +12474,7 @@
         <v>45441</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -12547,7 +12547,7 @@
         <v>45310</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -12620,7 +12620,7 @@
         <v>45229</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -12693,7 +12693,7 @@
         <v>44999</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -12766,7 +12766,7 @@
         <v>45527</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -12839,7 +12839,7 @@
         <v>44847</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -12912,7 +12912,7 @@
         <v>44778</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -12985,7 +12985,7 @@
         <v>45132</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -13058,7 +13058,7 @@
         <v>45478</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -13131,7 +13131,7 @@
         <v>45019</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13204,7 +13204,7 @@
         <v>45254</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13277,7 +13277,7 @@
         <v>45331</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13350,7 +13350,7 @@
         <v>45287</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -13423,7 +13423,7 @@
         <v>45366</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -13496,7 +13496,7 @@
         <v>45173</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -13569,7 +13569,7 @@
         <v>45245</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -13642,7 +13642,7 @@
         <v>45817</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -13715,7 +13715,7 @@
         <v>45782</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -13788,7 +13788,7 @@
         <v>45485</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -13861,7 +13861,7 @@
         <v>45560</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -13934,7 +13934,7 @@
         <v>45673</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -14007,7 +14007,7 @@
         <v>45834</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -14080,7 +14080,7 @@
         <v>45674</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -14153,7 +14153,7 @@
         <v>45687</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14226,7 +14226,7 @@
         <v>46084</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14299,7 +14299,7 @@
         <v>45436</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -14372,7 +14372,7 @@
         <v>44865</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -14445,7 +14445,7 @@
         <v>45454</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -14518,7 +14518,7 @@
         <v>45748</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -14591,7 +14591,7 @@
         <v>45890</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -14664,7 +14664,7 @@
         <v>45891</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -14742,7 +14742,7 @@
         <v>45891</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -14820,7 +14820,7 @@
         <v>44701</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -14898,7 +14898,7 @@
         <v>45300</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -14971,7 +14971,7 @@
         <v>44699</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -15044,7 +15044,7 @@
         <v>45790</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -15117,7 +15117,7 @@
         <v>45456</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -15190,7 +15190,7 @@
         <v>45429</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -15263,7 +15263,7 @@
         <v>45897</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -15336,7 +15336,7 @@
         <v>45405</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -15409,7 +15409,7 @@
         <v>45839</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -15482,7 +15482,7 @@
         <v>45840</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -15555,7 +15555,7 @@
         <v>44797</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -15628,7 +15628,7 @@
         <v>45898</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -15701,7 +15701,7 @@
         <v>45897</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -15774,7 +15774,7 @@
         <v>45035</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -15847,7 +15847,7 @@
         <v>45531</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -15920,7 +15920,7 @@
         <v>45775</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -15993,7 +15993,7 @@
         <v>45840</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -16071,7 +16071,7 @@
         <v>45905</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -16144,7 +16144,7 @@
         <v>45848</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -16217,7 +16217,7 @@
         <v>45259</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -16290,7 +16290,7 @@
         <v>45169</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -16363,7 +16363,7 @@
         <v>45104</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -16436,7 +16436,7 @@
         <v>44900</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -16509,7 +16509,7 @@
         <v>45838</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -16582,7 +16582,7 @@
         <v>45910</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -16655,7 +16655,7 @@
         <v>45910</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -16728,7 +16728,7 @@
         <v>44974</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -16801,7 +16801,7 @@
         <v>45617</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -16874,7 +16874,7 @@
         <v>45162</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -16947,7 +16947,7 @@
         <v>44694</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -17020,7 +17020,7 @@
         <v>45502</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -17093,7 +17093,7 @@
         <v>44974</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -17166,7 +17166,7 @@
         <v>45091</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -17239,7 +17239,7 @@
         <v>45918</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -17312,7 +17312,7 @@
         <v>44926</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -17390,7 +17390,7 @@
         <v>45922</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -17463,7 +17463,7 @@
         <v>45604</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -17536,7 +17536,7 @@
         <v>45097</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -17609,7 +17609,7 @@
         <v>45922</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -17682,7 +17682,7 @@
         <v>45922</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -17755,7 +17755,7 @@
         <v>45477</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -17828,7 +17828,7 @@
         <v>45265</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -17901,7 +17901,7 @@
         <v>45924</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -17974,7 +17974,7 @@
         <v>45084</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -18047,7 +18047,7 @@
         <v>45926</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -18120,7 +18120,7 @@
         <v>45926</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -18193,7 +18193,7 @@
         <v>45926</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -18266,7 +18266,7 @@
         <v>45929</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -18339,7 +18339,7 @@
         <v>44953</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -18412,7 +18412,7 @@
         <v>45019</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -18485,7 +18485,7 @@
         <v>45299</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -18558,7 +18558,7 @@
         <v>45931</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -18631,7 +18631,7 @@
         <v>45930</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -18704,7 +18704,7 @@
         <v>45931</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -18777,7 +18777,7 @@
         <v>45933</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -18850,7 +18850,7 @@
         <v>45933</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -18923,7 +18923,7 @@
         <v>45933</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -18996,7 +18996,7 @@
         <v>45645</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -19069,7 +19069,7 @@
         <v>45936</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -19142,7 +19142,7 @@
         <v>45366</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -19220,7 +19220,7 @@
         <v>45936</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -19293,7 +19293,7 @@
         <v>45936</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -19366,7 +19366,7 @@
         <v>45505</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -19439,7 +19439,7 @@
         <v>44903</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -19512,7 +19512,7 @@
         <v>45938</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -19585,7 +19585,7 @@
         <v>45939</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -19663,7 +19663,7 @@
         <v>45937</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -19736,7 +19736,7 @@
         <v>45096</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -19809,7 +19809,7 @@
         <v>45167</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -19882,7 +19882,7 @@
         <v>45352</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -19955,7 +19955,7 @@
         <v>46148</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -20028,7 +20028,7 @@
         <v>45944</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -20101,7 +20101,7 @@
         <v>45254</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -20174,7 +20174,7 @@
         <v>45254</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -20247,7 +20247,7 @@
         <v>45203</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -20320,7 +20320,7 @@
         <v>44481</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -20393,7 +20393,7 @@
         <v>46153</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -20466,7 +20466,7 @@
         <v>44750</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -20539,7 +20539,7 @@
         <v>44714</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -20612,7 +20612,7 @@
         <v>45441</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -20685,7 +20685,7 @@
         <v>45441</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -20758,7 +20758,7 @@
         <v>45441</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -20831,7 +20831,7 @@
         <v>45377</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -20909,7 +20909,7 @@
         <v>46153</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -20982,7 +20982,7 @@
         <v>46153</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -21055,7 +21055,7 @@
         <v>46153</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -21128,7 +21128,7 @@
         <v>46153</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -21201,7 +21201,7 @@
         <v>45957</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -21274,7 +21274,7 @@
         <v>46153</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -21347,7 +21347,7 @@
         <v>46153</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -21420,7 +21420,7 @@
         <v>45709</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -21493,7 +21493,7 @@
         <v>45170</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -21566,7 +21566,7 @@
         <v>45961</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -21639,7 +21639,7 @@
         <v>45922</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -21712,7 +21712,7 @@
         <v>44869</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -21785,7 +21785,7 @@
         <v>45754</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -21858,7 +21858,7 @@
         <v>45961</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -21931,7 +21931,7 @@
         <v>45751</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -22009,7 +22009,7 @@
         <v>45268</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -22082,7 +22082,7 @@
         <v>45441</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -22160,7 +22160,7 @@
         <v>45597</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -22233,7 +22233,7 @@
         <v>45092</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -22306,7 +22306,7 @@
         <v>45378</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -22379,7 +22379,7 @@
         <v>45382</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -22452,7 +22452,7 @@
         <v>45972</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -22525,7 +22525,7 @@
         <v>45972</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -22598,7 +22598,7 @@
         <v>45972</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -22671,7 +22671,7 @@
         <v>45429</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -22744,7 +22744,7 @@
         <v>45371</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -22817,7 +22817,7 @@
         <v>45979</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -22890,7 +22890,7 @@
         <v>45411</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -22963,7 +22963,7 @@
         <v>45981</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -23036,7 +23036,7 @@
         <v>45558</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -23109,7 +23109,7 @@
         <v>45981</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -23182,7 +23182,7 @@
         <v>44950</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -23255,7 +23255,7 @@
         <v>45246</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -23328,7 +23328,7 @@
         <v>45246</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -23401,7 +23401,7 @@
         <v>44697</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -23474,7 +23474,7 @@
         <v>46155</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -23547,7 +23547,7 @@
         <v>45580</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -23620,7 +23620,7 @@
         <v>45987</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -23693,7 +23693,7 @@
         <v>45159</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -23766,7 +23766,7 @@
         <v>46161</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -23844,7 +23844,7 @@
         <v>46161</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -23917,7 +23917,7 @@
         <v>45541</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -23990,7 +23990,7 @@
         <v>45989</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -24063,7 +24063,7 @@
         <v>46161</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -24141,7 +24141,7 @@
         <v>44635</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -24219,7 +24219,7 @@
         <v>45462</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -24292,7 +24292,7 @@
         <v>46161</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -24370,7 +24370,7 @@
         <v>46161</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -24443,7 +24443,7 @@
         <v>45042</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -24516,7 +24516,7 @@
         <v>46161</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -24594,7 +24594,7 @@
         <v>45352</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -24667,7 +24667,7 @@
         <v>44970</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -24740,7 +24740,7 @@
         <v>45568</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -24813,7 +24813,7 @@
         <v>45145</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -24886,7 +24886,7 @@
         <v>45995</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -24959,7 +24959,7 @@
         <v>44510</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -25032,7 +25032,7 @@
         <v>45624</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -25105,7 +25105,7 @@
         <v>45170</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -25178,7 +25178,7 @@
         <v>44965</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -25256,7 +25256,7 @@
         <v>44477</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -25329,7 +25329,7 @@
         <v>45257</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -25402,7 +25402,7 @@
         <v>45538</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -25475,7 +25475,7 @@
         <v>45456</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -25548,7 +25548,7 @@
         <v>45926</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -25621,7 +25621,7 @@
         <v>45351</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -25694,7 +25694,7 @@
         <v>45182</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -25767,7 +25767,7 @@
         <v>44489</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -25840,7 +25840,7 @@
         <v>45456</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -25913,7 +25913,7 @@
         <v>46169</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -25986,7 +25986,7 @@
         <v>45198</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -26059,7 +26059,7 @@
         <v>45752</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -26137,7 +26137,7 @@
         <v>44735</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -26210,7 +26210,7 @@
         <v>44539</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -26283,7 +26283,7 @@
         <v>44460</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -26356,7 +26356,7 @@
         <v>44460</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -26429,7 +26429,7 @@
         <v>46169</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -26502,7 +26502,7 @@
         <v>46169</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -26575,7 +26575,7 @@
         <v>45153</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -26648,7 +26648,7 @@
         <v>46020</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -26721,7 +26721,7 @@
         <v>45568</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -26794,7 +26794,7 @@
         <v>44970</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -26867,7 +26867,7 @@
         <v>44970</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -26940,7 +26940,7 @@
         <v>44641</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -27013,7 +27013,7 @@
         <v>45342</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -27091,7 +27091,7 @@
         <v>45737</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -27164,7 +27164,7 @@
         <v>45483</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -27237,7 +27237,7 @@
         <v>46170</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -27310,7 +27310,7 @@
         <v>46030</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -27383,7 +27383,7 @@
         <v>45061</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -27456,7 +27456,7 @@
         <v>44893</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -27529,7 +27529,7 @@
         <v>46171</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -27602,7 +27602,7 @@
         <v>45084</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -27675,7 +27675,7 @@
         <v>46174</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -27748,7 +27748,7 @@
         <v>44900</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -27821,7 +27821,7 @@
         <v>46042</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -27894,7 +27894,7 @@
         <v>45572</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -27967,7 +27967,7 @@
         <v>46042</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -28040,7 +28040,7 @@
         <v>45002</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -28113,7 +28113,7 @@
         <v>46044</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -28186,7 +28186,7 @@
         <v>46044</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -28259,7 +28259,7 @@
         <v>46044</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -28332,7 +28332,7 @@
         <v>44847</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -28405,7 +28405,7 @@
         <v>46174</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -28478,7 +28478,7 @@
         <v>46044</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -28551,7 +28551,7 @@
         <v>46175</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -28624,7 +28624,7 @@
         <v>46048</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -28697,7 +28697,7 @@
         <v>46049</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -28770,7 +28770,7 @@
         <v>46048</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -28843,7 +28843,7 @@
         <v>46048</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -28916,7 +28916,7 @@
         <v>46048</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -28989,7 +28989,7 @@
         <v>46048</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -29062,7 +29062,7 @@
         <v>46048</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -29135,7 +29135,7 @@
         <v>46048</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -29208,7 +29208,7 @@
         <v>46048</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -29281,7 +29281,7 @@
         <v>46048</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -29354,7 +29354,7 @@
         <v>46048</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -29427,7 +29427,7 @@
         <v>46048</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -29500,7 +29500,7 @@
         <v>46048</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -29573,7 +29573,7 @@
         <v>45432</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -29646,7 +29646,7 @@
         <v>46175</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -29719,7 +29719,7 @@
         <v>46174</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -29792,7 +29792,7 @@
         <v>46174</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -29865,7 +29865,7 @@
         <v>46052</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -29938,7 +29938,7 @@
         <v>45677</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -30011,7 +30011,7 @@
         <v>46055</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -30084,7 +30084,7 @@
         <v>46052</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -30157,7 +30157,7 @@
         <v>46178</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -30230,7 +30230,7 @@
         <v>45253</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -30303,7 +30303,7 @@
         <v>45253</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -30376,7 +30376,7 @@
         <v>46178</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -30449,7 +30449,7 @@
         <v>46057</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -30522,7 +30522,7 @@
         <v>45104</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -30595,7 +30595,7 @@
         <v>46062</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -30668,7 +30668,7 @@
         <v>46062</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -30741,7 +30741,7 @@
         <v>45715</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -30814,7 +30814,7 @@
         <v>45117</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -30887,7 +30887,7 @@
         <v>46064</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -30960,7 +30960,7 @@
         <v>45357</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -31033,7 +31033,7 @@
         <v>46065</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -31106,7 +31106,7 @@
         <v>45107</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -31179,7 +31179,7 @@
         <v>45400</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -31252,7 +31252,7 @@
         <v>46070</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -31325,7 +31325,7 @@
         <v>45267</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -31398,7 +31398,7 @@
         <v>46070</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -31471,7 +31471,7 @@
         <v>46183</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -31544,7 +31544,7 @@
         <v>44726</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -31617,7 +31617,7 @@
         <v>45351</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -31690,7 +31690,7 @@
         <v>45426</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -31763,7 +31763,7 @@
         <v>44872</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -31836,7 +31836,7 @@
         <v>45456</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -31909,7 +31909,7 @@
         <v>45091</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -31982,7 +31982,7 @@
         <v>46084</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -32055,7 +32055,7 @@
         <v>46084</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -32128,7 +32128,7 @@
         <v>46185</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -32201,7 +32201,7 @@
         <v>45462</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -32274,7 +32274,7 @@
         <v>46087</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -32347,7 +32347,7 @@
         <v>44469</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -32420,7 +32420,7 @@
         <v>46188</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -32493,7 +32493,7 @@
         <v>46188</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -32566,7 +32566,7 @@
         <v>45114</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -32639,7 +32639,7 @@
         <v>45225</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -32712,7 +32712,7 @@
         <v>46093</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -32785,7 +32785,7 @@
         <v>46093</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -32858,7 +32858,7 @@
         <v>45246</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -32931,7 +32931,7 @@
         <v>46093</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -33004,7 +33004,7 @@
         <v>45316</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -33082,7 +33082,7 @@
         <v>44601</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -33155,7 +33155,7 @@
         <v>44575</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -33228,7 +33228,7 @@
         <v>46196</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -33301,7 +33301,7 @@
         <v>45170</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -33374,7 +33374,7 @@
         <v>45334</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -33447,7 +33447,7 @@
         <v>45169</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -33520,7 +33520,7 @@
         <v>44729</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -33593,7 +33593,7 @@
         <v>46057</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -33666,7 +33666,7 @@
         <v>46199</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -33739,7 +33739,7 @@
         <v>46057</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -33812,7 +33812,7 @@
         <v>44796</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -33885,7 +33885,7 @@
         <v>46111</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -33958,7 +33958,7 @@
         <v>44995</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -34031,7 +34031,7 @@
         <v>44951</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -34104,7 +34104,7 @@
         <v>46111</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -34177,7 +34177,7 @@
         <v>46111</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -34250,7 +34250,7 @@
         <v>45110</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -34323,7 +34323,7 @@
         <v>46244</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -34396,7 +34396,7 @@
         <v>45432</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -34469,7 +34469,7 @@
         <v>44530</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -34542,7 +34542,7 @@
         <v>46120</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -34615,7 +34615,7 @@
         <v>46120</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -34688,7 +34688,7 @@
         <v>44980</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -34761,7 +34761,7 @@
         <v>46122</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -34834,7 +34834,7 @@
         <v>45350</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -34907,7 +34907,7 @@
         <v>45229</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -34980,7 +34980,7 @@
         <v>46121</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -35053,7 +35053,7 @@
         <v>46121</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -35126,7 +35126,7 @@
         <v>46121</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -35199,7 +35199,7 @@
         <v>46122</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -35272,7 +35272,7 @@
         <v>46122</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -35345,7 +35345,7 @@
         <v>46121</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -35418,7 +35418,7 @@
         <v>46122</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -35491,7 +35491,7 @@
         <v>46121</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -35564,7 +35564,7 @@
         <v>46121</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -35637,7 +35637,7 @@
         <v>46121</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -35710,7 +35710,7 @@
         <v>46121</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -35783,7 +35783,7 @@
         <v>45245</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -35856,7 +35856,7 @@
         <v>45531</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -35929,7 +35929,7 @@
         <v>46128</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -36002,7 +36002,7 @@
         <v>45352</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -36075,7 +36075,7 @@
         <v>45208</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -36148,7 +36148,7 @@
         <v>46245</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -36221,7 +36221,7 @@
         <v>45110</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -36294,7 +36294,7 @@
         <v>44756</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -36367,7 +36367,7 @@
         <v>45390</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -36440,7 +36440,7 @@
         <v>45238</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -36513,7 +36513,7 @@
         <v>44866</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -36586,7 +36586,7 @@
         <v>45989</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -36659,7 +36659,7 @@
         <v>45406</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -36732,7 +36732,7 @@
         <v>45414</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -36805,7 +36805,7 @@
         <v>45839</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -36878,7 +36878,7 @@
         <v>46084</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -36951,7 +36951,7 @@
         <v>45229</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -37024,7 +37024,7 @@
         <v>45524</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -37097,7 +37097,7 @@
         <v>44651</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -37170,7 +37170,7 @@
         <v>45092</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -37243,7 +37243,7 @@
         <v>46209</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -37316,7 +37316,7 @@
         <v>45455</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -37389,7 +37389,7 @@
         <v>46206</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -37462,7 +37462,7 @@
         <v>45051</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -37535,7 +37535,7 @@
         <v>46248</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -37608,7 +37608,7 @@
         <v>46247</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -37681,7 +37681,7 @@
         <v>46224</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -37754,7 +37754,7 @@
         <v>45770</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -37827,7 +37827,7 @@
         <v>46248</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -37900,7 +37900,7 @@
         <v>44469</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -37973,7 +37973,7 @@
         <v>45671</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -38046,7 +38046,7 @@
         <v>44813</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -38119,7 +38119,7 @@
         <v>46161</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -38192,7 +38192,7 @@
         <v>45162</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -38265,7 +38265,7 @@
         <v>45254</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -38338,7 +38338,7 @@
         <v>44900</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -38411,7 +38411,7 @@
         <v>44893</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -38484,7 +38484,7 @@
         <v>45327</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -38557,7 +38557,7 @@
         <v>45624</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -38630,7 +38630,7 @@
         <v>44712</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -38703,7 +38703,7 @@
         <v>44834</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -38776,7 +38776,7 @@
         <v>45229</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -38849,7 +38849,7 @@
         <v>44967</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -38922,7 +38922,7 @@
         <v>45544</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -38995,7 +38995,7 @@
         <v>45715</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -39068,7 +39068,7 @@
         <v>45700</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -39141,7 +39141,7 @@
         <v>45316</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -39214,7 +39214,7 @@
         <v>46261</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -39287,7 +39287,7 @@
         <v>45643</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -39360,7 +39360,7 @@
         <v>44900</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -39433,7 +39433,7 @@
         <v>46261</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -39506,7 +39506,7 @@
         <v>45368</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -39584,7 +39584,7 @@
         <v>45371</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -39657,7 +39657,7 @@
         <v>45371</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -39730,7 +39730,7 @@
         <v>46263</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -39803,7 +39803,7 @@
         <v>44477</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -39876,7 +39876,7 @@
         <v>45254</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -39949,7 +39949,7 @@
         <v>46224</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -40027,7 +40027,7 @@
         <v>46268</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -40100,7 +40100,7 @@
         <v>45229</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -40173,7 +40173,7 @@
         <v>46268</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -40246,7 +40246,7 @@
         <v>45035</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -40319,7 +40319,7 @@
         <v>46268</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -40392,7 +40392,7 @@
         <v>45299</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -40465,7 +40465,7 @@
         <v>45176</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -40543,7 +40543,7 @@
         <v>45638</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -40616,7 +40616,7 @@
         <v>45588</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -40694,7 +40694,7 @@
         <v>46273</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -40767,7 +40767,7 @@
         <v>46272</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -40840,7 +40840,7 @@
         <v>46272</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -40913,7 +40913,7 @@
         <v>45840</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -40991,7 +40991,7 @@
         <v>46273</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -41064,7 +41064,7 @@
         <v>45510</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -41137,7 +41137,7 @@
         <v>45559</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -41210,7 +41210,7 @@
         <v>45783</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -41283,7 +41283,7 @@
         <v>45616</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -41356,7 +41356,7 @@
         <v>46279</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -41429,7 +41429,7 @@
         <v>45483</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -41502,7 +41502,7 @@
         <v>45680</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -41575,7 +41575,7 @@
         <v>45616</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -41648,7 +41648,7 @@
         <v>46279</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -41721,7 +41721,7 @@
         <v>46279</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -41794,7 +41794,7 @@
         <v>45225</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -41867,7 +41867,7 @@
         <v>45618</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -41940,7 +41940,7 @@
         <v>46036</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -42013,7 +42013,7 @@
         <v>45726</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -42086,7 +42086,7 @@
         <v>45483</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -42159,7 +42159,7 @@
         <v>45589</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -42237,7 +42237,7 @@
         <v>45391</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -42310,7 +42310,7 @@
         <v>45786</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -42388,7 +42388,7 @@
         <v>45590</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -42461,7 +42461,7 @@
         <v>45609</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -42534,7 +42534,7 @@
         <v>45743</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -42612,7 +42612,7 @@
         <v>45743</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -42690,7 +42690,7 @@
         <v>45741</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -42763,7 +42763,7 @@
         <v>45793</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -42836,7 +42836,7 @@
         <v>45559</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -42909,7 +42909,7 @@
         <v>45681</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -42982,7 +42982,7 @@
         <v>45743</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -43060,7 +43060,7 @@
         <v>46273</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -43133,7 +43133,7 @@
         <v>44851</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -43206,7 +43206,7 @@
         <v>46281</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -43279,7 +43279,7 @@
         <v>46282</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -43352,7 +43352,7 @@
         <v>46241</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -43425,7 +43425,7 @@
         <v>45806</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -43498,7 +43498,7 @@
         <v>45609</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -43571,7 +43571,7 @@
         <v>45812</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -43644,7 +43644,7 @@
         <v>45706</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -43717,7 +43717,7 @@
         <v>45694</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -43790,7 +43790,7 @@
         <v>45708</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -43863,7 +43863,7 @@
         <v>45597</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -43936,7 +43936,7 @@
         <v>45387</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -44009,7 +44009,7 @@
         <v>45730</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -44082,7 +44082,7 @@
         <v>45820</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -44155,7 +44155,7 @@
         <v>44900</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -44228,7 +44228,7 @@
         <v>45825</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -44301,7 +44301,7 @@
         <v>45548</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -44374,7 +44374,7 @@
         <v>45831</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -44447,7 +44447,7 @@
         <v>45601</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -44520,7 +44520,7 @@
         <v>45835</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -44593,7 +44593,7 @@
         <v>45838</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -44666,7 +44666,7 @@
         <v>45836</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -44739,7 +44739,7 @@
         <v>45840</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -44812,7 +44812,7 @@
         <v>45840</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -44885,7 +44885,7 @@
         <v>45840</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -44958,7 +44958,7 @@
         <v>45800</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -45031,7 +45031,7 @@
         <v>45847</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -45104,7 +45104,7 @@
         <v>45847</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -45177,7 +45177,7 @@
         <v>45845</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -45250,7 +45250,7 @@
         <v>45845</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -45323,7 +45323,7 @@
         <v>45846</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -45401,7 +45401,7 @@
         <v>45846</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -45479,7 +45479,7 @@
         <v>45846</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -45557,7 +45557,7 @@
         <v>45803</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -45630,7 +45630,7 @@
         <v>45700</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -45703,7 +45703,7 @@
         <v>45700</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -45776,7 +45776,7 @@
         <v>45687</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -45849,7 +45849,7 @@
         <v>45190</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -45922,7 +45922,7 @@
         <v>45293</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -45995,7 +45995,7 @@
         <v>45392</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -46068,7 +46068,7 @@
         <v>45145</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -46141,7 +46141,7 @@
         <v>45623</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -46214,7 +46214,7 @@
         <v>44917</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -46287,7 +46287,7 @@
         <v>45190</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -46365,7 +46365,7 @@
         <v>45517</v>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -46438,7 +46438,7 @@
         <v>45545</v>
       </c>
       <c r="E610" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -46511,7 +46511,7 @@
         <v>45204</v>
       </c>
       <c r="E611" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
@@ -46584,7 +46584,7 @@
         <v>45395</v>
       </c>
       <c r="E612" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
@@ -46657,7 +46657,7 @@
         <v>45541</v>
       </c>
       <c r="E613" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
@@ -46730,7 +46730,7 @@
         <v>45677</v>
       </c>
       <c r="E614" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F614" t="inlineStr">
         <is>
@@ -46803,7 +46803,7 @@
         <v>45727</v>
       </c>
       <c r="E615" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F615" t="inlineStr">
         <is>
@@ -46876,7 +46876,7 @@
         <v>45252</v>
       </c>
       <c r="E616" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F616" t="inlineStr">
         <is>
@@ -46949,7 +46949,7 @@
         <v>45257</v>
       </c>
       <c r="E617" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F617" t="inlineStr">
         <is>
@@ -47022,7 +47022,7 @@
         <v>45309</v>
       </c>
       <c r="E618" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F618" t="inlineStr">
         <is>
@@ -47095,7 +47095,7 @@
         <v>45245</v>
       </c>
       <c r="E619" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F619" t="inlineStr">
         <is>
@@ -47168,7 +47168,7 @@
         <v>45288</v>
       </c>
       <c r="E620" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F620" t="inlineStr">
         <is>
@@ -47246,7 +47246,7 @@
         <v>44896</v>
       </c>
       <c r="E621" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F621" t="inlineStr">
         <is>
@@ -47319,7 +47319,7 @@
         <v>44592</v>
       </c>
       <c r="E622" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F622" t="inlineStr">
         <is>
@@ -47392,7 +47392,7 @@
         <v>45407</v>
       </c>
       <c r="E623" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F623" t="inlineStr">
         <is>
@@ -47465,7 +47465,7 @@
         <v>45589</v>
       </c>
       <c r="E624" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F624" t="inlineStr">
         <is>
@@ -47538,7 +47538,7 @@
         <v>45623</v>
       </c>
       <c r="E625" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F625" t="inlineStr">
         <is>
@@ -47611,7 +47611,7 @@
         <v>45769</v>
       </c>
       <c r="E626" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F626" t="inlineStr">
         <is>
@@ -47684,7 +47684,7 @@
         <v>45672</v>
       </c>
       <c r="E627" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F627" t="inlineStr">
         <is>
@@ -47757,7 +47757,7 @@
         <v>45672</v>
       </c>
       <c r="E628" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F628" t="inlineStr">
         <is>
@@ -47830,7 +47830,7 @@
         <v>45524</v>
       </c>
       <c r="E629" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F629" t="inlineStr">
         <is>
@@ -47903,7 +47903,7 @@
         <v>44508</v>
       </c>
       <c r="E630" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F630" t="inlineStr">
         <is>
@@ -47976,7 +47976,7 @@
         <v>44889</v>
       </c>
       <c r="E631" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F631" t="inlineStr">
         <is>
@@ -48049,7 +48049,7 @@
         <v>45199</v>
       </c>
       <c r="E632" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F632" t="inlineStr">
         <is>
@@ -48122,7 +48122,7 @@
         <v>44671</v>
       </c>
       <c r="E633" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F633" t="inlineStr">
         <is>
@@ -48195,7 +48195,7 @@
         <v>45176</v>
       </c>
       <c r="E634" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F634" t="inlineStr">
         <is>
@@ -48268,7 +48268,7 @@
         <v>45199</v>
       </c>
       <c r="E635" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F635" t="inlineStr">
         <is>
@@ -48341,7 +48341,7 @@
         <v>45372</v>
       </c>
       <c r="E636" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F636" t="inlineStr">
         <is>
@@ -48414,7 +48414,7 @@
         <v>44712</v>
       </c>
       <c r="E637" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F637" t="inlineStr">
         <is>
@@ -48487,7 +48487,7 @@
         <v>45395</v>
       </c>
       <c r="E638" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F638" t="inlineStr">
         <is>
@@ -48560,7 +48560,7 @@
         <v>44739</v>
       </c>
       <c r="E639" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F639" t="inlineStr">
         <is>
@@ -48633,7 +48633,7 @@
         <v>45230</v>
       </c>
       <c r="E640" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F640" t="inlineStr">
         <is>
@@ -48706,7 +48706,7 @@
         <v>45672</v>
       </c>
       <c r="E641" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F641" t="inlineStr">
         <is>
@@ -48779,7 +48779,7 @@
         <v>44701</v>
       </c>
       <c r="E642" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F642" t="inlineStr">
         <is>
@@ -48852,7 +48852,7 @@
         <v>45677</v>
       </c>
       <c r="E643" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F643" t="inlineStr">
         <is>
@@ -48925,7 +48925,7 @@
         <v>45361</v>
       </c>
       <c r="E644" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F644" t="inlineStr">
         <is>
@@ -48998,7 +48998,7 @@
         <v>45735</v>
       </c>
       <c r="E645" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F645" t="inlineStr">
         <is>
@@ -49071,7 +49071,7 @@
         <v>45610</v>
       </c>
       <c r="E646" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F646" t="inlineStr">
         <is>
@@ -49144,7 +49144,7 @@
         <v>45679</v>
       </c>
       <c r="E647" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F647" t="inlineStr">
         <is>
@@ -49217,7 +49217,7 @@
         <v>45735</v>
       </c>
       <c r="E648" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F648" t="inlineStr">
         <is>
@@ -49290,7 +49290,7 @@
         <v>44483</v>
       </c>
       <c r="E649" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F649" t="inlineStr">
         <is>
@@ -49363,7 +49363,7 @@
         <v>45272</v>
       </c>
       <c r="E650" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F650" t="inlineStr">
         <is>
@@ -49436,7 +49436,7 @@
         <v>45309</v>
       </c>
       <c r="E651" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F651" t="inlineStr">
         <is>
@@ -49509,7 +49509,7 @@
         <v>45432</v>
       </c>
       <c r="E652" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F652" t="inlineStr">
         <is>
@@ -49582,7 +49582,7 @@
         <v>45293</v>
       </c>
       <c r="E653" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F653" t="inlineStr">
         <is>
@@ -49655,7 +49655,7 @@
         <v>44483</v>
       </c>
       <c r="E654" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F654" t="inlineStr">
         <is>
@@ -49728,7 +49728,7 @@
         <v>44476</v>
       </c>
       <c r="E655" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F655" t="inlineStr">
         <is>
@@ -49801,7 +49801,7 @@
         <v>44671</v>
       </c>
       <c r="E656" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F656" t="inlineStr">
         <is>
@@ -49874,7 +49874,7 @@
         <v>45131</v>
       </c>
       <c r="E657" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F657" t="inlineStr">
         <is>
@@ -49947,7 +49947,7 @@
         <v>45574</v>
       </c>
       <c r="E658" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F658" t="inlineStr">
         <is>
@@ -50020,7 +50020,7 @@
         <v>45589</v>
       </c>
       <c r="E659" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F659" t="inlineStr">
         <is>
@@ -50093,7 +50093,7 @@
         <v>45546</v>
       </c>
       <c r="E660" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F660" t="inlineStr">
         <is>
@@ -50166,7 +50166,7 @@
         <v>45623</v>
       </c>
       <c r="E661" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F661" t="inlineStr">
         <is>
@@ -50239,7 +50239,7 @@
         <v>45838</v>
       </c>
       <c r="E662" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F662" t="inlineStr">
         <is>
@@ -50312,7 +50312,7 @@
         <v>44817</v>
       </c>
       <c r="E663" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F663" t="inlineStr">
         <is>
@@ -50385,7 +50385,7 @@
         <v>45257</v>
       </c>
       <c r="E664" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F664" t="inlineStr">
         <is>
@@ -50463,7 +50463,7 @@
         <v>45245</v>
       </c>
       <c r="E665" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F665" t="inlineStr">
         <is>
@@ -50536,7 +50536,7 @@
         <v>44964</v>
       </c>
       <c r="E666" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F666" t="inlineStr">
         <is>
@@ -50609,7 +50609,7 @@
         <v>45876</v>
       </c>
       <c r="E667" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F667" t="inlineStr">
         <is>
@@ -50682,7 +50682,7 @@
         <v>45877</v>
       </c>
       <c r="E668" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F668" t="inlineStr">
         <is>
@@ -50755,7 +50755,7 @@
         <v>45880</v>
       </c>
       <c r="E669" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F669" t="inlineStr">
         <is>
@@ -50828,7 +50828,7 @@
         <v>45880</v>
       </c>
       <c r="E670" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F670" t="inlineStr">
         <is>
@@ -50901,7 +50901,7 @@
         <v>45880</v>
       </c>
       <c r="E671" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F671" t="inlineStr">
         <is>
@@ -50974,7 +50974,7 @@
         <v>45880</v>
       </c>
       <c r="E672" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F672" t="inlineStr">
         <is>
@@ -51047,7 +51047,7 @@
         <v>45614</v>
       </c>
       <c r="E673" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F673" t="inlineStr">
         <is>
@@ -51125,7 +51125,7 @@
         <v>44631</v>
       </c>
       <c r="E674" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F674" t="inlineStr">
         <is>
@@ -51198,7 +51198,7 @@
         <v>44743</v>
       </c>
       <c r="E675" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F675" t="inlineStr">
         <is>
@@ -51271,7 +51271,7 @@
         <v>45375</v>
       </c>
       <c r="E676" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F676" t="inlineStr">
         <is>
@@ -51344,7 +51344,7 @@
         <v>44488</v>
       </c>
       <c r="E677" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F677" t="inlineStr">
         <is>
@@ -51417,7 +51417,7 @@
         <v>45604</v>
       </c>
       <c r="E678" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F678" t="inlineStr">
         <is>
@@ -51490,7 +51490,7 @@
         <v>45356</v>
       </c>
       <c r="E679" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F679" t="inlineStr">
         <is>
@@ -51563,7 +51563,7 @@
         <v>44613</v>
       </c>
       <c r="E680" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F680" t="inlineStr">
         <is>
@@ -51636,7 +51636,7 @@
         <v>45349</v>
       </c>
       <c r="E681" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F681" t="inlineStr">
         <is>
@@ -51709,7 +51709,7 @@
         <v>44608</v>
       </c>
       <c r="E682" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F682" t="inlineStr">
         <is>
@@ -51782,7 +51782,7 @@
         <v>44631</v>
       </c>
       <c r="E683" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F683" t="inlineStr">
         <is>
@@ -51855,7 +51855,7 @@
         <v>44631</v>
       </c>
       <c r="E684" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F684" t="inlineStr">
         <is>
@@ -51928,7 +51928,7 @@
         <v>45744</v>
       </c>
       <c r="E685" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F685" t="inlineStr">
         <is>
@@ -52001,7 +52001,7 @@
         <v>45714</v>
       </c>
       <c r="E686" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F686" t="inlineStr">
         <is>
@@ -52074,7 +52074,7 @@
         <v>45715</v>
       </c>
       <c r="E687" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F687" t="inlineStr">
         <is>
@@ -52147,7 +52147,7 @@
         <v>45709</v>
       </c>
       <c r="E688" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F688" t="inlineStr">
         <is>
@@ -52220,7 +52220,7 @@
         <v>45714</v>
       </c>
       <c r="E689" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F689" t="inlineStr">
         <is>
@@ -52293,7 +52293,7 @@
         <v>45813</v>
       </c>
       <c r="E690" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F690" t="inlineStr">
         <is>
@@ -52366,7 +52366,7 @@
         <v>45813</v>
       </c>
       <c r="E691" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F691" t="inlineStr">
         <is>
@@ -52439,7 +52439,7 @@
         <v>45813</v>
       </c>
       <c r="E692" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F692" t="inlineStr">
         <is>
@@ -52512,7 +52512,7 @@
         <v>45820</v>
       </c>
       <c r="E693" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F693" t="inlineStr">
         <is>
@@ -52585,7 +52585,7 @@
         <v>45827</v>
       </c>
       <c r="E694" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F694" t="inlineStr">
         <is>
@@ -52658,7 +52658,7 @@
         <v>45845</v>
       </c>
       <c r="E695" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F695" t="inlineStr">
         <is>
@@ -52731,7 +52731,7 @@
         <v>45883</v>
       </c>
       <c r="E696" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F696" t="inlineStr">
         <is>
@@ -52804,7 +52804,7 @@
         <v>45915</v>
       </c>
       <c r="E697" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F697" t="inlineStr">
         <is>
@@ -52877,7 +52877,7 @@
         <v>46041</v>
       </c>
       <c r="E698" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F698" t="inlineStr">
         <is>
@@ -52950,7 +52950,7 @@
         <v>46133</v>
       </c>
       <c r="E699" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F699" t="inlineStr">
         <is>
@@ -53023,7 +53023,7 @@
         <v>46147</v>
       </c>
       <c r="E700" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F700" t="inlineStr">
         <is>
@@ -53096,7 +53096,7 @@
         <v>46253</v>
       </c>
       <c r="E701" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F701" t="inlineStr">
         <is>
@@ -53169,7 +53169,7 @@
         <v>46211</v>
       </c>
       <c r="E702" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F702" t="inlineStr">
         <is>

--- a/Översikt HYLTE.xlsx
+++ b/Översikt HYLTE.xlsx
@@ -601,7 +601,7 @@
         <v>46090</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -718,7 +718,7 @@
         <v>45265</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -834,7 +834,7 @@
         <v>46066</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -945,7 +945,7 @@
         <v>44873</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1054,7 +1054,7 @@
         <v>45348</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1166,7 +1166,7 @@
         <v>45719</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1274,7 +1274,7 @@
         <v>45245</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1385,7 +1385,7 @@
         <v>46268</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1492,7 +1492,7 @@
         <v>45230</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1599,7 +1599,7 @@
         <v>45737</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1706,7 +1706,7 @@
         <v>46141</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1813,7 +1813,7 @@
         <v>46161</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1920,7 +1920,7 @@
         <v>44839</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2030,7 +2030,7 @@
         <v>46048</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2136,7 +2136,7 @@
         <v>45841</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2246,7 +2246,7 @@
         <v>45099</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2356,7 +2356,7 @@
         <v>45904</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2466,7 +2466,7 @@
         <v>46130</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2572,7 +2572,7 @@
         <v>44648</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2677,7 +2677,7 @@
         <v>44651</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2782,7 +2782,7 @@
         <v>44876</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2887,7 +2887,7 @@
         <v>45299</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2996,7 +2996,7 @@
         <v>45153</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3110,7 +3110,7 @@
         <v>45163</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3215,7 +3215,7 @@
         <v>45343</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3320,7 +3320,7 @@
         <v>45476</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3430,7 +3430,7 @@
         <v>45085</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3539,7 +3539,7 @@
         <v>45186</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3644,7 +3644,7 @@
         <v>45245</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3749,7 +3749,7 @@
         <v>45593</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3854,7 +3854,7 @@
         <v>45245</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3959,7 +3959,7 @@
         <v>45617</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4064,7 +4064,7 @@
         <v>45253</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4169,7 +4169,7 @@
         <v>45754</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4274,7 +4274,7 @@
         <v>46253</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4384,7 +4384,7 @@
         <v>44481</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4457,7 +4457,7 @@
         <v>44810</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4530,7 +4530,7 @@
         <v>44600</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4603,7 +4603,7 @@
         <v>44529</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4676,7 +4676,7 @@
         <v>44557</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4749,7 +4749,7 @@
         <v>44483</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4822,7 +4822,7 @@
         <v>44705</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4895,7 +4895,7 @@
         <v>44778</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4968,7 +4968,7 @@
         <v>44488</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5041,7 +5041,7 @@
         <v>44475</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5114,7 +5114,7 @@
         <v>44624</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5187,7 +5187,7 @@
         <v>44812</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5260,7 +5260,7 @@
         <v>44638</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5333,7 +5333,7 @@
         <v>44498</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5406,7 +5406,7 @@
         <v>44845</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5479,7 +5479,7 @@
         <v>44559</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5552,7 +5552,7 @@
         <v>44578</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5625,7 +5625,7 @@
         <v>44659</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5703,7 +5703,7 @@
         <v>44756</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5776,7 +5776,7 @@
         <v>44501</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5849,7 +5849,7 @@
         <v>44651</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5922,7 +5922,7 @@
         <v>44711</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5995,7 +5995,7 @@
         <v>44487</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6073,7 +6073,7 @@
         <v>44735</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6146,7 +6146,7 @@
         <v>44477</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6219,7 +6219,7 @@
         <v>44489</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6292,7 +6292,7 @@
         <v>44834</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6365,7 +6365,7 @@
         <v>44469</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6438,7 +6438,7 @@
         <v>44796</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6511,7 +6511,7 @@
         <v>44502</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6584,7 +6584,7 @@
         <v>44876</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6657,7 +6657,7 @@
         <v>44631</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6730,7 +6730,7 @@
         <v>44659</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6803,7 +6803,7 @@
         <v>44644</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6876,7 +6876,7 @@
         <v>44515</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6954,7 +6954,7 @@
         <v>44778</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7027,7 +7027,7 @@
         <v>44482</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7100,7 +7100,7 @@
         <v>44482</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7173,7 +7173,7 @@
         <v>44867</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7246,7 +7246,7 @@
         <v>44505</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7319,7 +7319,7 @@
         <v>44634</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7392,7 +7392,7 @@
         <v>44728</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7465,7 +7465,7 @@
         <v>44714</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7538,7 +7538,7 @@
         <v>44795</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7611,7 +7611,7 @@
         <v>44818</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7684,7 +7684,7 @@
         <v>44801</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7757,7 +7757,7 @@
         <v>44596</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7835,7 +7835,7 @@
         <v>44644</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7908,7 +7908,7 @@
         <v>44523</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7981,7 +7981,7 @@
         <v>44500</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8054,7 +8054,7 @@
         <v>44727</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8127,7 +8127,7 @@
         <v>44705</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8200,7 +8200,7 @@
         <v>44659</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8278,7 +8278,7 @@
         <v>44659</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8356,7 +8356,7 @@
         <v>44757</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8429,7 +8429,7 @@
         <v>44494</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8502,7 +8502,7 @@
         <v>44495</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8575,7 +8575,7 @@
         <v>45042</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8648,7 +8648,7 @@
         <v>45327</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8721,7 +8721,7 @@
         <v>45299</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8794,7 +8794,7 @@
         <v>44900</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8867,7 +8867,7 @@
         <v>44900</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8940,7 +8940,7 @@
         <v>45208</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -9013,7 +9013,7 @@
         <v>44866</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9086,7 +9086,7 @@
         <v>45254</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9159,7 +9159,7 @@
         <v>45331</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9232,7 +9232,7 @@
         <v>44847</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9305,7 +9305,7 @@
         <v>45254</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9378,7 +9378,7 @@
         <v>45254</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9451,7 +9451,7 @@
         <v>44872</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9524,7 +9524,7 @@
         <v>45441</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9597,7 +9597,7 @@
         <v>45254</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9670,7 +9670,7 @@
         <v>45254</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9743,7 +9743,7 @@
         <v>45378</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9816,7 +9816,7 @@
         <v>45382</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9889,7 +9889,7 @@
         <v>45061</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9962,7 +9962,7 @@
         <v>45752</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -10040,7 +10040,7 @@
         <v>45253</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10113,7 +10113,7 @@
         <v>45456</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10186,7 +10186,7 @@
         <v>45390</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10259,7 +10259,7 @@
         <v>44482</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10332,7 +10332,7 @@
         <v>45505</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10405,7 +10405,7 @@
         <v>45097</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10478,7 +10478,7 @@
         <v>45478</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10551,7 +10551,7 @@
         <v>44476</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10624,7 +10624,7 @@
         <v>46020</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10697,7 +10697,7 @@
         <v>45559</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -10770,7 +10770,7 @@
         <v>45681</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10843,7 +10843,7 @@
         <v>45743</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10921,7 +10921,7 @@
         <v>44851</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -10994,7 +10994,7 @@
         <v>45600</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -11067,7 +11067,7 @@
         <v>44495</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11140,7 +11140,7 @@
         <v>44487</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11218,7 +11218,7 @@
         <v>44950</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11291,7 +11291,7 @@
         <v>45299</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11364,7 +11364,7 @@
         <v>45793</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11437,7 +11437,7 @@
         <v>45352</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11510,7 +11510,7 @@
         <v>44865</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11583,7 +11583,7 @@
         <v>45834</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11656,7 +11656,7 @@
         <v>45840</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -11729,7 +11729,7 @@
         <v>45436</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -11802,7 +11802,7 @@
         <v>45673</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -11875,7 +11875,7 @@
         <v>45352</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -11948,7 +11948,7 @@
         <v>44477</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -12021,7 +12021,7 @@
         <v>44469</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -12094,7 +12094,7 @@
         <v>44834</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12167,7 +12167,7 @@
         <v>45890</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12240,7 +12240,7 @@
         <v>45748</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12313,7 +12313,7 @@
         <v>45891</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12391,7 +12391,7 @@
         <v>45891</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -12469,7 +12469,7 @@
         <v>46042</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -12542,7 +12542,7 @@
         <v>44896</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -12615,7 +12615,7 @@
         <v>46042</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -12688,7 +12688,7 @@
         <v>46044</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -12761,7 +12761,7 @@
         <v>46044</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -12834,7 +12834,7 @@
         <v>46044</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -12907,7 +12907,7 @@
         <v>46044</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -12980,7 +12980,7 @@
         <v>46048</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -13053,7 +13053,7 @@
         <v>45897</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -13126,7 +13126,7 @@
         <v>45897</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13199,7 +13199,7 @@
         <v>46048</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13272,7 +13272,7 @@
         <v>45429</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13345,7 +13345,7 @@
         <v>46048</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -13418,7 +13418,7 @@
         <v>46048</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -13491,7 +13491,7 @@
         <v>46048</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -13564,7 +13564,7 @@
         <v>46048</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -13637,7 +13637,7 @@
         <v>46048</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -13710,7 +13710,7 @@
         <v>46048</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -13783,7 +13783,7 @@
         <v>45839</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -13856,7 +13856,7 @@
         <v>45898</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -13929,7 +13929,7 @@
         <v>46048</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -14002,7 +14002,7 @@
         <v>46048</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -14075,7 +14075,7 @@
         <v>46048</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -14148,7 +14148,7 @@
         <v>46048</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14221,7 +14221,7 @@
         <v>46049</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14294,7 +14294,7 @@
         <v>44489</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -14367,7 +14367,7 @@
         <v>45905</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -14440,7 +14440,7 @@
         <v>45366</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -14513,7 +14513,7 @@
         <v>46052</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -14586,7 +14586,7 @@
         <v>45538</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -14659,7 +14659,7 @@
         <v>46052</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -14732,7 +14732,7 @@
         <v>45910</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -14805,7 +14805,7 @@
         <v>46055</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -14878,7 +14878,7 @@
         <v>45910</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -14951,7 +14951,7 @@
         <v>45838</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -15024,7 +15024,7 @@
         <v>46057</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -15097,7 +15097,7 @@
         <v>46062</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -15170,7 +15170,7 @@
         <v>45671</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -15243,7 +15243,7 @@
         <v>45918</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -15316,7 +15316,7 @@
         <v>46062</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -15389,7 +15389,7 @@
         <v>46064</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -15462,7 +15462,7 @@
         <v>45558</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -15535,7 +15535,7 @@
         <v>45922</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -15608,7 +15608,7 @@
         <v>45922</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -15681,7 +15681,7 @@
         <v>45922</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -15754,7 +15754,7 @@
         <v>46065</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -15827,7 +15827,7 @@
         <v>46070</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -15900,7 +15900,7 @@
         <v>46070</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -15973,7 +15973,7 @@
         <v>45924</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -16046,7 +16046,7 @@
         <v>45926</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -16119,7 +16119,7 @@
         <v>45926</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -16192,7 +16192,7 @@
         <v>45926</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -16265,7 +16265,7 @@
         <v>44719</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -16338,7 +16338,7 @@
         <v>45929</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -16411,7 +16411,7 @@
         <v>45931</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -16484,7 +16484,7 @@
         <v>45806</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -16557,7 +16557,7 @@
         <v>45931</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -16630,7 +16630,7 @@
         <v>44701</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -16708,7 +16708,7 @@
         <v>45609</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -16781,7 +16781,7 @@
         <v>45259</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -16854,7 +16854,7 @@
         <v>44714</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -16927,7 +16927,7 @@
         <v>45930</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -17000,7 +17000,7 @@
         <v>46084</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -17073,7 +17073,7 @@
         <v>46084</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -17146,7 +17146,7 @@
         <v>46087</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -17219,7 +17219,7 @@
         <v>45933</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -17292,7 +17292,7 @@
         <v>45936</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -17365,7 +17365,7 @@
         <v>45936</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -17438,7 +17438,7 @@
         <v>45933</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -17511,7 +17511,7 @@
         <v>45933</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -17584,7 +17584,7 @@
         <v>44974</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -17657,7 +17657,7 @@
         <v>45936</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -17730,7 +17730,7 @@
         <v>45937</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -17803,7 +17803,7 @@
         <v>45229</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -17876,7 +17876,7 @@
         <v>45198</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -17949,7 +17949,7 @@
         <v>46093</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -18022,7 +18022,7 @@
         <v>46093</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -18095,7 +18095,7 @@
         <v>45938</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -18168,7 +18168,7 @@
         <v>44481</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -18241,7 +18241,7 @@
         <v>46093</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -18314,7 +18314,7 @@
         <v>44900</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -18387,7 +18387,7 @@
         <v>45441</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -18460,7 +18460,7 @@
         <v>44926</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -18538,7 +18538,7 @@
         <v>45944</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -18611,7 +18611,7 @@
         <v>44756</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -18684,7 +18684,7 @@
         <v>45162</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -18757,7 +18757,7 @@
         <v>45162</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -18830,7 +18830,7 @@
         <v>45268</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -18903,7 +18903,7 @@
         <v>44903</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -18976,7 +18976,7 @@
         <v>44999</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -19049,7 +19049,7 @@
         <v>46057</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -19122,7 +19122,7 @@
         <v>45812</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -19195,7 +19195,7 @@
         <v>46057</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -19268,7 +19268,7 @@
         <v>46111</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -19341,7 +19341,7 @@
         <v>46111</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -19414,7 +19414,7 @@
         <v>46111</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -19487,7 +19487,7 @@
         <v>45957</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -19560,7 +19560,7 @@
         <v>45254</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -19633,7 +19633,7 @@
         <v>45460</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -19706,7 +19706,7 @@
         <v>44965</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -19784,7 +19784,7 @@
         <v>45751</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -19862,7 +19862,7 @@
         <v>46121</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -19935,7 +19935,7 @@
         <v>46120</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -20008,7 +20008,7 @@
         <v>45961</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -20081,7 +20081,7 @@
         <v>45961</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -20154,7 +20154,7 @@
         <v>46121</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -20227,7 +20227,7 @@
         <v>46121</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -20300,7 +20300,7 @@
         <v>46121</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -20373,7 +20373,7 @@
         <v>46121</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -20446,7 +20446,7 @@
         <v>46120</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -20519,7 +20519,7 @@
         <v>46121</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -20592,7 +20592,7 @@
         <v>46121</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -20665,7 +20665,7 @@
         <v>44970</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -20738,7 +20738,7 @@
         <v>44970</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -20811,7 +20811,7 @@
         <v>45922</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -20884,7 +20884,7 @@
         <v>46122</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -20957,7 +20957,7 @@
         <v>46122</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -21030,7 +21030,7 @@
         <v>45107</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -21103,7 +21103,7 @@
         <v>46122</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -21176,7 +21176,7 @@
         <v>46122</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -21249,7 +21249,7 @@
         <v>46121</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -21322,7 +21322,7 @@
         <v>45972</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -21395,7 +21395,7 @@
         <v>45456</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -21468,7 +21468,7 @@
         <v>45972</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -21541,7 +21541,7 @@
         <v>45092</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -21614,7 +21614,7 @@
         <v>45972</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -21687,7 +21687,7 @@
         <v>45730</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -21760,7 +21760,7 @@
         <v>45229</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -21833,7 +21833,7 @@
         <v>45002</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -21906,7 +21906,7 @@
         <v>45694</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -21979,7 +21979,7 @@
         <v>45107</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -22052,7 +22052,7 @@
         <v>46128</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -22125,7 +22125,7 @@
         <v>45597</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -22198,7 +22198,7 @@
         <v>45645</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -22271,7 +22271,7 @@
         <v>45708</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -22344,7 +22344,7 @@
         <v>45145</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -22417,7 +22417,7 @@
         <v>45979</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -22490,7 +22490,7 @@
         <v>45387</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -22563,7 +22563,7 @@
         <v>45981</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -22636,7 +22636,7 @@
         <v>45981</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -22709,7 +22709,7 @@
         <v>45790</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -22782,7 +22782,7 @@
         <v>45638</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -22855,7 +22855,7 @@
         <v>45987</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -22928,7 +22928,7 @@
         <v>45568</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -23001,7 +23001,7 @@
         <v>45989</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -23074,7 +23074,7 @@
         <v>44712</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -23147,7 +23147,7 @@
         <v>45840</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -23225,7 +23225,7 @@
         <v>45995</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -23298,7 +23298,7 @@
         <v>44729</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -23371,7 +23371,7 @@
         <v>45775</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -23444,7 +23444,7 @@
         <v>45782</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -23517,7 +23517,7 @@
         <v>45483</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -23590,7 +23590,7 @@
         <v>44699</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -23663,7 +23663,7 @@
         <v>45524</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -23736,7 +23736,7 @@
         <v>44980</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -23809,7 +23809,7 @@
         <v>45246</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -23882,7 +23882,7 @@
         <v>45715</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -23955,7 +23955,7 @@
         <v>45989</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -24028,7 +24028,7 @@
         <v>46084</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -24101,7 +24101,7 @@
         <v>45706</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -24174,7 +24174,7 @@
         <v>45351</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -24247,7 +24247,7 @@
         <v>45544</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -24320,7 +24320,7 @@
         <v>45926</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -24393,7 +24393,7 @@
         <v>45820</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -24466,7 +24466,7 @@
         <v>45229</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -24539,7 +24539,7 @@
         <v>44900</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -24612,7 +24612,7 @@
         <v>45531</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -24685,7 +24685,7 @@
         <v>45817</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -24758,7 +24758,7 @@
         <v>46084</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -24831,7 +24831,7 @@
         <v>45839</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -24904,7 +24904,7 @@
         <v>44539</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -24977,7 +24977,7 @@
         <v>45502</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -25050,7 +25050,7 @@
         <v>45848</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -25123,7 +25123,7 @@
         <v>45825</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -25196,7 +25196,7 @@
         <v>44910</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -25269,7 +25269,7 @@
         <v>45617</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -25342,7 +25342,7 @@
         <v>44477</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -25415,7 +25415,7 @@
         <v>45548</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -25488,7 +25488,7 @@
         <v>45019</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -25561,7 +25561,7 @@
         <v>45257</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -25634,7 +25634,7 @@
         <v>45831</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -25707,7 +25707,7 @@
         <v>45754</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -25780,7 +25780,7 @@
         <v>46148</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -25853,7 +25853,7 @@
         <v>45091</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -25926,7 +25926,7 @@
         <v>46153</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -25999,7 +25999,7 @@
         <v>46153</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -26072,7 +26072,7 @@
         <v>46153</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -26145,7 +26145,7 @@
         <v>46153</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -26218,7 +26218,7 @@
         <v>45601</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -26291,7 +26291,7 @@
         <v>44869</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -26364,7 +26364,7 @@
         <v>45709</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -26437,7 +26437,7 @@
         <v>46153</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -26510,7 +26510,7 @@
         <v>46153</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -26583,7 +26583,7 @@
         <v>46153</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -26656,7 +26656,7 @@
         <v>45096</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -26729,7 +26729,7 @@
         <v>44900</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -26807,7 +26807,7 @@
         <v>46155</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -26880,7 +26880,7 @@
         <v>45104</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -26953,7 +26953,7 @@
         <v>45441</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -27026,7 +27026,7 @@
         <v>45441</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -27099,7 +27099,7 @@
         <v>45835</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -27172,7 +27172,7 @@
         <v>45836</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -27245,7 +27245,7 @@
         <v>45229</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -27318,7 +27318,7 @@
         <v>46161</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -27396,7 +27396,7 @@
         <v>46161</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -27469,7 +27469,7 @@
         <v>45838</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -27542,7 +27542,7 @@
         <v>45840</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -27615,7 +27615,7 @@
         <v>45840</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -27688,7 +27688,7 @@
         <v>45840</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -27761,7 +27761,7 @@
         <v>45110</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -27834,7 +27834,7 @@
         <v>46161</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -27912,7 +27912,7 @@
         <v>46161</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -27990,7 +27990,7 @@
         <v>46161</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -28063,7 +28063,7 @@
         <v>46161</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -28141,7 +28141,7 @@
         <v>45170</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -28214,7 +28214,7 @@
         <v>45845</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -28287,7 +28287,7 @@
         <v>45845</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -28360,7 +28360,7 @@
         <v>45800</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -28433,7 +28433,7 @@
         <v>45846</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -28511,7 +28511,7 @@
         <v>45310</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -28584,7 +28584,7 @@
         <v>45846</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -28662,7 +28662,7 @@
         <v>45846</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -28740,7 +28740,7 @@
         <v>45847</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -28813,7 +28813,7 @@
         <v>45694</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -28886,7 +28886,7 @@
         <v>45847</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -28959,7 +28959,7 @@
         <v>45406</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -29032,7 +29032,7 @@
         <v>45803</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -29105,7 +29105,7 @@
         <v>44967</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -29178,7 +29178,7 @@
         <v>45110</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -29251,7 +29251,7 @@
         <v>45145</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -29324,7 +29324,7 @@
         <v>45117</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -29397,7 +29397,7 @@
         <v>46169</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -29470,7 +29470,7 @@
         <v>45352</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -29543,7 +29543,7 @@
         <v>46169</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -29616,7 +29616,7 @@
         <v>46169</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -29689,7 +29689,7 @@
         <v>45405</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -29762,7 +29762,7 @@
         <v>46171</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -29835,7 +29835,7 @@
         <v>46170</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -29908,7 +29908,7 @@
         <v>44530</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -29981,7 +29981,7 @@
         <v>45104</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -30054,7 +30054,7 @@
         <v>45454</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -30127,7 +30127,7 @@
         <v>44601</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -30200,7 +30200,7 @@
         <v>46174</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -30273,7 +30273,7 @@
         <v>44510</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -30346,7 +30346,7 @@
         <v>46175</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -30419,7 +30419,7 @@
         <v>46175</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -30492,7 +30492,7 @@
         <v>45700</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -30565,7 +30565,7 @@
         <v>45700</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -30638,7 +30638,7 @@
         <v>45182</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -30711,7 +30711,7 @@
         <v>45539</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -30784,7 +30784,7 @@
         <v>46174</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -30857,7 +30857,7 @@
         <v>45687</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -30930,7 +30930,7 @@
         <v>46174</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -31003,7 +31003,7 @@
         <v>45253</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -31076,7 +31076,7 @@
         <v>46178</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -31149,7 +31149,7 @@
         <v>46178</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -31222,7 +31222,7 @@
         <v>45531</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -31295,7 +31295,7 @@
         <v>45838</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -31368,7 +31368,7 @@
         <v>46174</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -31441,7 +31441,7 @@
         <v>45715</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -31514,7 +31514,7 @@
         <v>45182</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -31587,7 +31587,7 @@
         <v>45414</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -31660,7 +31660,7 @@
         <v>45288</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -31738,7 +31738,7 @@
         <v>45309</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -31811,7 +31811,7 @@
         <v>45407</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -31884,7 +31884,7 @@
         <v>45677</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -31957,7 +31957,7 @@
         <v>45257</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -32030,7 +32030,7 @@
         <v>45643</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -32103,7 +32103,7 @@
         <v>45114</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -32176,7 +32176,7 @@
         <v>45395</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -32249,7 +32249,7 @@
         <v>44671</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -32322,7 +32322,7 @@
         <v>45524</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -32395,7 +32395,7 @@
         <v>45272</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -32468,7 +32468,7 @@
         <v>44483</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -32541,7 +32541,7 @@
         <v>45245</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -32614,7 +32614,7 @@
         <v>45679</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -32687,7 +32687,7 @@
         <v>46183</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -32760,7 +32760,7 @@
         <v>45610</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -32833,7 +32833,7 @@
         <v>45432</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -32906,7 +32906,7 @@
         <v>44712</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -32979,7 +32979,7 @@
         <v>45131</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -33052,7 +33052,7 @@
         <v>45176</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -33125,7 +33125,7 @@
         <v>45372</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -33198,7 +33198,7 @@
         <v>45361</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -33271,7 +33271,7 @@
         <v>45541</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -33344,7 +33344,7 @@
         <v>45257</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -33422,7 +33422,7 @@
         <v>45727</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -33495,7 +33495,7 @@
         <v>46185</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -33568,7 +33568,7 @@
         <v>44917</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -33641,7 +33641,7 @@
         <v>45735</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -33714,7 +33714,7 @@
         <v>45672</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -33787,7 +33787,7 @@
         <v>45204</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -33860,7 +33860,7 @@
         <v>45293</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -33933,7 +33933,7 @@
         <v>45245</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -34006,7 +34006,7 @@
         <v>44671</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -34079,7 +34079,7 @@
         <v>44896</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -34152,7 +34152,7 @@
         <v>44970</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -34225,7 +34225,7 @@
         <v>44592</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -34298,7 +34298,7 @@
         <v>45538</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -34371,7 +34371,7 @@
         <v>45293</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -34444,7 +34444,7 @@
         <v>45623</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -34517,7 +34517,7 @@
         <v>45199</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -34590,7 +34590,7 @@
         <v>45769</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -34663,7 +34663,7 @@
         <v>46188</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -34736,7 +34736,7 @@
         <v>45392</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -34809,7 +34809,7 @@
         <v>45395</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -34882,7 +34882,7 @@
         <v>45589</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -34955,7 +34955,7 @@
         <v>45546</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -35028,7 +35028,7 @@
         <v>44701</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -35101,7 +35101,7 @@
         <v>45145</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -35174,7 +35174,7 @@
         <v>45517</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -35247,7 +35247,7 @@
         <v>45230</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -35320,7 +35320,7 @@
         <v>45677</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -35393,7 +35393,7 @@
         <v>45672</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -35466,7 +35466,7 @@
         <v>45672</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -35539,7 +35539,7 @@
         <v>44483</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -35612,7 +35612,7 @@
         <v>44476</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -35685,7 +35685,7 @@
         <v>44964</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -35758,7 +35758,7 @@
         <v>45735</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -35831,7 +35831,7 @@
         <v>44739</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -35904,7 +35904,7 @@
         <v>45170</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -35977,7 +35977,7 @@
         <v>45309</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -36050,7 +36050,7 @@
         <v>44508</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -36123,7 +36123,7 @@
         <v>45623</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -36196,7 +36196,7 @@
         <v>45252</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -36269,7 +36269,7 @@
         <v>45589</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -36342,7 +36342,7 @@
         <v>45190</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -36415,7 +36415,7 @@
         <v>44817</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -36488,7 +36488,7 @@
         <v>45462</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -36561,7 +36561,7 @@
         <v>46188</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -36634,7 +36634,7 @@
         <v>45574</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -36707,7 +36707,7 @@
         <v>45545</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -36780,7 +36780,7 @@
         <v>45199</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -36853,7 +36853,7 @@
         <v>45190</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -36931,7 +36931,7 @@
         <v>44889</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -37004,7 +37004,7 @@
         <v>45623</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -37077,7 +37077,7 @@
         <v>45170</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -37150,7 +37150,7 @@
         <v>45876</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -37223,7 +37223,7 @@
         <v>45880</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -37296,7 +37296,7 @@
         <v>45880</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -37369,7 +37369,7 @@
         <v>46196</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -37442,7 +37442,7 @@
         <v>45604</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -37515,7 +37515,7 @@
         <v>45877</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -37588,7 +37588,7 @@
         <v>45880</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -37661,7 +37661,7 @@
         <v>45091</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -37734,7 +37734,7 @@
         <v>45880</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -37807,7 +37807,7 @@
         <v>45597</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -37880,7 +37880,7 @@
         <v>46199</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -37953,7 +37953,7 @@
         <v>44641</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -38026,7 +38026,7 @@
         <v>45432</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -38099,7 +38099,7 @@
         <v>45159</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -38172,7 +38172,7 @@
         <v>45456</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -38245,7 +38245,7 @@
         <v>45366</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -38323,7 +38323,7 @@
         <v>44697</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -38396,7 +38396,7 @@
         <v>45194</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -38469,7 +38469,7 @@
         <v>46209</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -38542,7 +38542,7 @@
         <v>46161</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -38615,7 +38615,7 @@
         <v>46206</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -38688,7 +38688,7 @@
         <v>45203</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -38761,7 +38761,7 @@
         <v>45677</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -38834,7 +38834,7 @@
         <v>45132</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -38907,7 +38907,7 @@
         <v>45173</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -38980,7 +38980,7 @@
         <v>45153</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -39053,7 +39053,7 @@
         <v>45084</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -39126,7 +39126,7 @@
         <v>45254</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -39199,7 +39199,7 @@
         <v>45211</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -39272,7 +39272,7 @@
         <v>45568</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -39345,7 +39345,7 @@
         <v>45441</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -39423,7 +39423,7 @@
         <v>45456</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -39496,7 +39496,7 @@
         <v>45225</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -39569,7 +39569,7 @@
         <v>45181</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -39642,7 +39642,7 @@
         <v>46261</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -39715,7 +39715,7 @@
         <v>44823</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -39788,7 +39788,7 @@
         <v>45238</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -39861,7 +39861,7 @@
         <v>46261</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -39934,7 +39934,7 @@
         <v>45287</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -40007,7 +40007,7 @@
         <v>44701</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -40085,7 +40085,7 @@
         <v>44735</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -40158,7 +40158,7 @@
         <v>44651</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -40231,7 +40231,7 @@
         <v>45169</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -40304,7 +40304,7 @@
         <v>45316</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -40382,7 +40382,7 @@
         <v>45167</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -40455,7 +40455,7 @@
         <v>45254</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -40528,7 +40528,7 @@
         <v>45254</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -40601,7 +40601,7 @@
         <v>45245</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -40674,7 +40674,7 @@
         <v>46263</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -40747,7 +40747,7 @@
         <v>46224</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -40825,7 +40825,7 @@
         <v>44778</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -40898,7 +40898,7 @@
         <v>46268</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -40971,7 +40971,7 @@
         <v>44847</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -41044,7 +41044,7 @@
         <v>46268</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -41117,7 +41117,7 @@
         <v>46268</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -41190,7 +41190,7 @@
         <v>44694</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -41263,7 +41263,7 @@
         <v>46272</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -41336,7 +41336,7 @@
         <v>45245</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -41409,7 +41409,7 @@
         <v>45092</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -41482,7 +41482,7 @@
         <v>45051</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -41555,7 +41555,7 @@
         <v>45098</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -41633,7 +41633,7 @@
         <v>45351</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -41706,7 +41706,7 @@
         <v>44797</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -41779,7 +41779,7 @@
         <v>45267</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -41852,7 +41852,7 @@
         <v>46273</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -41925,7 +41925,7 @@
         <v>44974</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -41998,7 +41998,7 @@
         <v>45840</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -42076,7 +42076,7 @@
         <v>46273</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -42149,7 +42149,7 @@
         <v>46272</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -42222,7 +42222,7 @@
         <v>44559</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -42295,7 +42295,7 @@
         <v>44893</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -42368,7 +42368,7 @@
         <v>46279</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -42441,7 +42441,7 @@
         <v>46279</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -42514,7 +42514,7 @@
         <v>46279</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -42587,7 +42587,7 @@
         <v>45455</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -42660,7 +42660,7 @@
         <v>46036</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -42733,7 +42733,7 @@
         <v>45104</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -42806,7 +42806,7 @@
         <v>45334</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -42879,7 +42879,7 @@
         <v>45352</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -42952,7 +42952,7 @@
         <v>45715</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -43025,7 +43025,7 @@
         <v>45316</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -43098,7 +43098,7 @@
         <v>46282</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -43171,7 +43171,7 @@
         <v>44796</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -43244,7 +43244,7 @@
         <v>44901</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -43317,7 +43317,7 @@
         <v>45589</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -43390,7 +43390,7 @@
         <v>46281</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -43463,7 +43463,7 @@
         <v>45939</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -43541,7 +43541,7 @@
         <v>44899</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -43614,7 +43614,7 @@
         <v>46241</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -43687,7 +43687,7 @@
         <v>46286</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -43760,7 +43760,7 @@
         <v>44995</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -43833,7 +43833,7 @@
         <v>45548</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -43906,7 +43906,7 @@
         <v>44958</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -43979,7 +43979,7 @@
         <v>46273</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -44052,7 +44052,7 @@
         <v>46286</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -44125,7 +44125,7 @@
         <v>44575</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -44198,7 +44198,7 @@
         <v>46283</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -44271,7 +44271,7 @@
         <v>45572</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -44344,7 +44344,7 @@
         <v>46283</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -44417,7 +44417,7 @@
         <v>46245</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -44490,7 +44490,7 @@
         <v>44951</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -44563,7 +44563,7 @@
         <v>45265</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -44636,7 +44636,7 @@
         <v>45432</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -44709,7 +44709,7 @@
         <v>46283</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -44782,7 +44782,7 @@
         <v>46244</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -44855,7 +44855,7 @@
         <v>46030</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -44928,7 +44928,7 @@
         <v>46281</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -45001,7 +45001,7 @@
         <v>46281</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -45074,7 +45074,7 @@
         <v>45132</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -45147,7 +45147,7 @@
         <v>45246</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -45220,7 +45220,7 @@
         <v>45246</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -45293,7 +45293,7 @@
         <v>45426</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -45366,7 +45366,7 @@
         <v>46248</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -45439,7 +45439,7 @@
         <v>45371</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -45512,7 +45512,7 @@
         <v>46248</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -45585,7 +45585,7 @@
         <v>46247</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -45658,7 +45658,7 @@
         <v>45411</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -45731,7 +45731,7 @@
         <v>46224</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -45804,7 +45804,7 @@
         <v>45400</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -45877,7 +45877,7 @@
         <v>45441</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -45955,7 +45955,7 @@
         <v>45624</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -46028,7 +46028,7 @@
         <v>45580</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -46101,7 +46101,7 @@
         <v>45568</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -46174,7 +46174,7 @@
         <v>44714</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -46252,7 +46252,7 @@
         <v>44813</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -46325,7 +46325,7 @@
         <v>45163</v>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -46398,7 +46398,7 @@
         <v>44851</v>
       </c>
       <c r="E610" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -46471,7 +46471,7 @@
         <v>44851</v>
       </c>
       <c r="E611" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
@@ -46544,7 +46544,7 @@
         <v>45035</v>
       </c>
       <c r="E612" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
@@ -46617,7 +46617,7 @@
         <v>44726</v>
       </c>
       <c r="E613" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
@@ -46690,7 +46690,7 @@
         <v>45019</v>
       </c>
       <c r="E614" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F614" t="inlineStr">
         <is>
@@ -46763,7 +46763,7 @@
         <v>45350</v>
       </c>
       <c r="E615" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F615" t="inlineStr">
         <is>
@@ -46836,7 +46836,7 @@
         <v>45434</v>
       </c>
       <c r="E616" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F616" t="inlineStr">
         <is>
@@ -46909,7 +46909,7 @@
         <v>44469</v>
       </c>
       <c r="E617" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F617" t="inlineStr">
         <is>
@@ -46982,7 +46982,7 @@
         <v>44900</v>
       </c>
       <c r="E618" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F618" t="inlineStr">
         <is>
@@ -47055,7 +47055,7 @@
         <v>45357</v>
       </c>
       <c r="E619" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F619" t="inlineStr">
         <is>
@@ -47128,7 +47128,7 @@
         <v>45429</v>
       </c>
       <c r="E620" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F620" t="inlineStr">
         <is>
@@ -47201,7 +47201,7 @@
         <v>45002</v>
       </c>
       <c r="E621" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F621" t="inlineStr">
         <is>
@@ -47274,7 +47274,7 @@
         <v>45684</v>
       </c>
       <c r="E622" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F622" t="inlineStr">
         <is>
@@ -47347,7 +47347,7 @@
         <v>45342</v>
       </c>
       <c r="E623" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F623" t="inlineStr">
         <is>
@@ -47425,7 +47425,7 @@
         <v>45477</v>
       </c>
       <c r="E624" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F624" t="inlineStr">
         <is>
@@ -47498,7 +47498,7 @@
         <v>45371</v>
       </c>
       <c r="E625" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F625" t="inlineStr">
         <is>
@@ -47571,7 +47571,7 @@
         <v>44953</v>
       </c>
       <c r="E626" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F626" t="inlineStr">
         <is>
@@ -47644,7 +47644,7 @@
         <v>45624</v>
       </c>
       <c r="E627" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F627" t="inlineStr">
         <is>
@@ -47717,7 +47717,7 @@
         <v>45169</v>
       </c>
       <c r="E628" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F628" t="inlineStr">
         <is>
@@ -47790,7 +47790,7 @@
         <v>45229</v>
       </c>
       <c r="E629" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F629" t="inlineStr">
         <is>
@@ -47863,7 +47863,7 @@
         <v>45770</v>
       </c>
       <c r="E630" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F630" t="inlineStr">
         <is>
@@ -47936,7 +47936,7 @@
         <v>45674</v>
       </c>
       <c r="E631" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F631" t="inlineStr">
         <is>
@@ -48009,7 +48009,7 @@
         <v>45035</v>
       </c>
       <c r="E632" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F632" t="inlineStr">
         <is>
@@ -48082,7 +48082,7 @@
         <v>44635</v>
       </c>
       <c r="E633" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F633" t="inlineStr">
         <is>
@@ -48160,7 +48160,7 @@
         <v>45700</v>
       </c>
       <c r="E634" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F634" t="inlineStr">
         <is>
@@ -48233,7 +48233,7 @@
         <v>45084</v>
       </c>
       <c r="E635" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F635" t="inlineStr">
         <is>
@@ -48306,7 +48306,7 @@
         <v>45229</v>
       </c>
       <c r="E636" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F636" t="inlineStr">
         <is>
@@ -48379,7 +48379,7 @@
         <v>45252</v>
       </c>
       <c r="E637" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F637" t="inlineStr">
         <is>
@@ -48452,7 +48452,7 @@
         <v>44750</v>
       </c>
       <c r="E638" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F638" t="inlineStr">
         <is>
@@ -48525,7 +48525,7 @@
         <v>45368</v>
       </c>
       <c r="E639" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F639" t="inlineStr">
         <is>
@@ -48603,7 +48603,7 @@
         <v>44893</v>
       </c>
       <c r="E640" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F640" t="inlineStr">
         <is>
@@ -48676,7 +48676,7 @@
         <v>45541</v>
       </c>
       <c r="E641" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F641" t="inlineStr">
         <is>
@@ -48749,7 +48749,7 @@
         <v>45527</v>
       </c>
       <c r="E642" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F642" t="inlineStr">
         <is>
@@ -48822,7 +48822,7 @@
         <v>45062</v>
       </c>
       <c r="E643" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F643" t="inlineStr">
         <is>
@@ -48895,7 +48895,7 @@
         <v>45371</v>
       </c>
       <c r="E644" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F644" t="inlineStr">
         <is>
@@ -48968,7 +48968,7 @@
         <v>44868</v>
       </c>
       <c r="E645" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F645" t="inlineStr">
         <is>
@@ -49041,7 +49041,7 @@
         <v>45737</v>
       </c>
       <c r="E646" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F646" t="inlineStr">
         <is>
@@ -49114,7 +49114,7 @@
         <v>45258</v>
       </c>
       <c r="E647" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F647" t="inlineStr">
         <is>
@@ -49187,7 +49187,7 @@
         <v>45485</v>
       </c>
       <c r="E648" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F648" t="inlineStr">
         <is>
@@ -49260,7 +49260,7 @@
         <v>45462</v>
       </c>
       <c r="E649" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F649" t="inlineStr">
         <is>
@@ -49333,7 +49333,7 @@
         <v>45560</v>
       </c>
       <c r="E650" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F650" t="inlineStr">
         <is>
@@ -49406,7 +49406,7 @@
         <v>45089</v>
       </c>
       <c r="E651" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F651" t="inlineStr">
         <is>
@@ -49479,7 +49479,7 @@
         <v>45300</v>
       </c>
       <c r="E652" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F652" t="inlineStr">
         <is>
@@ -49552,7 +49552,7 @@
         <v>45352</v>
       </c>
       <c r="E653" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F653" t="inlineStr">
         <is>
@@ -49625,7 +49625,7 @@
         <v>45377</v>
       </c>
       <c r="E654" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F654" t="inlineStr">
         <is>
@@ -49703,7 +49703,7 @@
         <v>45176</v>
       </c>
       <c r="E655" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F655" t="inlineStr">
         <is>
@@ -49781,7 +49781,7 @@
         <v>45638</v>
       </c>
       <c r="E656" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F656" t="inlineStr">
         <is>
@@ -49854,7 +49854,7 @@
         <v>45588</v>
       </c>
       <c r="E657" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F657" t="inlineStr">
         <is>
@@ -49932,7 +49932,7 @@
         <v>45616</v>
       </c>
       <c r="E658" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F658" t="inlineStr">
         <is>
@@ -50005,7 +50005,7 @@
         <v>45391</v>
       </c>
       <c r="E659" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F659" t="inlineStr">
         <is>
@@ -50078,7 +50078,7 @@
         <v>45510</v>
       </c>
       <c r="E660" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F660" t="inlineStr">
         <is>
@@ -50151,7 +50151,7 @@
         <v>45783</v>
       </c>
       <c r="E661" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F661" t="inlineStr">
         <is>
@@ -50224,7 +50224,7 @@
         <v>45616</v>
       </c>
       <c r="E662" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F662" t="inlineStr">
         <is>
@@ -50297,7 +50297,7 @@
         <v>45786</v>
       </c>
       <c r="E663" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F663" t="inlineStr">
         <is>
@@ -50375,7 +50375,7 @@
         <v>45559</v>
       </c>
       <c r="E664" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F664" t="inlineStr">
         <is>
@@ -50448,7 +50448,7 @@
         <v>45680</v>
       </c>
       <c r="E665" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F665" t="inlineStr">
         <is>
@@ -50521,7 +50521,7 @@
         <v>45225</v>
       </c>
       <c r="E666" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F666" t="inlineStr">
         <is>
@@ -50594,7 +50594,7 @@
         <v>45589</v>
       </c>
       <c r="E667" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F667" t="inlineStr">
         <is>
@@ -50672,7 +50672,7 @@
         <v>45618</v>
       </c>
       <c r="E668" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F668" t="inlineStr">
         <is>
@@ -50745,7 +50745,7 @@
         <v>45726</v>
       </c>
       <c r="E669" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F669" t="inlineStr">
         <is>
@@ -50818,7 +50818,7 @@
         <v>45741</v>
       </c>
       <c r="E670" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F670" t="inlineStr">
         <is>
@@ -50891,7 +50891,7 @@
         <v>45483</v>
       </c>
       <c r="E671" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F671" t="inlineStr">
         <is>
@@ -50964,7 +50964,7 @@
         <v>45609</v>
       </c>
       <c r="E672" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F672" t="inlineStr">
         <is>
@@ -51037,7 +51037,7 @@
         <v>45483</v>
       </c>
       <c r="E673" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F673" t="inlineStr">
         <is>
@@ -51110,7 +51110,7 @@
         <v>45743</v>
       </c>
       <c r="E674" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F674" t="inlineStr">
         <is>
@@ -51188,7 +51188,7 @@
         <v>45590</v>
       </c>
       <c r="E675" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F675" t="inlineStr">
         <is>
@@ -51261,7 +51261,7 @@
         <v>45743</v>
       </c>
       <c r="E676" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F676" t="inlineStr">
         <is>
@@ -51339,7 +51339,7 @@
         <v>44631</v>
       </c>
       <c r="E677" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F677" t="inlineStr">
         <is>
@@ -51412,7 +51412,7 @@
         <v>44613</v>
       </c>
       <c r="E678" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F678" t="inlineStr">
         <is>
@@ -51485,7 +51485,7 @@
         <v>44608</v>
       </c>
       <c r="E679" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F679" t="inlineStr">
         <is>
@@ -51558,7 +51558,7 @@
         <v>44631</v>
       </c>
       <c r="E680" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F680" t="inlineStr">
         <is>
@@ -51631,7 +51631,7 @@
         <v>44631</v>
       </c>
       <c r="E681" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F681" t="inlineStr">
         <is>
@@ -51704,7 +51704,7 @@
         <v>45614</v>
       </c>
       <c r="E682" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F682" t="inlineStr">
         <is>
@@ -51782,7 +51782,7 @@
         <v>44743</v>
       </c>
       <c r="E683" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F683" t="inlineStr">
         <is>
@@ -51855,7 +51855,7 @@
         <v>45375</v>
       </c>
       <c r="E684" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F684" t="inlineStr">
         <is>
@@ -51928,7 +51928,7 @@
         <v>44488</v>
       </c>
       <c r="E685" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F685" t="inlineStr">
         <is>
@@ -52001,7 +52001,7 @@
         <v>45604</v>
       </c>
       <c r="E686" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F686" t="inlineStr">
         <is>
@@ -52074,7 +52074,7 @@
         <v>45356</v>
       </c>
       <c r="E687" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F687" t="inlineStr">
         <is>
@@ -52147,7 +52147,7 @@
         <v>45349</v>
       </c>
       <c r="E688" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F688" t="inlineStr">
         <is>
@@ -52220,7 +52220,7 @@
         <v>45744</v>
       </c>
       <c r="E689" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F689" t="inlineStr">
         <is>
@@ -52293,7 +52293,7 @@
         <v>45714</v>
       </c>
       <c r="E690" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F690" t="inlineStr">
         <is>
@@ -52366,7 +52366,7 @@
         <v>45715</v>
       </c>
       <c r="E691" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F691" t="inlineStr">
         <is>
@@ -52439,7 +52439,7 @@
         <v>45709</v>
       </c>
       <c r="E692" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F692" t="inlineStr">
         <is>
@@ -52512,7 +52512,7 @@
         <v>45714</v>
       </c>
       <c r="E693" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F693" t="inlineStr">
         <is>
@@ -52585,7 +52585,7 @@
         <v>45813</v>
       </c>
       <c r="E694" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F694" t="inlineStr">
         <is>
@@ -52658,7 +52658,7 @@
         <v>45813</v>
       </c>
       <c r="E695" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F695" t="inlineStr">
         <is>
@@ -52731,7 +52731,7 @@
         <v>45813</v>
       </c>
       <c r="E696" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F696" t="inlineStr">
         <is>
@@ -52804,7 +52804,7 @@
         <v>45820</v>
       </c>
       <c r="E697" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F697" t="inlineStr">
         <is>
@@ -52877,7 +52877,7 @@
         <v>45827</v>
       </c>
       <c r="E698" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F698" t="inlineStr">
         <is>
@@ -52950,7 +52950,7 @@
         <v>45845</v>
       </c>
       <c r="E699" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F699" t="inlineStr">
         <is>
@@ -53023,7 +53023,7 @@
         <v>45883</v>
       </c>
       <c r="E700" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F700" t="inlineStr">
         <is>
@@ -53096,7 +53096,7 @@
         <v>45915</v>
       </c>
       <c r="E701" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F701" t="inlineStr">
         <is>
@@ -53169,7 +53169,7 @@
         <v>46041</v>
       </c>
       <c r="E702" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F702" t="inlineStr">
         <is>
@@ -53242,7 +53242,7 @@
         <v>46133</v>
       </c>
       <c r="E703" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F703" t="inlineStr">
         <is>
@@ -53315,7 +53315,7 @@
         <v>46147</v>
       </c>
       <c r="E704" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F704" t="inlineStr">
         <is>
@@ -53388,7 +53388,7 @@
         <v>46253</v>
       </c>
       <c r="E705" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F705" t="inlineStr">
         <is>
@@ -53461,7 +53461,7 @@
         <v>46211</v>
       </c>
       <c r="E706" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F706" t="inlineStr">
         <is>
@@ -53534,7 +53534,7 @@
         <v>46290</v>
       </c>
       <c r="E707" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F707" t="inlineStr">
         <is>

--- a/Översikt HYLTE.xlsx
+++ b/Översikt HYLTE.xlsx
@@ -601,7 +601,7 @@
         <v>46090</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -718,7 +718,7 @@
         <v>45265</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -834,7 +834,7 @@
         <v>46066</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -945,7 +945,7 @@
         <v>44873</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1054,7 +1054,7 @@
         <v>45348</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1166,7 +1166,7 @@
         <v>45719</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1274,7 +1274,7 @@
         <v>45245</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1385,7 +1385,7 @@
         <v>46268</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1492,7 +1492,7 @@
         <v>45230</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1599,7 +1599,7 @@
         <v>45737</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1706,7 +1706,7 @@
         <v>46141</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1813,7 +1813,7 @@
         <v>46161</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1920,7 +1920,7 @@
         <v>44839</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2030,7 +2030,7 @@
         <v>46048</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2136,7 +2136,7 @@
         <v>45841</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2246,7 +2246,7 @@
         <v>45099</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2356,7 +2356,7 @@
         <v>45904</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2466,7 +2466,7 @@
         <v>46130</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2572,7 +2572,7 @@
         <v>44648</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2677,7 +2677,7 @@
         <v>44651</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2782,7 +2782,7 @@
         <v>44876</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2887,7 +2887,7 @@
         <v>45299</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2996,7 +2996,7 @@
         <v>45153</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3110,7 +3110,7 @@
         <v>45163</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3215,7 +3215,7 @@
         <v>45343</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3320,7 +3320,7 @@
         <v>45476</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3430,7 +3430,7 @@
         <v>45085</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3539,7 +3539,7 @@
         <v>45186</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3644,7 +3644,7 @@
         <v>45245</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3749,7 +3749,7 @@
         <v>45593</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3854,7 +3854,7 @@
         <v>45245</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3959,7 +3959,7 @@
         <v>45617</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4064,7 +4064,7 @@
         <v>45253</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4169,7 +4169,7 @@
         <v>45754</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4274,7 +4274,7 @@
         <v>46253</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4384,7 +4384,7 @@
         <v>44481</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4457,7 +4457,7 @@
         <v>44810</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4530,7 +4530,7 @@
         <v>44600</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4603,7 +4603,7 @@
         <v>44529</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4676,7 +4676,7 @@
         <v>44557</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4749,7 +4749,7 @@
         <v>44483</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4822,7 +4822,7 @@
         <v>44705</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4895,7 +4895,7 @@
         <v>44778</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4968,7 +4968,7 @@
         <v>44488</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5041,7 +5041,7 @@
         <v>44475</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5114,7 +5114,7 @@
         <v>44624</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5187,7 +5187,7 @@
         <v>44812</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5260,7 +5260,7 @@
         <v>44638</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5333,7 +5333,7 @@
         <v>44498</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5406,7 +5406,7 @@
         <v>44845</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5479,7 +5479,7 @@
         <v>44559</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5552,7 +5552,7 @@
         <v>44578</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5625,7 +5625,7 @@
         <v>44659</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5703,7 +5703,7 @@
         <v>44756</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5776,7 +5776,7 @@
         <v>44501</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5849,7 +5849,7 @@
         <v>44651</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5922,7 +5922,7 @@
         <v>44711</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5995,7 +5995,7 @@
         <v>44487</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6073,7 +6073,7 @@
         <v>44735</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6146,7 +6146,7 @@
         <v>44477</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6219,7 +6219,7 @@
         <v>44489</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6292,7 +6292,7 @@
         <v>44834</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6365,7 +6365,7 @@
         <v>44469</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6438,7 +6438,7 @@
         <v>44796</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6511,7 +6511,7 @@
         <v>44502</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6584,7 +6584,7 @@
         <v>44876</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6657,7 +6657,7 @@
         <v>44631</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6730,7 +6730,7 @@
         <v>44659</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6803,7 +6803,7 @@
         <v>44644</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6876,7 +6876,7 @@
         <v>44515</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6954,7 +6954,7 @@
         <v>44778</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7027,7 +7027,7 @@
         <v>44482</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7100,7 +7100,7 @@
         <v>44482</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7173,7 +7173,7 @@
         <v>44867</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7246,7 +7246,7 @@
         <v>44505</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7319,7 +7319,7 @@
         <v>44634</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7392,7 +7392,7 @@
         <v>44728</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7465,7 +7465,7 @@
         <v>44714</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7538,7 +7538,7 @@
         <v>44795</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7611,7 +7611,7 @@
         <v>44818</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7684,7 +7684,7 @@
         <v>44801</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7757,7 +7757,7 @@
         <v>44596</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7835,7 +7835,7 @@
         <v>44644</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7908,7 +7908,7 @@
         <v>44523</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7981,7 +7981,7 @@
         <v>44500</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8054,7 +8054,7 @@
         <v>44727</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8127,7 +8127,7 @@
         <v>44705</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8200,7 +8200,7 @@
         <v>44659</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8278,7 +8278,7 @@
         <v>44659</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8356,7 +8356,7 @@
         <v>44757</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8429,7 +8429,7 @@
         <v>44494</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8502,7 +8502,7 @@
         <v>44495</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8575,7 +8575,7 @@
         <v>45042</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8648,7 +8648,7 @@
         <v>45327</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8721,7 +8721,7 @@
         <v>45299</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8794,7 +8794,7 @@
         <v>44900</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8867,7 +8867,7 @@
         <v>44900</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8940,7 +8940,7 @@
         <v>45208</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -9013,7 +9013,7 @@
         <v>44866</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9086,7 +9086,7 @@
         <v>45254</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9159,7 +9159,7 @@
         <v>45331</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9232,7 +9232,7 @@
         <v>44847</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9305,7 +9305,7 @@
         <v>45254</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9378,7 +9378,7 @@
         <v>45254</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9451,7 +9451,7 @@
         <v>44872</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9524,7 +9524,7 @@
         <v>45441</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9597,7 +9597,7 @@
         <v>45254</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9670,7 +9670,7 @@
         <v>45254</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9743,7 +9743,7 @@
         <v>45378</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9816,7 +9816,7 @@
         <v>45382</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9889,7 +9889,7 @@
         <v>45061</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9962,7 +9962,7 @@
         <v>45752</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -10040,7 +10040,7 @@
         <v>45253</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10113,7 +10113,7 @@
         <v>45456</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10186,7 +10186,7 @@
         <v>45390</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10259,7 +10259,7 @@
         <v>44482</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10332,7 +10332,7 @@
         <v>45505</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10405,7 +10405,7 @@
         <v>45097</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10478,7 +10478,7 @@
         <v>45478</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10551,7 +10551,7 @@
         <v>44476</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10624,7 +10624,7 @@
         <v>46020</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10697,7 +10697,7 @@
         <v>45559</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -10770,7 +10770,7 @@
         <v>45681</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10843,7 +10843,7 @@
         <v>45743</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10921,7 +10921,7 @@
         <v>44851</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -10994,7 +10994,7 @@
         <v>45600</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -11067,7 +11067,7 @@
         <v>44495</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11140,7 +11140,7 @@
         <v>44487</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11218,7 +11218,7 @@
         <v>44950</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11291,7 +11291,7 @@
         <v>45299</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11364,7 +11364,7 @@
         <v>45793</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11437,7 +11437,7 @@
         <v>45352</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11510,7 +11510,7 @@
         <v>44865</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11583,7 +11583,7 @@
         <v>45834</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11656,7 +11656,7 @@
         <v>45840</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -11729,7 +11729,7 @@
         <v>45436</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -11802,7 +11802,7 @@
         <v>45673</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -11875,7 +11875,7 @@
         <v>45352</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -11948,7 +11948,7 @@
         <v>44477</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -12021,7 +12021,7 @@
         <v>44469</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -12094,7 +12094,7 @@
         <v>44834</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12167,7 +12167,7 @@
         <v>45890</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12240,7 +12240,7 @@
         <v>45748</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12313,7 +12313,7 @@
         <v>45891</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12391,7 +12391,7 @@
         <v>45891</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -12469,7 +12469,7 @@
         <v>46042</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -12542,7 +12542,7 @@
         <v>44896</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -12615,7 +12615,7 @@
         <v>46042</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -12688,7 +12688,7 @@
         <v>46044</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -12761,7 +12761,7 @@
         <v>46044</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -12834,7 +12834,7 @@
         <v>46044</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -12907,7 +12907,7 @@
         <v>46044</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -12980,7 +12980,7 @@
         <v>46048</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -13053,7 +13053,7 @@
         <v>45897</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -13126,7 +13126,7 @@
         <v>45897</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13199,7 +13199,7 @@
         <v>46048</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13272,7 +13272,7 @@
         <v>45429</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13345,7 +13345,7 @@
         <v>46048</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -13418,7 +13418,7 @@
         <v>46048</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -13491,7 +13491,7 @@
         <v>46048</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -13564,7 +13564,7 @@
         <v>46048</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -13637,7 +13637,7 @@
         <v>46048</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -13710,7 +13710,7 @@
         <v>46048</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -13783,7 +13783,7 @@
         <v>45839</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -13856,7 +13856,7 @@
         <v>45898</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -13929,7 +13929,7 @@
         <v>46048</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -14002,7 +14002,7 @@
         <v>46048</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -14075,7 +14075,7 @@
         <v>46048</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -14148,7 +14148,7 @@
         <v>46048</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14221,7 +14221,7 @@
         <v>46049</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14294,7 +14294,7 @@
         <v>44489</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -14367,7 +14367,7 @@
         <v>45905</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -14440,7 +14440,7 @@
         <v>45366</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -14513,7 +14513,7 @@
         <v>46052</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -14586,7 +14586,7 @@
         <v>45538</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -14659,7 +14659,7 @@
         <v>46052</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -14732,7 +14732,7 @@
         <v>45910</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -14805,7 +14805,7 @@
         <v>46055</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -14878,7 +14878,7 @@
         <v>45910</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -14951,7 +14951,7 @@
         <v>45838</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -15024,7 +15024,7 @@
         <v>46057</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -15097,7 +15097,7 @@
         <v>46062</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -15170,7 +15170,7 @@
         <v>45671</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -15243,7 +15243,7 @@
         <v>45918</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -15316,7 +15316,7 @@
         <v>46062</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -15389,7 +15389,7 @@
         <v>46064</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -15462,7 +15462,7 @@
         <v>45558</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -15535,7 +15535,7 @@
         <v>45922</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -15608,7 +15608,7 @@
         <v>45922</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -15681,7 +15681,7 @@
         <v>45922</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -15754,7 +15754,7 @@
         <v>46065</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -15827,7 +15827,7 @@
         <v>46070</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -15900,7 +15900,7 @@
         <v>46070</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -15973,7 +15973,7 @@
         <v>45924</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -16046,7 +16046,7 @@
         <v>45926</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -16119,7 +16119,7 @@
         <v>45926</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -16192,7 +16192,7 @@
         <v>45926</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -16265,7 +16265,7 @@
         <v>44719</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -16338,7 +16338,7 @@
         <v>45929</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -16411,7 +16411,7 @@
         <v>45931</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -16484,7 +16484,7 @@
         <v>45806</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -16557,7 +16557,7 @@
         <v>45931</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -16630,7 +16630,7 @@
         <v>44701</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -16708,7 +16708,7 @@
         <v>45609</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -16781,7 +16781,7 @@
         <v>45259</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -16854,7 +16854,7 @@
         <v>44714</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -16927,7 +16927,7 @@
         <v>45930</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -17000,7 +17000,7 @@
         <v>46084</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -17073,7 +17073,7 @@
         <v>46084</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -17146,7 +17146,7 @@
         <v>46087</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -17219,7 +17219,7 @@
         <v>45933</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -17292,7 +17292,7 @@
         <v>45936</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -17365,7 +17365,7 @@
         <v>45936</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -17438,7 +17438,7 @@
         <v>45933</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -17511,7 +17511,7 @@
         <v>45933</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -17584,7 +17584,7 @@
         <v>44974</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -17657,7 +17657,7 @@
         <v>45936</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -17730,7 +17730,7 @@
         <v>45937</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -17803,7 +17803,7 @@
         <v>45229</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -17876,7 +17876,7 @@
         <v>45198</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -17949,7 +17949,7 @@
         <v>46093</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -18022,7 +18022,7 @@
         <v>46093</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -18095,7 +18095,7 @@
         <v>45938</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -18168,7 +18168,7 @@
         <v>44481</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -18241,7 +18241,7 @@
         <v>46093</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -18314,7 +18314,7 @@
         <v>44900</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -18387,7 +18387,7 @@
         <v>45441</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -18460,7 +18460,7 @@
         <v>44926</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -18538,7 +18538,7 @@
         <v>45944</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -18611,7 +18611,7 @@
         <v>44756</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -18684,7 +18684,7 @@
         <v>45162</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -18757,7 +18757,7 @@
         <v>45162</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -18830,7 +18830,7 @@
         <v>45268</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -18903,7 +18903,7 @@
         <v>44903</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -18976,7 +18976,7 @@
         <v>44999</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -19049,7 +19049,7 @@
         <v>46057</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -19122,7 +19122,7 @@
         <v>45812</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -19195,7 +19195,7 @@
         <v>46057</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -19268,7 +19268,7 @@
         <v>46111</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -19341,7 +19341,7 @@
         <v>46111</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -19414,7 +19414,7 @@
         <v>46111</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -19487,7 +19487,7 @@
         <v>45957</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -19560,7 +19560,7 @@
         <v>45254</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -19633,7 +19633,7 @@
         <v>45460</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -19706,7 +19706,7 @@
         <v>44965</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -19784,7 +19784,7 @@
         <v>45751</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -19862,7 +19862,7 @@
         <v>46121</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -19935,7 +19935,7 @@
         <v>46120</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -20008,7 +20008,7 @@
         <v>45961</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -20081,7 +20081,7 @@
         <v>45961</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -20154,7 +20154,7 @@
         <v>46121</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -20227,7 +20227,7 @@
         <v>46121</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -20300,7 +20300,7 @@
         <v>46121</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -20373,7 +20373,7 @@
         <v>46121</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -20446,7 +20446,7 @@
         <v>46120</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -20519,7 +20519,7 @@
         <v>46121</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -20592,7 +20592,7 @@
         <v>46121</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -20665,7 +20665,7 @@
         <v>44970</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -20738,7 +20738,7 @@
         <v>44970</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -20811,7 +20811,7 @@
         <v>45922</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -20884,7 +20884,7 @@
         <v>46122</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -20957,7 +20957,7 @@
         <v>46122</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -21030,7 +21030,7 @@
         <v>45107</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -21103,7 +21103,7 @@
         <v>46122</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -21176,7 +21176,7 @@
         <v>46122</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -21249,7 +21249,7 @@
         <v>46121</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -21322,7 +21322,7 @@
         <v>45972</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -21395,7 +21395,7 @@
         <v>45456</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -21468,7 +21468,7 @@
         <v>45972</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -21541,7 +21541,7 @@
         <v>45092</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -21614,7 +21614,7 @@
         <v>45972</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -21687,7 +21687,7 @@
         <v>45730</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -21760,7 +21760,7 @@
         <v>45229</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -21833,7 +21833,7 @@
         <v>45002</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -21906,7 +21906,7 @@
         <v>45694</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -21979,7 +21979,7 @@
         <v>45107</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -22052,7 +22052,7 @@
         <v>46128</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -22125,7 +22125,7 @@
         <v>45597</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -22198,7 +22198,7 @@
         <v>45645</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -22271,7 +22271,7 @@
         <v>45708</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -22344,7 +22344,7 @@
         <v>45145</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -22417,7 +22417,7 @@
         <v>45979</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -22490,7 +22490,7 @@
         <v>45387</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -22563,7 +22563,7 @@
         <v>45981</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -22636,7 +22636,7 @@
         <v>45981</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -22709,7 +22709,7 @@
         <v>45790</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -22782,7 +22782,7 @@
         <v>45638</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -22855,7 +22855,7 @@
         <v>45987</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -22928,7 +22928,7 @@
         <v>45568</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -23001,7 +23001,7 @@
         <v>45989</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -23074,7 +23074,7 @@
         <v>44712</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -23147,7 +23147,7 @@
         <v>45840</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -23225,7 +23225,7 @@
         <v>45995</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -23298,7 +23298,7 @@
         <v>44729</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -23371,7 +23371,7 @@
         <v>45775</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -23444,7 +23444,7 @@
         <v>45782</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -23517,7 +23517,7 @@
         <v>45483</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -23590,7 +23590,7 @@
         <v>44699</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -23663,7 +23663,7 @@
         <v>45524</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -23736,7 +23736,7 @@
         <v>44980</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -23809,7 +23809,7 @@
         <v>45246</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -23882,7 +23882,7 @@
         <v>45715</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -23955,7 +23955,7 @@
         <v>45989</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -24028,7 +24028,7 @@
         <v>46084</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -24101,7 +24101,7 @@
         <v>45706</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -24174,7 +24174,7 @@
         <v>45351</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -24247,7 +24247,7 @@
         <v>45544</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -24320,7 +24320,7 @@
         <v>45926</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -24393,7 +24393,7 @@
         <v>45820</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -24466,7 +24466,7 @@
         <v>45229</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -24539,7 +24539,7 @@
         <v>44900</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -24612,7 +24612,7 @@
         <v>45531</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -24685,7 +24685,7 @@
         <v>45817</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -24758,7 +24758,7 @@
         <v>46084</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -24831,7 +24831,7 @@
         <v>45839</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -24904,7 +24904,7 @@
         <v>44539</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -24977,7 +24977,7 @@
         <v>45502</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -25050,7 +25050,7 @@
         <v>45848</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -25123,7 +25123,7 @@
         <v>45825</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -25196,7 +25196,7 @@
         <v>44910</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -25269,7 +25269,7 @@
         <v>45617</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -25342,7 +25342,7 @@
         <v>44477</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -25415,7 +25415,7 @@
         <v>45548</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -25488,7 +25488,7 @@
         <v>45019</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -25561,7 +25561,7 @@
         <v>45257</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -25634,7 +25634,7 @@
         <v>45831</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -25707,7 +25707,7 @@
         <v>45754</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -25780,7 +25780,7 @@
         <v>46148</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -25853,7 +25853,7 @@
         <v>45091</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -25926,7 +25926,7 @@
         <v>46153</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -25999,7 +25999,7 @@
         <v>46153</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -26072,7 +26072,7 @@
         <v>46153</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -26145,7 +26145,7 @@
         <v>46153</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -26218,7 +26218,7 @@
         <v>45601</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -26291,7 +26291,7 @@
         <v>44869</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -26364,7 +26364,7 @@
         <v>45709</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -26437,7 +26437,7 @@
         <v>46153</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -26510,7 +26510,7 @@
         <v>46153</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -26583,7 +26583,7 @@
         <v>46153</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -26656,7 +26656,7 @@
         <v>45096</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -26729,7 +26729,7 @@
         <v>44900</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -26807,7 +26807,7 @@
         <v>46155</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -26880,7 +26880,7 @@
         <v>45104</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -26953,7 +26953,7 @@
         <v>45441</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -27026,7 +27026,7 @@
         <v>45441</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -27099,7 +27099,7 @@
         <v>45835</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -27172,7 +27172,7 @@
         <v>45836</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -27245,7 +27245,7 @@
         <v>45229</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -27318,7 +27318,7 @@
         <v>46161</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -27396,7 +27396,7 @@
         <v>46161</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -27469,7 +27469,7 @@
         <v>45838</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -27542,7 +27542,7 @@
         <v>45840</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -27615,7 +27615,7 @@
         <v>45840</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -27688,7 +27688,7 @@
         <v>45840</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -27761,7 +27761,7 @@
         <v>45110</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -27834,7 +27834,7 @@
         <v>46161</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -27912,7 +27912,7 @@
         <v>46161</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -27990,7 +27990,7 @@
         <v>46161</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -28063,7 +28063,7 @@
         <v>46161</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -28141,7 +28141,7 @@
         <v>45170</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -28214,7 +28214,7 @@
         <v>45845</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -28287,7 +28287,7 @@
         <v>45845</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -28360,7 +28360,7 @@
         <v>45800</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -28433,7 +28433,7 @@
         <v>45846</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -28511,7 +28511,7 @@
         <v>45310</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -28584,7 +28584,7 @@
         <v>45846</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -28662,7 +28662,7 @@
         <v>45846</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -28740,7 +28740,7 @@
         <v>45847</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -28813,7 +28813,7 @@
         <v>45694</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -28886,7 +28886,7 @@
         <v>45847</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -28959,7 +28959,7 @@
         <v>45406</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -29032,7 +29032,7 @@
         <v>45803</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -29105,7 +29105,7 @@
         <v>44967</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -29178,7 +29178,7 @@
         <v>45110</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -29251,7 +29251,7 @@
         <v>45145</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -29324,7 +29324,7 @@
         <v>45117</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -29397,7 +29397,7 @@
         <v>46169</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -29470,7 +29470,7 @@
         <v>45352</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -29543,7 +29543,7 @@
         <v>46169</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -29616,7 +29616,7 @@
         <v>46169</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -29689,7 +29689,7 @@
         <v>45405</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -29762,7 +29762,7 @@
         <v>46171</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -29835,7 +29835,7 @@
         <v>46170</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -29908,7 +29908,7 @@
         <v>44530</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -29981,7 +29981,7 @@
         <v>45104</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -30054,7 +30054,7 @@
         <v>45454</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -30127,7 +30127,7 @@
         <v>44601</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -30200,7 +30200,7 @@
         <v>46174</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -30273,7 +30273,7 @@
         <v>44510</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -30346,7 +30346,7 @@
         <v>46175</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -30419,7 +30419,7 @@
         <v>46175</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -30492,7 +30492,7 @@
         <v>45700</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -30565,7 +30565,7 @@
         <v>45700</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -30638,7 +30638,7 @@
         <v>45182</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -30711,7 +30711,7 @@
         <v>45539</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -30784,7 +30784,7 @@
         <v>46174</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -30857,7 +30857,7 @@
         <v>45687</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -30930,7 +30930,7 @@
         <v>46174</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -31003,7 +31003,7 @@
         <v>45253</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -31076,7 +31076,7 @@
         <v>46178</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -31149,7 +31149,7 @@
         <v>46178</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -31222,7 +31222,7 @@
         <v>45531</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -31295,7 +31295,7 @@
         <v>45838</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -31368,7 +31368,7 @@
         <v>46174</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -31441,7 +31441,7 @@
         <v>45715</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -31514,7 +31514,7 @@
         <v>45182</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -31587,7 +31587,7 @@
         <v>45414</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -31660,7 +31660,7 @@
         <v>45288</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -31738,7 +31738,7 @@
         <v>45309</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -31811,7 +31811,7 @@
         <v>45407</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -31884,7 +31884,7 @@
         <v>45677</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -31957,7 +31957,7 @@
         <v>45257</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -32030,7 +32030,7 @@
         <v>45643</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -32103,7 +32103,7 @@
         <v>45114</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -32176,7 +32176,7 @@
         <v>45395</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -32249,7 +32249,7 @@
         <v>44671</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -32322,7 +32322,7 @@
         <v>45524</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -32395,7 +32395,7 @@
         <v>45272</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -32468,7 +32468,7 @@
         <v>44483</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -32541,7 +32541,7 @@
         <v>45245</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -32614,7 +32614,7 @@
         <v>45679</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -32687,7 +32687,7 @@
         <v>46183</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -32760,7 +32760,7 @@
         <v>45610</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -32833,7 +32833,7 @@
         <v>45432</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -32906,7 +32906,7 @@
         <v>44712</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -32979,7 +32979,7 @@
         <v>45131</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -33052,7 +33052,7 @@
         <v>45176</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -33125,7 +33125,7 @@
         <v>45372</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -33198,7 +33198,7 @@
         <v>45361</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -33271,7 +33271,7 @@
         <v>45541</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -33344,7 +33344,7 @@
         <v>45257</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -33422,7 +33422,7 @@
         <v>45727</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -33495,7 +33495,7 @@
         <v>46185</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -33568,7 +33568,7 @@
         <v>44917</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -33641,7 +33641,7 @@
         <v>45735</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -33714,7 +33714,7 @@
         <v>45672</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -33787,7 +33787,7 @@
         <v>45204</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -33860,7 +33860,7 @@
         <v>45293</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -33933,7 +33933,7 @@
         <v>45245</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -34006,7 +34006,7 @@
         <v>44671</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -34079,7 +34079,7 @@
         <v>44896</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -34152,7 +34152,7 @@
         <v>44970</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -34225,7 +34225,7 @@
         <v>44592</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -34298,7 +34298,7 @@
         <v>45538</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -34371,7 +34371,7 @@
         <v>45293</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -34444,7 +34444,7 @@
         <v>45623</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -34517,7 +34517,7 @@
         <v>45199</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -34590,7 +34590,7 @@
         <v>45769</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -34663,7 +34663,7 @@
         <v>46188</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -34736,7 +34736,7 @@
         <v>45392</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -34809,7 +34809,7 @@
         <v>45395</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -34882,7 +34882,7 @@
         <v>45589</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -34955,7 +34955,7 @@
         <v>45546</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -35028,7 +35028,7 @@
         <v>44701</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -35101,7 +35101,7 @@
         <v>45145</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -35174,7 +35174,7 @@
         <v>45517</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -35247,7 +35247,7 @@
         <v>45230</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -35320,7 +35320,7 @@
         <v>45677</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -35393,7 +35393,7 @@
         <v>45672</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -35466,7 +35466,7 @@
         <v>45672</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -35539,7 +35539,7 @@
         <v>44483</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -35612,7 +35612,7 @@
         <v>44476</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -35685,7 +35685,7 @@
         <v>44964</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -35758,7 +35758,7 @@
         <v>45735</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -35831,7 +35831,7 @@
         <v>44739</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -35904,7 +35904,7 @@
         <v>45170</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -35977,7 +35977,7 @@
         <v>45309</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -36050,7 +36050,7 @@
         <v>44508</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -36123,7 +36123,7 @@
         <v>45623</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -36196,7 +36196,7 @@
         <v>45252</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -36269,7 +36269,7 @@
         <v>45589</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -36342,7 +36342,7 @@
         <v>45190</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -36415,7 +36415,7 @@
         <v>44817</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -36488,7 +36488,7 @@
         <v>45462</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -36561,7 +36561,7 @@
         <v>46188</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -36634,7 +36634,7 @@
         <v>45574</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -36707,7 +36707,7 @@
         <v>45545</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -36780,7 +36780,7 @@
         <v>45199</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -36853,7 +36853,7 @@
         <v>45190</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -36931,7 +36931,7 @@
         <v>44889</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -37004,7 +37004,7 @@
         <v>45623</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -37077,7 +37077,7 @@
         <v>45170</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -37150,7 +37150,7 @@
         <v>45876</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -37223,7 +37223,7 @@
         <v>45880</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -37296,7 +37296,7 @@
         <v>45880</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -37369,7 +37369,7 @@
         <v>46196</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -37442,7 +37442,7 @@
         <v>45604</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -37515,7 +37515,7 @@
         <v>45877</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -37588,7 +37588,7 @@
         <v>45880</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -37661,7 +37661,7 @@
         <v>45091</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -37734,7 +37734,7 @@
         <v>45880</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -37807,7 +37807,7 @@
         <v>45597</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -37880,7 +37880,7 @@
         <v>46199</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -37953,7 +37953,7 @@
         <v>44641</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -38026,7 +38026,7 @@
         <v>45432</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -38099,7 +38099,7 @@
         <v>45159</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -38172,7 +38172,7 @@
         <v>45456</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -38245,7 +38245,7 @@
         <v>45366</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -38323,7 +38323,7 @@
         <v>44697</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -38396,7 +38396,7 @@
         <v>45194</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -38469,7 +38469,7 @@
         <v>46209</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -38542,7 +38542,7 @@
         <v>46161</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -38615,7 +38615,7 @@
         <v>46206</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -38688,7 +38688,7 @@
         <v>45203</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -38761,7 +38761,7 @@
         <v>45677</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -38834,7 +38834,7 @@
         <v>45132</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -38907,7 +38907,7 @@
         <v>45173</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -38980,7 +38980,7 @@
         <v>45153</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -39053,7 +39053,7 @@
         <v>45084</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -39126,7 +39126,7 @@
         <v>45254</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -39199,7 +39199,7 @@
         <v>45211</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -39272,7 +39272,7 @@
         <v>45568</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -39345,7 +39345,7 @@
         <v>45441</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -39423,7 +39423,7 @@
         <v>45456</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -39496,7 +39496,7 @@
         <v>45225</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -39569,7 +39569,7 @@
         <v>45181</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -39642,7 +39642,7 @@
         <v>46261</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -39715,7 +39715,7 @@
         <v>44823</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -39788,7 +39788,7 @@
         <v>45238</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -39861,7 +39861,7 @@
         <v>46261</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -39934,7 +39934,7 @@
         <v>45287</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -40007,7 +40007,7 @@
         <v>44701</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -40085,7 +40085,7 @@
         <v>44735</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -40158,7 +40158,7 @@
         <v>44651</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -40231,7 +40231,7 @@
         <v>45169</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -40304,7 +40304,7 @@
         <v>45316</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -40382,7 +40382,7 @@
         <v>45167</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -40455,7 +40455,7 @@
         <v>45254</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -40528,7 +40528,7 @@
         <v>45254</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -40601,7 +40601,7 @@
         <v>45245</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -40674,7 +40674,7 @@
         <v>46263</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -40747,7 +40747,7 @@
         <v>46224</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -40825,7 +40825,7 @@
         <v>44778</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -40898,7 +40898,7 @@
         <v>46268</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -40971,7 +40971,7 @@
         <v>44847</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -41044,7 +41044,7 @@
         <v>46268</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -41117,7 +41117,7 @@
         <v>46268</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -41190,7 +41190,7 @@
         <v>44694</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -41263,7 +41263,7 @@
         <v>46272</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -41336,7 +41336,7 @@
         <v>45245</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -41409,7 +41409,7 @@
         <v>45092</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -41482,7 +41482,7 @@
         <v>45051</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -41555,7 +41555,7 @@
         <v>45098</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -41633,7 +41633,7 @@
         <v>45351</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -41706,7 +41706,7 @@
         <v>44797</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -41779,7 +41779,7 @@
         <v>45267</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -41852,7 +41852,7 @@
         <v>46273</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -41925,7 +41925,7 @@
         <v>44974</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -41998,7 +41998,7 @@
         <v>45840</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -42076,7 +42076,7 @@
         <v>46273</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -42149,7 +42149,7 @@
         <v>46272</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -42222,7 +42222,7 @@
         <v>44559</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -42295,7 +42295,7 @@
         <v>44893</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -42368,7 +42368,7 @@
         <v>46279</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -42441,7 +42441,7 @@
         <v>46279</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -42514,7 +42514,7 @@
         <v>46279</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -42587,7 +42587,7 @@
         <v>45455</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -42660,7 +42660,7 @@
         <v>46036</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -42733,7 +42733,7 @@
         <v>45104</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -42806,7 +42806,7 @@
         <v>45334</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -42879,7 +42879,7 @@
         <v>45352</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -42952,7 +42952,7 @@
         <v>45715</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -43025,7 +43025,7 @@
         <v>45316</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -43098,7 +43098,7 @@
         <v>46282</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -43171,7 +43171,7 @@
         <v>44796</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -43244,7 +43244,7 @@
         <v>44901</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -43317,7 +43317,7 @@
         <v>45589</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -43390,7 +43390,7 @@
         <v>46281</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -43463,7 +43463,7 @@
         <v>45939</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -43541,7 +43541,7 @@
         <v>44899</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -43614,7 +43614,7 @@
         <v>46241</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -43687,7 +43687,7 @@
         <v>46286</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -43760,7 +43760,7 @@
         <v>44995</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -43833,7 +43833,7 @@
         <v>45548</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -43906,7 +43906,7 @@
         <v>44958</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -43979,7 +43979,7 @@
         <v>46273</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -44052,7 +44052,7 @@
         <v>46286</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -44125,7 +44125,7 @@
         <v>44575</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -44198,7 +44198,7 @@
         <v>46283</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -44271,7 +44271,7 @@
         <v>45572</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -44344,7 +44344,7 @@
         <v>46283</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -44417,7 +44417,7 @@
         <v>46245</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -44490,7 +44490,7 @@
         <v>44951</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -44563,7 +44563,7 @@
         <v>45265</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -44636,7 +44636,7 @@
         <v>45432</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -44709,7 +44709,7 @@
         <v>46283</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -44782,7 +44782,7 @@
         <v>46244</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -44855,7 +44855,7 @@
         <v>46030</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -44928,7 +44928,7 @@
         <v>46281</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -45001,7 +45001,7 @@
         <v>46281</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -45074,7 +45074,7 @@
         <v>45132</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -45147,7 +45147,7 @@
         <v>45246</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -45220,7 +45220,7 @@
         <v>45246</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -45293,7 +45293,7 @@
         <v>45426</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -45366,7 +45366,7 @@
         <v>46248</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -45439,7 +45439,7 @@
         <v>45371</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -45512,7 +45512,7 @@
         <v>46248</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -45585,7 +45585,7 @@
         <v>46247</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -45658,7 +45658,7 @@
         <v>45411</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -45731,7 +45731,7 @@
         <v>46224</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -45804,7 +45804,7 @@
         <v>45400</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -45877,7 +45877,7 @@
         <v>45441</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -45955,7 +45955,7 @@
         <v>45624</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -46028,7 +46028,7 @@
         <v>45580</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -46101,7 +46101,7 @@
         <v>45568</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -46174,7 +46174,7 @@
         <v>44714</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -46252,7 +46252,7 @@
         <v>44813</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -46325,7 +46325,7 @@
         <v>45163</v>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -46398,7 +46398,7 @@
         <v>44851</v>
       </c>
       <c r="E610" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -46471,7 +46471,7 @@
         <v>44851</v>
       </c>
       <c r="E611" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
@@ -46544,7 +46544,7 @@
         <v>45035</v>
       </c>
       <c r="E612" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
@@ -46617,7 +46617,7 @@
         <v>44726</v>
       </c>
       <c r="E613" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
@@ -46690,7 +46690,7 @@
         <v>45019</v>
       </c>
       <c r="E614" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F614" t="inlineStr">
         <is>
@@ -46763,7 +46763,7 @@
         <v>45350</v>
       </c>
       <c r="E615" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F615" t="inlineStr">
         <is>
@@ -46836,7 +46836,7 @@
         <v>45434</v>
       </c>
       <c r="E616" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F616" t="inlineStr">
         <is>
@@ -46909,7 +46909,7 @@
         <v>44469</v>
       </c>
       <c r="E617" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F617" t="inlineStr">
         <is>
@@ -46982,7 +46982,7 @@
         <v>44900</v>
       </c>
       <c r="E618" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F618" t="inlineStr">
         <is>
@@ -47055,7 +47055,7 @@
         <v>45357</v>
       </c>
       <c r="E619" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F619" t="inlineStr">
         <is>
@@ -47128,7 +47128,7 @@
         <v>45429</v>
       </c>
       <c r="E620" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F620" t="inlineStr">
         <is>
@@ -47201,7 +47201,7 @@
         <v>45002</v>
       </c>
       <c r="E621" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F621" t="inlineStr">
         <is>
@@ -47274,7 +47274,7 @@
         <v>45684</v>
       </c>
       <c r="E622" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F622" t="inlineStr">
         <is>
@@ -47347,7 +47347,7 @@
         <v>45342</v>
       </c>
       <c r="E623" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F623" t="inlineStr">
         <is>
@@ -47425,7 +47425,7 @@
         <v>45477</v>
       </c>
       <c r="E624" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F624" t="inlineStr">
         <is>
@@ -47498,7 +47498,7 @@
         <v>45371</v>
       </c>
       <c r="E625" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F625" t="inlineStr">
         <is>
@@ -47571,7 +47571,7 @@
         <v>44953</v>
       </c>
       <c r="E626" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F626" t="inlineStr">
         <is>
@@ -47644,7 +47644,7 @@
         <v>45624</v>
       </c>
       <c r="E627" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F627" t="inlineStr">
         <is>
@@ -47717,7 +47717,7 @@
         <v>45169</v>
       </c>
       <c r="E628" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F628" t="inlineStr">
         <is>
@@ -47790,7 +47790,7 @@
         <v>45229</v>
       </c>
       <c r="E629" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F629" t="inlineStr">
         <is>
@@ -47863,7 +47863,7 @@
         <v>45770</v>
       </c>
       <c r="E630" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F630" t="inlineStr">
         <is>
@@ -47936,7 +47936,7 @@
         <v>45674</v>
       </c>
       <c r="E631" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F631" t="inlineStr">
         <is>
@@ -48009,7 +48009,7 @@
         <v>45035</v>
       </c>
       <c r="E632" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F632" t="inlineStr">
         <is>
@@ -48082,7 +48082,7 @@
         <v>44635</v>
       </c>
       <c r="E633" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F633" t="inlineStr">
         <is>
@@ -48160,7 +48160,7 @@
         <v>45700</v>
       </c>
       <c r="E634" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F634" t="inlineStr">
         <is>
@@ -48233,7 +48233,7 @@
         <v>45084</v>
       </c>
       <c r="E635" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F635" t="inlineStr">
         <is>
@@ -48306,7 +48306,7 @@
         <v>45229</v>
       </c>
       <c r="E636" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F636" t="inlineStr">
         <is>
@@ -48379,7 +48379,7 @@
         <v>45252</v>
       </c>
       <c r="E637" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F637" t="inlineStr">
         <is>
@@ -48452,7 +48452,7 @@
         <v>44750</v>
       </c>
       <c r="E638" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F638" t="inlineStr">
         <is>
@@ -48525,7 +48525,7 @@
         <v>45368</v>
       </c>
       <c r="E639" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F639" t="inlineStr">
         <is>
@@ -48603,7 +48603,7 @@
         <v>44893</v>
       </c>
       <c r="E640" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F640" t="inlineStr">
         <is>
@@ -48676,7 +48676,7 @@
         <v>45541</v>
       </c>
       <c r="E641" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F641" t="inlineStr">
         <is>
@@ -48749,7 +48749,7 @@
         <v>45527</v>
       </c>
       <c r="E642" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F642" t="inlineStr">
         <is>
@@ -48822,7 +48822,7 @@
         <v>45062</v>
       </c>
       <c r="E643" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F643" t="inlineStr">
         <is>
@@ -48895,7 +48895,7 @@
         <v>45371</v>
       </c>
       <c r="E644" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F644" t="inlineStr">
         <is>
@@ -48968,7 +48968,7 @@
         <v>44868</v>
       </c>
       <c r="E645" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F645" t="inlineStr">
         <is>
@@ -49041,7 +49041,7 @@
         <v>45737</v>
       </c>
       <c r="E646" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F646" t="inlineStr">
         <is>
@@ -49114,7 +49114,7 @@
         <v>45258</v>
       </c>
       <c r="E647" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F647" t="inlineStr">
         <is>
@@ -49187,7 +49187,7 @@
         <v>45485</v>
       </c>
       <c r="E648" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F648" t="inlineStr">
         <is>
@@ -49260,7 +49260,7 @@
         <v>45462</v>
       </c>
       <c r="E649" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F649" t="inlineStr">
         <is>
@@ -49333,7 +49333,7 @@
         <v>45560</v>
       </c>
       <c r="E650" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F650" t="inlineStr">
         <is>
@@ -49406,7 +49406,7 @@
         <v>45089</v>
       </c>
       <c r="E651" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F651" t="inlineStr">
         <is>
@@ -49479,7 +49479,7 @@
         <v>45300</v>
       </c>
       <c r="E652" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F652" t="inlineStr">
         <is>
@@ -49552,7 +49552,7 @@
         <v>45352</v>
       </c>
       <c r="E653" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F653" t="inlineStr">
         <is>
@@ -49625,7 +49625,7 @@
         <v>45377</v>
       </c>
       <c r="E654" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F654" t="inlineStr">
         <is>
@@ -49703,7 +49703,7 @@
         <v>45176</v>
       </c>
       <c r="E655" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F655" t="inlineStr">
         <is>
@@ -49781,7 +49781,7 @@
         <v>45638</v>
       </c>
       <c r="E656" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F656" t="inlineStr">
         <is>
@@ -49854,7 +49854,7 @@
         <v>45588</v>
       </c>
       <c r="E657" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F657" t="inlineStr">
         <is>
@@ -49932,7 +49932,7 @@
         <v>45616</v>
       </c>
       <c r="E658" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F658" t="inlineStr">
         <is>
@@ -50005,7 +50005,7 @@
         <v>45391</v>
       </c>
       <c r="E659" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F659" t="inlineStr">
         <is>
@@ -50078,7 +50078,7 @@
         <v>45510</v>
       </c>
       <c r="E660" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F660" t="inlineStr">
         <is>
@@ -50151,7 +50151,7 @@
         <v>45783</v>
       </c>
       <c r="E661" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F661" t="inlineStr">
         <is>
@@ -50224,7 +50224,7 @@
         <v>45616</v>
       </c>
       <c r="E662" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F662" t="inlineStr">
         <is>
@@ -50297,7 +50297,7 @@
         <v>45786</v>
       </c>
       <c r="E663" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F663" t="inlineStr">
         <is>
@@ -50375,7 +50375,7 @@
         <v>45559</v>
       </c>
       <c r="E664" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F664" t="inlineStr">
         <is>
@@ -50448,7 +50448,7 @@
         <v>45680</v>
       </c>
       <c r="E665" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F665" t="inlineStr">
         <is>
@@ -50521,7 +50521,7 @@
         <v>45225</v>
       </c>
       <c r="E666" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F666" t="inlineStr">
         <is>
@@ -50594,7 +50594,7 @@
         <v>45589</v>
       </c>
       <c r="E667" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F667" t="inlineStr">
         <is>
@@ -50672,7 +50672,7 @@
         <v>45618</v>
       </c>
       <c r="E668" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F668" t="inlineStr">
         <is>
@@ -50745,7 +50745,7 @@
         <v>45726</v>
       </c>
       <c r="E669" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F669" t="inlineStr">
         <is>
@@ -50818,7 +50818,7 @@
         <v>45741</v>
       </c>
       <c r="E670" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F670" t="inlineStr">
         <is>
@@ -50891,7 +50891,7 @@
         <v>45483</v>
       </c>
       <c r="E671" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F671" t="inlineStr">
         <is>
@@ -50964,7 +50964,7 @@
         <v>45609</v>
       </c>
       <c r="E672" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F672" t="inlineStr">
         <is>
@@ -51037,7 +51037,7 @@
         <v>45483</v>
       </c>
       <c r="E673" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F673" t="inlineStr">
         <is>
@@ -51110,7 +51110,7 @@
         <v>45743</v>
       </c>
       <c r="E674" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F674" t="inlineStr">
         <is>
@@ -51188,7 +51188,7 @@
         <v>45590</v>
       </c>
       <c r="E675" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F675" t="inlineStr">
         <is>
@@ -51261,7 +51261,7 @@
         <v>45743</v>
       </c>
       <c r="E676" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F676" t="inlineStr">
         <is>
@@ -51339,7 +51339,7 @@
         <v>44631</v>
       </c>
       <c r="E677" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F677" t="inlineStr">
         <is>
@@ -51412,7 +51412,7 @@
         <v>44613</v>
       </c>
       <c r="E678" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F678" t="inlineStr">
         <is>
@@ -51485,7 +51485,7 @@
         <v>44608</v>
       </c>
       <c r="E679" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F679" t="inlineStr">
         <is>
@@ -51558,7 +51558,7 @@
         <v>44631</v>
       </c>
       <c r="E680" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F680" t="inlineStr">
         <is>
@@ -51631,7 +51631,7 @@
         <v>44631</v>
       </c>
       <c r="E681" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F681" t="inlineStr">
         <is>
@@ -51704,7 +51704,7 @@
         <v>45614</v>
       </c>
       <c r="E682" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F682" t="inlineStr">
         <is>
@@ -51782,7 +51782,7 @@
         <v>44743</v>
       </c>
       <c r="E683" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F683" t="inlineStr">
         <is>
@@ -51855,7 +51855,7 @@
         <v>45375</v>
       </c>
       <c r="E684" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F684" t="inlineStr">
         <is>
@@ -51928,7 +51928,7 @@
         <v>44488</v>
       </c>
       <c r="E685" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F685" t="inlineStr">
         <is>
@@ -52001,7 +52001,7 @@
         <v>45604</v>
       </c>
       <c r="E686" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F686" t="inlineStr">
         <is>
@@ -52074,7 +52074,7 @@
         <v>45356</v>
       </c>
       <c r="E687" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F687" t="inlineStr">
         <is>
@@ -52147,7 +52147,7 @@
         <v>45349</v>
       </c>
       <c r="E688" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F688" t="inlineStr">
         <is>
@@ -52220,7 +52220,7 @@
         <v>45744</v>
       </c>
       <c r="E689" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F689" t="inlineStr">
         <is>
@@ -52293,7 +52293,7 @@
         <v>45714</v>
       </c>
       <c r="E690" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F690" t="inlineStr">
         <is>
@@ -52366,7 +52366,7 @@
         <v>45715</v>
       </c>
       <c r="E691" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F691" t="inlineStr">
         <is>
@@ -52439,7 +52439,7 @@
         <v>45709</v>
       </c>
       <c r="E692" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F692" t="inlineStr">
         <is>
@@ -52512,7 +52512,7 @@
         <v>45714</v>
       </c>
       <c r="E693" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F693" t="inlineStr">
         <is>
@@ -52585,7 +52585,7 @@
         <v>45813</v>
       </c>
       <c r="E694" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F694" t="inlineStr">
         <is>
@@ -52658,7 +52658,7 @@
         <v>45813</v>
       </c>
       <c r="E695" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F695" t="inlineStr">
         <is>
@@ -52731,7 +52731,7 @@
         <v>45813</v>
       </c>
       <c r="E696" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F696" t="inlineStr">
         <is>
@@ -52804,7 +52804,7 @@
         <v>45820</v>
       </c>
       <c r="E697" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F697" t="inlineStr">
         <is>
@@ -52877,7 +52877,7 @@
         <v>45827</v>
       </c>
       <c r="E698" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F698" t="inlineStr">
         <is>
@@ -52950,7 +52950,7 @@
         <v>45845</v>
       </c>
       <c r="E699" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F699" t="inlineStr">
         <is>
@@ -53023,7 +53023,7 @@
         <v>45883</v>
       </c>
       <c r="E700" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F700" t="inlineStr">
         <is>
@@ -53096,7 +53096,7 @@
         <v>45915</v>
       </c>
       <c r="E701" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F701" t="inlineStr">
         <is>
@@ -53169,7 +53169,7 @@
         <v>46041</v>
       </c>
       <c r="E702" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F702" t="inlineStr">
         <is>
@@ -53242,7 +53242,7 @@
         <v>46133</v>
       </c>
       <c r="E703" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F703" t="inlineStr">
         <is>
@@ -53315,7 +53315,7 @@
         <v>46147</v>
       </c>
       <c r="E704" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F704" t="inlineStr">
         <is>
@@ -53388,7 +53388,7 @@
         <v>46253</v>
       </c>
       <c r="E705" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F705" t="inlineStr">
         <is>
@@ -53461,7 +53461,7 @@
         <v>46211</v>
       </c>
       <c r="E706" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F706" t="inlineStr">
         <is>
@@ -53534,7 +53534,7 @@
         <v>46290</v>
       </c>
       <c r="E707" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F707" t="inlineStr">
         <is>

--- a/Översikt HYLTE.xlsx
+++ b/Översikt HYLTE.xlsx
@@ -601,7 +601,7 @@
         <v>46090</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -718,7 +718,7 @@
         <v>45265</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -834,7 +834,7 @@
         <v>46066</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -945,7 +945,7 @@
         <v>44873</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1054,7 +1054,7 @@
         <v>45348</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1166,7 +1166,7 @@
         <v>45719</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1274,7 +1274,7 @@
         <v>46268</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1381,7 +1381,7 @@
         <v>45245</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1492,7 +1492,7 @@
         <v>45230</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1599,7 +1599,7 @@
         <v>45737</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1706,7 +1706,7 @@
         <v>46141</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1813,7 +1813,7 @@
         <v>46161</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1920,7 +1920,7 @@
         <v>44839</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2030,7 +2030,7 @@
         <v>46048</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2136,7 +2136,7 @@
         <v>45841</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2246,7 +2246,7 @@
         <v>45099</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2356,7 +2356,7 @@
         <v>45904</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2466,7 +2466,7 @@
         <v>46130</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2572,7 +2572,7 @@
         <v>44648</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2677,7 +2677,7 @@
         <v>44651</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2782,7 +2782,7 @@
         <v>44876</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2887,7 +2887,7 @@
         <v>45617</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2992,7 +2992,7 @@
         <v>45299</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3101,7 +3101,7 @@
         <v>45245</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3206,7 +3206,7 @@
         <v>45343</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3311,7 +3311,7 @@
         <v>45476</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3421,7 +3421,7 @@
         <v>45163</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3526,7 +3526,7 @@
         <v>45245</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3631,7 +3631,7 @@
         <v>45593</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3736,7 +3736,7 @@
         <v>45153</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3850,7 +3850,7 @@
         <v>45186</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3955,7 +3955,7 @@
         <v>45085</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4064,7 +4064,7 @@
         <v>45253</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4169,7 +4169,7 @@
         <v>45754</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4274,7 +4274,7 @@
         <v>46253</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4384,7 +4384,7 @@
         <v>44810</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4457,7 +4457,7 @@
         <v>44481</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4530,7 +4530,7 @@
         <v>44600</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4603,7 +4603,7 @@
         <v>44557</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4676,7 +4676,7 @@
         <v>44529</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4749,7 +4749,7 @@
         <v>44483</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4822,7 +4822,7 @@
         <v>44705</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4895,7 +4895,7 @@
         <v>44778</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4968,7 +4968,7 @@
         <v>44488</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5041,7 +5041,7 @@
         <v>44475</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5114,7 +5114,7 @@
         <v>44624</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5187,7 +5187,7 @@
         <v>44812</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5260,7 +5260,7 @@
         <v>44638</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5333,7 +5333,7 @@
         <v>44498</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5406,7 +5406,7 @@
         <v>44845</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5479,7 +5479,7 @@
         <v>44559</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5552,7 +5552,7 @@
         <v>44578</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5625,7 +5625,7 @@
         <v>44659</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5703,7 +5703,7 @@
         <v>44756</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5776,7 +5776,7 @@
         <v>44501</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5849,7 +5849,7 @@
         <v>44651</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5922,7 +5922,7 @@
         <v>44711</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5995,7 +5995,7 @@
         <v>44487</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6073,7 +6073,7 @@
         <v>44735</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6146,7 +6146,7 @@
         <v>44477</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6219,7 +6219,7 @@
         <v>44489</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6292,7 +6292,7 @@
         <v>44834</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6365,7 +6365,7 @@
         <v>44796</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6438,7 +6438,7 @@
         <v>44502</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6511,7 +6511,7 @@
         <v>44631</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6584,7 +6584,7 @@
         <v>44876</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6657,7 +6657,7 @@
         <v>44659</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6730,7 +6730,7 @@
         <v>44644</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6803,7 +6803,7 @@
         <v>44515</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6881,7 +6881,7 @@
         <v>44778</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6954,7 +6954,7 @@
         <v>44482</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7027,7 +7027,7 @@
         <v>44482</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7100,7 +7100,7 @@
         <v>44867</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7173,7 +7173,7 @@
         <v>44505</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7246,7 +7246,7 @@
         <v>44634</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7319,7 +7319,7 @@
         <v>44728</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7392,7 +7392,7 @@
         <v>44714</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7465,7 +7465,7 @@
         <v>44795</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7538,7 +7538,7 @@
         <v>44818</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7611,7 +7611,7 @@
         <v>44801</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7684,7 +7684,7 @@
         <v>44596</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7762,7 +7762,7 @@
         <v>44644</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7835,7 +7835,7 @@
         <v>44523</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7908,7 +7908,7 @@
         <v>44500</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7981,7 +7981,7 @@
         <v>44727</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8054,7 +8054,7 @@
         <v>44705</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8127,7 +8127,7 @@
         <v>44659</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8205,7 +8205,7 @@
         <v>44659</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8283,7 +8283,7 @@
         <v>44757</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8356,7 +8356,7 @@
         <v>44495</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8429,7 +8429,7 @@
         <v>45460</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8502,7 +8502,7 @@
         <v>44494</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8575,7 +8575,7 @@
         <v>45002</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8648,7 +8648,7 @@
         <v>45568</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8721,7 +8721,7 @@
         <v>44487</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8799,7 +8799,7 @@
         <v>44900</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8877,7 +8877,7 @@
         <v>44851</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8950,7 +8950,7 @@
         <v>44851</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -9023,7 +9023,7 @@
         <v>45062</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9096,7 +9096,7 @@
         <v>45132</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9169,7 +9169,7 @@
         <v>45715</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9242,7 +9242,7 @@
         <v>44714</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9320,7 +9320,7 @@
         <v>44476</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9393,7 +9393,7 @@
         <v>44958</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9466,7 +9466,7 @@
         <v>44899</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9539,7 +9539,7 @@
         <v>45107</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9612,7 +9612,7 @@
         <v>44559</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9685,7 +9685,7 @@
         <v>45211</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9758,7 +9758,7 @@
         <v>45258</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9831,7 +9831,7 @@
         <v>45229</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9904,7 +9904,7 @@
         <v>45548</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9977,7 +9977,7 @@
         <v>45589</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -10050,7 +10050,7 @@
         <v>45225</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10123,7 +10123,7 @@
         <v>45618</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10196,7 +10196,7 @@
         <v>45254</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10269,7 +10269,7 @@
         <v>45254</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10342,7 +10342,7 @@
         <v>45726</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10415,7 +10415,7 @@
         <v>45483</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10488,7 +10488,7 @@
         <v>45254</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10561,7 +10561,7 @@
         <v>45254</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10634,7 +10634,7 @@
         <v>45098</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10712,7 +10712,7 @@
         <v>45589</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -10790,7 +10790,7 @@
         <v>45391</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10863,7 +10863,7 @@
         <v>45786</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10941,7 +10941,7 @@
         <v>44868</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -11014,7 +11014,7 @@
         <v>45926</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -11087,7 +11087,7 @@
         <v>44910</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11160,7 +11160,7 @@
         <v>45840</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11233,7 +11233,7 @@
         <v>44823</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11306,7 +11306,7 @@
         <v>45351</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11379,7 +11379,7 @@
         <v>45590</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11452,7 +11452,7 @@
         <v>45539</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11525,7 +11525,7 @@
         <v>45538</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11598,7 +11598,7 @@
         <v>45673</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11671,7 +11671,7 @@
         <v>45104</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -11744,7 +11744,7 @@
         <v>45684</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -11817,7 +11817,7 @@
         <v>45609</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -11890,7 +11890,7 @@
         <v>45743</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -11968,7 +11968,7 @@
         <v>45600</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -12041,7 +12041,7 @@
         <v>45834</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -12114,7 +12114,7 @@
         <v>44539</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12187,7 +12187,7 @@
         <v>45436</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12260,7 +12260,7 @@
         <v>46020</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12333,7 +12333,7 @@
         <v>45352</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12406,7 +12406,7 @@
         <v>45352</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -12479,7 +12479,7 @@
         <v>45748</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -12552,7 +12552,7 @@
         <v>45890</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -12625,7 +12625,7 @@
         <v>45891</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -12703,7 +12703,7 @@
         <v>45891</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -12781,7 +12781,7 @@
         <v>44719</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -12854,7 +12854,7 @@
         <v>45743</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -12932,7 +12932,7 @@
         <v>45741</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -13005,7 +13005,7 @@
         <v>44896</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -13078,7 +13078,7 @@
         <v>45897</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -13151,7 +13151,7 @@
         <v>45839</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13224,7 +13224,7 @@
         <v>45898</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13297,7 +13297,7 @@
         <v>45897</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13370,7 +13370,7 @@
         <v>45638</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -13443,7 +13443,7 @@
         <v>45434</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -13516,7 +13516,7 @@
         <v>45793</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -13589,7 +13589,7 @@
         <v>45905</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -13662,7 +13662,7 @@
         <v>46042</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -13735,7 +13735,7 @@
         <v>45838</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -13808,7 +13808,7 @@
         <v>46042</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -13881,7 +13881,7 @@
         <v>45559</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -13954,7 +13954,7 @@
         <v>45681</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -14027,7 +14027,7 @@
         <v>45910</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -14100,7 +14100,7 @@
         <v>45743</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -14178,7 +14178,7 @@
         <v>46044</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14251,7 +14251,7 @@
         <v>44851</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14324,7 +14324,7 @@
         <v>45910</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -14397,7 +14397,7 @@
         <v>46044</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -14470,7 +14470,7 @@
         <v>46044</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -14543,7 +14543,7 @@
         <v>46044</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -14616,7 +14616,7 @@
         <v>45163</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -14689,7 +14689,7 @@
         <v>46048</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -14762,7 +14762,7 @@
         <v>46049</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -14835,7 +14835,7 @@
         <v>46048</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -14908,7 +14908,7 @@
         <v>46048</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -14981,7 +14981,7 @@
         <v>46048</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -15054,7 +15054,7 @@
         <v>46048</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -15127,7 +15127,7 @@
         <v>45089</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -15200,7 +15200,7 @@
         <v>46048</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -15273,7 +15273,7 @@
         <v>46048</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -15346,7 +15346,7 @@
         <v>46048</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -15419,7 +15419,7 @@
         <v>46048</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -15492,7 +15492,7 @@
         <v>46048</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -15565,7 +15565,7 @@
         <v>46048</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -15638,7 +15638,7 @@
         <v>46048</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -15711,7 +15711,7 @@
         <v>45252</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -15784,7 +15784,7 @@
         <v>45145</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -15857,7 +15857,7 @@
         <v>45918</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -15930,7 +15930,7 @@
         <v>45806</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -16003,7 +16003,7 @@
         <v>45922</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -16076,7 +16076,7 @@
         <v>46052</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -16149,7 +16149,7 @@
         <v>45922</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -16222,7 +16222,7 @@
         <v>45609</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -16295,7 +16295,7 @@
         <v>46055</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -16368,7 +16368,7 @@
         <v>45922</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -16441,7 +16441,7 @@
         <v>46052</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -16514,7 +16514,7 @@
         <v>45924</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -16587,7 +16587,7 @@
         <v>45926</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -16660,7 +16660,7 @@
         <v>46057</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -16733,7 +16733,7 @@
         <v>45926</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -16806,7 +16806,7 @@
         <v>45926</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -16879,7 +16879,7 @@
         <v>45929</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -16952,7 +16952,7 @@
         <v>45194</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -17025,7 +17025,7 @@
         <v>45931</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -17098,7 +17098,7 @@
         <v>44482</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -17171,7 +17171,7 @@
         <v>46062</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -17244,7 +17244,7 @@
         <v>44701</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -17322,7 +17322,7 @@
         <v>45182</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -17395,7 +17395,7 @@
         <v>45930</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -17468,7 +17468,7 @@
         <v>46062</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -17541,7 +17541,7 @@
         <v>45931</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -17614,7 +17614,7 @@
         <v>46064</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -17687,7 +17687,7 @@
         <v>45933</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -17760,7 +17760,7 @@
         <v>45933</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -17833,7 +17833,7 @@
         <v>46065</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -17906,7 +17906,7 @@
         <v>45933</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -17979,7 +17979,7 @@
         <v>45936</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -18052,7 +18052,7 @@
         <v>44901</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -18125,7 +18125,7 @@
         <v>45181</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -18198,7 +18198,7 @@
         <v>45936</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -18271,7 +18271,7 @@
         <v>45936</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -18344,7 +18344,7 @@
         <v>44495</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -18417,7 +18417,7 @@
         <v>46070</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -18490,7 +18490,7 @@
         <v>45938</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -18563,7 +18563,7 @@
         <v>45694</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -18636,7 +18636,7 @@
         <v>46070</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -18709,7 +18709,7 @@
         <v>45937</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -18782,7 +18782,7 @@
         <v>45441</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -18860,7 +18860,7 @@
         <v>45441</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -18933,7 +18933,7 @@
         <v>45944</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -19006,7 +19006,7 @@
         <v>45310</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -19079,7 +19079,7 @@
         <v>45229</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -19152,7 +19152,7 @@
         <v>45812</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -19225,7 +19225,7 @@
         <v>46084</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -19298,7 +19298,7 @@
         <v>46084</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -19371,7 +19371,7 @@
         <v>45957</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -19444,7 +19444,7 @@
         <v>44999</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -19517,7 +19517,7 @@
         <v>46087</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -19590,7 +19590,7 @@
         <v>45527</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -19663,7 +19663,7 @@
         <v>45961</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -19736,7 +19736,7 @@
         <v>45922</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -19809,7 +19809,7 @@
         <v>45961</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -19882,7 +19882,7 @@
         <v>45751</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -19960,7 +19960,7 @@
         <v>44847</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -20033,7 +20033,7 @@
         <v>45706</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -20106,7 +20106,7 @@
         <v>46093</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -20179,7 +20179,7 @@
         <v>46093</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -20252,7 +20252,7 @@
         <v>46093</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -20325,7 +20325,7 @@
         <v>44778</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -20398,7 +20398,7 @@
         <v>45972</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -20471,7 +20471,7 @@
         <v>45972</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -20544,7 +20544,7 @@
         <v>45173</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -20617,7 +20617,7 @@
         <v>45972</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -20690,7 +20690,7 @@
         <v>45132</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -20763,7 +20763,7 @@
         <v>45478</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -20836,7 +20836,7 @@
         <v>46057</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -20909,7 +20909,7 @@
         <v>45979</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -20982,7 +20982,7 @@
         <v>45019</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -21055,7 +21055,7 @@
         <v>45694</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -21128,7 +21128,7 @@
         <v>46057</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -21201,7 +21201,7 @@
         <v>45708</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -21274,7 +21274,7 @@
         <v>45597</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -21347,7 +21347,7 @@
         <v>45387</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -21420,7 +21420,7 @@
         <v>45981</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -21493,7 +21493,7 @@
         <v>45981</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -21566,7 +21566,7 @@
         <v>45730</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -21639,7 +21639,7 @@
         <v>45254</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -21712,7 +21712,7 @@
         <v>46111</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -21785,7 +21785,7 @@
         <v>45331</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -21858,7 +21858,7 @@
         <v>46111</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -21931,7 +21931,7 @@
         <v>45287</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -22004,7 +22004,7 @@
         <v>46111</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -22077,7 +22077,7 @@
         <v>45820</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -22150,7 +22150,7 @@
         <v>44900</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -22223,7 +22223,7 @@
         <v>45987</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -22296,7 +22296,7 @@
         <v>45366</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -22369,7 +22369,7 @@
         <v>45989</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -22442,7 +22442,7 @@
         <v>46120</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -22515,7 +22515,7 @@
         <v>46120</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -22588,7 +22588,7 @@
         <v>45825</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -22661,7 +22661,7 @@
         <v>46122</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -22734,7 +22734,7 @@
         <v>46121</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -22807,7 +22807,7 @@
         <v>46121</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -22880,7 +22880,7 @@
         <v>46121</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -22953,7 +22953,7 @@
         <v>46122</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -23026,7 +23026,7 @@
         <v>45245</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -23099,7 +23099,7 @@
         <v>46122</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -23172,7 +23172,7 @@
         <v>46121</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -23245,7 +23245,7 @@
         <v>46122</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -23318,7 +23318,7 @@
         <v>46121</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -23391,7 +23391,7 @@
         <v>46121</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -23464,7 +23464,7 @@
         <v>46121</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -23537,7 +23537,7 @@
         <v>46121</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -23610,7 +23610,7 @@
         <v>45548</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -23683,7 +23683,7 @@
         <v>45485</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -23756,7 +23756,7 @@
         <v>45560</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -23829,7 +23829,7 @@
         <v>45995</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -23902,7 +23902,7 @@
         <v>46128</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -23975,7 +23975,7 @@
         <v>45674</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -24048,7 +24048,7 @@
         <v>45831</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -24121,7 +24121,7 @@
         <v>44865</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -24194,7 +24194,7 @@
         <v>45601</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -24267,7 +24267,7 @@
         <v>45454</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -24340,7 +24340,7 @@
         <v>45835</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -24413,7 +24413,7 @@
         <v>44701</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -24491,7 +24491,7 @@
         <v>45300</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -24564,7 +24564,7 @@
         <v>45989</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -24637,7 +24637,7 @@
         <v>45838</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -24710,7 +24710,7 @@
         <v>45839</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -24783,7 +24783,7 @@
         <v>46084</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -24856,7 +24856,7 @@
         <v>45524</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -24929,7 +24929,7 @@
         <v>45456</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -25002,7 +25002,7 @@
         <v>45836</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -25075,7 +25075,7 @@
         <v>45429</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -25148,7 +25148,7 @@
         <v>45405</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -25221,7 +25221,7 @@
         <v>45840</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -25294,7 +25294,7 @@
         <v>44797</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -25367,7 +25367,7 @@
         <v>45840</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -25440,7 +25440,7 @@
         <v>45035</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -25513,7 +25513,7 @@
         <v>45840</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -25586,7 +25586,7 @@
         <v>45800</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -25659,7 +25659,7 @@
         <v>45817</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -25732,7 +25732,7 @@
         <v>45259</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -25805,7 +25805,7 @@
         <v>45782</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -25878,7 +25878,7 @@
         <v>45169</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -25951,7 +25951,7 @@
         <v>45847</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -26024,7 +26024,7 @@
         <v>45847</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -26097,7 +26097,7 @@
         <v>45845</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -26170,7 +26170,7 @@
         <v>45845</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -26243,7 +26243,7 @@
         <v>45104</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -26316,7 +26316,7 @@
         <v>45846</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -26394,7 +26394,7 @@
         <v>44900</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -26467,7 +26467,7 @@
         <v>45846</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -26545,7 +26545,7 @@
         <v>45846</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -26623,7 +26623,7 @@
         <v>46084</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -26696,7 +26696,7 @@
         <v>44974</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -26769,7 +26769,7 @@
         <v>45162</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -26842,7 +26842,7 @@
         <v>45803</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -26915,7 +26915,7 @@
         <v>44694</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -26988,7 +26988,7 @@
         <v>45502</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -27061,7 +27061,7 @@
         <v>44974</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -27134,7 +27134,7 @@
         <v>45091</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -27207,7 +27207,7 @@
         <v>44926</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -27285,7 +27285,7 @@
         <v>45604</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -27358,7 +27358,7 @@
         <v>45097</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -27431,7 +27431,7 @@
         <v>44699</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -27504,7 +27504,7 @@
         <v>45790</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -27577,7 +27577,7 @@
         <v>45477</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -27650,7 +27650,7 @@
         <v>45265</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -27723,7 +27723,7 @@
         <v>45084</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -27796,7 +27796,7 @@
         <v>45531</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -27869,7 +27869,7 @@
         <v>45775</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -27942,7 +27942,7 @@
         <v>45840</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -28020,7 +28020,7 @@
         <v>44953</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -28093,7 +28093,7 @@
         <v>45019</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -28166,7 +28166,7 @@
         <v>45299</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -28239,7 +28239,7 @@
         <v>45848</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -28312,7 +28312,7 @@
         <v>45645</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -28385,7 +28385,7 @@
         <v>45366</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -28463,7 +28463,7 @@
         <v>45505</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -28536,7 +28536,7 @@
         <v>45700</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -28609,7 +28609,7 @@
         <v>45700</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -28682,7 +28682,7 @@
         <v>44903</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -28755,7 +28755,7 @@
         <v>45096</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -28828,7 +28828,7 @@
         <v>45617</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -28901,7 +28901,7 @@
         <v>45167</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -28974,7 +28974,7 @@
         <v>45687</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -29047,7 +29047,7 @@
         <v>45352</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -29120,7 +29120,7 @@
         <v>45190</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -29193,7 +29193,7 @@
         <v>45293</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -29266,7 +29266,7 @@
         <v>45392</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -29339,7 +29339,7 @@
         <v>45145</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -29412,7 +29412,7 @@
         <v>45623</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -29485,7 +29485,7 @@
         <v>44917</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -29558,7 +29558,7 @@
         <v>45190</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -29636,7 +29636,7 @@
         <v>45517</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -29709,7 +29709,7 @@
         <v>45545</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -29782,7 +29782,7 @@
         <v>45204</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -29855,7 +29855,7 @@
         <v>45395</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -29928,7 +29928,7 @@
         <v>45541</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -30001,7 +30001,7 @@
         <v>45677</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -30074,7 +30074,7 @@
         <v>45727</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -30147,7 +30147,7 @@
         <v>45252</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -30220,7 +30220,7 @@
         <v>45257</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -30293,7 +30293,7 @@
         <v>45254</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -30366,7 +30366,7 @@
         <v>45309</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -30439,7 +30439,7 @@
         <v>45245</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -30512,7 +30512,7 @@
         <v>45254</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -30585,7 +30585,7 @@
         <v>45288</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -30663,7 +30663,7 @@
         <v>44896</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -30736,7 +30736,7 @@
         <v>44592</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -30809,7 +30809,7 @@
         <v>45407</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -30882,7 +30882,7 @@
         <v>45589</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -30955,7 +30955,7 @@
         <v>45623</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -31028,7 +31028,7 @@
         <v>45769</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -31101,7 +31101,7 @@
         <v>45672</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -31174,7 +31174,7 @@
         <v>45672</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -31247,7 +31247,7 @@
         <v>45524</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -31320,7 +31320,7 @@
         <v>44508</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -31393,7 +31393,7 @@
         <v>44889</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -31466,7 +31466,7 @@
         <v>45199</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -31539,7 +31539,7 @@
         <v>44671</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -31612,7 +31612,7 @@
         <v>45176</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -31685,7 +31685,7 @@
         <v>45199</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -31758,7 +31758,7 @@
         <v>45372</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -31831,7 +31831,7 @@
         <v>44712</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -31904,7 +31904,7 @@
         <v>45395</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -31977,7 +31977,7 @@
         <v>45203</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -32050,7 +32050,7 @@
         <v>44481</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -32123,7 +32123,7 @@
         <v>44739</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -32196,7 +32196,7 @@
         <v>45230</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -32269,7 +32269,7 @@
         <v>45672</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -32342,7 +32342,7 @@
         <v>44701</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -32415,7 +32415,7 @@
         <v>45677</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -32488,7 +32488,7 @@
         <v>45361</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -32561,7 +32561,7 @@
         <v>45735</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -32634,7 +32634,7 @@
         <v>45610</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -32707,7 +32707,7 @@
         <v>45679</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -32780,7 +32780,7 @@
         <v>45735</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -32853,7 +32853,7 @@
         <v>44750</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -32926,7 +32926,7 @@
         <v>44483</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -32999,7 +32999,7 @@
         <v>44714</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -33072,7 +33072,7 @@
         <v>45441</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -33145,7 +33145,7 @@
         <v>45441</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -33218,7 +33218,7 @@
         <v>45441</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -33291,7 +33291,7 @@
         <v>45377</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -33369,7 +33369,7 @@
         <v>45272</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -33442,7 +33442,7 @@
         <v>45309</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -33515,7 +33515,7 @@
         <v>45432</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -33588,7 +33588,7 @@
         <v>46148</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -33661,7 +33661,7 @@
         <v>45293</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -33734,7 +33734,7 @@
         <v>44483</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -33807,7 +33807,7 @@
         <v>44476</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -33880,7 +33880,7 @@
         <v>44671</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -33953,7 +33953,7 @@
         <v>45131</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -34026,7 +34026,7 @@
         <v>45574</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -34099,7 +34099,7 @@
         <v>45589</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -34172,7 +34172,7 @@
         <v>45546</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -34245,7 +34245,7 @@
         <v>45623</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -34318,7 +34318,7 @@
         <v>45838</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -34391,7 +34391,7 @@
         <v>46153</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -34464,7 +34464,7 @@
         <v>44817</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -34537,7 +34537,7 @@
         <v>45257</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -34615,7 +34615,7 @@
         <v>45245</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -34688,7 +34688,7 @@
         <v>44964</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -34761,7 +34761,7 @@
         <v>45170</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -34834,7 +34834,7 @@
         <v>46153</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -34907,7 +34907,7 @@
         <v>46153</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -34980,7 +34980,7 @@
         <v>46153</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -35053,7 +35053,7 @@
         <v>46153</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -35126,7 +35126,7 @@
         <v>46153</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -35199,7 +35199,7 @@
         <v>46153</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -35272,7 +35272,7 @@
         <v>44869</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -35345,7 +35345,7 @@
         <v>45709</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -35418,7 +35418,7 @@
         <v>45754</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -35491,7 +35491,7 @@
         <v>45268</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -35564,7 +35564,7 @@
         <v>45441</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -35642,7 +35642,7 @@
         <v>45597</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -35715,7 +35715,7 @@
         <v>45092</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -35788,7 +35788,7 @@
         <v>46155</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -35861,7 +35861,7 @@
         <v>45378</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -35934,7 +35934,7 @@
         <v>46161</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -36012,7 +36012,7 @@
         <v>46161</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -36085,7 +36085,7 @@
         <v>46161</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -36163,7 +36163,7 @@
         <v>45382</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -36236,7 +36236,7 @@
         <v>46161</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -36314,7 +36314,7 @@
         <v>46161</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -36387,7 +36387,7 @@
         <v>46161</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -36465,7 +36465,7 @@
         <v>45876</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -36538,7 +36538,7 @@
         <v>45429</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -36611,7 +36611,7 @@
         <v>45371</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -36684,7 +36684,7 @@
         <v>45411</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -36757,7 +36757,7 @@
         <v>45558</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -36830,7 +36830,7 @@
         <v>44950</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -36903,7 +36903,7 @@
         <v>45246</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -36976,7 +36976,7 @@
         <v>45246</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -37049,7 +37049,7 @@
         <v>45877</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -37122,7 +37122,7 @@
         <v>44697</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -37195,7 +37195,7 @@
         <v>45880</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -37268,7 +37268,7 @@
         <v>45880</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -37341,7 +37341,7 @@
         <v>46169</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -37414,7 +37414,7 @@
         <v>46169</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -37487,7 +37487,7 @@
         <v>46169</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -37560,7 +37560,7 @@
         <v>45580</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -37633,7 +37633,7 @@
         <v>45880</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -37706,7 +37706,7 @@
         <v>46170</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -37779,7 +37779,7 @@
         <v>45159</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -37852,7 +37852,7 @@
         <v>46171</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -37925,7 +37925,7 @@
         <v>45541</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -37998,7 +37998,7 @@
         <v>45880</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -38071,7 +38071,7 @@
         <v>44635</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -38149,7 +38149,7 @@
         <v>46174</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -38222,7 +38222,7 @@
         <v>46174</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -38295,7 +38295,7 @@
         <v>45462</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -38368,7 +38368,7 @@
         <v>46175</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -38441,7 +38441,7 @@
         <v>46175</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -38514,7 +38514,7 @@
         <v>46174</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -38587,7 +38587,7 @@
         <v>46174</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -38660,7 +38660,7 @@
         <v>45042</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -38733,7 +38733,7 @@
         <v>46178</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -38806,7 +38806,7 @@
         <v>46178</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -38879,7 +38879,7 @@
         <v>45352</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -38952,7 +38952,7 @@
         <v>44970</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -39025,7 +39025,7 @@
         <v>45568</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -39098,7 +39098,7 @@
         <v>45145</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -39171,7 +39171,7 @@
         <v>46183</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -39244,7 +39244,7 @@
         <v>44510</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -39317,7 +39317,7 @@
         <v>45624</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -39390,7 +39390,7 @@
         <v>45170</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -39463,7 +39463,7 @@
         <v>46185</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -39536,7 +39536,7 @@
         <v>44965</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -39614,7 +39614,7 @@
         <v>44477</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -39687,7 +39687,7 @@
         <v>45257</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -39760,7 +39760,7 @@
         <v>45538</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -39833,7 +39833,7 @@
         <v>45456</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -39906,7 +39906,7 @@
         <v>46188</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -39979,7 +39979,7 @@
         <v>46188</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -40052,7 +40052,7 @@
         <v>45182</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -40125,7 +40125,7 @@
         <v>44489</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -40198,7 +40198,7 @@
         <v>45456</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -40271,7 +40271,7 @@
         <v>46196</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -40344,7 +40344,7 @@
         <v>45198</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -40417,7 +40417,7 @@
         <v>45752</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -40495,7 +40495,7 @@
         <v>44735</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -40568,7 +40568,7 @@
         <v>46199</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -40641,7 +40641,7 @@
         <v>45153</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -40714,7 +40714,7 @@
         <v>45568</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -40787,7 +40787,7 @@
         <v>44970</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -40860,7 +40860,7 @@
         <v>44970</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -40933,7 +40933,7 @@
         <v>44641</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -41006,7 +41006,7 @@
         <v>45342</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -41084,7 +41084,7 @@
         <v>45737</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -41157,7 +41157,7 @@
         <v>45483</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -41230,7 +41230,7 @@
         <v>45061</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -41303,7 +41303,7 @@
         <v>44893</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -41376,7 +41376,7 @@
         <v>46209</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -41449,7 +41449,7 @@
         <v>46206</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -41522,7 +41522,7 @@
         <v>45084</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -41595,7 +41595,7 @@
         <v>44900</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -41668,7 +41668,7 @@
         <v>46161</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -41741,7 +41741,7 @@
         <v>45572</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -41814,7 +41814,7 @@
         <v>45002</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -41887,7 +41887,7 @@
         <v>44847</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -41960,7 +41960,7 @@
         <v>45432</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -42033,7 +42033,7 @@
         <v>45677</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -42106,7 +42106,7 @@
         <v>46261</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -42179,7 +42179,7 @@
         <v>46261</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -42252,7 +42252,7 @@
         <v>45253</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -42325,7 +42325,7 @@
         <v>45253</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -42398,7 +42398,7 @@
         <v>45104</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -42471,7 +42471,7 @@
         <v>46263</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -42544,7 +42544,7 @@
         <v>45715</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -42617,7 +42617,7 @@
         <v>45117</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -42690,7 +42690,7 @@
         <v>45357</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -42763,7 +42763,7 @@
         <v>45107</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -42836,7 +42836,7 @@
         <v>46224</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -42914,7 +42914,7 @@
         <v>45267</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -42987,7 +42987,7 @@
         <v>46268</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -43060,7 +43060,7 @@
         <v>46268</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -43133,7 +43133,7 @@
         <v>46268</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -43206,7 +43206,7 @@
         <v>44726</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -43279,7 +43279,7 @@
         <v>45351</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -43352,7 +43352,7 @@
         <v>45426</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -43425,7 +43425,7 @@
         <v>44872</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -43498,7 +43498,7 @@
         <v>45456</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -43571,7 +43571,7 @@
         <v>46273</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -43644,7 +43644,7 @@
         <v>46272</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -43717,7 +43717,7 @@
         <v>46272</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -43790,7 +43790,7 @@
         <v>45840</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -43868,7 +43868,7 @@
         <v>45091</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -43941,7 +43941,7 @@
         <v>46273</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -44014,7 +44014,7 @@
         <v>46279</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -44087,7 +44087,7 @@
         <v>46279</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -44160,7 +44160,7 @@
         <v>46279</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -44233,7 +44233,7 @@
         <v>46036</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -44306,7 +44306,7 @@
         <v>45462</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -44379,7 +44379,7 @@
         <v>45114</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -44452,7 +44452,7 @@
         <v>45225</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -44525,7 +44525,7 @@
         <v>45246</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -44598,7 +44598,7 @@
         <v>46281</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -44671,7 +44671,7 @@
         <v>45316</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -44749,7 +44749,7 @@
         <v>44601</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -44822,7 +44822,7 @@
         <v>46282</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -44895,7 +44895,7 @@
         <v>46241</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -44968,7 +44968,7 @@
         <v>44575</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -45041,7 +45041,7 @@
         <v>45170</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -45114,7 +45114,7 @@
         <v>45334</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -45187,7 +45187,7 @@
         <v>45169</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -45260,7 +45260,7 @@
         <v>44729</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -45333,7 +45333,7 @@
         <v>46273</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -45406,7 +45406,7 @@
         <v>46283</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -45479,7 +45479,7 @@
         <v>45939</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -45557,7 +45557,7 @@
         <v>46286</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -45630,7 +45630,7 @@
         <v>46281</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -45703,7 +45703,7 @@
         <v>46283</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -45776,7 +45776,7 @@
         <v>46030</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -45849,7 +45849,7 @@
         <v>46281</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -45922,7 +45922,7 @@
         <v>44796</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -45995,7 +45995,7 @@
         <v>44995</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -46068,7 +46068,7 @@
         <v>46283</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -46141,7 +46141,7 @@
         <v>46286</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -46214,7 +46214,7 @@
         <v>44951</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -46287,7 +46287,7 @@
         <v>45110</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -46360,7 +46360,7 @@
         <v>46224</v>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -46433,7 +46433,7 @@
         <v>45432</v>
       </c>
       <c r="E610" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -46506,7 +46506,7 @@
         <v>44530</v>
       </c>
       <c r="E611" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
@@ -46579,7 +46579,7 @@
         <v>44980</v>
       </c>
       <c r="E612" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
@@ -46652,7 +46652,7 @@
         <v>46247</v>
       </c>
       <c r="E613" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
@@ -46725,7 +46725,7 @@
         <v>45350</v>
       </c>
       <c r="E614" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F614" t="inlineStr">
         <is>
@@ -46798,7 +46798,7 @@
         <v>46245</v>
       </c>
       <c r="E615" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F615" t="inlineStr">
         <is>
@@ -46871,7 +46871,7 @@
         <v>45229</v>
       </c>
       <c r="E616" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F616" t="inlineStr">
         <is>
@@ -46944,7 +46944,7 @@
         <v>46292</v>
       </c>
       <c r="E617" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F617" t="inlineStr">
         <is>
@@ -47017,7 +47017,7 @@
         <v>45245</v>
       </c>
       <c r="E618" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F618" t="inlineStr">
         <is>
@@ -47090,7 +47090,7 @@
         <v>45531</v>
       </c>
       <c r="E619" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F619" t="inlineStr">
         <is>
@@ -47163,7 +47163,7 @@
         <v>45352</v>
       </c>
       <c r="E620" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F620" t="inlineStr">
         <is>
@@ -47236,7 +47236,7 @@
         <v>45208</v>
       </c>
       <c r="E621" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F621" t="inlineStr">
         <is>
@@ -47309,7 +47309,7 @@
         <v>45400</v>
       </c>
       <c r="E622" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F622" t="inlineStr">
         <is>
@@ -47382,7 +47382,7 @@
         <v>45110</v>
       </c>
       <c r="E623" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F623" t="inlineStr">
         <is>
@@ -47455,7 +47455,7 @@
         <v>46293</v>
       </c>
       <c r="E624" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F624" t="inlineStr">
         <is>
@@ -47528,7 +47528,7 @@
         <v>46292</v>
       </c>
       <c r="E625" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F625" t="inlineStr">
         <is>
@@ -47601,7 +47601,7 @@
         <v>44756</v>
       </c>
       <c r="E626" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F626" t="inlineStr">
         <is>
@@ -47674,7 +47674,7 @@
         <v>46248</v>
       </c>
       <c r="E627" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F627" t="inlineStr">
         <is>
@@ -47747,7 +47747,7 @@
         <v>45390</v>
       </c>
       <c r="E628" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F628" t="inlineStr">
         <is>
@@ -47820,7 +47820,7 @@
         <v>45238</v>
       </c>
       <c r="E629" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F629" t="inlineStr">
         <is>
@@ -47893,7 +47893,7 @@
         <v>46292</v>
       </c>
       <c r="E630" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F630" t="inlineStr">
         <is>
@@ -47966,7 +47966,7 @@
         <v>46248</v>
       </c>
       <c r="E631" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F631" t="inlineStr">
         <is>
@@ -48039,7 +48039,7 @@
         <v>46292</v>
       </c>
       <c r="E632" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F632" t="inlineStr">
         <is>
@@ -48112,7 +48112,7 @@
         <v>46292</v>
       </c>
       <c r="E633" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F633" t="inlineStr">
         <is>
@@ -48185,7 +48185,7 @@
         <v>46292</v>
       </c>
       <c r="E634" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F634" t="inlineStr">
         <is>
@@ -48258,7 +48258,7 @@
         <v>46292</v>
       </c>
       <c r="E635" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F635" t="inlineStr">
         <is>
@@ -48331,7 +48331,7 @@
         <v>46294</v>
       </c>
       <c r="E636" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F636" t="inlineStr">
         <is>
@@ -48409,7 +48409,7 @@
         <v>44866</v>
       </c>
       <c r="E637" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F637" t="inlineStr">
         <is>
@@ -48482,7 +48482,7 @@
         <v>45406</v>
       </c>
       <c r="E638" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F638" t="inlineStr">
         <is>
@@ -48555,7 +48555,7 @@
         <v>45414</v>
       </c>
       <c r="E639" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F639" t="inlineStr">
         <is>
@@ -48628,7 +48628,7 @@
         <v>45229</v>
       </c>
       <c r="E640" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F640" t="inlineStr">
         <is>
@@ -48701,7 +48701,7 @@
         <v>44651</v>
       </c>
       <c r="E641" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F641" t="inlineStr">
         <is>
@@ -48774,7 +48774,7 @@
         <v>45092</v>
       </c>
       <c r="E642" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F642" t="inlineStr">
         <is>
@@ -48847,7 +48847,7 @@
         <v>45455</v>
       </c>
       <c r="E643" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F643" t="inlineStr">
         <is>
@@ -48920,7 +48920,7 @@
         <v>45051</v>
       </c>
       <c r="E644" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F644" t="inlineStr">
         <is>
@@ -48993,7 +48993,7 @@
         <v>45770</v>
       </c>
       <c r="E645" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F645" t="inlineStr">
         <is>
@@ -49066,7 +49066,7 @@
         <v>46244</v>
       </c>
       <c r="E646" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F646" t="inlineStr">
         <is>
@@ -49139,7 +49139,7 @@
         <v>46295</v>
       </c>
       <c r="E647" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F647" t="inlineStr">
         <is>
@@ -49212,7 +49212,7 @@
         <v>45671</v>
       </c>
       <c r="E648" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F648" t="inlineStr">
         <is>
@@ -49285,7 +49285,7 @@
         <v>44813</v>
       </c>
       <c r="E649" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F649" t="inlineStr">
         <is>
@@ -49358,7 +49358,7 @@
         <v>45162</v>
       </c>
       <c r="E650" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F650" t="inlineStr">
         <is>
@@ -49431,7 +49431,7 @@
         <v>45254</v>
       </c>
       <c r="E651" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F651" t="inlineStr">
         <is>
@@ -49504,7 +49504,7 @@
         <v>44900</v>
       </c>
       <c r="E652" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F652" t="inlineStr">
         <is>
@@ -49577,7 +49577,7 @@
         <v>44893</v>
       </c>
       <c r="E653" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F653" t="inlineStr">
         <is>
@@ -49650,7 +49650,7 @@
         <v>45327</v>
       </c>
       <c r="E654" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F654" t="inlineStr">
         <is>
@@ -49723,7 +49723,7 @@
         <v>45624</v>
       </c>
       <c r="E655" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F655" t="inlineStr">
         <is>
@@ -49796,7 +49796,7 @@
         <v>44712</v>
       </c>
       <c r="E656" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F656" t="inlineStr">
         <is>
@@ -49869,7 +49869,7 @@
         <v>44834</v>
       </c>
       <c r="E657" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F657" t="inlineStr">
         <is>
@@ -49942,7 +49942,7 @@
         <v>45229</v>
       </c>
       <c r="E658" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F658" t="inlineStr">
         <is>
@@ -50015,7 +50015,7 @@
         <v>44967</v>
       </c>
       <c r="E659" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F659" t="inlineStr">
         <is>
@@ -50088,7 +50088,7 @@
         <v>45544</v>
       </c>
       <c r="E660" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F660" t="inlineStr">
         <is>
@@ -50161,7 +50161,7 @@
         <v>45715</v>
       </c>
       <c r="E661" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F661" t="inlineStr">
         <is>
@@ -50234,7 +50234,7 @@
         <v>45700</v>
       </c>
       <c r="E662" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F662" t="inlineStr">
         <is>
@@ -50307,7 +50307,7 @@
         <v>45316</v>
       </c>
       <c r="E663" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F663" t="inlineStr">
         <is>
@@ -50380,7 +50380,7 @@
         <v>45643</v>
       </c>
       <c r="E664" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F664" t="inlineStr">
         <is>
@@ -50453,7 +50453,7 @@
         <v>44900</v>
       </c>
       <c r="E665" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F665" t="inlineStr">
         <is>
@@ -50526,7 +50526,7 @@
         <v>45368</v>
       </c>
       <c r="E666" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F666" t="inlineStr">
         <is>
@@ -50604,7 +50604,7 @@
         <v>45371</v>
       </c>
       <c r="E667" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F667" t="inlineStr">
         <is>
@@ -50677,7 +50677,7 @@
         <v>45371</v>
       </c>
       <c r="E668" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F668" t="inlineStr">
         <is>
@@ -50750,7 +50750,7 @@
         <v>44477</v>
       </c>
       <c r="E669" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F669" t="inlineStr">
         <is>
@@ -50823,7 +50823,7 @@
         <v>45254</v>
       </c>
       <c r="E670" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F670" t="inlineStr">
         <is>
@@ -50896,7 +50896,7 @@
         <v>45229</v>
       </c>
       <c r="E671" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F671" t="inlineStr">
         <is>
@@ -50969,7 +50969,7 @@
         <v>45035</v>
       </c>
       <c r="E672" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F672" t="inlineStr">
         <is>
@@ -51042,7 +51042,7 @@
         <v>45299</v>
       </c>
       <c r="E673" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F673" t="inlineStr">
         <is>
@@ -51115,7 +51115,7 @@
         <v>45176</v>
       </c>
       <c r="E674" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F674" t="inlineStr">
         <is>
@@ -51193,7 +51193,7 @@
         <v>45638</v>
       </c>
       <c r="E675" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F675" t="inlineStr">
         <is>
@@ -51266,7 +51266,7 @@
         <v>45588</v>
       </c>
       <c r="E676" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F676" t="inlineStr">
         <is>
@@ -51344,7 +51344,7 @@
         <v>45510</v>
       </c>
       <c r="E677" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F677" t="inlineStr">
         <is>
@@ -51417,7 +51417,7 @@
         <v>45559</v>
       </c>
       <c r="E678" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F678" t="inlineStr">
         <is>
@@ -51490,7 +51490,7 @@
         <v>45783</v>
       </c>
       <c r="E679" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F679" t="inlineStr">
         <is>
@@ -51563,7 +51563,7 @@
         <v>45616</v>
       </c>
       <c r="E680" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F680" t="inlineStr">
         <is>
@@ -51636,7 +51636,7 @@
         <v>45483</v>
       </c>
       <c r="E681" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F681" t="inlineStr">
         <is>
@@ -51709,7 +51709,7 @@
         <v>45680</v>
       </c>
       <c r="E682" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F682" t="inlineStr">
         <is>
@@ -51782,7 +51782,7 @@
         <v>45616</v>
       </c>
       <c r="E683" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F683" t="inlineStr">
         <is>
@@ -51855,7 +51855,7 @@
         <v>45614</v>
       </c>
       <c r="E684" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F684" t="inlineStr">
         <is>
@@ -51933,7 +51933,7 @@
         <v>44631</v>
       </c>
       <c r="E685" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F685" t="inlineStr">
         <is>
@@ -52006,7 +52006,7 @@
         <v>44743</v>
       </c>
       <c r="E686" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F686" t="inlineStr">
         <is>
@@ -52079,7 +52079,7 @@
         <v>45375</v>
       </c>
       <c r="E687" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F687" t="inlineStr">
         <is>
@@ -52152,7 +52152,7 @@
         <v>44488</v>
       </c>
       <c r="E688" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F688" t="inlineStr">
         <is>
@@ -52225,7 +52225,7 @@
         <v>45604</v>
       </c>
       <c r="E689" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F689" t="inlineStr">
         <is>
@@ -52298,7 +52298,7 @@
         <v>45356</v>
       </c>
       <c r="E690" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F690" t="inlineStr">
         <is>
@@ -52371,7 +52371,7 @@
         <v>44613</v>
       </c>
       <c r="E691" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F691" t="inlineStr">
         <is>
@@ -52444,7 +52444,7 @@
         <v>45349</v>
       </c>
       <c r="E692" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F692" t="inlineStr">
         <is>
@@ -52517,7 +52517,7 @@
         <v>44608</v>
       </c>
       <c r="E693" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F693" t="inlineStr">
         <is>
@@ -52590,7 +52590,7 @@
         <v>44631</v>
       </c>
       <c r="E694" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F694" t="inlineStr">
         <is>
@@ -52663,7 +52663,7 @@
         <v>44631</v>
       </c>
       <c r="E695" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F695" t="inlineStr">
         <is>
@@ -52736,7 +52736,7 @@
         <v>45744</v>
       </c>
       <c r="E696" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F696" t="inlineStr">
         <is>
@@ -52809,7 +52809,7 @@
         <v>45714</v>
       </c>
       <c r="E697" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F697" t="inlineStr">
         <is>
@@ -52882,7 +52882,7 @@
         <v>45715</v>
       </c>
       <c r="E698" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F698" t="inlineStr">
         <is>
@@ -52955,7 +52955,7 @@
         <v>45709</v>
       </c>
       <c r="E699" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F699" t="inlineStr">
         <is>
@@ -53028,7 +53028,7 @@
         <v>45714</v>
       </c>
       <c r="E700" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F700" t="inlineStr">
         <is>
@@ -53101,7 +53101,7 @@
         <v>45813</v>
       </c>
       <c r="E701" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F701" t="inlineStr">
         <is>
@@ -53174,7 +53174,7 @@
         <v>45813</v>
       </c>
       <c r="E702" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F702" t="inlineStr">
         <is>
@@ -53247,7 +53247,7 @@
         <v>45813</v>
       </c>
       <c r="E703" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F703" t="inlineStr">
         <is>
@@ -53320,7 +53320,7 @@
         <v>45820</v>
       </c>
       <c r="E704" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F704" t="inlineStr">
         <is>
@@ -53393,7 +53393,7 @@
         <v>45827</v>
       </c>
       <c r="E705" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F705" t="inlineStr">
         <is>
@@ -53466,7 +53466,7 @@
         <v>45845</v>
       </c>
       <c r="E706" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F706" t="inlineStr">
         <is>
@@ -53539,7 +53539,7 @@
         <v>45883</v>
       </c>
       <c r="E707" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F707" t="inlineStr">
         <is>
@@ -53612,7 +53612,7 @@
         <v>45915</v>
       </c>
       <c r="E708" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F708" t="inlineStr">
         <is>
@@ -53685,7 +53685,7 @@
         <v>46041</v>
       </c>
       <c r="E709" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F709" t="inlineStr">
         <is>
@@ -53758,7 +53758,7 @@
         <v>46133</v>
       </c>
       <c r="E710" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F710" t="inlineStr">
         <is>
@@ -53831,7 +53831,7 @@
         <v>46147</v>
       </c>
       <c r="E711" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F711" t="inlineStr">
         <is>
@@ -53904,7 +53904,7 @@
         <v>46211</v>
       </c>
       <c r="E712" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F712" t="inlineStr">
         <is>
@@ -53977,7 +53977,7 @@
         <v>46290</v>
       </c>
       <c r="E713" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F713" t="inlineStr">
         <is>
@@ -54050,7 +54050,7 @@
         <v>46253</v>
       </c>
       <c r="E714" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F714" t="inlineStr">
         <is>

--- a/Översikt HYLTE.xlsx
+++ b/Översikt HYLTE.xlsx
@@ -601,7 +601,7 @@
         <v>46090</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -718,7 +718,7 @@
         <v>45265</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -834,7 +834,7 @@
         <v>46066</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -945,7 +945,7 @@
         <v>44873</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1054,7 +1054,7 @@
         <v>45348</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1166,7 +1166,7 @@
         <v>45719</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1274,7 +1274,7 @@
         <v>46268</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1381,7 +1381,7 @@
         <v>45245</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1492,7 +1492,7 @@
         <v>45230</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1599,7 +1599,7 @@
         <v>45737</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1706,7 +1706,7 @@
         <v>46141</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1813,7 +1813,7 @@
         <v>46161</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1920,7 +1920,7 @@
         <v>44839</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2030,7 +2030,7 @@
         <v>46048</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2136,7 +2136,7 @@
         <v>45841</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2246,7 +2246,7 @@
         <v>45099</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2356,7 +2356,7 @@
         <v>45904</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2466,7 +2466,7 @@
         <v>46130</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2572,7 +2572,7 @@
         <v>44648</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2677,7 +2677,7 @@
         <v>44651</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2782,7 +2782,7 @@
         <v>44876</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2887,7 +2887,7 @@
         <v>45617</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2992,7 +2992,7 @@
         <v>45299</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3101,7 +3101,7 @@
         <v>45245</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3206,7 +3206,7 @@
         <v>45343</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3311,7 +3311,7 @@
         <v>45476</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3421,7 +3421,7 @@
         <v>45163</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3526,7 +3526,7 @@
         <v>45245</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3631,7 +3631,7 @@
         <v>45593</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3736,7 +3736,7 @@
         <v>45153</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3850,7 +3850,7 @@
         <v>45186</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3955,7 +3955,7 @@
         <v>45085</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4064,7 +4064,7 @@
         <v>45253</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4169,7 +4169,7 @@
         <v>45754</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4274,7 +4274,7 @@
         <v>46253</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4384,7 +4384,7 @@
         <v>44810</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4457,7 +4457,7 @@
         <v>44481</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4530,7 +4530,7 @@
         <v>44600</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4603,7 +4603,7 @@
         <v>44557</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4676,7 +4676,7 @@
         <v>44529</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4749,7 +4749,7 @@
         <v>44483</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4822,7 +4822,7 @@
         <v>44705</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4895,7 +4895,7 @@
         <v>44778</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4968,7 +4968,7 @@
         <v>44488</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5041,7 +5041,7 @@
         <v>44475</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5114,7 +5114,7 @@
         <v>44624</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5187,7 +5187,7 @@
         <v>44812</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5260,7 +5260,7 @@
         <v>44638</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5333,7 +5333,7 @@
         <v>44498</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5406,7 +5406,7 @@
         <v>44845</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5479,7 +5479,7 @@
         <v>44559</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5552,7 +5552,7 @@
         <v>44578</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5625,7 +5625,7 @@
         <v>44659</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5703,7 +5703,7 @@
         <v>44756</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5776,7 +5776,7 @@
         <v>44501</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5849,7 +5849,7 @@
         <v>44651</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5922,7 +5922,7 @@
         <v>44711</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5995,7 +5995,7 @@
         <v>44487</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6073,7 +6073,7 @@
         <v>44735</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6146,7 +6146,7 @@
         <v>44477</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6219,7 +6219,7 @@
         <v>44489</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6292,7 +6292,7 @@
         <v>44834</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6365,7 +6365,7 @@
         <v>44796</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6438,7 +6438,7 @@
         <v>44502</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6511,7 +6511,7 @@
         <v>44631</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6584,7 +6584,7 @@
         <v>44876</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6657,7 +6657,7 @@
         <v>44659</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6730,7 +6730,7 @@
         <v>44644</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6803,7 +6803,7 @@
         <v>44515</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6881,7 +6881,7 @@
         <v>44778</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6954,7 +6954,7 @@
         <v>44482</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7027,7 +7027,7 @@
         <v>44482</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7100,7 +7100,7 @@
         <v>44867</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7173,7 +7173,7 @@
         <v>44505</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7246,7 +7246,7 @@
         <v>44634</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7319,7 +7319,7 @@
         <v>44728</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7392,7 +7392,7 @@
         <v>44714</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7465,7 +7465,7 @@
         <v>44795</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7538,7 +7538,7 @@
         <v>44818</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7611,7 +7611,7 @@
         <v>44801</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7684,7 +7684,7 @@
         <v>44596</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7762,7 +7762,7 @@
         <v>44644</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7835,7 +7835,7 @@
         <v>44523</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7908,7 +7908,7 @@
         <v>44500</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7981,7 +7981,7 @@
         <v>44727</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8054,7 +8054,7 @@
         <v>44705</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8127,7 +8127,7 @@
         <v>44659</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8205,7 +8205,7 @@
         <v>44659</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8283,7 +8283,7 @@
         <v>44757</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8356,7 +8356,7 @@
         <v>44495</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8429,7 +8429,7 @@
         <v>45460</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8502,7 +8502,7 @@
         <v>44494</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8575,7 +8575,7 @@
         <v>45002</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8648,7 +8648,7 @@
         <v>45568</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8721,7 +8721,7 @@
         <v>44487</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8799,7 +8799,7 @@
         <v>44900</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8877,7 +8877,7 @@
         <v>44851</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8950,7 +8950,7 @@
         <v>44851</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -9023,7 +9023,7 @@
         <v>45062</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9096,7 +9096,7 @@
         <v>45132</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9169,7 +9169,7 @@
         <v>45715</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9242,7 +9242,7 @@
         <v>44714</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9320,7 +9320,7 @@
         <v>44476</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9393,7 +9393,7 @@
         <v>44958</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9466,7 +9466,7 @@
         <v>44899</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9539,7 +9539,7 @@
         <v>45107</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9612,7 +9612,7 @@
         <v>44559</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9685,7 +9685,7 @@
         <v>45211</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9758,7 +9758,7 @@
         <v>45258</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9831,7 +9831,7 @@
         <v>45229</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9904,7 +9904,7 @@
         <v>45548</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9977,7 +9977,7 @@
         <v>45589</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -10050,7 +10050,7 @@
         <v>45225</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10123,7 +10123,7 @@
         <v>45618</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10196,7 +10196,7 @@
         <v>45254</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10269,7 +10269,7 @@
         <v>45254</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10342,7 +10342,7 @@
         <v>45726</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10415,7 +10415,7 @@
         <v>45483</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10488,7 +10488,7 @@
         <v>45254</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10561,7 +10561,7 @@
         <v>45254</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10634,7 +10634,7 @@
         <v>45098</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10712,7 +10712,7 @@
         <v>45589</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -10790,7 +10790,7 @@
         <v>45391</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10863,7 +10863,7 @@
         <v>45786</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10941,7 +10941,7 @@
         <v>44868</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -11014,7 +11014,7 @@
         <v>45926</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -11087,7 +11087,7 @@
         <v>44910</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11160,7 +11160,7 @@
         <v>45840</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11233,7 +11233,7 @@
         <v>44823</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11306,7 +11306,7 @@
         <v>45351</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11379,7 +11379,7 @@
         <v>45590</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11452,7 +11452,7 @@
         <v>45539</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11525,7 +11525,7 @@
         <v>45538</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11598,7 +11598,7 @@
         <v>45673</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11671,7 +11671,7 @@
         <v>45104</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -11744,7 +11744,7 @@
         <v>45684</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -11817,7 +11817,7 @@
         <v>45609</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -11890,7 +11890,7 @@
         <v>45743</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -11968,7 +11968,7 @@
         <v>45600</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -12041,7 +12041,7 @@
         <v>45834</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -12114,7 +12114,7 @@
         <v>44539</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12187,7 +12187,7 @@
         <v>45436</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12260,7 +12260,7 @@
         <v>46020</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12333,7 +12333,7 @@
         <v>45352</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12406,7 +12406,7 @@
         <v>45352</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -12479,7 +12479,7 @@
         <v>45748</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -12552,7 +12552,7 @@
         <v>45890</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -12625,7 +12625,7 @@
         <v>45891</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -12703,7 +12703,7 @@
         <v>45891</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -12781,7 +12781,7 @@
         <v>44719</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -12854,7 +12854,7 @@
         <v>45743</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -12932,7 +12932,7 @@
         <v>45741</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -13005,7 +13005,7 @@
         <v>44896</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -13078,7 +13078,7 @@
         <v>45897</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -13151,7 +13151,7 @@
         <v>45839</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13224,7 +13224,7 @@
         <v>45898</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13297,7 +13297,7 @@
         <v>45897</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13370,7 +13370,7 @@
         <v>45638</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -13443,7 +13443,7 @@
         <v>45434</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -13516,7 +13516,7 @@
         <v>45793</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -13589,7 +13589,7 @@
         <v>45905</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -13662,7 +13662,7 @@
         <v>46042</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -13735,7 +13735,7 @@
         <v>45838</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -13808,7 +13808,7 @@
         <v>46042</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -13881,7 +13881,7 @@
         <v>45559</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -13954,7 +13954,7 @@
         <v>45681</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -14027,7 +14027,7 @@
         <v>45910</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -14100,7 +14100,7 @@
         <v>45743</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -14178,7 +14178,7 @@
         <v>46044</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14251,7 +14251,7 @@
         <v>44851</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14324,7 +14324,7 @@
         <v>45910</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -14397,7 +14397,7 @@
         <v>46044</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -14470,7 +14470,7 @@
         <v>46044</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -14543,7 +14543,7 @@
         <v>46044</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -14616,7 +14616,7 @@
         <v>45163</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -14689,7 +14689,7 @@
         <v>46048</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -14762,7 +14762,7 @@
         <v>46049</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -14835,7 +14835,7 @@
         <v>46048</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -14908,7 +14908,7 @@
         <v>46048</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -14981,7 +14981,7 @@
         <v>46048</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -15054,7 +15054,7 @@
         <v>46048</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -15127,7 +15127,7 @@
         <v>45089</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -15200,7 +15200,7 @@
         <v>46048</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -15273,7 +15273,7 @@
         <v>46048</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -15346,7 +15346,7 @@
         <v>46048</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -15419,7 +15419,7 @@
         <v>46048</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -15492,7 +15492,7 @@
         <v>46048</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -15565,7 +15565,7 @@
         <v>46048</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -15638,7 +15638,7 @@
         <v>46048</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -15711,7 +15711,7 @@
         <v>45252</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -15784,7 +15784,7 @@
         <v>45145</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -15857,7 +15857,7 @@
         <v>45918</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -15930,7 +15930,7 @@
         <v>45806</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -16003,7 +16003,7 @@
         <v>45922</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -16076,7 +16076,7 @@
         <v>46052</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -16149,7 +16149,7 @@
         <v>45922</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -16222,7 +16222,7 @@
         <v>45609</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -16295,7 +16295,7 @@
         <v>46055</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -16368,7 +16368,7 @@
         <v>45922</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -16441,7 +16441,7 @@
         <v>46052</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -16514,7 +16514,7 @@
         <v>45924</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -16587,7 +16587,7 @@
         <v>45926</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -16660,7 +16660,7 @@
         <v>46057</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -16733,7 +16733,7 @@
         <v>45926</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -16806,7 +16806,7 @@
         <v>45926</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -16879,7 +16879,7 @@
         <v>45929</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -16952,7 +16952,7 @@
         <v>45194</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -17025,7 +17025,7 @@
         <v>45931</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -17098,7 +17098,7 @@
         <v>44482</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -17171,7 +17171,7 @@
         <v>46062</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -17244,7 +17244,7 @@
         <v>44701</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -17322,7 +17322,7 @@
         <v>45182</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -17395,7 +17395,7 @@
         <v>45930</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -17468,7 +17468,7 @@
         <v>46062</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -17541,7 +17541,7 @@
         <v>45931</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -17614,7 +17614,7 @@
         <v>46064</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -17687,7 +17687,7 @@
         <v>45933</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -17760,7 +17760,7 @@
         <v>45933</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -17833,7 +17833,7 @@
         <v>46065</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -17906,7 +17906,7 @@
         <v>45933</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -17979,7 +17979,7 @@
         <v>45936</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -18052,7 +18052,7 @@
         <v>44901</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -18125,7 +18125,7 @@
         <v>45181</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -18198,7 +18198,7 @@
         <v>45936</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -18271,7 +18271,7 @@
         <v>45936</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -18344,7 +18344,7 @@
         <v>44495</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -18417,7 +18417,7 @@
         <v>46070</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -18490,7 +18490,7 @@
         <v>45938</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -18563,7 +18563,7 @@
         <v>45694</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -18636,7 +18636,7 @@
         <v>46070</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -18709,7 +18709,7 @@
         <v>45937</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -18782,7 +18782,7 @@
         <v>45441</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -18860,7 +18860,7 @@
         <v>45441</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -18933,7 +18933,7 @@
         <v>45944</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -19006,7 +19006,7 @@
         <v>45310</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -19079,7 +19079,7 @@
         <v>45229</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -19152,7 +19152,7 @@
         <v>45812</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -19225,7 +19225,7 @@
         <v>46084</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -19298,7 +19298,7 @@
         <v>46084</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -19371,7 +19371,7 @@
         <v>45957</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -19444,7 +19444,7 @@
         <v>44999</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -19517,7 +19517,7 @@
         <v>46087</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -19590,7 +19590,7 @@
         <v>45527</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -19663,7 +19663,7 @@
         <v>45961</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -19736,7 +19736,7 @@
         <v>45922</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -19809,7 +19809,7 @@
         <v>45961</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -19882,7 +19882,7 @@
         <v>45751</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -19960,7 +19960,7 @@
         <v>44847</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -20033,7 +20033,7 @@
         <v>45706</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -20106,7 +20106,7 @@
         <v>46093</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -20179,7 +20179,7 @@
         <v>46093</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -20252,7 +20252,7 @@
         <v>46093</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -20325,7 +20325,7 @@
         <v>44778</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -20398,7 +20398,7 @@
         <v>45972</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -20471,7 +20471,7 @@
         <v>45972</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -20544,7 +20544,7 @@
         <v>45173</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -20617,7 +20617,7 @@
         <v>45972</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -20690,7 +20690,7 @@
         <v>45132</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -20763,7 +20763,7 @@
         <v>45478</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -20836,7 +20836,7 @@
         <v>46057</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -20909,7 +20909,7 @@
         <v>45979</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -20982,7 +20982,7 @@
         <v>45019</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -21055,7 +21055,7 @@
         <v>45694</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -21128,7 +21128,7 @@
         <v>46057</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -21201,7 +21201,7 @@
         <v>45708</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -21274,7 +21274,7 @@
         <v>45597</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -21347,7 +21347,7 @@
         <v>45387</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -21420,7 +21420,7 @@
         <v>45981</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -21493,7 +21493,7 @@
         <v>45981</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -21566,7 +21566,7 @@
         <v>45730</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -21639,7 +21639,7 @@
         <v>45254</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -21712,7 +21712,7 @@
         <v>46111</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -21785,7 +21785,7 @@
         <v>45331</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -21858,7 +21858,7 @@
         <v>46111</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -21931,7 +21931,7 @@
         <v>45287</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -22004,7 +22004,7 @@
         <v>46111</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -22077,7 +22077,7 @@
         <v>45820</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -22150,7 +22150,7 @@
         <v>44900</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -22223,7 +22223,7 @@
         <v>45987</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -22296,7 +22296,7 @@
         <v>45366</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -22369,7 +22369,7 @@
         <v>45989</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -22442,7 +22442,7 @@
         <v>46120</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -22515,7 +22515,7 @@
         <v>46120</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -22588,7 +22588,7 @@
         <v>45825</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -22661,7 +22661,7 @@
         <v>46122</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -22734,7 +22734,7 @@
         <v>46121</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -22807,7 +22807,7 @@
         <v>46121</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -22880,7 +22880,7 @@
         <v>46121</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -22953,7 +22953,7 @@
         <v>46122</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -23026,7 +23026,7 @@
         <v>45245</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -23099,7 +23099,7 @@
         <v>46122</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -23172,7 +23172,7 @@
         <v>46121</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -23245,7 +23245,7 @@
         <v>46122</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -23318,7 +23318,7 @@
         <v>46121</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -23391,7 +23391,7 @@
         <v>46121</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -23464,7 +23464,7 @@
         <v>46121</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -23537,7 +23537,7 @@
         <v>46121</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -23610,7 +23610,7 @@
         <v>45548</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -23683,7 +23683,7 @@
         <v>45485</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -23756,7 +23756,7 @@
         <v>45560</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -23829,7 +23829,7 @@
         <v>45995</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -23902,7 +23902,7 @@
         <v>46128</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -23975,7 +23975,7 @@
         <v>45674</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -24048,7 +24048,7 @@
         <v>45831</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -24121,7 +24121,7 @@
         <v>44865</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -24194,7 +24194,7 @@
         <v>45601</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -24267,7 +24267,7 @@
         <v>45454</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -24340,7 +24340,7 @@
         <v>45835</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -24413,7 +24413,7 @@
         <v>44701</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -24491,7 +24491,7 @@
         <v>45300</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -24564,7 +24564,7 @@
         <v>45989</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -24637,7 +24637,7 @@
         <v>45838</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -24710,7 +24710,7 @@
         <v>45839</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -24783,7 +24783,7 @@
         <v>46084</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -24856,7 +24856,7 @@
         <v>45524</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -24929,7 +24929,7 @@
         <v>45456</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -25002,7 +25002,7 @@
         <v>45836</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -25075,7 +25075,7 @@
         <v>45429</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -25148,7 +25148,7 @@
         <v>45405</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -25221,7 +25221,7 @@
         <v>45840</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -25294,7 +25294,7 @@
         <v>44797</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -25367,7 +25367,7 @@
         <v>45840</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -25440,7 +25440,7 @@
         <v>45035</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -25513,7 +25513,7 @@
         <v>45840</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -25586,7 +25586,7 @@
         <v>45800</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -25659,7 +25659,7 @@
         <v>45817</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -25732,7 +25732,7 @@
         <v>45259</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -25805,7 +25805,7 @@
         <v>45782</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -25878,7 +25878,7 @@
         <v>45169</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -25951,7 +25951,7 @@
         <v>45847</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -26024,7 +26024,7 @@
         <v>45847</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -26097,7 +26097,7 @@
         <v>45845</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -26170,7 +26170,7 @@
         <v>45845</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -26243,7 +26243,7 @@
         <v>45104</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -26316,7 +26316,7 @@
         <v>45846</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -26394,7 +26394,7 @@
         <v>44900</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -26467,7 +26467,7 @@
         <v>45846</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -26545,7 +26545,7 @@
         <v>45846</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -26623,7 +26623,7 @@
         <v>46084</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -26696,7 +26696,7 @@
         <v>44974</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -26769,7 +26769,7 @@
         <v>45162</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -26842,7 +26842,7 @@
         <v>45803</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -26915,7 +26915,7 @@
         <v>44694</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -26988,7 +26988,7 @@
         <v>45502</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -27061,7 +27061,7 @@
         <v>44974</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -27134,7 +27134,7 @@
         <v>45091</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -27207,7 +27207,7 @@
         <v>44926</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -27285,7 +27285,7 @@
         <v>45604</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -27358,7 +27358,7 @@
         <v>45097</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -27431,7 +27431,7 @@
         <v>44699</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -27504,7 +27504,7 @@
         <v>45790</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -27577,7 +27577,7 @@
         <v>45477</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -27650,7 +27650,7 @@
         <v>45265</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -27723,7 +27723,7 @@
         <v>45084</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -27796,7 +27796,7 @@
         <v>45531</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -27869,7 +27869,7 @@
         <v>45775</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -27942,7 +27942,7 @@
         <v>45840</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -28020,7 +28020,7 @@
         <v>44953</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -28093,7 +28093,7 @@
         <v>45019</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -28166,7 +28166,7 @@
         <v>45299</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -28239,7 +28239,7 @@
         <v>45848</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -28312,7 +28312,7 @@
         <v>45645</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -28385,7 +28385,7 @@
         <v>45366</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -28463,7 +28463,7 @@
         <v>45505</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -28536,7 +28536,7 @@
         <v>45700</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -28609,7 +28609,7 @@
         <v>45700</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -28682,7 +28682,7 @@
         <v>44903</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -28755,7 +28755,7 @@
         <v>45096</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -28828,7 +28828,7 @@
         <v>45617</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -28901,7 +28901,7 @@
         <v>45167</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -28974,7 +28974,7 @@
         <v>45687</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -29047,7 +29047,7 @@
         <v>45352</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -29120,7 +29120,7 @@
         <v>45190</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -29193,7 +29193,7 @@
         <v>45293</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -29266,7 +29266,7 @@
         <v>45392</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -29339,7 +29339,7 @@
         <v>45145</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -29412,7 +29412,7 @@
         <v>45623</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -29485,7 +29485,7 @@
         <v>44917</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -29558,7 +29558,7 @@
         <v>45190</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -29636,7 +29636,7 @@
         <v>45517</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -29709,7 +29709,7 @@
         <v>45545</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -29782,7 +29782,7 @@
         <v>45204</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -29855,7 +29855,7 @@
         <v>45395</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -29928,7 +29928,7 @@
         <v>45541</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -30001,7 +30001,7 @@
         <v>45677</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -30074,7 +30074,7 @@
         <v>45727</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -30147,7 +30147,7 @@
         <v>45252</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -30220,7 +30220,7 @@
         <v>45257</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -30293,7 +30293,7 @@
         <v>45254</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -30366,7 +30366,7 @@
         <v>45309</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -30439,7 +30439,7 @@
         <v>45245</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -30512,7 +30512,7 @@
         <v>45254</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -30585,7 +30585,7 @@
         <v>45288</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -30663,7 +30663,7 @@
         <v>44896</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -30736,7 +30736,7 @@
         <v>44592</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -30809,7 +30809,7 @@
         <v>45407</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -30882,7 +30882,7 @@
         <v>45589</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -30955,7 +30955,7 @@
         <v>45623</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -31028,7 +31028,7 @@
         <v>45769</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -31101,7 +31101,7 @@
         <v>45672</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -31174,7 +31174,7 @@
         <v>45672</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -31247,7 +31247,7 @@
         <v>45524</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -31320,7 +31320,7 @@
         <v>44508</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -31393,7 +31393,7 @@
         <v>44889</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -31466,7 +31466,7 @@
         <v>45199</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -31539,7 +31539,7 @@
         <v>44671</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -31612,7 +31612,7 @@
         <v>45176</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -31685,7 +31685,7 @@
         <v>45199</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -31758,7 +31758,7 @@
         <v>45372</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -31831,7 +31831,7 @@
         <v>44712</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -31904,7 +31904,7 @@
         <v>45395</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -31977,7 +31977,7 @@
         <v>45203</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -32050,7 +32050,7 @@
         <v>44481</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -32123,7 +32123,7 @@
         <v>44739</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -32196,7 +32196,7 @@
         <v>45230</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -32269,7 +32269,7 @@
         <v>45672</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -32342,7 +32342,7 @@
         <v>44701</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -32415,7 +32415,7 @@
         <v>45677</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -32488,7 +32488,7 @@
         <v>45361</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -32561,7 +32561,7 @@
         <v>45735</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -32634,7 +32634,7 @@
         <v>45610</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -32707,7 +32707,7 @@
         <v>45679</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -32780,7 +32780,7 @@
         <v>45735</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -32853,7 +32853,7 @@
         <v>44750</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -32926,7 +32926,7 @@
         <v>44483</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -32999,7 +32999,7 @@
         <v>44714</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -33072,7 +33072,7 @@
         <v>45441</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -33145,7 +33145,7 @@
         <v>45441</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -33218,7 +33218,7 @@
         <v>45441</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -33291,7 +33291,7 @@
         <v>45377</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -33369,7 +33369,7 @@
         <v>45272</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -33442,7 +33442,7 @@
         <v>45309</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -33515,7 +33515,7 @@
         <v>45432</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -33588,7 +33588,7 @@
         <v>46148</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -33661,7 +33661,7 @@
         <v>45293</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -33734,7 +33734,7 @@
         <v>44483</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -33807,7 +33807,7 @@
         <v>44476</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -33880,7 +33880,7 @@
         <v>44671</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -33953,7 +33953,7 @@
         <v>45131</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -34026,7 +34026,7 @@
         <v>45574</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -34099,7 +34099,7 @@
         <v>45589</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -34172,7 +34172,7 @@
         <v>45546</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -34245,7 +34245,7 @@
         <v>45623</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -34318,7 +34318,7 @@
         <v>45838</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -34391,7 +34391,7 @@
         <v>46153</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -34464,7 +34464,7 @@
         <v>44817</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -34537,7 +34537,7 @@
         <v>45257</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -34615,7 +34615,7 @@
         <v>45245</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -34688,7 +34688,7 @@
         <v>44964</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -34761,7 +34761,7 @@
         <v>45170</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -34834,7 +34834,7 @@
         <v>46153</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -34907,7 +34907,7 @@
         <v>46153</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -34980,7 +34980,7 @@
         <v>46153</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -35053,7 +35053,7 @@
         <v>46153</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -35126,7 +35126,7 @@
         <v>46153</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -35199,7 +35199,7 @@
         <v>46153</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -35272,7 +35272,7 @@
         <v>44869</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -35345,7 +35345,7 @@
         <v>45709</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -35418,7 +35418,7 @@
         <v>45754</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -35491,7 +35491,7 @@
         <v>45268</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -35564,7 +35564,7 @@
         <v>45441</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -35642,7 +35642,7 @@
         <v>45597</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -35715,7 +35715,7 @@
         <v>45092</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -35788,7 +35788,7 @@
         <v>46155</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -35861,7 +35861,7 @@
         <v>45378</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -35934,7 +35934,7 @@
         <v>46161</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -36012,7 +36012,7 @@
         <v>46161</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -36085,7 +36085,7 @@
         <v>46161</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -36163,7 +36163,7 @@
         <v>45382</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -36236,7 +36236,7 @@
         <v>46161</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -36314,7 +36314,7 @@
         <v>46161</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -36387,7 +36387,7 @@
         <v>46161</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -36465,7 +36465,7 @@
         <v>45876</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -36538,7 +36538,7 @@
         <v>45429</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -36611,7 +36611,7 @@
         <v>45371</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -36684,7 +36684,7 @@
         <v>45411</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -36757,7 +36757,7 @@
         <v>45558</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -36830,7 +36830,7 @@
         <v>44950</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -36903,7 +36903,7 @@
         <v>45246</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -36976,7 +36976,7 @@
         <v>45246</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -37049,7 +37049,7 @@
         <v>45877</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -37122,7 +37122,7 @@
         <v>44697</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -37195,7 +37195,7 @@
         <v>45880</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -37268,7 +37268,7 @@
         <v>45880</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -37341,7 +37341,7 @@
         <v>46169</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -37414,7 +37414,7 @@
         <v>46169</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -37487,7 +37487,7 @@
         <v>46169</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -37560,7 +37560,7 @@
         <v>45580</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -37633,7 +37633,7 @@
         <v>45880</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -37706,7 +37706,7 @@
         <v>46170</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -37779,7 +37779,7 @@
         <v>45159</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -37852,7 +37852,7 @@
         <v>46171</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -37925,7 +37925,7 @@
         <v>45541</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -37998,7 +37998,7 @@
         <v>45880</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -38071,7 +38071,7 @@
         <v>44635</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -38149,7 +38149,7 @@
         <v>46174</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -38222,7 +38222,7 @@
         <v>46174</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -38295,7 +38295,7 @@
         <v>45462</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -38368,7 +38368,7 @@
         <v>46175</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -38441,7 +38441,7 @@
         <v>46175</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -38514,7 +38514,7 @@
         <v>46174</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -38587,7 +38587,7 @@
         <v>46174</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -38660,7 +38660,7 @@
         <v>45042</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -38733,7 +38733,7 @@
         <v>46178</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -38806,7 +38806,7 @@
         <v>46178</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -38879,7 +38879,7 @@
         <v>45352</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -38952,7 +38952,7 @@
         <v>44970</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -39025,7 +39025,7 @@
         <v>45568</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -39098,7 +39098,7 @@
         <v>45145</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -39171,7 +39171,7 @@
         <v>46183</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -39244,7 +39244,7 @@
         <v>44510</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -39317,7 +39317,7 @@
         <v>45624</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -39390,7 +39390,7 @@
         <v>45170</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -39463,7 +39463,7 @@
         <v>46185</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -39536,7 +39536,7 @@
         <v>44965</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -39614,7 +39614,7 @@
         <v>44477</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -39687,7 +39687,7 @@
         <v>45257</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -39760,7 +39760,7 @@
         <v>45538</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -39833,7 +39833,7 @@
         <v>45456</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -39906,7 +39906,7 @@
         <v>46188</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -39979,7 +39979,7 @@
         <v>46188</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -40052,7 +40052,7 @@
         <v>45182</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -40125,7 +40125,7 @@
         <v>44489</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -40198,7 +40198,7 @@
         <v>45456</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -40271,7 +40271,7 @@
         <v>46196</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -40344,7 +40344,7 @@
         <v>45198</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -40417,7 +40417,7 @@
         <v>45752</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -40495,7 +40495,7 @@
         <v>44735</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -40568,7 +40568,7 @@
         <v>46199</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -40641,7 +40641,7 @@
         <v>45153</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -40714,7 +40714,7 @@
         <v>45568</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -40787,7 +40787,7 @@
         <v>44970</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -40860,7 +40860,7 @@
         <v>44970</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -40933,7 +40933,7 @@
         <v>44641</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -41006,7 +41006,7 @@
         <v>45342</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -41084,7 +41084,7 @@
         <v>45737</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -41157,7 +41157,7 @@
         <v>45483</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -41230,7 +41230,7 @@
         <v>45061</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -41303,7 +41303,7 @@
         <v>44893</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -41376,7 +41376,7 @@
         <v>46209</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -41449,7 +41449,7 @@
         <v>46206</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -41522,7 +41522,7 @@
         <v>45084</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -41595,7 +41595,7 @@
         <v>44900</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -41668,7 +41668,7 @@
         <v>46161</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -41741,7 +41741,7 @@
         <v>45572</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -41814,7 +41814,7 @@
         <v>45002</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -41887,7 +41887,7 @@
         <v>44847</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -41960,7 +41960,7 @@
         <v>45432</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -42033,7 +42033,7 @@
         <v>45677</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -42106,7 +42106,7 @@
         <v>46261</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -42179,7 +42179,7 @@
         <v>46261</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -42252,7 +42252,7 @@
         <v>45253</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -42325,7 +42325,7 @@
         <v>45253</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -42398,7 +42398,7 @@
         <v>45104</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -42471,7 +42471,7 @@
         <v>46263</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -42544,7 +42544,7 @@
         <v>45715</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -42617,7 +42617,7 @@
         <v>45117</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -42690,7 +42690,7 @@
         <v>45357</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -42763,7 +42763,7 @@
         <v>45107</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -42836,7 +42836,7 @@
         <v>46224</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -42914,7 +42914,7 @@
         <v>45267</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -42987,7 +42987,7 @@
         <v>46268</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -43060,7 +43060,7 @@
         <v>46268</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -43133,7 +43133,7 @@
         <v>46268</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -43206,7 +43206,7 @@
         <v>44726</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -43279,7 +43279,7 @@
         <v>45351</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -43352,7 +43352,7 @@
         <v>45426</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -43425,7 +43425,7 @@
         <v>44872</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -43498,7 +43498,7 @@
         <v>45456</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -43571,7 +43571,7 @@
         <v>46273</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -43644,7 +43644,7 @@
         <v>46272</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -43717,7 +43717,7 @@
         <v>46272</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -43790,7 +43790,7 @@
         <v>45840</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -43868,7 +43868,7 @@
         <v>45091</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -43941,7 +43941,7 @@
         <v>46273</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -44014,7 +44014,7 @@
         <v>46279</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -44087,7 +44087,7 @@
         <v>46279</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -44160,7 +44160,7 @@
         <v>46279</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -44233,7 +44233,7 @@
         <v>46036</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -44306,7 +44306,7 @@
         <v>45462</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -44379,7 +44379,7 @@
         <v>45114</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -44452,7 +44452,7 @@
         <v>45225</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -44525,7 +44525,7 @@
         <v>45246</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -44598,7 +44598,7 @@
         <v>46281</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -44671,7 +44671,7 @@
         <v>45316</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -44749,7 +44749,7 @@
         <v>44601</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -44822,7 +44822,7 @@
         <v>46282</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -44895,7 +44895,7 @@
         <v>46241</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -44968,7 +44968,7 @@
         <v>44575</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -45041,7 +45041,7 @@
         <v>45170</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -45114,7 +45114,7 @@
         <v>45334</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -45187,7 +45187,7 @@
         <v>45169</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -45260,7 +45260,7 @@
         <v>44729</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -45333,7 +45333,7 @@
         <v>46273</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -45406,7 +45406,7 @@
         <v>46283</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -45479,7 +45479,7 @@
         <v>45939</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -45557,7 +45557,7 @@
         <v>46286</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -45630,7 +45630,7 @@
         <v>46281</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -45703,7 +45703,7 @@
         <v>46283</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -45776,7 +45776,7 @@
         <v>46030</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -45849,7 +45849,7 @@
         <v>46281</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -45922,7 +45922,7 @@
         <v>44796</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -45995,7 +45995,7 @@
         <v>44995</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -46068,7 +46068,7 @@
         <v>46283</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -46141,7 +46141,7 @@
         <v>46286</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -46214,7 +46214,7 @@
         <v>44951</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -46287,7 +46287,7 @@
         <v>45110</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -46360,7 +46360,7 @@
         <v>46224</v>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -46433,7 +46433,7 @@
         <v>45432</v>
       </c>
       <c r="E610" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -46506,7 +46506,7 @@
         <v>44530</v>
       </c>
       <c r="E611" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
@@ -46579,7 +46579,7 @@
         <v>44980</v>
       </c>
       <c r="E612" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
@@ -46652,7 +46652,7 @@
         <v>46247</v>
       </c>
       <c r="E613" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
@@ -46725,7 +46725,7 @@
         <v>45350</v>
       </c>
       <c r="E614" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F614" t="inlineStr">
         <is>
@@ -46798,7 +46798,7 @@
         <v>46245</v>
       </c>
       <c r="E615" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F615" t="inlineStr">
         <is>
@@ -46871,7 +46871,7 @@
         <v>45229</v>
       </c>
       <c r="E616" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F616" t="inlineStr">
         <is>
@@ -46944,7 +46944,7 @@
         <v>46292</v>
       </c>
       <c r="E617" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F617" t="inlineStr">
         <is>
@@ -47017,7 +47017,7 @@
         <v>45245</v>
       </c>
       <c r="E618" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F618" t="inlineStr">
         <is>
@@ -47090,7 +47090,7 @@
         <v>45531</v>
       </c>
       <c r="E619" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F619" t="inlineStr">
         <is>
@@ -47163,7 +47163,7 @@
         <v>45352</v>
       </c>
       <c r="E620" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F620" t="inlineStr">
         <is>
@@ -47236,7 +47236,7 @@
         <v>45208</v>
       </c>
       <c r="E621" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F621" t="inlineStr">
         <is>
@@ -47309,7 +47309,7 @@
         <v>45400</v>
       </c>
       <c r="E622" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F622" t="inlineStr">
         <is>
@@ -47382,7 +47382,7 @@
         <v>45110</v>
       </c>
       <c r="E623" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F623" t="inlineStr">
         <is>
@@ -47455,7 +47455,7 @@
         <v>46293</v>
       </c>
       <c r="E624" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F624" t="inlineStr">
         <is>
@@ -47528,7 +47528,7 @@
         <v>46292</v>
       </c>
       <c r="E625" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F625" t="inlineStr">
         <is>
@@ -47601,7 +47601,7 @@
         <v>44756</v>
       </c>
       <c r="E626" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F626" t="inlineStr">
         <is>
@@ -47674,7 +47674,7 @@
         <v>46248</v>
       </c>
       <c r="E627" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F627" t="inlineStr">
         <is>
@@ -47747,7 +47747,7 @@
         <v>45390</v>
       </c>
       <c r="E628" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F628" t="inlineStr">
         <is>
@@ -47820,7 +47820,7 @@
         <v>45238</v>
       </c>
       <c r="E629" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F629" t="inlineStr">
         <is>
@@ -47893,7 +47893,7 @@
         <v>46292</v>
       </c>
       <c r="E630" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F630" t="inlineStr">
         <is>
@@ -47966,7 +47966,7 @@
         <v>46248</v>
       </c>
       <c r="E631" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F631" t="inlineStr">
         <is>
@@ -48039,7 +48039,7 @@
         <v>46292</v>
       </c>
       <c r="E632" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F632" t="inlineStr">
         <is>
@@ -48112,7 +48112,7 @@
         <v>46292</v>
       </c>
       <c r="E633" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F633" t="inlineStr">
         <is>
@@ -48185,7 +48185,7 @@
         <v>46292</v>
       </c>
       <c r="E634" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F634" t="inlineStr">
         <is>
@@ -48258,7 +48258,7 @@
         <v>46292</v>
       </c>
       <c r="E635" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F635" t="inlineStr">
         <is>
@@ -48331,7 +48331,7 @@
         <v>46294</v>
       </c>
       <c r="E636" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F636" t="inlineStr">
         <is>
@@ -48409,7 +48409,7 @@
         <v>44866</v>
       </c>
       <c r="E637" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F637" t="inlineStr">
         <is>
@@ -48482,7 +48482,7 @@
         <v>45406</v>
       </c>
       <c r="E638" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F638" t="inlineStr">
         <is>
@@ -48555,7 +48555,7 @@
         <v>45414</v>
       </c>
       <c r="E639" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F639" t="inlineStr">
         <is>
@@ -48628,7 +48628,7 @@
         <v>45229</v>
       </c>
       <c r="E640" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F640" t="inlineStr">
         <is>
@@ -48701,7 +48701,7 @@
         <v>44651</v>
       </c>
       <c r="E641" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F641" t="inlineStr">
         <is>
@@ -48774,7 +48774,7 @@
         <v>45092</v>
       </c>
       <c r="E642" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F642" t="inlineStr">
         <is>
@@ -48847,7 +48847,7 @@
         <v>45455</v>
       </c>
       <c r="E643" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F643" t="inlineStr">
         <is>
@@ -48920,7 +48920,7 @@
         <v>45051</v>
       </c>
       <c r="E644" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F644" t="inlineStr">
         <is>
@@ -48993,7 +48993,7 @@
         <v>45770</v>
       </c>
       <c r="E645" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F645" t="inlineStr">
         <is>
@@ -49066,7 +49066,7 @@
         <v>46244</v>
       </c>
       <c r="E646" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F646" t="inlineStr">
         <is>
@@ -49139,7 +49139,7 @@
         <v>46295</v>
       </c>
       <c r="E647" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F647" t="inlineStr">
         <is>
@@ -49212,7 +49212,7 @@
         <v>45671</v>
       </c>
       <c r="E648" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F648" t="inlineStr">
         <is>
@@ -49285,7 +49285,7 @@
         <v>44813</v>
       </c>
       <c r="E649" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F649" t="inlineStr">
         <is>
@@ -49358,7 +49358,7 @@
         <v>45162</v>
       </c>
       <c r="E650" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F650" t="inlineStr">
         <is>
@@ -49431,7 +49431,7 @@
         <v>45254</v>
       </c>
       <c r="E651" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F651" t="inlineStr">
         <is>
@@ -49504,7 +49504,7 @@
         <v>44900</v>
       </c>
       <c r="E652" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F652" t="inlineStr">
         <is>
@@ -49577,7 +49577,7 @@
         <v>44893</v>
       </c>
       <c r="E653" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F653" t="inlineStr">
         <is>
@@ -49650,7 +49650,7 @@
         <v>45327</v>
       </c>
       <c r="E654" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F654" t="inlineStr">
         <is>
@@ -49723,7 +49723,7 @@
         <v>45624</v>
       </c>
       <c r="E655" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F655" t="inlineStr">
         <is>
@@ -49796,7 +49796,7 @@
         <v>44712</v>
       </c>
       <c r="E656" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F656" t="inlineStr">
         <is>
@@ -49869,7 +49869,7 @@
         <v>44834</v>
       </c>
       <c r="E657" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F657" t="inlineStr">
         <is>
@@ -49942,7 +49942,7 @@
         <v>45229</v>
       </c>
       <c r="E658" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F658" t="inlineStr">
         <is>
@@ -50015,7 +50015,7 @@
         <v>44967</v>
       </c>
       <c r="E659" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F659" t="inlineStr">
         <is>
@@ -50088,7 +50088,7 @@
         <v>45544</v>
       </c>
       <c r="E660" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F660" t="inlineStr">
         <is>
@@ -50161,7 +50161,7 @@
         <v>45715</v>
       </c>
       <c r="E661" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F661" t="inlineStr">
         <is>
@@ -50234,7 +50234,7 @@
         <v>45700</v>
       </c>
       <c r="E662" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F662" t="inlineStr">
         <is>
@@ -50307,7 +50307,7 @@
         <v>45316</v>
       </c>
       <c r="E663" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F663" t="inlineStr">
         <is>
@@ -50380,7 +50380,7 @@
         <v>45643</v>
       </c>
       <c r="E664" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F664" t="inlineStr">
         <is>
@@ -50453,7 +50453,7 @@
         <v>44900</v>
       </c>
       <c r="E665" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F665" t="inlineStr">
         <is>
@@ -50526,7 +50526,7 @@
         <v>45368</v>
       </c>
       <c r="E666" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F666" t="inlineStr">
         <is>
@@ -50604,7 +50604,7 @@
         <v>45371</v>
       </c>
       <c r="E667" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F667" t="inlineStr">
         <is>
@@ -50677,7 +50677,7 @@
         <v>45371</v>
       </c>
       <c r="E668" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F668" t="inlineStr">
         <is>
@@ -50750,7 +50750,7 @@
         <v>44477</v>
       </c>
       <c r="E669" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F669" t="inlineStr">
         <is>
@@ -50823,7 +50823,7 @@
         <v>45254</v>
       </c>
       <c r="E670" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F670" t="inlineStr">
         <is>
@@ -50896,7 +50896,7 @@
         <v>45229</v>
       </c>
       <c r="E671" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F671" t="inlineStr">
         <is>
@@ -50969,7 +50969,7 @@
         <v>45035</v>
       </c>
       <c r="E672" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F672" t="inlineStr">
         <is>
@@ -51042,7 +51042,7 @@
         <v>45299</v>
       </c>
       <c r="E673" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F673" t="inlineStr">
         <is>
@@ -51115,7 +51115,7 @@
         <v>45176</v>
       </c>
       <c r="E674" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F674" t="inlineStr">
         <is>
@@ -51193,7 +51193,7 @@
         <v>45638</v>
       </c>
       <c r="E675" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F675" t="inlineStr">
         <is>
@@ -51266,7 +51266,7 @@
         <v>45588</v>
       </c>
       <c r="E676" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F676" t="inlineStr">
         <is>
@@ -51344,7 +51344,7 @@
         <v>45510</v>
       </c>
       <c r="E677" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F677" t="inlineStr">
         <is>
@@ -51417,7 +51417,7 @@
         <v>45559</v>
       </c>
       <c r="E678" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F678" t="inlineStr">
         <is>
@@ -51490,7 +51490,7 @@
         <v>45783</v>
       </c>
       <c r="E679" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F679" t="inlineStr">
         <is>
@@ -51563,7 +51563,7 @@
         <v>45616</v>
       </c>
       <c r="E680" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F680" t="inlineStr">
         <is>
@@ -51636,7 +51636,7 @@
         <v>45483</v>
       </c>
       <c r="E681" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F681" t="inlineStr">
         <is>
@@ -51709,7 +51709,7 @@
         <v>45680</v>
       </c>
       <c r="E682" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F682" t="inlineStr">
         <is>
@@ -51782,7 +51782,7 @@
         <v>45616</v>
       </c>
       <c r="E683" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F683" t="inlineStr">
         <is>
@@ -51855,7 +51855,7 @@
         <v>45614</v>
       </c>
       <c r="E684" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F684" t="inlineStr">
         <is>
@@ -51933,7 +51933,7 @@
         <v>44631</v>
       </c>
       <c r="E685" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F685" t="inlineStr">
         <is>
@@ -52006,7 +52006,7 @@
         <v>44743</v>
       </c>
       <c r="E686" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F686" t="inlineStr">
         <is>
@@ -52079,7 +52079,7 @@
         <v>45375</v>
       </c>
       <c r="E687" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F687" t="inlineStr">
         <is>
@@ -52152,7 +52152,7 @@
         <v>44488</v>
       </c>
       <c r="E688" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F688" t="inlineStr">
         <is>
@@ -52225,7 +52225,7 @@
         <v>45604</v>
       </c>
       <c r="E689" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F689" t="inlineStr">
         <is>
@@ -52298,7 +52298,7 @@
         <v>45356</v>
       </c>
       <c r="E690" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F690" t="inlineStr">
         <is>
@@ -52371,7 +52371,7 @@
         <v>44613</v>
       </c>
       <c r="E691" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F691" t="inlineStr">
         <is>
@@ -52444,7 +52444,7 @@
         <v>45349</v>
       </c>
       <c r="E692" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F692" t="inlineStr">
         <is>
@@ -52517,7 +52517,7 @@
         <v>44608</v>
       </c>
       <c r="E693" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F693" t="inlineStr">
         <is>
@@ -52590,7 +52590,7 @@
         <v>44631</v>
       </c>
       <c r="E694" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F694" t="inlineStr">
         <is>
@@ -52663,7 +52663,7 @@
         <v>44631</v>
       </c>
       <c r="E695" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F695" t="inlineStr">
         <is>
@@ -52736,7 +52736,7 @@
         <v>45744</v>
       </c>
       <c r="E696" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F696" t="inlineStr">
         <is>
@@ -52809,7 +52809,7 @@
         <v>45714</v>
       </c>
       <c r="E697" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F697" t="inlineStr">
         <is>
@@ -52882,7 +52882,7 @@
         <v>45715</v>
       </c>
       <c r="E698" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F698" t="inlineStr">
         <is>
@@ -52955,7 +52955,7 @@
         <v>45709</v>
       </c>
       <c r="E699" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F699" t="inlineStr">
         <is>
@@ -53028,7 +53028,7 @@
         <v>45714</v>
       </c>
       <c r="E700" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F700" t="inlineStr">
         <is>
@@ -53101,7 +53101,7 @@
         <v>45813</v>
       </c>
       <c r="E701" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F701" t="inlineStr">
         <is>
@@ -53174,7 +53174,7 @@
         <v>45813</v>
       </c>
       <c r="E702" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F702" t="inlineStr">
         <is>
@@ -53247,7 +53247,7 @@
         <v>45813</v>
       </c>
       <c r="E703" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F703" t="inlineStr">
         <is>
@@ -53320,7 +53320,7 @@
         <v>45820</v>
       </c>
       <c r="E704" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F704" t="inlineStr">
         <is>
@@ -53393,7 +53393,7 @@
         <v>45827</v>
       </c>
       <c r="E705" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F705" t="inlineStr">
         <is>
@@ -53466,7 +53466,7 @@
         <v>45845</v>
       </c>
       <c r="E706" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F706" t="inlineStr">
         <is>
@@ -53539,7 +53539,7 @@
         <v>45883</v>
       </c>
       <c r="E707" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F707" t="inlineStr">
         <is>
@@ -53612,7 +53612,7 @@
         <v>45915</v>
       </c>
       <c r="E708" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F708" t="inlineStr">
         <is>
@@ -53685,7 +53685,7 @@
         <v>46041</v>
       </c>
       <c r="E709" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F709" t="inlineStr">
         <is>
@@ -53758,7 +53758,7 @@
         <v>46133</v>
       </c>
       <c r="E710" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F710" t="inlineStr">
         <is>
@@ -53831,7 +53831,7 @@
         <v>46147</v>
       </c>
       <c r="E711" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F711" t="inlineStr">
         <is>
@@ -53904,7 +53904,7 @@
         <v>46211</v>
       </c>
       <c r="E712" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F712" t="inlineStr">
         <is>
@@ -53977,7 +53977,7 @@
         <v>46290</v>
       </c>
       <c r="E713" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F713" t="inlineStr">
         <is>
@@ -54050,7 +54050,7 @@
         <v>46253</v>
       </c>
       <c r="E714" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F714" t="inlineStr">
         <is>

--- a/Översikt HYLTE.xlsx
+++ b/Översikt HYLTE.xlsx
@@ -601,7 +601,7 @@
         <v>46090</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -718,7 +718,7 @@
         <v>45265</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -834,7 +834,7 @@
         <v>46066</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -945,7 +945,7 @@
         <v>44873</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1054,7 +1054,7 @@
         <v>45348</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1166,7 +1166,7 @@
         <v>45719</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1274,7 +1274,7 @@
         <v>45245</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1385,7 +1385,7 @@
         <v>46268</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1492,7 +1492,7 @@
         <v>45230</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1599,7 +1599,7 @@
         <v>45737</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1706,7 +1706,7 @@
         <v>46141</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1813,7 +1813,7 @@
         <v>46161</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1920,7 +1920,7 @@
         <v>44839</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2030,7 +2030,7 @@
         <v>45841</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2140,7 +2140,7 @@
         <v>45099</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2250,7 +2250,7 @@
         <v>46048</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2356,7 +2356,7 @@
         <v>45904</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2466,7 +2466,7 @@
         <v>46304</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2576,7 +2576,7 @@
         <v>46130</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2682,7 +2682,7 @@
         <v>44648</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2787,7 +2787,7 @@
         <v>44651</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2892,7 +2892,7 @@
         <v>44876</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2997,7 +2997,7 @@
         <v>45593</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3102,7 +3102,7 @@
         <v>45245</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3207,7 +3207,7 @@
         <v>45299</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3316,7 +3316,7 @@
         <v>45617</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3421,7 +3421,7 @@
         <v>45343</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3526,7 +3526,7 @@
         <v>45476</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3636,7 +3636,7 @@
         <v>45085</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3745,7 +3745,7 @@
         <v>45153</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3859,7 +3859,7 @@
         <v>45163</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3964,7 +3964,7 @@
         <v>45186</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4069,7 +4069,7 @@
         <v>45245</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4174,7 +4174,7 @@
         <v>45253</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4279,7 +4279,7 @@
         <v>45754</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4384,7 +4384,7 @@
         <v>46253</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4494,7 +4494,7 @@
         <v>44810</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4567,7 +4567,7 @@
         <v>44481</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4640,7 +4640,7 @@
         <v>44600</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4713,7 +4713,7 @@
         <v>44529</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4786,7 +4786,7 @@
         <v>44557</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4859,7 +4859,7 @@
         <v>44705</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4932,7 +4932,7 @@
         <v>44483</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5005,7 +5005,7 @@
         <v>44778</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5078,7 +5078,7 @@
         <v>44488</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5151,7 +5151,7 @@
         <v>44624</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5224,7 +5224,7 @@
         <v>44812</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5297,7 +5297,7 @@
         <v>44638</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5370,7 +5370,7 @@
         <v>44498</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5443,7 +5443,7 @@
         <v>44845</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5516,7 +5516,7 @@
         <v>44559</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5589,7 +5589,7 @@
         <v>44659</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5667,7 +5667,7 @@
         <v>44578</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5740,7 +5740,7 @@
         <v>44756</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5813,7 +5813,7 @@
         <v>44501</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5886,7 +5886,7 @@
         <v>44651</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5959,7 +5959,7 @@
         <v>44711</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6032,7 +6032,7 @@
         <v>44487</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6110,7 +6110,7 @@
         <v>44714</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6183,7 +6183,7 @@
         <v>44834</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6256,7 +6256,7 @@
         <v>44735</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6329,7 +6329,7 @@
         <v>44482</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6402,7 +6402,7 @@
         <v>44482</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6475,7 +6475,7 @@
         <v>44867</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6548,7 +6548,7 @@
         <v>44505</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6621,7 +6621,7 @@
         <v>44796</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6694,7 +6694,7 @@
         <v>44795</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6767,7 +6767,7 @@
         <v>44634</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6840,7 +6840,7 @@
         <v>44502</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6913,7 +6913,7 @@
         <v>44818</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6986,7 +6986,7 @@
         <v>44489</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7059,7 +7059,7 @@
         <v>44631</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7132,7 +7132,7 @@
         <v>44801</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7205,7 +7205,7 @@
         <v>44876</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7278,7 +7278,7 @@
         <v>44659</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7351,7 +7351,7 @@
         <v>44596</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7429,7 +7429,7 @@
         <v>44644</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7502,7 +7502,7 @@
         <v>44728</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7575,7 +7575,7 @@
         <v>44515</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7653,7 +7653,7 @@
         <v>44644</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7726,7 +7726,7 @@
         <v>44523</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7799,7 +7799,7 @@
         <v>44500</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7872,7 +7872,7 @@
         <v>44727</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7945,7 +7945,7 @@
         <v>44900</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8018,7 +8018,7 @@
         <v>44778</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8091,7 +8091,7 @@
         <v>44705</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8164,7 +8164,7 @@
         <v>44659</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8242,7 +8242,7 @@
         <v>44659</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8320,7 +8320,7 @@
         <v>44900</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8393,7 +8393,7 @@
         <v>44757</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8466,7 +8466,7 @@
         <v>44866</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8539,7 +8539,7 @@
         <v>44494</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8612,7 +8612,7 @@
         <v>45091</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8685,7 +8685,7 @@
         <v>45002</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8758,7 +8758,7 @@
         <v>45331</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8831,7 +8831,7 @@
         <v>45684</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8904,7 +8904,7 @@
         <v>44495</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8977,7 +8977,7 @@
         <v>44847</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -9050,7 +9050,7 @@
         <v>45254</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9123,7 +9123,7 @@
         <v>45254</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9196,7 +9196,7 @@
         <v>45342</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9274,7 +9274,7 @@
         <v>44872</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9347,7 +9347,7 @@
         <v>45477</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9420,7 +9420,7 @@
         <v>45371</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9493,7 +9493,7 @@
         <v>44953</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9566,7 +9566,7 @@
         <v>45390</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9639,7 +9639,7 @@
         <v>44869</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9712,7 +9712,7 @@
         <v>45096</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9785,7 +9785,7 @@
         <v>44900</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9863,7 +9863,7 @@
         <v>45104</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9936,7 +9936,7 @@
         <v>45624</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -10009,7 +10009,7 @@
         <v>45042</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -10082,7 +10082,7 @@
         <v>45169</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10155,7 +10155,7 @@
         <v>45229</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10228,7 +10228,7 @@
         <v>45327</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10301,7 +10301,7 @@
         <v>45770</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10374,7 +10374,7 @@
         <v>45441</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10447,7 +10447,7 @@
         <v>45441</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10520,7 +10520,7 @@
         <v>45674</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10593,7 +10593,7 @@
         <v>45035</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10666,7 +10666,7 @@
         <v>45229</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10739,7 +10739,7 @@
         <v>44635</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -10817,7 +10817,7 @@
         <v>45441</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10890,7 +10890,7 @@
         <v>45254</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10963,7 +10963,7 @@
         <v>45254</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -11036,7 +11036,7 @@
         <v>45752</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -11114,7 +11114,7 @@
         <v>45700</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11187,7 +11187,7 @@
         <v>45110</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11260,7 +11260,7 @@
         <v>45378</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11333,7 +11333,7 @@
         <v>45382</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11406,7 +11406,7 @@
         <v>45061</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11479,7 +11479,7 @@
         <v>45084</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11552,7 +11552,7 @@
         <v>45456</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11625,7 +11625,7 @@
         <v>45253</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11698,7 +11698,7 @@
         <v>45229</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -11771,7 +11771,7 @@
         <v>45170</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -11844,7 +11844,7 @@
         <v>45299</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -11917,7 +11917,7 @@
         <v>45310</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -11990,7 +11990,7 @@
         <v>45208</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -12063,7 +12063,7 @@
         <v>45254</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -12136,7 +12136,7 @@
         <v>45252</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12209,7 +12209,7 @@
         <v>45694</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12282,7 +12282,7 @@
         <v>44750</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12355,7 +12355,7 @@
         <v>45368</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12433,7 +12433,7 @@
         <v>45406</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -12506,7 +12506,7 @@
         <v>44967</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -12579,7 +12579,7 @@
         <v>45110</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -12652,7 +12652,7 @@
         <v>44893</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -12725,7 +12725,7 @@
         <v>45145</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -12798,7 +12798,7 @@
         <v>45117</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -12871,7 +12871,7 @@
         <v>45352</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -12944,7 +12944,7 @@
         <v>45541</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -13017,7 +13017,7 @@
         <v>45527</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -13090,7 +13090,7 @@
         <v>44482</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -13163,7 +13163,7 @@
         <v>45097</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13236,7 +13236,7 @@
         <v>45062</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13309,7 +13309,7 @@
         <v>45478</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13382,7 +13382,7 @@
         <v>45834</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -13455,7 +13455,7 @@
         <v>45371</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -13528,7 +13528,7 @@
         <v>45405</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -13601,7 +13601,7 @@
         <v>45600</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -13674,7 +13674,7 @@
         <v>44495</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -13747,7 +13747,7 @@
         <v>44487</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -13825,7 +13825,7 @@
         <v>45840</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -13898,7 +13898,7 @@
         <v>45436</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -13971,7 +13971,7 @@
         <v>44868</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -14044,7 +14044,7 @@
         <v>45673</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -14117,7 +14117,7 @@
         <v>44950</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -14190,7 +14190,7 @@
         <v>45299</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14263,7 +14263,7 @@
         <v>44530</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14336,7 +14336,7 @@
         <v>45104</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -14409,7 +14409,7 @@
         <v>45737</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -14482,7 +14482,7 @@
         <v>45454</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -14555,7 +14555,7 @@
         <v>44601</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -14628,7 +14628,7 @@
         <v>45258</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -14701,7 +14701,7 @@
         <v>45485</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -14774,7 +14774,7 @@
         <v>45462</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -14847,7 +14847,7 @@
         <v>44510</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -14920,7 +14920,7 @@
         <v>45890</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -14993,7 +14993,7 @@
         <v>45748</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -15066,7 +15066,7 @@
         <v>45891</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -15144,7 +15144,7 @@
         <v>45891</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -15222,7 +15222,7 @@
         <v>45352</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -15295,7 +15295,7 @@
         <v>45560</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -15368,7 +15368,7 @@
         <v>44865</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -15441,7 +15441,7 @@
         <v>45897</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -15514,7 +15514,7 @@
         <v>45897</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -15587,7 +15587,7 @@
         <v>45089</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -15660,7 +15660,7 @@
         <v>45839</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -15733,7 +15733,7 @@
         <v>45300</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -15806,7 +15806,7 @@
         <v>45352</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -15879,7 +15879,7 @@
         <v>45898</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -15952,7 +15952,7 @@
         <v>45352</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -16025,7 +16025,7 @@
         <v>44834</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -16098,7 +16098,7 @@
         <v>45182</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -16171,7 +16171,7 @@
         <v>45539</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -16244,7 +16244,7 @@
         <v>45253</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -16317,7 +16317,7 @@
         <v>45377</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -16395,7 +16395,7 @@
         <v>44896</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -16468,7 +16468,7 @@
         <v>45905</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -16541,7 +16541,7 @@
         <v>45531</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -16614,7 +16614,7 @@
         <v>45176</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -16692,7 +16692,7 @@
         <v>45429</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -16765,7 +16765,7 @@
         <v>45910</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -16838,7 +16838,7 @@
         <v>45638</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -16911,7 +16911,7 @@
         <v>45910</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -16984,7 +16984,7 @@
         <v>45838</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -17057,7 +17057,7 @@
         <v>45715</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -17130,7 +17130,7 @@
         <v>45182</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -17203,7 +17203,7 @@
         <v>45588</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -17281,7 +17281,7 @@
         <v>45414</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -17354,7 +17354,7 @@
         <v>44489</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -17427,7 +17427,7 @@
         <v>45366</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -17500,7 +17500,7 @@
         <v>45538</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -17573,7 +17573,7 @@
         <v>45643</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -17646,7 +17646,7 @@
         <v>45114</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -17719,7 +17719,7 @@
         <v>45616</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -17792,7 +17792,7 @@
         <v>45918</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -17865,7 +17865,7 @@
         <v>45391</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -17938,7 +17938,7 @@
         <v>45510</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -18011,7 +18011,7 @@
         <v>44970</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -18084,7 +18084,7 @@
         <v>45783</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -18157,7 +18157,7 @@
         <v>45616</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -18230,7 +18230,7 @@
         <v>45538</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -18303,7 +18303,7 @@
         <v>45786</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -18381,7 +18381,7 @@
         <v>45559</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -18454,7 +18454,7 @@
         <v>45680</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -18527,7 +18527,7 @@
         <v>45922</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -18600,7 +18600,7 @@
         <v>45671</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -18673,7 +18673,7 @@
         <v>45225</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -18746,7 +18746,7 @@
         <v>45589</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -18824,7 +18824,7 @@
         <v>45618</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -18897,7 +18897,7 @@
         <v>45170</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -18970,7 +18970,7 @@
         <v>45922</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -19043,7 +19043,7 @@
         <v>45462</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -19116,7 +19116,7 @@
         <v>45558</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -19189,7 +19189,7 @@
         <v>45922</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -19262,7 +19262,7 @@
         <v>45726</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -19335,7 +19335,7 @@
         <v>45741</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -19408,7 +19408,7 @@
         <v>45483</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -19481,7 +19481,7 @@
         <v>45609</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -19554,7 +19554,7 @@
         <v>45170</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -19627,7 +19627,7 @@
         <v>45924</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -19700,7 +19700,7 @@
         <v>45926</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -19773,7 +19773,7 @@
         <v>45926</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -19846,7 +19846,7 @@
         <v>45926</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -19919,7 +19919,7 @@
         <v>45483</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -19992,7 +19992,7 @@
         <v>45743</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -20070,7 +20070,7 @@
         <v>45590</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -20143,7 +20143,7 @@
         <v>45929</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -20216,7 +20216,7 @@
         <v>44719</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -20289,7 +20289,7 @@
         <v>45743</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -20367,7 +20367,7 @@
         <v>45604</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -20440,7 +20440,7 @@
         <v>45091</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -20513,7 +20513,7 @@
         <v>45559</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -20586,7 +20586,7 @@
         <v>45681</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -20659,7 +20659,7 @@
         <v>45743</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -20737,7 +20737,7 @@
         <v>44851</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -20810,7 +20810,7 @@
         <v>45931</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -20883,7 +20883,7 @@
         <v>45597</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -20956,7 +20956,7 @@
         <v>45793</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -21029,7 +21029,7 @@
         <v>44701</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -21107,7 +21107,7 @@
         <v>45931</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -21180,7 +21180,7 @@
         <v>45259</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -21253,7 +21253,7 @@
         <v>44714</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -21326,7 +21326,7 @@
         <v>44641</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -21399,7 +21399,7 @@
         <v>45930</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -21472,7 +21472,7 @@
         <v>44974</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -21545,7 +21545,7 @@
         <v>45432</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -21618,7 +21618,7 @@
         <v>45159</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -21691,7 +21691,7 @@
         <v>45933</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -21764,7 +21764,7 @@
         <v>45229</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -21837,7 +21837,7 @@
         <v>45936</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -21910,7 +21910,7 @@
         <v>45936</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -21983,7 +21983,7 @@
         <v>45198</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -22056,7 +22056,7 @@
         <v>45933</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -22129,7 +22129,7 @@
         <v>45933</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -22202,7 +22202,7 @@
         <v>44481</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -22275,7 +22275,7 @@
         <v>45456</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -22348,7 +22348,7 @@
         <v>45936</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -22421,7 +22421,7 @@
         <v>44900</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -22494,7 +22494,7 @@
         <v>45366</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -22572,7 +22572,7 @@
         <v>45441</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -22645,7 +22645,7 @@
         <v>44926</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -22723,7 +22723,7 @@
         <v>44697</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -22796,7 +22796,7 @@
         <v>44756</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -22869,7 +22869,7 @@
         <v>45162</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -22942,7 +22942,7 @@
         <v>45162</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -23015,7 +23015,7 @@
         <v>45268</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -23088,7 +23088,7 @@
         <v>45194</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -23161,7 +23161,7 @@
         <v>44903</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -23234,7 +23234,7 @@
         <v>45937</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -23307,7 +23307,7 @@
         <v>45806</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -23380,7 +23380,7 @@
         <v>44999</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -23453,7 +23453,7 @@
         <v>45938</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -23526,7 +23526,7 @@
         <v>45609</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -23599,7 +23599,7 @@
         <v>45203</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -23672,7 +23672,7 @@
         <v>45812</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -23745,7 +23745,7 @@
         <v>45944</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -23818,7 +23818,7 @@
         <v>45677</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -23891,7 +23891,7 @@
         <v>45730</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -23964,7 +23964,7 @@
         <v>45132</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -24037,7 +24037,7 @@
         <v>45694</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -24110,7 +24110,7 @@
         <v>45597</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -24183,7 +24183,7 @@
         <v>45708</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -24256,7 +24256,7 @@
         <v>45387</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -24329,7 +24329,7 @@
         <v>45254</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -24402,7 +24402,7 @@
         <v>45706</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -24475,7 +24475,7 @@
         <v>45820</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -24548,7 +24548,7 @@
         <v>45460</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -24621,7 +24621,7 @@
         <v>44965</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -24699,7 +24699,7 @@
         <v>44900</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -24772,7 +24772,7 @@
         <v>45173</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -24845,7 +24845,7 @@
         <v>45153</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -24918,7 +24918,7 @@
         <v>44970</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -24991,7 +24991,7 @@
         <v>44970</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -25064,7 +25064,7 @@
         <v>45825</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -25137,7 +25137,7 @@
         <v>45084</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -25210,7 +25210,7 @@
         <v>45254</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -25283,7 +25283,7 @@
         <v>45211</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -25356,7 +25356,7 @@
         <v>45568</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -25429,7 +25429,7 @@
         <v>45107</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -25502,7 +25502,7 @@
         <v>45441</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -25580,7 +25580,7 @@
         <v>45548</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -25653,7 +25653,7 @@
         <v>45456</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -25726,7 +25726,7 @@
         <v>45831</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -25799,7 +25799,7 @@
         <v>45456</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -25872,7 +25872,7 @@
         <v>45092</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -25945,7 +25945,7 @@
         <v>45957</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -26018,7 +26018,7 @@
         <v>45229</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -26091,7 +26091,7 @@
         <v>45751</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -26169,7 +26169,7 @@
         <v>45002</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -26242,7 +26242,7 @@
         <v>45225</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -26315,7 +26315,7 @@
         <v>45601</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -26388,7 +26388,7 @@
         <v>45107</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -26461,7 +26461,7 @@
         <v>45961</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -26534,7 +26534,7 @@
         <v>45181</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -26607,7 +26607,7 @@
         <v>45961</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -26680,7 +26680,7 @@
         <v>45645</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -26753,7 +26753,7 @@
         <v>44823</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -26826,7 +26826,7 @@
         <v>45835</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -26899,7 +26899,7 @@
         <v>45836</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -26972,7 +26972,7 @@
         <v>45238</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -27045,7 +27045,7 @@
         <v>45145</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -27118,7 +27118,7 @@
         <v>45922</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -27191,7 +27191,7 @@
         <v>45838</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -27264,7 +27264,7 @@
         <v>45840</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -27337,7 +27337,7 @@
         <v>45840</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -27410,7 +27410,7 @@
         <v>45840</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -27483,7 +27483,7 @@
         <v>45287</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -27556,7 +27556,7 @@
         <v>44701</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -27634,7 +27634,7 @@
         <v>44735</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -27707,7 +27707,7 @@
         <v>44651</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -27780,7 +27780,7 @@
         <v>45169</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -27853,7 +27853,7 @@
         <v>45638</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -27926,7 +27926,7 @@
         <v>45972</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -27999,7 +27999,7 @@
         <v>45972</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -28072,7 +28072,7 @@
         <v>45972</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -28145,7 +28145,7 @@
         <v>45568</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -28218,7 +28218,7 @@
         <v>45845</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -28291,7 +28291,7 @@
         <v>45845</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -28364,7 +28364,7 @@
         <v>45800</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -28437,7 +28437,7 @@
         <v>45846</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -28515,7 +28515,7 @@
         <v>45846</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -28593,7 +28593,7 @@
         <v>45846</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -28671,7 +28671,7 @@
         <v>44712</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -28744,7 +28744,7 @@
         <v>45316</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -28822,7 +28822,7 @@
         <v>45167</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -28895,7 +28895,7 @@
         <v>45847</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -28968,7 +28968,7 @@
         <v>45254</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -29041,7 +29041,7 @@
         <v>45254</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -29114,7 +29114,7 @@
         <v>45245</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -29187,7 +29187,7 @@
         <v>45847</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -29260,7 +29260,7 @@
         <v>45803</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -29333,7 +29333,7 @@
         <v>44778</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -29406,7 +29406,7 @@
         <v>44729</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -29479,7 +29479,7 @@
         <v>45483</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -29552,7 +29552,7 @@
         <v>44847</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -29625,7 +29625,7 @@
         <v>44980</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -29698,7 +29698,7 @@
         <v>45246</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -29771,7 +29771,7 @@
         <v>44694</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -29844,7 +29844,7 @@
         <v>45715</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -29917,7 +29917,7 @@
         <v>45700</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -29990,7 +29990,7 @@
         <v>45700</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -30063,7 +30063,7 @@
         <v>45687</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -30136,7 +30136,7 @@
         <v>45245</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -30209,7 +30209,7 @@
         <v>45092</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -30282,7 +30282,7 @@
         <v>45051</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -30355,7 +30355,7 @@
         <v>45838</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -30428,7 +30428,7 @@
         <v>45544</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -30501,7 +30501,7 @@
         <v>45098</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -30579,7 +30579,7 @@
         <v>45979</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -30652,7 +30652,7 @@
         <v>45351</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -30725,7 +30725,7 @@
         <v>44797</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -30798,7 +30798,7 @@
         <v>45288</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -30876,7 +30876,7 @@
         <v>45309</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -30949,7 +30949,7 @@
         <v>45407</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -31022,7 +31022,7 @@
         <v>45677</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -31095,7 +31095,7 @@
         <v>45257</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -31168,7 +31168,7 @@
         <v>45395</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -31241,7 +31241,7 @@
         <v>44671</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -31314,7 +31314,7 @@
         <v>45524</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -31387,7 +31387,7 @@
         <v>45272</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -31460,7 +31460,7 @@
         <v>44483</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -31533,7 +31533,7 @@
         <v>45267</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -31606,7 +31606,7 @@
         <v>45245</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -31679,7 +31679,7 @@
         <v>45679</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -31752,7 +31752,7 @@
         <v>45610</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -31825,7 +31825,7 @@
         <v>45432</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -31898,7 +31898,7 @@
         <v>44712</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -31971,7 +31971,7 @@
         <v>45131</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -32044,7 +32044,7 @@
         <v>45176</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -32117,7 +32117,7 @@
         <v>45372</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -32190,7 +32190,7 @@
         <v>45361</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -32263,7 +32263,7 @@
         <v>45541</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -32336,7 +32336,7 @@
         <v>45257</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -32414,7 +32414,7 @@
         <v>45727</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -32487,7 +32487,7 @@
         <v>44974</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -32560,7 +32560,7 @@
         <v>44917</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -32633,7 +32633,7 @@
         <v>45735</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -32706,7 +32706,7 @@
         <v>45672</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -32779,7 +32779,7 @@
         <v>45204</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -32852,7 +32852,7 @@
         <v>45293</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -32925,7 +32925,7 @@
         <v>45245</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -32998,7 +32998,7 @@
         <v>44671</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -33071,7 +33071,7 @@
         <v>44896</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -33144,7 +33144,7 @@
         <v>44592</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -33217,7 +33217,7 @@
         <v>45293</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -33290,7 +33290,7 @@
         <v>45623</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -33363,7 +33363,7 @@
         <v>45199</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -33436,7 +33436,7 @@
         <v>45769</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -33509,7 +33509,7 @@
         <v>45392</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -33582,7 +33582,7 @@
         <v>45395</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -33655,7 +33655,7 @@
         <v>45229</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -33728,7 +33728,7 @@
         <v>45589</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -33801,7 +33801,7 @@
         <v>45546</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -33874,7 +33874,7 @@
         <v>44701</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -33947,7 +33947,7 @@
         <v>45145</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -34020,7 +34020,7 @@
         <v>45517</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -34093,7 +34093,7 @@
         <v>45230</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -34166,7 +34166,7 @@
         <v>45677</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -34239,7 +34239,7 @@
         <v>45672</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -34312,7 +34312,7 @@
         <v>45672</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -34385,7 +34385,7 @@
         <v>44483</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -34458,7 +34458,7 @@
         <v>44964</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -34531,7 +34531,7 @@
         <v>45735</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -34604,7 +34604,7 @@
         <v>44739</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -34677,7 +34677,7 @@
         <v>45309</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -34750,7 +34750,7 @@
         <v>44508</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -34823,7 +34823,7 @@
         <v>45623</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -34896,7 +34896,7 @@
         <v>45252</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -34969,7 +34969,7 @@
         <v>45589</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -35042,7 +35042,7 @@
         <v>45190</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -35115,7 +35115,7 @@
         <v>44817</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -35188,7 +35188,7 @@
         <v>45574</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -35261,7 +35261,7 @@
         <v>45545</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -35334,7 +35334,7 @@
         <v>45199</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -35407,7 +35407,7 @@
         <v>45190</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -35485,7 +35485,7 @@
         <v>44889</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -35558,7 +35558,7 @@
         <v>45623</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -35631,7 +35631,7 @@
         <v>45880</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -35704,7 +35704,7 @@
         <v>45880</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -35777,7 +35777,7 @@
         <v>45502</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -35850,7 +35850,7 @@
         <v>44559</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -35923,7 +35923,7 @@
         <v>45877</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -35996,7 +35996,7 @@
         <v>45880</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -36069,7 +36069,7 @@
         <v>44893</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -36142,7 +36142,7 @@
         <v>45880</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -36215,7 +36215,7 @@
         <v>45981</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -36288,7 +36288,7 @@
         <v>45981</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -36361,7 +36361,7 @@
         <v>44910</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -36434,7 +36434,7 @@
         <v>45455</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -36507,7 +36507,7 @@
         <v>45104</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -36580,7 +36580,7 @@
         <v>45334</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -36653,7 +36653,7 @@
         <v>45352</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -36726,7 +36726,7 @@
         <v>46057</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -36799,7 +36799,7 @@
         <v>45715</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -36872,7 +36872,7 @@
         <v>45316</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -36945,7 +36945,7 @@
         <v>45987</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -37018,7 +37018,7 @@
         <v>44796</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -37091,7 +37091,7 @@
         <v>46057</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -37164,7 +37164,7 @@
         <v>45019</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -37237,7 +37237,7 @@
         <v>45257</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -37310,7 +37310,7 @@
         <v>46111</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -37383,7 +37383,7 @@
         <v>44901</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -37456,7 +37456,7 @@
         <v>45589</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -37529,7 +37529,7 @@
         <v>46111</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -37602,7 +37602,7 @@
         <v>45989</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -37675,7 +37675,7 @@
         <v>46111</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -37748,7 +37748,7 @@
         <v>45754</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -37821,7 +37821,7 @@
         <v>44899</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -37894,7 +37894,7 @@
         <v>46121</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -37967,7 +37967,7 @@
         <v>46120</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -38040,7 +38040,7 @@
         <v>46121</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -38113,7 +38113,7 @@
         <v>46121</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -38186,7 +38186,7 @@
         <v>46121</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -38259,7 +38259,7 @@
         <v>46121</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -38332,7 +38332,7 @@
         <v>46120</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -38405,7 +38405,7 @@
         <v>46121</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -38478,7 +38478,7 @@
         <v>46121</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -38551,7 +38551,7 @@
         <v>44995</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -38624,7 +38624,7 @@
         <v>45548</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -38697,7 +38697,7 @@
         <v>46122</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -38770,7 +38770,7 @@
         <v>45995</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -38843,7 +38843,7 @@
         <v>46122</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -38916,7 +38916,7 @@
         <v>44958</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -38989,7 +38989,7 @@
         <v>46122</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -39062,7 +39062,7 @@
         <v>46122</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -39135,7 +39135,7 @@
         <v>46121</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -39208,7 +39208,7 @@
         <v>44575</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -39281,7 +39281,7 @@
         <v>45572</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -39354,7 +39354,7 @@
         <v>46128</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -39427,7 +39427,7 @@
         <v>44951</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -39500,7 +39500,7 @@
         <v>45265</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -39573,7 +39573,7 @@
         <v>45351</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -39646,7 +39646,7 @@
         <v>45432</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -39719,7 +39719,7 @@
         <v>45926</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -39792,7 +39792,7 @@
         <v>45790</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -39865,7 +39865,7 @@
         <v>45132</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -39938,7 +39938,7 @@
         <v>45246</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -40011,7 +40011,7 @@
         <v>45246</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -40084,7 +40084,7 @@
         <v>45426</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -40157,7 +40157,7 @@
         <v>45371</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -40230,7 +40230,7 @@
         <v>45411</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -40303,7 +40303,7 @@
         <v>45840</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -40381,7 +40381,7 @@
         <v>44539</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -40454,7 +40454,7 @@
         <v>46020</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -40527,7 +40527,7 @@
         <v>45441</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -40605,7 +40605,7 @@
         <v>45775</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -40678,7 +40678,7 @@
         <v>45624</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -40751,7 +40751,7 @@
         <v>45782</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -40824,7 +40824,7 @@
         <v>44699</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -40897,7 +40897,7 @@
         <v>45524</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -40970,7 +40970,7 @@
         <v>45580</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -41043,7 +41043,7 @@
         <v>45568</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -41116,7 +41116,7 @@
         <v>45989</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -41189,7 +41189,7 @@
         <v>46084</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -41262,7 +41262,7 @@
         <v>44714</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -41340,7 +41340,7 @@
         <v>44813</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -41413,7 +41413,7 @@
         <v>45163</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -41486,7 +41486,7 @@
         <v>44851</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -41559,7 +41559,7 @@
         <v>44851</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -41632,7 +41632,7 @@
         <v>45035</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -41705,7 +41705,7 @@
         <v>44726</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -41778,7 +41778,7 @@
         <v>46042</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -41851,7 +41851,7 @@
         <v>45531</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -41924,7 +41924,7 @@
         <v>45817</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -41997,7 +41997,7 @@
         <v>46084</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -42070,7 +42070,7 @@
         <v>45839</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -42143,7 +42143,7 @@
         <v>46042</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -42216,7 +42216,7 @@
         <v>45848</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -42289,7 +42289,7 @@
         <v>46044</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -42362,7 +42362,7 @@
         <v>46044</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -42435,7 +42435,7 @@
         <v>45019</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -42508,7 +42508,7 @@
         <v>45350</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -42581,7 +42581,7 @@
         <v>46044</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -42654,7 +42654,7 @@
         <v>45434</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -42727,7 +42727,7 @@
         <v>46044</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -42800,7 +42800,7 @@
         <v>46048</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -42873,7 +42873,7 @@
         <v>46048</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -42946,7 +42946,7 @@
         <v>46048</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -43019,7 +43019,7 @@
         <v>46048</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -43092,7 +43092,7 @@
         <v>46048</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -43165,7 +43165,7 @@
         <v>46048</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -43238,7 +43238,7 @@
         <v>44900</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -43311,7 +43311,7 @@
         <v>45357</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -43384,7 +43384,7 @@
         <v>45429</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -43457,7 +43457,7 @@
         <v>46048</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -43530,7 +43530,7 @@
         <v>46048</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -43603,7 +43603,7 @@
         <v>46048</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -43676,7 +43676,7 @@
         <v>46048</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -43749,7 +43749,7 @@
         <v>46048</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -43822,7 +43822,7 @@
         <v>46048</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -43895,7 +43895,7 @@
         <v>46049</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -43968,7 +43968,7 @@
         <v>45617</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -44041,7 +44041,7 @@
         <v>46052</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -44114,7 +44114,7 @@
         <v>46052</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -44187,7 +44187,7 @@
         <v>46055</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -44260,7 +44260,7 @@
         <v>46057</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -44333,7 +44333,7 @@
         <v>46062</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -44406,7 +44406,7 @@
         <v>46062</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -44479,7 +44479,7 @@
         <v>46064</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -44552,7 +44552,7 @@
         <v>46148</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -44625,7 +44625,7 @@
         <v>46065</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -44698,7 +44698,7 @@
         <v>46070</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -44771,7 +44771,7 @@
         <v>46153</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -44844,7 +44844,7 @@
         <v>46153</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -44917,7 +44917,7 @@
         <v>46153</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -44990,7 +44990,7 @@
         <v>46153</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -45063,7 +45063,7 @@
         <v>45709</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -45136,7 +45136,7 @@
         <v>46153</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -45209,7 +45209,7 @@
         <v>46153</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -45282,7 +45282,7 @@
         <v>46153</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -45355,7 +45355,7 @@
         <v>46084</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -45428,7 +45428,7 @@
         <v>46155</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -45501,7 +45501,7 @@
         <v>46084</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -45574,7 +45574,7 @@
         <v>46087</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -45647,7 +45647,7 @@
         <v>46161</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -45725,7 +45725,7 @@
         <v>46161</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -45798,7 +45798,7 @@
         <v>46093</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -45871,7 +45871,7 @@
         <v>46093</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -45944,7 +45944,7 @@
         <v>46093</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -46017,7 +46017,7 @@
         <v>46161</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -46095,7 +46095,7 @@
         <v>46161</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -46168,7 +46168,7 @@
         <v>46161</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -46246,7 +46246,7 @@
         <v>46169</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -46319,7 +46319,7 @@
         <v>46169</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -46392,7 +46392,7 @@
         <v>46169</v>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -46465,7 +46465,7 @@
         <v>46171</v>
       </c>
       <c r="E610" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -46538,7 +46538,7 @@
         <v>46170</v>
       </c>
       <c r="E611" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
@@ -46611,7 +46611,7 @@
         <v>46174</v>
       </c>
       <c r="E612" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
@@ -46684,7 +46684,7 @@
         <v>46175</v>
       </c>
       <c r="E613" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
@@ -46757,7 +46757,7 @@
         <v>46174</v>
       </c>
       <c r="E614" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F614" t="inlineStr">
         <is>
@@ -46830,7 +46830,7 @@
         <v>46174</v>
       </c>
       <c r="E615" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F615" t="inlineStr">
         <is>
@@ -46903,7 +46903,7 @@
         <v>46178</v>
       </c>
       <c r="E616" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F616" t="inlineStr">
         <is>
@@ -46976,7 +46976,7 @@
         <v>46178</v>
       </c>
       <c r="E617" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F617" t="inlineStr">
         <is>
@@ -47049,7 +47049,7 @@
         <v>46174</v>
       </c>
       <c r="E618" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F618" t="inlineStr">
         <is>
@@ -47122,7 +47122,7 @@
         <v>46183</v>
       </c>
       <c r="E619" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F619" t="inlineStr">
         <is>
@@ -47195,7 +47195,7 @@
         <v>46185</v>
       </c>
       <c r="E620" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F620" t="inlineStr">
         <is>
@@ -47268,7 +47268,7 @@
         <v>46188</v>
       </c>
       <c r="E621" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F621" t="inlineStr">
         <is>
@@ -47341,7 +47341,7 @@
         <v>46188</v>
       </c>
       <c r="E622" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F622" t="inlineStr">
         <is>
@@ -47414,7 +47414,7 @@
         <v>46196</v>
       </c>
       <c r="E623" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F623" t="inlineStr">
         <is>
@@ -47487,7 +47487,7 @@
         <v>46199</v>
       </c>
       <c r="E624" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F624" t="inlineStr">
         <is>
@@ -47560,7 +47560,7 @@
         <v>46209</v>
       </c>
       <c r="E625" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F625" t="inlineStr">
         <is>
@@ -47633,7 +47633,7 @@
         <v>46206</v>
       </c>
       <c r="E626" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F626" t="inlineStr">
         <is>
@@ -47706,7 +47706,7 @@
         <v>46263</v>
       </c>
       <c r="E627" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F627" t="inlineStr">
         <is>
@@ -47779,7 +47779,7 @@
         <v>46224</v>
       </c>
       <c r="E628" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F628" t="inlineStr">
         <is>
@@ -47857,7 +47857,7 @@
         <v>46268</v>
       </c>
       <c r="E629" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F629" t="inlineStr">
         <is>
@@ -47930,7 +47930,7 @@
         <v>46268</v>
       </c>
       <c r="E630" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F630" t="inlineStr">
         <is>
@@ -48003,7 +48003,7 @@
         <v>46268</v>
       </c>
       <c r="E631" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F631" t="inlineStr">
         <is>
@@ -48076,7 +48076,7 @@
         <v>46272</v>
       </c>
       <c r="E632" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F632" t="inlineStr">
         <is>
@@ -48149,7 +48149,7 @@
         <v>46273</v>
       </c>
       <c r="E633" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F633" t="inlineStr">
         <is>
@@ -48222,7 +48222,7 @@
         <v>45840</v>
       </c>
       <c r="E634" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F634" t="inlineStr">
         <is>
@@ -48300,7 +48300,7 @@
         <v>46273</v>
       </c>
       <c r="E635" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F635" t="inlineStr">
         <is>
@@ -48373,7 +48373,7 @@
         <v>46272</v>
       </c>
       <c r="E636" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F636" t="inlineStr">
         <is>
@@ -48446,7 +48446,7 @@
         <v>46279</v>
       </c>
       <c r="E637" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F637" t="inlineStr">
         <is>
@@ -48519,7 +48519,7 @@
         <v>46279</v>
       </c>
       <c r="E638" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F638" t="inlineStr">
         <is>
@@ -48592,7 +48592,7 @@
         <v>46279</v>
       </c>
       <c r="E639" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F639" t="inlineStr">
         <is>
@@ -48665,7 +48665,7 @@
         <v>46036</v>
       </c>
       <c r="E640" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F640" t="inlineStr">
         <is>
@@ -48738,7 +48738,7 @@
         <v>46282</v>
       </c>
       <c r="E641" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F641" t="inlineStr">
         <is>
@@ -48811,7 +48811,7 @@
         <v>46281</v>
       </c>
       <c r="E642" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F642" t="inlineStr">
         <is>
@@ -48884,7 +48884,7 @@
         <v>45939</v>
       </c>
       <c r="E643" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F643" t="inlineStr">
         <is>
@@ -48962,7 +48962,7 @@
         <v>46241</v>
       </c>
       <c r="E644" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F644" t="inlineStr">
         <is>
@@ -49035,7 +49035,7 @@
         <v>46286</v>
       </c>
       <c r="E645" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F645" t="inlineStr">
         <is>
@@ -49108,7 +49108,7 @@
         <v>46273</v>
       </c>
       <c r="E646" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F646" t="inlineStr">
         <is>
@@ -49181,7 +49181,7 @@
         <v>46286</v>
       </c>
       <c r="E647" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F647" t="inlineStr">
         <is>
@@ -49254,7 +49254,7 @@
         <v>46283</v>
       </c>
       <c r="E648" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F648" t="inlineStr">
         <is>
@@ -49327,7 +49327,7 @@
         <v>46283</v>
       </c>
       <c r="E649" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F649" t="inlineStr">
         <is>
@@ -49400,7 +49400,7 @@
         <v>46245</v>
       </c>
       <c r="E650" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F650" t="inlineStr">
         <is>
@@ -49473,7 +49473,7 @@
         <v>46283</v>
       </c>
       <c r="E651" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F651" t="inlineStr">
         <is>
@@ -49546,7 +49546,7 @@
         <v>46030</v>
       </c>
       <c r="E652" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F652" t="inlineStr">
         <is>
@@ -49619,7 +49619,7 @@
         <v>46281</v>
       </c>
       <c r="E653" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F653" t="inlineStr">
         <is>
@@ -49692,7 +49692,7 @@
         <v>46281</v>
       </c>
       <c r="E654" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F654" t="inlineStr">
         <is>
@@ -49765,7 +49765,7 @@
         <v>46247</v>
       </c>
       <c r="E655" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F655" t="inlineStr">
         <is>
@@ -49838,7 +49838,7 @@
         <v>46224</v>
       </c>
       <c r="E656" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F656" t="inlineStr">
         <is>
@@ -49911,7 +49911,7 @@
         <v>45400</v>
       </c>
       <c r="E657" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F657" t="inlineStr">
         <is>
@@ -49984,7 +49984,7 @@
         <v>46293</v>
       </c>
       <c r="E658" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F658" t="inlineStr">
         <is>
@@ -50057,7 +50057,7 @@
         <v>46248</v>
       </c>
       <c r="E659" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F659" t="inlineStr">
         <is>
@@ -50130,7 +50130,7 @@
         <v>46292</v>
       </c>
       <c r="E660" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F660" t="inlineStr">
         <is>
@@ -50203,7 +50203,7 @@
         <v>46248</v>
       </c>
       <c r="E661" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F661" t="inlineStr">
         <is>
@@ -50276,7 +50276,7 @@
         <v>46295</v>
       </c>
       <c r="E662" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F662" t="inlineStr">
         <is>
@@ -50349,7 +50349,7 @@
         <v>46161</v>
       </c>
       <c r="E663" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F663" t="inlineStr">
         <is>
@@ -50427,7 +50427,7 @@
         <v>46244</v>
       </c>
       <c r="E664" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F664" t="inlineStr">
         <is>
@@ -50500,7 +50500,7 @@
         <v>46070</v>
       </c>
       <c r="E665" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F665" t="inlineStr">
         <is>
@@ -50573,7 +50573,7 @@
         <v>45876</v>
       </c>
       <c r="E666" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F666" t="inlineStr">
         <is>
@@ -50646,7 +50646,7 @@
         <v>46302</v>
       </c>
       <c r="E667" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F667" t="inlineStr">
         <is>
@@ -50719,7 +50719,7 @@
         <v>46302</v>
       </c>
       <c r="E668" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F668" t="inlineStr">
         <is>
@@ -50792,7 +50792,7 @@
         <v>46261</v>
       </c>
       <c r="E669" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F669" t="inlineStr">
         <is>
@@ -50865,7 +50865,7 @@
         <v>46294</v>
       </c>
       <c r="E670" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F670" t="inlineStr">
         <is>
@@ -50943,7 +50943,7 @@
         <v>46292</v>
       </c>
       <c r="E671" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F671" t="inlineStr">
         <is>
@@ -51016,7 +51016,7 @@
         <v>46292</v>
       </c>
       <c r="E672" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F672" t="inlineStr">
         <is>
@@ -51089,7 +51089,7 @@
         <v>46292</v>
       </c>
       <c r="E673" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F673" t="inlineStr">
         <is>
@@ -51162,7 +51162,7 @@
         <v>46292</v>
       </c>
       <c r="E674" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F674" t="inlineStr">
         <is>
@@ -51235,7 +51235,7 @@
         <v>46292</v>
       </c>
       <c r="E675" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F675" t="inlineStr">
         <is>
@@ -51308,7 +51308,7 @@
         <v>46261</v>
       </c>
       <c r="E676" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F676" t="inlineStr">
         <is>
@@ -51381,7 +51381,7 @@
         <v>46292</v>
       </c>
       <c r="E677" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F677" t="inlineStr">
         <is>
@@ -51454,7 +51454,7 @@
         <v>44631</v>
       </c>
       <c r="E678" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F678" t="inlineStr">
         <is>
@@ -51527,7 +51527,7 @@
         <v>44613</v>
       </c>
       <c r="E679" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F679" t="inlineStr">
         <is>
@@ -51600,7 +51600,7 @@
         <v>44608</v>
       </c>
       <c r="E680" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F680" t="inlineStr">
         <is>
@@ -51673,7 +51673,7 @@
         <v>44631</v>
       </c>
       <c r="E681" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F681" t="inlineStr">
         <is>
@@ -51746,7 +51746,7 @@
         <v>44631</v>
       </c>
       <c r="E682" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F682" t="inlineStr">
         <is>
@@ -51819,7 +51819,7 @@
         <v>45614</v>
       </c>
       <c r="E683" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F683" t="inlineStr">
         <is>
@@ -51897,7 +51897,7 @@
         <v>44743</v>
       </c>
       <c r="E684" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F684" t="inlineStr">
         <is>
@@ -51970,7 +51970,7 @@
         <v>45375</v>
       </c>
       <c r="E685" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F685" t="inlineStr">
         <is>
@@ -52043,7 +52043,7 @@
         <v>44488</v>
       </c>
       <c r="E686" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F686" t="inlineStr">
         <is>
@@ -52116,7 +52116,7 @@
         <v>45604</v>
       </c>
       <c r="E687" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F687" t="inlineStr">
         <is>
@@ -52189,7 +52189,7 @@
         <v>45356</v>
       </c>
       <c r="E688" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F688" t="inlineStr">
         <is>
@@ -52262,7 +52262,7 @@
         <v>45349</v>
       </c>
       <c r="E689" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F689" t="inlineStr">
         <is>
@@ -52335,7 +52335,7 @@
         <v>45744</v>
       </c>
       <c r="E690" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F690" t="inlineStr">
         <is>
@@ -52408,7 +52408,7 @@
         <v>45714</v>
       </c>
       <c r="E691" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F691" t="inlineStr">
         <is>
@@ -52481,7 +52481,7 @@
         <v>45715</v>
       </c>
       <c r="E692" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F692" t="inlineStr">
         <is>
@@ -52554,7 +52554,7 @@
         <v>45709</v>
       </c>
       <c r="E693" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F693" t="inlineStr">
         <is>
@@ -52627,7 +52627,7 @@
         <v>45714</v>
       </c>
       <c r="E694" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F694" t="inlineStr">
         <is>
@@ -52700,7 +52700,7 @@
         <v>45813</v>
       </c>
       <c r="E695" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F695" t="inlineStr">
         <is>
@@ -52773,7 +52773,7 @@
         <v>45813</v>
       </c>
       <c r="E696" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F696" t="inlineStr">
         <is>
@@ -52846,7 +52846,7 @@
         <v>45813</v>
       </c>
       <c r="E697" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F697" t="inlineStr">
         <is>
@@ -52919,7 +52919,7 @@
         <v>45820</v>
       </c>
       <c r="E698" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F698" t="inlineStr">
         <is>
@@ -52992,7 +52992,7 @@
         <v>45827</v>
       </c>
       <c r="E699" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F699" t="inlineStr">
         <is>
@@ -53065,7 +53065,7 @@
         <v>45845</v>
       </c>
       <c r="E700" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F700" t="inlineStr">
         <is>
@@ -53138,7 +53138,7 @@
         <v>45883</v>
       </c>
       <c r="E701" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F701" t="inlineStr">
         <is>
@@ -53211,7 +53211,7 @@
         <v>45915</v>
       </c>
       <c r="E702" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F702" t="inlineStr">
         <is>
@@ -53284,7 +53284,7 @@
         <v>46041</v>
       </c>
       <c r="E703" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F703" t="inlineStr">
         <is>
@@ -53357,7 +53357,7 @@
         <v>46133</v>
       </c>
       <c r="E704" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F704" t="inlineStr">
         <is>
@@ -53430,7 +53430,7 @@
         <v>46147</v>
       </c>
       <c r="E705" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F705" t="inlineStr">
         <is>
@@ -53503,7 +53503,7 @@
         <v>46211</v>
       </c>
       <c r="E706" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F706" t="inlineStr">
         <is>
@@ -53576,7 +53576,7 @@
         <v>46290</v>
       </c>
       <c r="E707" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F707" t="inlineStr">
         <is>
@@ -53649,7 +53649,7 @@
         <v>46253</v>
       </c>
       <c r="E708" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F708" t="inlineStr">
         <is>

--- a/Översikt HYLTE.xlsx
+++ b/Översikt HYLTE.xlsx
@@ -601,7 +601,7 @@
         <v>46090</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -718,7 +718,7 @@
         <v>45265</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -834,7 +834,7 @@
         <v>46066</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -945,7 +945,7 @@
         <v>44873</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1054,7 +1054,7 @@
         <v>45348</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1166,7 +1166,7 @@
         <v>45719</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1274,7 +1274,7 @@
         <v>45245</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1385,7 +1385,7 @@
         <v>46268</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1492,7 +1492,7 @@
         <v>45230</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1599,7 +1599,7 @@
         <v>45737</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1706,7 +1706,7 @@
         <v>46141</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1813,7 +1813,7 @@
         <v>46161</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1920,7 +1920,7 @@
         <v>44839</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2030,7 +2030,7 @@
         <v>45841</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2140,7 +2140,7 @@
         <v>45099</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2250,7 +2250,7 @@
         <v>46048</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2356,7 +2356,7 @@
         <v>45904</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2466,7 +2466,7 @@
         <v>46304</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2576,7 +2576,7 @@
         <v>46130</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2682,7 +2682,7 @@
         <v>44648</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2787,7 +2787,7 @@
         <v>44651</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2892,7 +2892,7 @@
         <v>44876</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2997,7 +2997,7 @@
         <v>45593</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3102,7 +3102,7 @@
         <v>45245</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3207,7 +3207,7 @@
         <v>45299</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3316,7 +3316,7 @@
         <v>45617</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3421,7 +3421,7 @@
         <v>45343</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3526,7 +3526,7 @@
         <v>45476</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3636,7 +3636,7 @@
         <v>45085</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3745,7 +3745,7 @@
         <v>45153</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3859,7 +3859,7 @@
         <v>45163</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3964,7 +3964,7 @@
         <v>45186</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4069,7 +4069,7 @@
         <v>45245</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4174,7 +4174,7 @@
         <v>45253</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4279,7 +4279,7 @@
         <v>45754</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4384,7 +4384,7 @@
         <v>46253</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4494,7 +4494,7 @@
         <v>44810</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4567,7 +4567,7 @@
         <v>44481</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4640,7 +4640,7 @@
         <v>44600</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4713,7 +4713,7 @@
         <v>44529</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4786,7 +4786,7 @@
         <v>44557</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4859,7 +4859,7 @@
         <v>44705</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4932,7 +4932,7 @@
         <v>44483</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5005,7 +5005,7 @@
         <v>44778</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5078,7 +5078,7 @@
         <v>44488</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5151,7 +5151,7 @@
         <v>44624</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5224,7 +5224,7 @@
         <v>44812</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5297,7 +5297,7 @@
         <v>44638</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5370,7 +5370,7 @@
         <v>44498</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5443,7 +5443,7 @@
         <v>44845</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5516,7 +5516,7 @@
         <v>44559</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5589,7 +5589,7 @@
         <v>44659</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5667,7 +5667,7 @@
         <v>44578</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5740,7 +5740,7 @@
         <v>44756</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5813,7 +5813,7 @@
         <v>44501</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5886,7 +5886,7 @@
         <v>44651</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5959,7 +5959,7 @@
         <v>44711</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6032,7 +6032,7 @@
         <v>44487</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6110,7 +6110,7 @@
         <v>44714</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6183,7 +6183,7 @@
         <v>44834</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6256,7 +6256,7 @@
         <v>44735</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6329,7 +6329,7 @@
         <v>44482</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6402,7 +6402,7 @@
         <v>44482</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6475,7 +6475,7 @@
         <v>44867</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6548,7 +6548,7 @@
         <v>44505</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6621,7 +6621,7 @@
         <v>44796</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6694,7 +6694,7 @@
         <v>44795</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6767,7 +6767,7 @@
         <v>44634</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6840,7 +6840,7 @@
         <v>44502</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6913,7 +6913,7 @@
         <v>44818</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6986,7 +6986,7 @@
         <v>44489</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7059,7 +7059,7 @@
         <v>44631</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7132,7 +7132,7 @@
         <v>44801</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7205,7 +7205,7 @@
         <v>44876</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7278,7 +7278,7 @@
         <v>44659</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7351,7 +7351,7 @@
         <v>44596</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7429,7 +7429,7 @@
         <v>44644</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7502,7 +7502,7 @@
         <v>44728</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7575,7 +7575,7 @@
         <v>44515</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7653,7 +7653,7 @@
         <v>44644</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7726,7 +7726,7 @@
         <v>44523</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7799,7 +7799,7 @@
         <v>44500</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7872,7 +7872,7 @@
         <v>44727</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7945,7 +7945,7 @@
         <v>44900</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8018,7 +8018,7 @@
         <v>44778</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8091,7 +8091,7 @@
         <v>44705</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8164,7 +8164,7 @@
         <v>44659</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8242,7 +8242,7 @@
         <v>44659</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8320,7 +8320,7 @@
         <v>44900</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8393,7 +8393,7 @@
         <v>44757</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8466,7 +8466,7 @@
         <v>44866</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8539,7 +8539,7 @@
         <v>44494</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8612,7 +8612,7 @@
         <v>45091</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8685,7 +8685,7 @@
         <v>45002</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8758,7 +8758,7 @@
         <v>45331</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8831,7 +8831,7 @@
         <v>45684</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8904,7 +8904,7 @@
         <v>44495</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8977,7 +8977,7 @@
         <v>44847</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -9050,7 +9050,7 @@
         <v>45254</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9123,7 +9123,7 @@
         <v>45254</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9196,7 +9196,7 @@
         <v>45342</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9274,7 +9274,7 @@
         <v>44872</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9347,7 +9347,7 @@
         <v>45477</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9420,7 +9420,7 @@
         <v>45371</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9493,7 +9493,7 @@
         <v>44953</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9566,7 +9566,7 @@
         <v>45390</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9639,7 +9639,7 @@
         <v>44869</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9712,7 +9712,7 @@
         <v>45096</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9785,7 +9785,7 @@
         <v>44900</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9863,7 +9863,7 @@
         <v>45104</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9936,7 +9936,7 @@
         <v>45624</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -10009,7 +10009,7 @@
         <v>45042</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -10082,7 +10082,7 @@
         <v>45169</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10155,7 +10155,7 @@
         <v>45229</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10228,7 +10228,7 @@
         <v>45327</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10301,7 +10301,7 @@
         <v>45770</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10374,7 +10374,7 @@
         <v>45441</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10447,7 +10447,7 @@
         <v>45441</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10520,7 +10520,7 @@
         <v>45674</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10593,7 +10593,7 @@
         <v>45035</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10666,7 +10666,7 @@
         <v>45229</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10739,7 +10739,7 @@
         <v>44635</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -10817,7 +10817,7 @@
         <v>45441</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10890,7 +10890,7 @@
         <v>45254</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10963,7 +10963,7 @@
         <v>45254</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -11036,7 +11036,7 @@
         <v>45752</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -11114,7 +11114,7 @@
         <v>45700</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11187,7 +11187,7 @@
         <v>45110</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11260,7 +11260,7 @@
         <v>45378</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11333,7 +11333,7 @@
         <v>45382</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11406,7 +11406,7 @@
         <v>45061</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11479,7 +11479,7 @@
         <v>45084</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11552,7 +11552,7 @@
         <v>45456</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11625,7 +11625,7 @@
         <v>45253</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11698,7 +11698,7 @@
         <v>45229</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -11771,7 +11771,7 @@
         <v>45170</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -11844,7 +11844,7 @@
         <v>45299</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -11917,7 +11917,7 @@
         <v>45310</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -11990,7 +11990,7 @@
         <v>45208</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -12063,7 +12063,7 @@
         <v>45254</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -12136,7 +12136,7 @@
         <v>45252</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12209,7 +12209,7 @@
         <v>45694</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12282,7 +12282,7 @@
         <v>44750</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12355,7 +12355,7 @@
         <v>45368</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12433,7 +12433,7 @@
         <v>45406</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -12506,7 +12506,7 @@
         <v>44967</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -12579,7 +12579,7 @@
         <v>45110</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -12652,7 +12652,7 @@
         <v>44893</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -12725,7 +12725,7 @@
         <v>45145</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -12798,7 +12798,7 @@
         <v>45117</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -12871,7 +12871,7 @@
         <v>45352</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -12944,7 +12944,7 @@
         <v>45541</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -13017,7 +13017,7 @@
         <v>45527</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -13090,7 +13090,7 @@
         <v>44482</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -13163,7 +13163,7 @@
         <v>45097</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13236,7 +13236,7 @@
         <v>45062</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13309,7 +13309,7 @@
         <v>45478</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13382,7 +13382,7 @@
         <v>45834</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -13455,7 +13455,7 @@
         <v>45371</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -13528,7 +13528,7 @@
         <v>45405</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -13601,7 +13601,7 @@
         <v>45600</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -13674,7 +13674,7 @@
         <v>44495</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -13747,7 +13747,7 @@
         <v>44487</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -13825,7 +13825,7 @@
         <v>45840</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -13898,7 +13898,7 @@
         <v>45436</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -13971,7 +13971,7 @@
         <v>44868</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -14044,7 +14044,7 @@
         <v>45673</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -14117,7 +14117,7 @@
         <v>44950</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -14190,7 +14190,7 @@
         <v>45299</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14263,7 +14263,7 @@
         <v>44530</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14336,7 +14336,7 @@
         <v>45104</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -14409,7 +14409,7 @@
         <v>45737</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -14482,7 +14482,7 @@
         <v>45454</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -14555,7 +14555,7 @@
         <v>44601</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -14628,7 +14628,7 @@
         <v>45258</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -14701,7 +14701,7 @@
         <v>45485</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -14774,7 +14774,7 @@
         <v>45462</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -14847,7 +14847,7 @@
         <v>44510</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -14920,7 +14920,7 @@
         <v>45890</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -14993,7 +14993,7 @@
         <v>45748</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -15066,7 +15066,7 @@
         <v>45891</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -15144,7 +15144,7 @@
         <v>45891</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -15222,7 +15222,7 @@
         <v>45352</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -15295,7 +15295,7 @@
         <v>45560</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -15368,7 +15368,7 @@
         <v>44865</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -15441,7 +15441,7 @@
         <v>45897</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -15514,7 +15514,7 @@
         <v>45897</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -15587,7 +15587,7 @@
         <v>45089</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -15660,7 +15660,7 @@
         <v>45839</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -15733,7 +15733,7 @@
         <v>45300</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -15806,7 +15806,7 @@
         <v>45352</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -15879,7 +15879,7 @@
         <v>45898</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -15952,7 +15952,7 @@
         <v>45352</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -16025,7 +16025,7 @@
         <v>44834</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -16098,7 +16098,7 @@
         <v>45182</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -16171,7 +16171,7 @@
         <v>45539</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -16244,7 +16244,7 @@
         <v>45253</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -16317,7 +16317,7 @@
         <v>45377</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -16395,7 +16395,7 @@
         <v>44896</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -16468,7 +16468,7 @@
         <v>45905</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -16541,7 +16541,7 @@
         <v>45531</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -16614,7 +16614,7 @@
         <v>45176</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -16692,7 +16692,7 @@
         <v>45429</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -16765,7 +16765,7 @@
         <v>45910</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -16838,7 +16838,7 @@
         <v>45638</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -16911,7 +16911,7 @@
         <v>45910</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -16984,7 +16984,7 @@
         <v>45838</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -17057,7 +17057,7 @@
         <v>45715</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -17130,7 +17130,7 @@
         <v>45182</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -17203,7 +17203,7 @@
         <v>45588</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -17281,7 +17281,7 @@
         <v>45414</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -17354,7 +17354,7 @@
         <v>44489</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -17427,7 +17427,7 @@
         <v>45366</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -17500,7 +17500,7 @@
         <v>45538</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -17573,7 +17573,7 @@
         <v>45643</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -17646,7 +17646,7 @@
         <v>45114</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -17719,7 +17719,7 @@
         <v>45616</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -17792,7 +17792,7 @@
         <v>45918</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -17865,7 +17865,7 @@
         <v>45391</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -17938,7 +17938,7 @@
         <v>45510</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -18011,7 +18011,7 @@
         <v>44970</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -18084,7 +18084,7 @@
         <v>45783</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -18157,7 +18157,7 @@
         <v>45616</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -18230,7 +18230,7 @@
         <v>45538</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -18303,7 +18303,7 @@
         <v>45786</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -18381,7 +18381,7 @@
         <v>45559</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -18454,7 +18454,7 @@
         <v>45680</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -18527,7 +18527,7 @@
         <v>45922</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -18600,7 +18600,7 @@
         <v>45671</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -18673,7 +18673,7 @@
         <v>45225</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -18746,7 +18746,7 @@
         <v>45589</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -18824,7 +18824,7 @@
         <v>45618</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -18897,7 +18897,7 @@
         <v>45170</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -18970,7 +18970,7 @@
         <v>45922</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -19043,7 +19043,7 @@
         <v>45462</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -19116,7 +19116,7 @@
         <v>45558</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -19189,7 +19189,7 @@
         <v>45922</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -19262,7 +19262,7 @@
         <v>45726</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -19335,7 +19335,7 @@
         <v>45741</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -19408,7 +19408,7 @@
         <v>45483</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -19481,7 +19481,7 @@
         <v>45609</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -19554,7 +19554,7 @@
         <v>45170</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -19627,7 +19627,7 @@
         <v>45924</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -19700,7 +19700,7 @@
         <v>45926</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -19773,7 +19773,7 @@
         <v>45926</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -19846,7 +19846,7 @@
         <v>45926</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -19919,7 +19919,7 @@
         <v>45483</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -19992,7 +19992,7 @@
         <v>45743</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -20070,7 +20070,7 @@
         <v>45590</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -20143,7 +20143,7 @@
         <v>45929</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -20216,7 +20216,7 @@
         <v>44719</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -20289,7 +20289,7 @@
         <v>45743</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -20367,7 +20367,7 @@
         <v>45604</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -20440,7 +20440,7 @@
         <v>45091</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -20513,7 +20513,7 @@
         <v>45559</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -20586,7 +20586,7 @@
         <v>45681</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -20659,7 +20659,7 @@
         <v>45743</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -20737,7 +20737,7 @@
         <v>44851</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -20810,7 +20810,7 @@
         <v>45931</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -20883,7 +20883,7 @@
         <v>45597</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -20956,7 +20956,7 @@
         <v>45793</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -21029,7 +21029,7 @@
         <v>44701</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -21107,7 +21107,7 @@
         <v>45931</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -21180,7 +21180,7 @@
         <v>45259</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -21253,7 +21253,7 @@
         <v>44714</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -21326,7 +21326,7 @@
         <v>44641</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -21399,7 +21399,7 @@
         <v>45930</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -21472,7 +21472,7 @@
         <v>44974</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -21545,7 +21545,7 @@
         <v>45432</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -21618,7 +21618,7 @@
         <v>45159</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -21691,7 +21691,7 @@
         <v>45933</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -21764,7 +21764,7 @@
         <v>45229</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -21837,7 +21837,7 @@
         <v>45936</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -21910,7 +21910,7 @@
         <v>45936</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -21983,7 +21983,7 @@
         <v>45198</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -22056,7 +22056,7 @@
         <v>45933</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -22129,7 +22129,7 @@
         <v>45933</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -22202,7 +22202,7 @@
         <v>44481</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -22275,7 +22275,7 @@
         <v>45456</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -22348,7 +22348,7 @@
         <v>45936</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -22421,7 +22421,7 @@
         <v>44900</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -22494,7 +22494,7 @@
         <v>45366</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -22572,7 +22572,7 @@
         <v>45441</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -22645,7 +22645,7 @@
         <v>44926</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -22723,7 +22723,7 @@
         <v>44697</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -22796,7 +22796,7 @@
         <v>44756</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -22869,7 +22869,7 @@
         <v>45162</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -22942,7 +22942,7 @@
         <v>45162</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -23015,7 +23015,7 @@
         <v>45268</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -23088,7 +23088,7 @@
         <v>45194</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -23161,7 +23161,7 @@
         <v>44903</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -23234,7 +23234,7 @@
         <v>45937</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -23307,7 +23307,7 @@
         <v>45806</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -23380,7 +23380,7 @@
         <v>44999</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -23453,7 +23453,7 @@
         <v>45938</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -23526,7 +23526,7 @@
         <v>45609</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -23599,7 +23599,7 @@
         <v>45203</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -23672,7 +23672,7 @@
         <v>45812</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -23745,7 +23745,7 @@
         <v>45944</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -23818,7 +23818,7 @@
         <v>45677</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -23891,7 +23891,7 @@
         <v>45730</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -23964,7 +23964,7 @@
         <v>45132</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -24037,7 +24037,7 @@
         <v>45694</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -24110,7 +24110,7 @@
         <v>45597</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -24183,7 +24183,7 @@
         <v>45708</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -24256,7 +24256,7 @@
         <v>45387</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -24329,7 +24329,7 @@
         <v>45254</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -24402,7 +24402,7 @@
         <v>45706</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -24475,7 +24475,7 @@
         <v>45820</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -24548,7 +24548,7 @@
         <v>45460</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -24621,7 +24621,7 @@
         <v>44965</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -24699,7 +24699,7 @@
         <v>44900</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -24772,7 +24772,7 @@
         <v>45173</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -24845,7 +24845,7 @@
         <v>45153</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -24918,7 +24918,7 @@
         <v>44970</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -24991,7 +24991,7 @@
         <v>44970</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -25064,7 +25064,7 @@
         <v>45825</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -25137,7 +25137,7 @@
         <v>45084</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -25210,7 +25210,7 @@
         <v>45254</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -25283,7 +25283,7 @@
         <v>45211</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -25356,7 +25356,7 @@
         <v>45568</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -25429,7 +25429,7 @@
         <v>45107</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -25502,7 +25502,7 @@
         <v>45441</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -25580,7 +25580,7 @@
         <v>45548</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -25653,7 +25653,7 @@
         <v>45456</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -25726,7 +25726,7 @@
         <v>45831</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -25799,7 +25799,7 @@
         <v>45456</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -25872,7 +25872,7 @@
         <v>45092</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -25945,7 +25945,7 @@
         <v>45957</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -26018,7 +26018,7 @@
         <v>45229</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -26091,7 +26091,7 @@
         <v>45751</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -26169,7 +26169,7 @@
         <v>45002</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -26242,7 +26242,7 @@
         <v>45225</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -26315,7 +26315,7 @@
         <v>45601</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -26388,7 +26388,7 @@
         <v>45107</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -26461,7 +26461,7 @@
         <v>45961</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -26534,7 +26534,7 @@
         <v>45181</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -26607,7 +26607,7 @@
         <v>45961</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -26680,7 +26680,7 @@
         <v>45645</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -26753,7 +26753,7 @@
         <v>44823</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -26826,7 +26826,7 @@
         <v>45835</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -26899,7 +26899,7 @@
         <v>45836</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -26972,7 +26972,7 @@
         <v>45238</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -27045,7 +27045,7 @@
         <v>45145</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -27118,7 +27118,7 @@
         <v>45922</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -27191,7 +27191,7 @@
         <v>45838</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -27264,7 +27264,7 @@
         <v>45840</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -27337,7 +27337,7 @@
         <v>45840</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -27410,7 +27410,7 @@
         <v>45840</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -27483,7 +27483,7 @@
         <v>45287</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -27556,7 +27556,7 @@
         <v>44701</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -27634,7 +27634,7 @@
         <v>44735</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -27707,7 +27707,7 @@
         <v>44651</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -27780,7 +27780,7 @@
         <v>45169</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -27853,7 +27853,7 @@
         <v>45638</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -27926,7 +27926,7 @@
         <v>45972</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -27999,7 +27999,7 @@
         <v>45972</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -28072,7 +28072,7 @@
         <v>45972</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -28145,7 +28145,7 @@
         <v>45568</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -28218,7 +28218,7 @@
         <v>45845</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -28291,7 +28291,7 @@
         <v>45845</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -28364,7 +28364,7 @@
         <v>45800</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -28437,7 +28437,7 @@
         <v>45846</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -28515,7 +28515,7 @@
         <v>45846</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -28593,7 +28593,7 @@
         <v>45846</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -28671,7 +28671,7 @@
         <v>44712</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -28744,7 +28744,7 @@
         <v>45316</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -28822,7 +28822,7 @@
         <v>45167</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -28895,7 +28895,7 @@
         <v>45847</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -28968,7 +28968,7 @@
         <v>45254</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -29041,7 +29041,7 @@
         <v>45254</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -29114,7 +29114,7 @@
         <v>45245</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -29187,7 +29187,7 @@
         <v>45847</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -29260,7 +29260,7 @@
         <v>45803</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -29333,7 +29333,7 @@
         <v>44778</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -29406,7 +29406,7 @@
         <v>44729</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -29479,7 +29479,7 @@
         <v>45483</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -29552,7 +29552,7 @@
         <v>44847</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -29625,7 +29625,7 @@
         <v>44980</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -29698,7 +29698,7 @@
         <v>45246</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -29771,7 +29771,7 @@
         <v>44694</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -29844,7 +29844,7 @@
         <v>45715</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -29917,7 +29917,7 @@
         <v>45700</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -29990,7 +29990,7 @@
         <v>45700</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -30063,7 +30063,7 @@
         <v>45687</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -30136,7 +30136,7 @@
         <v>45245</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -30209,7 +30209,7 @@
         <v>45092</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -30282,7 +30282,7 @@
         <v>45051</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -30355,7 +30355,7 @@
         <v>45838</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -30428,7 +30428,7 @@
         <v>45544</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -30501,7 +30501,7 @@
         <v>45098</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -30579,7 +30579,7 @@
         <v>45979</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -30652,7 +30652,7 @@
         <v>45351</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -30725,7 +30725,7 @@
         <v>44797</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -30798,7 +30798,7 @@
         <v>45288</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -30876,7 +30876,7 @@
         <v>45309</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -30949,7 +30949,7 @@
         <v>45407</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -31022,7 +31022,7 @@
         <v>45677</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -31095,7 +31095,7 @@
         <v>45257</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -31168,7 +31168,7 @@
         <v>45395</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -31241,7 +31241,7 @@
         <v>44671</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -31314,7 +31314,7 @@
         <v>45524</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -31387,7 +31387,7 @@
         <v>45272</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -31460,7 +31460,7 @@
         <v>44483</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -31533,7 +31533,7 @@
         <v>45267</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -31606,7 +31606,7 @@
         <v>45245</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -31679,7 +31679,7 @@
         <v>45679</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -31752,7 +31752,7 @@
         <v>45610</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -31825,7 +31825,7 @@
         <v>45432</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -31898,7 +31898,7 @@
         <v>44712</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -31971,7 +31971,7 @@
         <v>45131</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -32044,7 +32044,7 @@
         <v>45176</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -32117,7 +32117,7 @@
         <v>45372</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -32190,7 +32190,7 @@
         <v>45361</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -32263,7 +32263,7 @@
         <v>45541</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -32336,7 +32336,7 @@
         <v>45257</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -32414,7 +32414,7 @@
         <v>45727</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -32487,7 +32487,7 @@
         <v>44974</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -32560,7 +32560,7 @@
         <v>44917</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -32633,7 +32633,7 @@
         <v>45735</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -32706,7 +32706,7 @@
         <v>45672</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -32779,7 +32779,7 @@
         <v>45204</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -32852,7 +32852,7 @@
         <v>45293</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -32925,7 +32925,7 @@
         <v>45245</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -32998,7 +32998,7 @@
         <v>44671</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -33071,7 +33071,7 @@
         <v>44896</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -33144,7 +33144,7 @@
         <v>44592</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -33217,7 +33217,7 @@
         <v>45293</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -33290,7 +33290,7 @@
         <v>45623</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -33363,7 +33363,7 @@
         <v>45199</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -33436,7 +33436,7 @@
         <v>45769</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -33509,7 +33509,7 @@
         <v>45392</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -33582,7 +33582,7 @@
         <v>45395</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -33655,7 +33655,7 @@
         <v>45229</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -33728,7 +33728,7 @@
         <v>45589</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -33801,7 +33801,7 @@
         <v>45546</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -33874,7 +33874,7 @@
         <v>44701</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -33947,7 +33947,7 @@
         <v>45145</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -34020,7 +34020,7 @@
         <v>45517</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -34093,7 +34093,7 @@
         <v>45230</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -34166,7 +34166,7 @@
         <v>45677</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -34239,7 +34239,7 @@
         <v>45672</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -34312,7 +34312,7 @@
         <v>45672</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -34385,7 +34385,7 @@
         <v>44483</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -34458,7 +34458,7 @@
         <v>44964</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -34531,7 +34531,7 @@
         <v>45735</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -34604,7 +34604,7 @@
         <v>44739</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -34677,7 +34677,7 @@
         <v>45309</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -34750,7 +34750,7 @@
         <v>44508</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -34823,7 +34823,7 @@
         <v>45623</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -34896,7 +34896,7 @@
         <v>45252</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -34969,7 +34969,7 @@
         <v>45589</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -35042,7 +35042,7 @@
         <v>45190</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -35115,7 +35115,7 @@
         <v>44817</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -35188,7 +35188,7 @@
         <v>45574</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -35261,7 +35261,7 @@
         <v>45545</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -35334,7 +35334,7 @@
         <v>45199</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -35407,7 +35407,7 @@
         <v>45190</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -35485,7 +35485,7 @@
         <v>44889</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -35558,7 +35558,7 @@
         <v>45623</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -35631,7 +35631,7 @@
         <v>45880</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -35704,7 +35704,7 @@
         <v>45880</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -35777,7 +35777,7 @@
         <v>45502</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -35850,7 +35850,7 @@
         <v>44559</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -35923,7 +35923,7 @@
         <v>45877</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -35996,7 +35996,7 @@
         <v>45880</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -36069,7 +36069,7 @@
         <v>44893</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -36142,7 +36142,7 @@
         <v>45880</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -36215,7 +36215,7 @@
         <v>45981</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -36288,7 +36288,7 @@
         <v>45981</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -36361,7 +36361,7 @@
         <v>44910</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -36434,7 +36434,7 @@
         <v>45455</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -36507,7 +36507,7 @@
         <v>45104</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -36580,7 +36580,7 @@
         <v>45334</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -36653,7 +36653,7 @@
         <v>45352</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -36726,7 +36726,7 @@
         <v>46057</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -36799,7 +36799,7 @@
         <v>45715</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -36872,7 +36872,7 @@
         <v>45316</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -36945,7 +36945,7 @@
         <v>45987</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -37018,7 +37018,7 @@
         <v>44796</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -37091,7 +37091,7 @@
         <v>46057</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -37164,7 +37164,7 @@
         <v>45019</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -37237,7 +37237,7 @@
         <v>45257</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -37310,7 +37310,7 @@
         <v>46111</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -37383,7 +37383,7 @@
         <v>44901</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -37456,7 +37456,7 @@
         <v>45589</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -37529,7 +37529,7 @@
         <v>46111</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -37602,7 +37602,7 @@
         <v>45989</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -37675,7 +37675,7 @@
         <v>46111</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -37748,7 +37748,7 @@
         <v>45754</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -37821,7 +37821,7 @@
         <v>44899</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -37894,7 +37894,7 @@
         <v>46121</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -37967,7 +37967,7 @@
         <v>46120</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -38040,7 +38040,7 @@
         <v>46121</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -38113,7 +38113,7 @@
         <v>46121</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -38186,7 +38186,7 @@
         <v>46121</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -38259,7 +38259,7 @@
         <v>46121</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -38332,7 +38332,7 @@
         <v>46120</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -38405,7 +38405,7 @@
         <v>46121</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -38478,7 +38478,7 @@
         <v>46121</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -38551,7 +38551,7 @@
         <v>44995</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -38624,7 +38624,7 @@
         <v>45548</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -38697,7 +38697,7 @@
         <v>46122</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -38770,7 +38770,7 @@
         <v>45995</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -38843,7 +38843,7 @@
         <v>46122</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -38916,7 +38916,7 @@
         <v>44958</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -38989,7 +38989,7 @@
         <v>46122</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -39062,7 +39062,7 @@
         <v>46122</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -39135,7 +39135,7 @@
         <v>46121</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -39208,7 +39208,7 @@
         <v>44575</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -39281,7 +39281,7 @@
         <v>45572</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -39354,7 +39354,7 @@
         <v>46128</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -39427,7 +39427,7 @@
         <v>44951</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -39500,7 +39500,7 @@
         <v>45265</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -39573,7 +39573,7 @@
         <v>45351</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -39646,7 +39646,7 @@
         <v>45432</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -39719,7 +39719,7 @@
         <v>45926</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -39792,7 +39792,7 @@
         <v>45790</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -39865,7 +39865,7 @@
         <v>45132</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -39938,7 +39938,7 @@
         <v>45246</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -40011,7 +40011,7 @@
         <v>45246</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -40084,7 +40084,7 @@
         <v>45426</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -40157,7 +40157,7 @@
         <v>45371</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -40230,7 +40230,7 @@
         <v>45411</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -40303,7 +40303,7 @@
         <v>45840</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -40381,7 +40381,7 @@
         <v>44539</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -40454,7 +40454,7 @@
         <v>46020</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -40527,7 +40527,7 @@
         <v>45441</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -40605,7 +40605,7 @@
         <v>45775</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -40678,7 +40678,7 @@
         <v>45624</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -40751,7 +40751,7 @@
         <v>45782</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -40824,7 +40824,7 @@
         <v>44699</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -40897,7 +40897,7 @@
         <v>45524</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -40970,7 +40970,7 @@
         <v>45580</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -41043,7 +41043,7 @@
         <v>45568</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -41116,7 +41116,7 @@
         <v>45989</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -41189,7 +41189,7 @@
         <v>46084</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -41262,7 +41262,7 @@
         <v>44714</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -41340,7 +41340,7 @@
         <v>44813</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -41413,7 +41413,7 @@
         <v>45163</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -41486,7 +41486,7 @@
         <v>44851</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -41559,7 +41559,7 @@
         <v>44851</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -41632,7 +41632,7 @@
         <v>45035</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -41705,7 +41705,7 @@
         <v>44726</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -41778,7 +41778,7 @@
         <v>46042</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -41851,7 +41851,7 @@
         <v>45531</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -41924,7 +41924,7 @@
         <v>45817</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -41997,7 +41997,7 @@
         <v>46084</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -42070,7 +42070,7 @@
         <v>45839</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -42143,7 +42143,7 @@
         <v>46042</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -42216,7 +42216,7 @@
         <v>45848</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -42289,7 +42289,7 @@
         <v>46044</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -42362,7 +42362,7 @@
         <v>46044</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -42435,7 +42435,7 @@
         <v>45019</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -42508,7 +42508,7 @@
         <v>45350</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -42581,7 +42581,7 @@
         <v>46044</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -42654,7 +42654,7 @@
         <v>45434</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -42727,7 +42727,7 @@
         <v>46044</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -42800,7 +42800,7 @@
         <v>46048</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -42873,7 +42873,7 @@
         <v>46048</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -42946,7 +42946,7 @@
         <v>46048</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -43019,7 +43019,7 @@
         <v>46048</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -43092,7 +43092,7 @@
         <v>46048</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -43165,7 +43165,7 @@
         <v>46048</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -43238,7 +43238,7 @@
         <v>44900</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -43311,7 +43311,7 @@
         <v>45357</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -43384,7 +43384,7 @@
         <v>45429</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -43457,7 +43457,7 @@
         <v>46048</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -43530,7 +43530,7 @@
         <v>46048</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -43603,7 +43603,7 @@
         <v>46048</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -43676,7 +43676,7 @@
         <v>46048</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -43749,7 +43749,7 @@
         <v>46048</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -43822,7 +43822,7 @@
         <v>46048</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -43895,7 +43895,7 @@
         <v>46049</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -43968,7 +43968,7 @@
         <v>45617</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -44041,7 +44041,7 @@
         <v>46052</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -44114,7 +44114,7 @@
         <v>46052</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -44187,7 +44187,7 @@
         <v>46055</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -44260,7 +44260,7 @@
         <v>46057</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -44333,7 +44333,7 @@
         <v>46062</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -44406,7 +44406,7 @@
         <v>46062</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -44479,7 +44479,7 @@
         <v>46064</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -44552,7 +44552,7 @@
         <v>46148</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -44625,7 +44625,7 @@
         <v>46065</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -44698,7 +44698,7 @@
         <v>46070</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -44771,7 +44771,7 @@
         <v>46153</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -44844,7 +44844,7 @@
         <v>46153</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -44917,7 +44917,7 @@
         <v>46153</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -44990,7 +44990,7 @@
         <v>46153</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -45063,7 +45063,7 @@
         <v>45709</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -45136,7 +45136,7 @@
         <v>46153</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -45209,7 +45209,7 @@
         <v>46153</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -45282,7 +45282,7 @@
         <v>46153</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -45355,7 +45355,7 @@
         <v>46084</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -45428,7 +45428,7 @@
         <v>46155</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -45501,7 +45501,7 @@
         <v>46084</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -45574,7 +45574,7 @@
         <v>46087</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -45647,7 +45647,7 @@
         <v>46161</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -45725,7 +45725,7 @@
         <v>46161</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -45798,7 +45798,7 @@
         <v>46093</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -45871,7 +45871,7 @@
         <v>46093</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -45944,7 +45944,7 @@
         <v>46093</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -46017,7 +46017,7 @@
         <v>46161</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -46095,7 +46095,7 @@
         <v>46161</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -46168,7 +46168,7 @@
         <v>46161</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -46246,7 +46246,7 @@
         <v>46169</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -46319,7 +46319,7 @@
         <v>46169</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -46392,7 +46392,7 @@
         <v>46169</v>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -46465,7 +46465,7 @@
         <v>46171</v>
       </c>
       <c r="E610" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -46538,7 +46538,7 @@
         <v>46170</v>
       </c>
       <c r="E611" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
@@ -46611,7 +46611,7 @@
         <v>46174</v>
       </c>
       <c r="E612" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
@@ -46684,7 +46684,7 @@
         <v>46175</v>
       </c>
       <c r="E613" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
@@ -46757,7 +46757,7 @@
         <v>46174</v>
       </c>
       <c r="E614" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F614" t="inlineStr">
         <is>
@@ -46830,7 +46830,7 @@
         <v>46174</v>
       </c>
       <c r="E615" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F615" t="inlineStr">
         <is>
@@ -46903,7 +46903,7 @@
         <v>46178</v>
       </c>
       <c r="E616" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F616" t="inlineStr">
         <is>
@@ -46976,7 +46976,7 @@
         <v>46178</v>
       </c>
       <c r="E617" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F617" t="inlineStr">
         <is>
@@ -47049,7 +47049,7 @@
         <v>46174</v>
       </c>
       <c r="E618" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F618" t="inlineStr">
         <is>
@@ -47122,7 +47122,7 @@
         <v>46183</v>
       </c>
       <c r="E619" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F619" t="inlineStr">
         <is>
@@ -47195,7 +47195,7 @@
         <v>46185</v>
       </c>
       <c r="E620" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F620" t="inlineStr">
         <is>
@@ -47268,7 +47268,7 @@
         <v>46188</v>
       </c>
       <c r="E621" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F621" t="inlineStr">
         <is>
@@ -47341,7 +47341,7 @@
         <v>46188</v>
       </c>
       <c r="E622" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F622" t="inlineStr">
         <is>
@@ -47414,7 +47414,7 @@
         <v>46196</v>
       </c>
       <c r="E623" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F623" t="inlineStr">
         <is>
@@ -47487,7 +47487,7 @@
         <v>46199</v>
       </c>
       <c r="E624" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F624" t="inlineStr">
         <is>
@@ -47560,7 +47560,7 @@
         <v>46209</v>
       </c>
       <c r="E625" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F625" t="inlineStr">
         <is>
@@ -47633,7 +47633,7 @@
         <v>46206</v>
       </c>
       <c r="E626" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F626" t="inlineStr">
         <is>
@@ -47706,7 +47706,7 @@
         <v>46263</v>
       </c>
       <c r="E627" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F627" t="inlineStr">
         <is>
@@ -47779,7 +47779,7 @@
         <v>46224</v>
       </c>
       <c r="E628" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F628" t="inlineStr">
         <is>
@@ -47857,7 +47857,7 @@
         <v>46268</v>
       </c>
       <c r="E629" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F629" t="inlineStr">
         <is>
@@ -47930,7 +47930,7 @@
         <v>46268</v>
       </c>
       <c r="E630" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F630" t="inlineStr">
         <is>
@@ -48003,7 +48003,7 @@
         <v>46268</v>
       </c>
       <c r="E631" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F631" t="inlineStr">
         <is>
@@ -48076,7 +48076,7 @@
         <v>46272</v>
       </c>
       <c r="E632" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F632" t="inlineStr">
         <is>
@@ -48149,7 +48149,7 @@
         <v>46273</v>
       </c>
       <c r="E633" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F633" t="inlineStr">
         <is>
@@ -48222,7 +48222,7 @@
         <v>45840</v>
       </c>
       <c r="E634" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F634" t="inlineStr">
         <is>
@@ -48300,7 +48300,7 @@
         <v>46273</v>
       </c>
       <c r="E635" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F635" t="inlineStr">
         <is>
@@ -48373,7 +48373,7 @@
         <v>46272</v>
       </c>
       <c r="E636" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F636" t="inlineStr">
         <is>
@@ -48446,7 +48446,7 @@
         <v>46279</v>
       </c>
       <c r="E637" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F637" t="inlineStr">
         <is>
@@ -48519,7 +48519,7 @@
         <v>46279</v>
       </c>
       <c r="E638" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F638" t="inlineStr">
         <is>
@@ -48592,7 +48592,7 @@
         <v>46279</v>
       </c>
       <c r="E639" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F639" t="inlineStr">
         <is>
@@ -48665,7 +48665,7 @@
         <v>46036</v>
       </c>
       <c r="E640" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F640" t="inlineStr">
         <is>
@@ -48738,7 +48738,7 @@
         <v>46282</v>
       </c>
       <c r="E641" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F641" t="inlineStr">
         <is>
@@ -48811,7 +48811,7 @@
         <v>46281</v>
       </c>
       <c r="E642" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F642" t="inlineStr">
         <is>
@@ -48884,7 +48884,7 @@
         <v>45939</v>
       </c>
       <c r="E643" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F643" t="inlineStr">
         <is>
@@ -48962,7 +48962,7 @@
         <v>46241</v>
       </c>
       <c r="E644" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F644" t="inlineStr">
         <is>
@@ -49035,7 +49035,7 @@
         <v>46286</v>
       </c>
       <c r="E645" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F645" t="inlineStr">
         <is>
@@ -49108,7 +49108,7 @@
         <v>46273</v>
       </c>
       <c r="E646" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F646" t="inlineStr">
         <is>
@@ -49181,7 +49181,7 @@
         <v>46286</v>
       </c>
       <c r="E647" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F647" t="inlineStr">
         <is>
@@ -49254,7 +49254,7 @@
         <v>46283</v>
       </c>
       <c r="E648" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F648" t="inlineStr">
         <is>
@@ -49327,7 +49327,7 @@
         <v>46283</v>
       </c>
       <c r="E649" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F649" t="inlineStr">
         <is>
@@ -49400,7 +49400,7 @@
         <v>46245</v>
       </c>
       <c r="E650" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F650" t="inlineStr">
         <is>
@@ -49473,7 +49473,7 @@
         <v>46283</v>
       </c>
       <c r="E651" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F651" t="inlineStr">
         <is>
@@ -49546,7 +49546,7 @@
         <v>46030</v>
       </c>
       <c r="E652" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F652" t="inlineStr">
         <is>
@@ -49619,7 +49619,7 @@
         <v>46281</v>
       </c>
       <c r="E653" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F653" t="inlineStr">
         <is>
@@ -49692,7 +49692,7 @@
         <v>46281</v>
       </c>
       <c r="E654" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F654" t="inlineStr">
         <is>
@@ -49765,7 +49765,7 @@
         <v>46247</v>
       </c>
       <c r="E655" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F655" t="inlineStr">
         <is>
@@ -49838,7 +49838,7 @@
         <v>46224</v>
       </c>
       <c r="E656" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F656" t="inlineStr">
         <is>
@@ -49911,7 +49911,7 @@
         <v>45400</v>
       </c>
       <c r="E657" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F657" t="inlineStr">
         <is>
@@ -49984,7 +49984,7 @@
         <v>46293</v>
       </c>
       <c r="E658" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F658" t="inlineStr">
         <is>
@@ -50057,7 +50057,7 @@
         <v>46248</v>
       </c>
       <c r="E659" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F659" t="inlineStr">
         <is>
@@ -50130,7 +50130,7 @@
         <v>46292</v>
       </c>
       <c r="E660" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F660" t="inlineStr">
         <is>
@@ -50203,7 +50203,7 @@
         <v>46248</v>
       </c>
       <c r="E661" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F661" t="inlineStr">
         <is>
@@ -50276,7 +50276,7 @@
         <v>46295</v>
       </c>
       <c r="E662" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F662" t="inlineStr">
         <is>
@@ -50349,7 +50349,7 @@
         <v>46161</v>
       </c>
       <c r="E663" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F663" t="inlineStr">
         <is>
@@ -50427,7 +50427,7 @@
         <v>46244</v>
       </c>
       <c r="E664" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F664" t="inlineStr">
         <is>
@@ -50500,7 +50500,7 @@
         <v>46070</v>
       </c>
       <c r="E665" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F665" t="inlineStr">
         <is>
@@ -50573,7 +50573,7 @@
         <v>45876</v>
       </c>
       <c r="E666" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F666" t="inlineStr">
         <is>
@@ -50646,7 +50646,7 @@
         <v>46302</v>
       </c>
       <c r="E667" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F667" t="inlineStr">
         <is>
@@ -50719,7 +50719,7 @@
         <v>46302</v>
       </c>
       <c r="E668" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F668" t="inlineStr">
         <is>
@@ -50792,7 +50792,7 @@
         <v>46261</v>
       </c>
       <c r="E669" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F669" t="inlineStr">
         <is>
@@ -50865,7 +50865,7 @@
         <v>46294</v>
       </c>
       <c r="E670" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F670" t="inlineStr">
         <is>
@@ -50943,7 +50943,7 @@
         <v>46292</v>
       </c>
       <c r="E671" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F671" t="inlineStr">
         <is>
@@ -51016,7 +51016,7 @@
         <v>46292</v>
       </c>
       <c r="E672" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F672" t="inlineStr">
         <is>
@@ -51089,7 +51089,7 @@
         <v>46292</v>
       </c>
       <c r="E673" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F673" t="inlineStr">
         <is>
@@ -51162,7 +51162,7 @@
         <v>46292</v>
       </c>
       <c r="E674" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F674" t="inlineStr">
         <is>
@@ -51235,7 +51235,7 @@
         <v>46292</v>
       </c>
       <c r="E675" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F675" t="inlineStr">
         <is>
@@ -51308,7 +51308,7 @@
         <v>46261</v>
       </c>
       <c r="E676" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F676" t="inlineStr">
         <is>
@@ -51381,7 +51381,7 @@
         <v>46292</v>
       </c>
       <c r="E677" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F677" t="inlineStr">
         <is>
@@ -51454,7 +51454,7 @@
         <v>44631</v>
       </c>
       <c r="E678" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F678" t="inlineStr">
         <is>
@@ -51527,7 +51527,7 @@
         <v>44613</v>
       </c>
       <c r="E679" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F679" t="inlineStr">
         <is>
@@ -51600,7 +51600,7 @@
         <v>44608</v>
       </c>
       <c r="E680" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F680" t="inlineStr">
         <is>
@@ -51673,7 +51673,7 @@
         <v>44631</v>
       </c>
       <c r="E681" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F681" t="inlineStr">
         <is>
@@ -51746,7 +51746,7 @@
         <v>44631</v>
       </c>
       <c r="E682" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F682" t="inlineStr">
         <is>
@@ -51819,7 +51819,7 @@
         <v>45614</v>
       </c>
       <c r="E683" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F683" t="inlineStr">
         <is>
@@ -51897,7 +51897,7 @@
         <v>44743</v>
       </c>
       <c r="E684" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F684" t="inlineStr">
         <is>
@@ -51970,7 +51970,7 @@
         <v>45375</v>
       </c>
       <c r="E685" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F685" t="inlineStr">
         <is>
@@ -52043,7 +52043,7 @@
         <v>44488</v>
       </c>
       <c r="E686" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F686" t="inlineStr">
         <is>
@@ -52116,7 +52116,7 @@
         <v>45604</v>
       </c>
       <c r="E687" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F687" t="inlineStr">
         <is>
@@ -52189,7 +52189,7 @@
         <v>45356</v>
       </c>
       <c r="E688" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F688" t="inlineStr">
         <is>
@@ -52262,7 +52262,7 @@
         <v>45349</v>
       </c>
       <c r="E689" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F689" t="inlineStr">
         <is>
@@ -52335,7 +52335,7 @@
         <v>45744</v>
       </c>
       <c r="E690" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F690" t="inlineStr">
         <is>
@@ -52408,7 +52408,7 @@
         <v>45714</v>
       </c>
       <c r="E691" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F691" t="inlineStr">
         <is>
@@ -52481,7 +52481,7 @@
         <v>45715</v>
       </c>
       <c r="E692" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F692" t="inlineStr">
         <is>
@@ -52554,7 +52554,7 @@
         <v>45709</v>
       </c>
       <c r="E693" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F693" t="inlineStr">
         <is>
@@ -52627,7 +52627,7 @@
         <v>45714</v>
       </c>
       <c r="E694" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F694" t="inlineStr">
         <is>
@@ -52700,7 +52700,7 @@
         <v>45813</v>
       </c>
       <c r="E695" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F695" t="inlineStr">
         <is>
@@ -52773,7 +52773,7 @@
         <v>45813</v>
       </c>
       <c r="E696" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F696" t="inlineStr">
         <is>
@@ -52846,7 +52846,7 @@
         <v>45813</v>
       </c>
       <c r="E697" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F697" t="inlineStr">
         <is>
@@ -52919,7 +52919,7 @@
         <v>45820</v>
       </c>
       <c r="E698" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F698" t="inlineStr">
         <is>
@@ -52992,7 +52992,7 @@
         <v>45827</v>
       </c>
       <c r="E699" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F699" t="inlineStr">
         <is>
@@ -53065,7 +53065,7 @@
         <v>45845</v>
       </c>
       <c r="E700" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F700" t="inlineStr">
         <is>
@@ -53138,7 +53138,7 @@
         <v>45883</v>
       </c>
       <c r="E701" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F701" t="inlineStr">
         <is>
@@ -53211,7 +53211,7 @@
         <v>45915</v>
       </c>
       <c r="E702" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F702" t="inlineStr">
         <is>
@@ -53284,7 +53284,7 @@
         <v>46041</v>
       </c>
       <c r="E703" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F703" t="inlineStr">
         <is>
@@ -53357,7 +53357,7 @@
         <v>46133</v>
       </c>
       <c r="E704" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F704" t="inlineStr">
         <is>
@@ -53430,7 +53430,7 @@
         <v>46147</v>
       </c>
       <c r="E705" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F705" t="inlineStr">
         <is>
@@ -53503,7 +53503,7 @@
         <v>46211</v>
       </c>
       <c r="E706" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F706" t="inlineStr">
         <is>
@@ -53576,7 +53576,7 @@
         <v>46290</v>
       </c>
       <c r="E707" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F707" t="inlineStr">
         <is>
@@ -53649,7 +53649,7 @@
         <v>46253</v>
       </c>
       <c r="E708" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F708" t="inlineStr">
         <is>

--- a/Översikt HYLTE.xlsx
+++ b/Översikt HYLTE.xlsx
@@ -601,7 +601,7 @@
         <v>46090</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -718,7 +718,7 @@
         <v>45265</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -834,7 +834,7 @@
         <v>46066</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -945,7 +945,7 @@
         <v>44873</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1054,7 +1054,7 @@
         <v>45348</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1166,7 +1166,7 @@
         <v>45719</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1274,7 +1274,7 @@
         <v>45245</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1385,7 +1385,7 @@
         <v>46268</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1492,7 +1492,7 @@
         <v>45230</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1599,7 +1599,7 @@
         <v>45737</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1706,7 +1706,7 @@
         <v>46141</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1813,7 +1813,7 @@
         <v>46161</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1920,7 +1920,7 @@
         <v>44839</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2030,7 +2030,7 @@
         <v>46048</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2136,7 +2136,7 @@
         <v>45904</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2246,7 +2246,7 @@
         <v>46304</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2356,7 +2356,7 @@
         <v>45841</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2466,7 +2466,7 @@
         <v>45099</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2576,7 +2576,7 @@
         <v>46130</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2682,7 +2682,7 @@
         <v>44648</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2787,7 +2787,7 @@
         <v>44651</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2892,7 +2892,7 @@
         <v>44876</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2997,7 +2997,7 @@
         <v>45245</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3102,7 +3102,7 @@
         <v>45343</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3207,7 +3207,7 @@
         <v>45476</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3317,7 +3317,7 @@
         <v>45163</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3422,7 +3422,7 @@
         <v>45299</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3531,7 +3531,7 @@
         <v>45245</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3636,7 +3636,7 @@
         <v>45593</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3741,7 +3741,7 @@
         <v>45153</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3855,7 +3855,7 @@
         <v>45186</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3960,7 +3960,7 @@
         <v>45085</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4069,7 +4069,7 @@
         <v>45617</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4174,7 +4174,7 @@
         <v>45253</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4279,7 +4279,7 @@
         <v>45754</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4384,7 +4384,7 @@
         <v>46253</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4494,7 +4494,7 @@
         <v>44810</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4567,7 +4567,7 @@
         <v>44600</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4640,7 +4640,7 @@
         <v>44529</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4713,7 +4713,7 @@
         <v>44557</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4786,7 +4786,7 @@
         <v>44705</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4859,7 +4859,7 @@
         <v>44778</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4932,7 +4932,7 @@
         <v>44488</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5005,7 +5005,7 @@
         <v>44624</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5078,7 +5078,7 @@
         <v>44812</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5151,7 +5151,7 @@
         <v>44638</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5224,7 +5224,7 @@
         <v>44498</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5297,7 +5297,7 @@
         <v>44845</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5370,7 +5370,7 @@
         <v>44559</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5443,7 +5443,7 @@
         <v>44578</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5516,7 +5516,7 @@
         <v>44659</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5594,7 +5594,7 @@
         <v>44756</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5667,7 +5667,7 @@
         <v>44501</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5740,7 +5740,7 @@
         <v>44651</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5813,7 +5813,7 @@
         <v>44711</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5886,7 +5886,7 @@
         <v>44487</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5964,7 +5964,7 @@
         <v>44735</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6037,7 +6037,7 @@
         <v>44489</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6110,7 +6110,7 @@
         <v>44834</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6183,7 +6183,7 @@
         <v>44796</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6256,7 +6256,7 @@
         <v>44502</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6329,7 +6329,7 @@
         <v>44631</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6402,7 +6402,7 @@
         <v>44876</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6475,7 +6475,7 @@
         <v>44659</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6548,7 +6548,7 @@
         <v>44644</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6621,7 +6621,7 @@
         <v>44515</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6699,7 +6699,7 @@
         <v>44778</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6772,7 +6772,7 @@
         <v>44867</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6845,7 +6845,7 @@
         <v>44505</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6918,7 +6918,7 @@
         <v>44634</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6991,7 +6991,7 @@
         <v>44728</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7064,7 +7064,7 @@
         <v>44714</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7137,7 +7137,7 @@
         <v>44795</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7210,7 +7210,7 @@
         <v>44818</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7283,7 +7283,7 @@
         <v>44801</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7356,7 +7356,7 @@
         <v>44596</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7434,7 +7434,7 @@
         <v>44644</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7507,7 +7507,7 @@
         <v>44523</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7580,7 +7580,7 @@
         <v>44500</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7653,7 +7653,7 @@
         <v>44727</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7726,7 +7726,7 @@
         <v>44705</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7799,7 +7799,7 @@
         <v>44659</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7877,7 +7877,7 @@
         <v>44659</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7955,7 +7955,7 @@
         <v>44757</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8028,7 +8028,7 @@
         <v>44494</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8101,7 +8101,7 @@
         <v>44495</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8174,7 +8174,7 @@
         <v>45460</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8247,7 +8247,7 @@
         <v>44487</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8325,7 +8325,7 @@
         <v>45132</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8398,7 +8398,7 @@
         <v>44851</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8471,7 +8471,7 @@
         <v>44851</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8544,7 +8544,7 @@
         <v>45715</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8617,7 +8617,7 @@
         <v>44714</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8695,7 +8695,7 @@
         <v>45002</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8768,7 +8768,7 @@
         <v>45568</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8841,7 +8841,7 @@
         <v>45062</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8914,7 +8914,7 @@
         <v>44900</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8992,7 +8992,7 @@
         <v>45107</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -9065,7 +9065,7 @@
         <v>44958</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9138,7 +9138,7 @@
         <v>44559</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9211,7 +9211,7 @@
         <v>45211</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9284,7 +9284,7 @@
         <v>44899</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9357,7 +9357,7 @@
         <v>45548</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9430,7 +9430,7 @@
         <v>45258</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9503,7 +9503,7 @@
         <v>45229</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9576,7 +9576,7 @@
         <v>45589</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9649,7 +9649,7 @@
         <v>45254</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9722,7 +9722,7 @@
         <v>45254</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9795,7 +9795,7 @@
         <v>45098</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9873,7 +9873,7 @@
         <v>45254</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9946,7 +9946,7 @@
         <v>45254</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -10019,7 +10019,7 @@
         <v>44910</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -10092,7 +10092,7 @@
         <v>44823</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10165,7 +10165,7 @@
         <v>45104</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10238,7 +10238,7 @@
         <v>45684</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10311,7 +10311,7 @@
         <v>45539</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10384,7 +10384,7 @@
         <v>45538</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10457,7 +10457,7 @@
         <v>44868</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10530,7 +10530,7 @@
         <v>45600</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10603,7 +10603,7 @@
         <v>45352</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10676,7 +10676,7 @@
         <v>45352</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10749,7 +10749,7 @@
         <v>44719</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -10822,7 +10822,7 @@
         <v>44896</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10895,7 +10895,7 @@
         <v>45638</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10968,7 +10968,7 @@
         <v>45434</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -11041,7 +11041,7 @@
         <v>45163</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -11114,7 +11114,7 @@
         <v>45089</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11187,7 +11187,7 @@
         <v>45145</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11260,7 +11260,7 @@
         <v>45252</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11333,7 +11333,7 @@
         <v>45194</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11406,7 +11406,7 @@
         <v>44495</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11479,7 +11479,7 @@
         <v>44901</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11552,7 +11552,7 @@
         <v>45181</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11625,7 +11625,7 @@
         <v>45694</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11698,7 +11698,7 @@
         <v>45310</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -11771,7 +11771,7 @@
         <v>45441</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -11849,7 +11849,7 @@
         <v>45441</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -11922,7 +11922,7 @@
         <v>45229</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -11995,7 +11995,7 @@
         <v>44701</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -12073,7 +12073,7 @@
         <v>45527</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -12146,7 +12146,7 @@
         <v>44999</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12219,7 +12219,7 @@
         <v>45182</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12292,7 +12292,7 @@
         <v>44847</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12365,7 +12365,7 @@
         <v>44778</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12438,7 +12438,7 @@
         <v>45132</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -12511,7 +12511,7 @@
         <v>45173</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -12584,7 +12584,7 @@
         <v>45478</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -12657,7 +12657,7 @@
         <v>45019</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -12730,7 +12730,7 @@
         <v>45254</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -12803,7 +12803,7 @@
         <v>45331</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -12876,7 +12876,7 @@
         <v>45287</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -12949,7 +12949,7 @@
         <v>45817</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -13022,7 +13022,7 @@
         <v>45782</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -13095,7 +13095,7 @@
         <v>45673</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -13168,7 +13168,7 @@
         <v>45366</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13241,7 +13241,7 @@
         <v>46084</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13314,7 +13314,7 @@
         <v>45245</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13387,7 +13387,7 @@
         <v>45834</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -13460,7 +13460,7 @@
         <v>45485</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -13533,7 +13533,7 @@
         <v>45560</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -13606,7 +13606,7 @@
         <v>45436</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -13679,7 +13679,7 @@
         <v>44699</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -13752,7 +13752,7 @@
         <v>45790</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -13825,7 +13825,7 @@
         <v>45674</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -13898,7 +13898,7 @@
         <v>45748</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -13971,7 +13971,7 @@
         <v>45890</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -14044,7 +14044,7 @@
         <v>45891</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -14122,7 +14122,7 @@
         <v>45891</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -14200,7 +14200,7 @@
         <v>45531</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14273,7 +14273,7 @@
         <v>45775</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14346,7 +14346,7 @@
         <v>45840</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -14419,7 +14419,7 @@
         <v>44865</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -14492,7 +14492,7 @@
         <v>45897</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -14565,7 +14565,7 @@
         <v>45840</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -14643,7 +14643,7 @@
         <v>45848</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -14716,7 +14716,7 @@
         <v>45839</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -14789,7 +14789,7 @@
         <v>45898</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -14862,7 +14862,7 @@
         <v>45897</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -14935,7 +14935,7 @@
         <v>45617</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -15008,7 +15008,7 @@
         <v>45454</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -15081,7 +15081,7 @@
         <v>44701</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -15159,7 +15159,7 @@
         <v>45300</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -15232,7 +15232,7 @@
         <v>45905</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -15305,7 +15305,7 @@
         <v>45838</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -15378,7 +15378,7 @@
         <v>45456</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -15451,7 +15451,7 @@
         <v>45910</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -15524,7 +15524,7 @@
         <v>45910</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -15597,7 +15597,7 @@
         <v>45429</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -15670,7 +15670,7 @@
         <v>45405</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -15743,7 +15743,7 @@
         <v>44797</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -15816,7 +15816,7 @@
         <v>45035</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -15889,7 +15889,7 @@
         <v>45918</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -15962,7 +15962,7 @@
         <v>45259</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -16035,7 +16035,7 @@
         <v>45169</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -16108,7 +16108,7 @@
         <v>45104</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -16181,7 +16181,7 @@
         <v>45922</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -16254,7 +16254,7 @@
         <v>44900</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -16327,7 +16327,7 @@
         <v>45922</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -16400,7 +16400,7 @@
         <v>45922</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -16473,7 +16473,7 @@
         <v>45924</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -16546,7 +16546,7 @@
         <v>44974</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -16619,7 +16619,7 @@
         <v>45926</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -16692,7 +16692,7 @@
         <v>46148</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -16765,7 +16765,7 @@
         <v>45162</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -16838,7 +16838,7 @@
         <v>45926</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -16911,7 +16911,7 @@
         <v>45926</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -16984,7 +16984,7 @@
         <v>45929</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -17057,7 +17057,7 @@
         <v>44694</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -17130,7 +17130,7 @@
         <v>45502</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -17203,7 +17203,7 @@
         <v>44974</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -17276,7 +17276,7 @@
         <v>45091</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -17349,7 +17349,7 @@
         <v>45931</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -17422,7 +17422,7 @@
         <v>46153</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -17495,7 +17495,7 @@
         <v>45930</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -17568,7 +17568,7 @@
         <v>45931</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -17641,7 +17641,7 @@
         <v>46153</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -17714,7 +17714,7 @@
         <v>46153</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -17787,7 +17787,7 @@
         <v>46153</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -17860,7 +17860,7 @@
         <v>46153</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -17933,7 +17933,7 @@
         <v>45933</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -18006,7 +18006,7 @@
         <v>45933</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -18079,7 +18079,7 @@
         <v>45933</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -18152,7 +18152,7 @@
         <v>46153</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -18225,7 +18225,7 @@
         <v>46153</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -18298,7 +18298,7 @@
         <v>45936</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -18371,7 +18371,7 @@
         <v>45936</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -18444,7 +18444,7 @@
         <v>45936</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -18517,7 +18517,7 @@
         <v>45709</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -18590,7 +18590,7 @@
         <v>44926</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -18668,7 +18668,7 @@
         <v>45604</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -18741,7 +18741,7 @@
         <v>45097</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -18814,7 +18814,7 @@
         <v>45477</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -18887,7 +18887,7 @@
         <v>45938</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -18960,7 +18960,7 @@
         <v>45265</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -19033,7 +19033,7 @@
         <v>45937</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -19106,7 +19106,7 @@
         <v>45084</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -19179,7 +19179,7 @@
         <v>45944</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -19252,7 +19252,7 @@
         <v>44953</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -19325,7 +19325,7 @@
         <v>45019</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -19398,7 +19398,7 @@
         <v>45299</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -19471,7 +19471,7 @@
         <v>45645</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -19544,7 +19544,7 @@
         <v>45366</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -19622,7 +19622,7 @@
         <v>45957</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -19695,7 +19695,7 @@
         <v>46155</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -19768,7 +19768,7 @@
         <v>44903</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -19841,7 +19841,7 @@
         <v>45961</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -19914,7 +19914,7 @@
         <v>45922</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -19987,7 +19987,7 @@
         <v>45096</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -20060,7 +20060,7 @@
         <v>45167</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -20133,7 +20133,7 @@
         <v>46161</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -20211,7 +20211,7 @@
         <v>46161</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -20284,7 +20284,7 @@
         <v>45961</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -20357,7 +20357,7 @@
         <v>45751</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -20435,7 +20435,7 @@
         <v>45352</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -20508,7 +20508,7 @@
         <v>46161</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -20586,7 +20586,7 @@
         <v>45254</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -20659,7 +20659,7 @@
         <v>45254</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -20732,7 +20732,7 @@
         <v>46161</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -20805,7 +20805,7 @@
         <v>46161</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -20883,7 +20883,7 @@
         <v>45203</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -20956,7 +20956,7 @@
         <v>45972</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -21029,7 +21029,7 @@
         <v>45972</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -21102,7 +21102,7 @@
         <v>44750</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -21175,7 +21175,7 @@
         <v>45972</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -21248,7 +21248,7 @@
         <v>44714</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -21321,7 +21321,7 @@
         <v>45441</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -21394,7 +21394,7 @@
         <v>45441</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -21467,7 +21467,7 @@
         <v>45441</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -21540,7 +21540,7 @@
         <v>45377</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -21618,7 +21618,7 @@
         <v>45979</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -21691,7 +21691,7 @@
         <v>45170</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -21764,7 +21764,7 @@
         <v>45981</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -21837,7 +21837,7 @@
         <v>45981</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -21910,7 +21910,7 @@
         <v>44869</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -21983,7 +21983,7 @@
         <v>45754</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -22056,7 +22056,7 @@
         <v>45268</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -22129,7 +22129,7 @@
         <v>45441</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -22207,7 +22207,7 @@
         <v>45597</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -22280,7 +22280,7 @@
         <v>45092</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -22353,7 +22353,7 @@
         <v>45987</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -22426,7 +22426,7 @@
         <v>45989</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -22499,7 +22499,7 @@
         <v>45378</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -22572,7 +22572,7 @@
         <v>46169</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -22645,7 +22645,7 @@
         <v>45382</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -22718,7 +22718,7 @@
         <v>46169</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -22791,7 +22791,7 @@
         <v>46169</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -22864,7 +22864,7 @@
         <v>45995</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -22937,7 +22937,7 @@
         <v>45429</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -23010,7 +23010,7 @@
         <v>45371</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -23083,7 +23083,7 @@
         <v>45411</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -23156,7 +23156,7 @@
         <v>45558</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -23229,7 +23229,7 @@
         <v>44950</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -23302,7 +23302,7 @@
         <v>45246</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -23375,7 +23375,7 @@
         <v>45246</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -23448,7 +23448,7 @@
         <v>44697</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -23521,7 +23521,7 @@
         <v>46170</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -23594,7 +23594,7 @@
         <v>45926</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -23667,7 +23667,7 @@
         <v>45351</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -23740,7 +23740,7 @@
         <v>46171</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -23813,7 +23813,7 @@
         <v>45580</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -23886,7 +23886,7 @@
         <v>45159</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -23959,7 +23959,7 @@
         <v>45541</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -24032,7 +24032,7 @@
         <v>46174</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -24105,7 +24105,7 @@
         <v>44635</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -24183,7 +24183,7 @@
         <v>45462</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -24256,7 +24256,7 @@
         <v>44539</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -24329,7 +24329,7 @@
         <v>45042</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -24402,7 +24402,7 @@
         <v>46174</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -24475,7 +24475,7 @@
         <v>45352</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -24548,7 +24548,7 @@
         <v>46020</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -24621,7 +24621,7 @@
         <v>44970</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -24694,7 +24694,7 @@
         <v>45568</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -24767,7 +24767,7 @@
         <v>45145</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -24840,7 +24840,7 @@
         <v>44510</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -24913,7 +24913,7 @@
         <v>45624</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -24986,7 +24986,7 @@
         <v>45170</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -25059,7 +25059,7 @@
         <v>44965</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -25137,7 +25137,7 @@
         <v>46175</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -25210,7 +25210,7 @@
         <v>45257</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -25283,7 +25283,7 @@
         <v>46174</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -25356,7 +25356,7 @@
         <v>46174</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -25429,7 +25429,7 @@
         <v>46178</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -25502,7 +25502,7 @@
         <v>46178</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -25575,7 +25575,7 @@
         <v>45538</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -25648,7 +25648,7 @@
         <v>45456</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -25721,7 +25721,7 @@
         <v>46042</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -25794,7 +25794,7 @@
         <v>46042</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -25867,7 +25867,7 @@
         <v>46044</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -25940,7 +25940,7 @@
         <v>46044</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -26013,7 +26013,7 @@
         <v>46044</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -26086,7 +26086,7 @@
         <v>46044</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -26159,7 +26159,7 @@
         <v>46048</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -26232,7 +26232,7 @@
         <v>46049</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -26305,7 +26305,7 @@
         <v>46048</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -26378,7 +26378,7 @@
         <v>46048</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -26451,7 +26451,7 @@
         <v>46048</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -26524,7 +26524,7 @@
         <v>46048</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -26597,7 +26597,7 @@
         <v>46048</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -26670,7 +26670,7 @@
         <v>46048</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -26743,7 +26743,7 @@
         <v>46048</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -26816,7 +26816,7 @@
         <v>46048</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -26889,7 +26889,7 @@
         <v>46048</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -26962,7 +26962,7 @@
         <v>46048</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -27035,7 +27035,7 @@
         <v>46048</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -27108,7 +27108,7 @@
         <v>45182</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -27181,7 +27181,7 @@
         <v>44489</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -27254,7 +27254,7 @@
         <v>45456</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -27327,7 +27327,7 @@
         <v>46052</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -27400,7 +27400,7 @@
         <v>46183</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -27473,7 +27473,7 @@
         <v>46055</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -27546,7 +27546,7 @@
         <v>46052</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -27619,7 +27619,7 @@
         <v>45198</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -27692,7 +27692,7 @@
         <v>45752</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -27770,7 +27770,7 @@
         <v>44735</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -27843,7 +27843,7 @@
         <v>46057</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -27916,7 +27916,7 @@
         <v>46062</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -27989,7 +27989,7 @@
         <v>46062</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -28062,7 +28062,7 @@
         <v>46064</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -28135,7 +28135,7 @@
         <v>45153</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -28208,7 +28208,7 @@
         <v>46065</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -28281,7 +28281,7 @@
         <v>45568</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -28354,7 +28354,7 @@
         <v>46185</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -28427,7 +28427,7 @@
         <v>46070</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -28500,7 +28500,7 @@
         <v>44970</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -28573,7 +28573,7 @@
         <v>44970</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -28646,7 +28646,7 @@
         <v>44641</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -28719,7 +28719,7 @@
         <v>45342</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -28797,7 +28797,7 @@
         <v>45737</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -28870,7 +28870,7 @@
         <v>45483</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -28943,7 +28943,7 @@
         <v>45061</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -29016,7 +29016,7 @@
         <v>44893</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -29089,7 +29089,7 @@
         <v>46188</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -29162,7 +29162,7 @@
         <v>46188</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -29235,7 +29235,7 @@
         <v>46084</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -29308,7 +29308,7 @@
         <v>45084</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -29381,7 +29381,7 @@
         <v>46084</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -29454,7 +29454,7 @@
         <v>44900</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -29527,7 +29527,7 @@
         <v>46087</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -29600,7 +29600,7 @@
         <v>45572</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -29673,7 +29673,7 @@
         <v>45002</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -29746,7 +29746,7 @@
         <v>46093</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -29819,7 +29819,7 @@
         <v>46093</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -29892,7 +29892,7 @@
         <v>44847</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -29965,7 +29965,7 @@
         <v>46093</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -30038,7 +30038,7 @@
         <v>45432</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -30111,7 +30111,7 @@
         <v>46196</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -30184,7 +30184,7 @@
         <v>45677</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -30257,7 +30257,7 @@
         <v>46057</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -30330,7 +30330,7 @@
         <v>46057</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -30403,7 +30403,7 @@
         <v>45253</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -30476,7 +30476,7 @@
         <v>45253</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -30549,7 +30549,7 @@
         <v>46199</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -30622,7 +30622,7 @@
         <v>46111</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -30695,7 +30695,7 @@
         <v>46111</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -30768,7 +30768,7 @@
         <v>46111</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -30841,7 +30841,7 @@
         <v>45104</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -30914,7 +30914,7 @@
         <v>45715</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -30987,7 +30987,7 @@
         <v>45117</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -31060,7 +31060,7 @@
         <v>46120</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -31133,7 +31133,7 @@
         <v>45357</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -31206,7 +31206,7 @@
         <v>46120</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -31279,7 +31279,7 @@
         <v>45107</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -31352,7 +31352,7 @@
         <v>46122</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -31425,7 +31425,7 @@
         <v>46121</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -31498,7 +31498,7 @@
         <v>46121</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -31571,7 +31571,7 @@
         <v>46121</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -31644,7 +31644,7 @@
         <v>46122</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -31717,7 +31717,7 @@
         <v>46122</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -31790,7 +31790,7 @@
         <v>46121</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -31863,7 +31863,7 @@
         <v>46122</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -31936,7 +31936,7 @@
         <v>46121</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -32009,7 +32009,7 @@
         <v>46121</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -32082,7 +32082,7 @@
         <v>46121</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -32155,7 +32155,7 @@
         <v>46121</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -32228,7 +32228,7 @@
         <v>45267</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -32301,7 +32301,7 @@
         <v>46128</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -32374,7 +32374,7 @@
         <v>44726</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -32447,7 +32447,7 @@
         <v>45351</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -32520,7 +32520,7 @@
         <v>45426</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -32593,7 +32593,7 @@
         <v>44872</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -32666,7 +32666,7 @@
         <v>45456</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -32739,7 +32739,7 @@
         <v>45091</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -32812,7 +32812,7 @@
         <v>45989</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -32885,7 +32885,7 @@
         <v>45462</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -32958,7 +32958,7 @@
         <v>46209</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -33031,7 +33031,7 @@
         <v>45839</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -33104,7 +33104,7 @@
         <v>46206</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -33177,7 +33177,7 @@
         <v>45524</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -33250,7 +33250,7 @@
         <v>45114</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -33323,7 +33323,7 @@
         <v>45225</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -33396,7 +33396,7 @@
         <v>45246</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -33469,7 +33469,7 @@
         <v>45316</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -33547,7 +33547,7 @@
         <v>44601</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -33620,7 +33620,7 @@
         <v>44575</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -33693,7 +33693,7 @@
         <v>45170</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -33766,7 +33766,7 @@
         <v>45334</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -33839,7 +33839,7 @@
         <v>45169</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -33912,7 +33912,7 @@
         <v>44729</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -33985,7 +33985,7 @@
         <v>44796</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -34058,7 +34058,7 @@
         <v>44995</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -34131,7 +34131,7 @@
         <v>44951</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -34204,7 +34204,7 @@
         <v>45110</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -34277,7 +34277,7 @@
         <v>45432</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -34350,7 +34350,7 @@
         <v>46224</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -34428,7 +34428,7 @@
         <v>44530</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -34501,7 +34501,7 @@
         <v>44980</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -34574,7 +34574,7 @@
         <v>45350</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -34647,7 +34647,7 @@
         <v>45229</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -34720,7 +34720,7 @@
         <v>46273</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -34793,7 +34793,7 @@
         <v>46272</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -34866,7 +34866,7 @@
         <v>46272</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -34939,7 +34939,7 @@
         <v>45840</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -35017,7 +35017,7 @@
         <v>45245</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -35090,7 +35090,7 @@
         <v>46273</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -35163,7 +35163,7 @@
         <v>45531</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -35236,7 +35236,7 @@
         <v>45352</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -35309,7 +35309,7 @@
         <v>45208</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -35382,7 +35382,7 @@
         <v>45110</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -35455,7 +35455,7 @@
         <v>44756</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -35528,7 +35528,7 @@
         <v>45390</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -35601,7 +35601,7 @@
         <v>45238</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -35674,7 +35674,7 @@
         <v>46279</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -35747,7 +35747,7 @@
         <v>44866</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -35820,7 +35820,7 @@
         <v>46279</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -35893,7 +35893,7 @@
         <v>46279</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -35966,7 +35966,7 @@
         <v>46036</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -36039,7 +36039,7 @@
         <v>45406</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -36112,7 +36112,7 @@
         <v>45414</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -36185,7 +36185,7 @@
         <v>45229</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -36258,7 +36258,7 @@
         <v>44651</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -36331,7 +36331,7 @@
         <v>45092</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -36404,7 +36404,7 @@
         <v>45455</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -36477,7 +36477,7 @@
         <v>46281</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -36550,7 +36550,7 @@
         <v>45051</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -36623,7 +36623,7 @@
         <v>46282</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -36696,7 +36696,7 @@
         <v>45770</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -36769,7 +36769,7 @@
         <v>46241</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -36842,7 +36842,7 @@
         <v>46273</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -36915,7 +36915,7 @@
         <v>45671</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -36988,7 +36988,7 @@
         <v>46283</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -37061,7 +37061,7 @@
         <v>45939</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -37139,7 +37139,7 @@
         <v>44813</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -37212,7 +37212,7 @@
         <v>45162</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -37285,7 +37285,7 @@
         <v>45254</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -37358,7 +37358,7 @@
         <v>46286</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -37431,7 +37431,7 @@
         <v>46281</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -37504,7 +37504,7 @@
         <v>46283</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -37577,7 +37577,7 @@
         <v>46030</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -37650,7 +37650,7 @@
         <v>46281</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -37723,7 +37723,7 @@
         <v>46283</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -37796,7 +37796,7 @@
         <v>46286</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -37869,7 +37869,7 @@
         <v>44900</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -37942,7 +37942,7 @@
         <v>46224</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -38015,7 +38015,7 @@
         <v>44893</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -38088,7 +38088,7 @@
         <v>45327</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -38161,7 +38161,7 @@
         <v>45624</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -38234,7 +38234,7 @@
         <v>46247</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -38307,7 +38307,7 @@
         <v>46245</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -38380,7 +38380,7 @@
         <v>44712</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -38453,7 +38453,7 @@
         <v>44834</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -38526,7 +38526,7 @@
         <v>45400</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -38599,7 +38599,7 @@
         <v>45229</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -38672,7 +38672,7 @@
         <v>44967</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -38745,7 +38745,7 @@
         <v>46293</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -38818,7 +38818,7 @@
         <v>45544</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -38891,7 +38891,7 @@
         <v>46248</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -38964,7 +38964,7 @@
         <v>45715</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -39037,7 +39037,7 @@
         <v>46248</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -39110,7 +39110,7 @@
         <v>45700</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -39183,7 +39183,7 @@
         <v>46292</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -39256,7 +39256,7 @@
         <v>45316</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -39329,7 +39329,7 @@
         <v>45643</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -39402,7 +39402,7 @@
         <v>44900</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -39475,7 +39475,7 @@
         <v>45368</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -39553,7 +39553,7 @@
         <v>45371</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -39626,7 +39626,7 @@
         <v>45371</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -39699,7 +39699,7 @@
         <v>45254</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -39772,7 +39772,7 @@
         <v>46244</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -39845,7 +39845,7 @@
         <v>46295</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -39918,7 +39918,7 @@
         <v>45229</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -39991,7 +39991,7 @@
         <v>45035</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -40064,7 +40064,7 @@
         <v>45299</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -40137,7 +40137,7 @@
         <v>45176</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -40215,7 +40215,7 @@
         <v>45638</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -40288,7 +40288,7 @@
         <v>45588</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -40366,7 +40366,7 @@
         <v>46070</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -40439,7 +40439,7 @@
         <v>45876</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -40512,7 +40512,7 @@
         <v>45510</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -40585,7 +40585,7 @@
         <v>45559</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -40658,7 +40658,7 @@
         <v>46161</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -40736,7 +40736,7 @@
         <v>45783</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -40809,7 +40809,7 @@
         <v>45616</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -40882,7 +40882,7 @@
         <v>45483</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -40955,7 +40955,7 @@
         <v>45680</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -41028,7 +41028,7 @@
         <v>45616</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -41101,7 +41101,7 @@
         <v>46292</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -41174,7 +41174,7 @@
         <v>45225</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -41247,7 +41247,7 @@
         <v>45618</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -41320,7 +41320,7 @@
         <v>45726</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -41393,7 +41393,7 @@
         <v>45483</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -41466,7 +41466,7 @@
         <v>45589</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -41544,7 +41544,7 @@
         <v>45391</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -41617,7 +41617,7 @@
         <v>45786</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -41695,7 +41695,7 @@
         <v>46292</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -41768,7 +41768,7 @@
         <v>46292</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -41841,7 +41841,7 @@
         <v>46292</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -41914,7 +41914,7 @@
         <v>46292</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -41987,7 +41987,7 @@
         <v>46302</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -42060,7 +42060,7 @@
         <v>46302</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -42133,7 +42133,7 @@
         <v>45590</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -42206,7 +42206,7 @@
         <v>46294</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -42284,7 +42284,7 @@
         <v>45609</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -42357,7 +42357,7 @@
         <v>45743</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -42435,7 +42435,7 @@
         <v>46292</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -42508,7 +42508,7 @@
         <v>45743</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -42586,7 +42586,7 @@
         <v>45741</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -42659,7 +42659,7 @@
         <v>45793</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -42732,7 +42732,7 @@
         <v>45559</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -42805,7 +42805,7 @@
         <v>45681</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -42878,7 +42878,7 @@
         <v>46261</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -42951,7 +42951,7 @@
         <v>45743</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -43029,7 +43029,7 @@
         <v>46261</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -43102,7 +43102,7 @@
         <v>44851</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -43175,7 +43175,7 @@
         <v>46263</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -43248,7 +43248,7 @@
         <v>45806</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -43321,7 +43321,7 @@
         <v>45609</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -43394,7 +43394,7 @@
         <v>45812</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -43467,7 +43467,7 @@
         <v>46268</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -43540,7 +43540,7 @@
         <v>46268</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -43613,7 +43613,7 @@
         <v>45706</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -43686,7 +43686,7 @@
         <v>45694</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -43759,7 +43759,7 @@
         <v>45708</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -43832,7 +43832,7 @@
         <v>45597</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -43905,7 +43905,7 @@
         <v>45387</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -43978,7 +43978,7 @@
         <v>45730</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -44051,7 +44051,7 @@
         <v>45820</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -44124,7 +44124,7 @@
         <v>44900</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -44197,7 +44197,7 @@
         <v>45825</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -44270,7 +44270,7 @@
         <v>45548</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -44343,7 +44343,7 @@
         <v>46268</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -44416,7 +44416,7 @@
         <v>45831</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -44489,7 +44489,7 @@
         <v>45601</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -44562,7 +44562,7 @@
         <v>45835</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -44635,7 +44635,7 @@
         <v>45838</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -44708,7 +44708,7 @@
         <v>45836</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -44781,7 +44781,7 @@
         <v>45840</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -44854,7 +44854,7 @@
         <v>45840</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -44927,7 +44927,7 @@
         <v>45840</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -45000,7 +45000,7 @@
         <v>45800</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -45073,7 +45073,7 @@
         <v>45847</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -45146,7 +45146,7 @@
         <v>45847</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -45219,7 +45219,7 @@
         <v>45845</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -45292,7 +45292,7 @@
         <v>45845</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -45365,7 +45365,7 @@
         <v>45846</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -45443,7 +45443,7 @@
         <v>45846</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -45521,7 +45521,7 @@
         <v>45846</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -45599,7 +45599,7 @@
         <v>45803</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -45672,7 +45672,7 @@
         <v>45700</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -45745,7 +45745,7 @@
         <v>45700</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -45818,7 +45818,7 @@
         <v>45687</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -45891,7 +45891,7 @@
         <v>45190</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -45964,7 +45964,7 @@
         <v>45293</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -46037,7 +46037,7 @@
         <v>45392</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -46110,7 +46110,7 @@
         <v>45145</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -46183,7 +46183,7 @@
         <v>45623</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -46256,7 +46256,7 @@
         <v>44917</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -46329,7 +46329,7 @@
         <v>45190</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -46407,7 +46407,7 @@
         <v>45517</v>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -46480,7 +46480,7 @@
         <v>45545</v>
       </c>
       <c r="E610" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -46553,7 +46553,7 @@
         <v>45204</v>
       </c>
       <c r="E611" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
@@ -46626,7 +46626,7 @@
         <v>45395</v>
       </c>
       <c r="E612" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
@@ -46699,7 +46699,7 @@
         <v>45541</v>
       </c>
       <c r="E613" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
@@ -46772,7 +46772,7 @@
         <v>45677</v>
       </c>
       <c r="E614" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F614" t="inlineStr">
         <is>
@@ -46845,7 +46845,7 @@
         <v>45727</v>
       </c>
       <c r="E615" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F615" t="inlineStr">
         <is>
@@ -46918,7 +46918,7 @@
         <v>45252</v>
       </c>
       <c r="E616" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F616" t="inlineStr">
         <is>
@@ -46991,7 +46991,7 @@
         <v>45257</v>
       </c>
       <c r="E617" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F617" t="inlineStr">
         <is>
@@ -47064,7 +47064,7 @@
         <v>45309</v>
       </c>
       <c r="E618" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F618" t="inlineStr">
         <is>
@@ -47137,7 +47137,7 @@
         <v>45245</v>
       </c>
       <c r="E619" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F619" t="inlineStr">
         <is>
@@ -47210,7 +47210,7 @@
         <v>45288</v>
       </c>
       <c r="E620" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F620" t="inlineStr">
         <is>
@@ -47288,7 +47288,7 @@
         <v>44896</v>
       </c>
       <c r="E621" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F621" t="inlineStr">
         <is>
@@ -47361,7 +47361,7 @@
         <v>44592</v>
       </c>
       <c r="E622" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F622" t="inlineStr">
         <is>
@@ -47434,7 +47434,7 @@
         <v>45407</v>
       </c>
       <c r="E623" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F623" t="inlineStr">
         <is>
@@ -47507,7 +47507,7 @@
         <v>45589</v>
       </c>
       <c r="E624" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F624" t="inlineStr">
         <is>
@@ -47580,7 +47580,7 @@
         <v>45623</v>
       </c>
       <c r="E625" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F625" t="inlineStr">
         <is>
@@ -47653,7 +47653,7 @@
         <v>45769</v>
       </c>
       <c r="E626" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F626" t="inlineStr">
         <is>
@@ -47726,7 +47726,7 @@
         <v>45672</v>
       </c>
       <c r="E627" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F627" t="inlineStr">
         <is>
@@ -47799,7 +47799,7 @@
         <v>45672</v>
       </c>
       <c r="E628" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F628" t="inlineStr">
         <is>
@@ -47872,7 +47872,7 @@
         <v>45524</v>
       </c>
       <c r="E629" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F629" t="inlineStr">
         <is>
@@ -47945,7 +47945,7 @@
         <v>44508</v>
       </c>
       <c r="E630" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F630" t="inlineStr">
         <is>
@@ -48018,7 +48018,7 @@
         <v>44889</v>
       </c>
       <c r="E631" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F631" t="inlineStr">
         <is>
@@ -48091,7 +48091,7 @@
         <v>45199</v>
       </c>
       <c r="E632" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F632" t="inlineStr">
         <is>
@@ -48164,7 +48164,7 @@
         <v>44671</v>
       </c>
       <c r="E633" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F633" t="inlineStr">
         <is>
@@ -48237,7 +48237,7 @@
         <v>45176</v>
       </c>
       <c r="E634" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F634" t="inlineStr">
         <is>
@@ -48310,7 +48310,7 @@
         <v>45199</v>
       </c>
       <c r="E635" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F635" t="inlineStr">
         <is>
@@ -48383,7 +48383,7 @@
         <v>45372</v>
       </c>
       <c r="E636" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F636" t="inlineStr">
         <is>
@@ -48456,7 +48456,7 @@
         <v>44712</v>
       </c>
       <c r="E637" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F637" t="inlineStr">
         <is>
@@ -48529,7 +48529,7 @@
         <v>45395</v>
       </c>
       <c r="E638" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F638" t="inlineStr">
         <is>
@@ -48602,7 +48602,7 @@
         <v>44739</v>
       </c>
       <c r="E639" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F639" t="inlineStr">
         <is>
@@ -48675,7 +48675,7 @@
         <v>45230</v>
       </c>
       <c r="E640" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F640" t="inlineStr">
         <is>
@@ -48748,7 +48748,7 @@
         <v>45672</v>
       </c>
       <c r="E641" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F641" t="inlineStr">
         <is>
@@ -48821,7 +48821,7 @@
         <v>44701</v>
       </c>
       <c r="E642" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F642" t="inlineStr">
         <is>
@@ -48894,7 +48894,7 @@
         <v>45677</v>
       </c>
       <c r="E643" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F643" t="inlineStr">
         <is>
@@ -48967,7 +48967,7 @@
         <v>45361</v>
       </c>
       <c r="E644" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F644" t="inlineStr">
         <is>
@@ -49040,7 +49040,7 @@
         <v>45735</v>
       </c>
       <c r="E645" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F645" t="inlineStr">
         <is>
@@ -49113,7 +49113,7 @@
         <v>45610</v>
       </c>
       <c r="E646" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F646" t="inlineStr">
         <is>
@@ -49186,7 +49186,7 @@
         <v>45679</v>
       </c>
       <c r="E647" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F647" t="inlineStr">
         <is>
@@ -49259,7 +49259,7 @@
         <v>45735</v>
       </c>
       <c r="E648" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F648" t="inlineStr">
         <is>
@@ -49332,7 +49332,7 @@
         <v>45272</v>
       </c>
       <c r="E649" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F649" t="inlineStr">
         <is>
@@ -49405,7 +49405,7 @@
         <v>45309</v>
       </c>
       <c r="E650" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F650" t="inlineStr">
         <is>
@@ -49478,7 +49478,7 @@
         <v>45432</v>
       </c>
       <c r="E651" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F651" t="inlineStr">
         <is>
@@ -49551,7 +49551,7 @@
         <v>45293</v>
       </c>
       <c r="E652" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F652" t="inlineStr">
         <is>
@@ -49624,7 +49624,7 @@
         <v>44671</v>
       </c>
       <c r="E653" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F653" t="inlineStr">
         <is>
@@ -49697,7 +49697,7 @@
         <v>45131</v>
       </c>
       <c r="E654" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F654" t="inlineStr">
         <is>
@@ -49770,7 +49770,7 @@
         <v>45574</v>
       </c>
       <c r="E655" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F655" t="inlineStr">
         <is>
@@ -49843,7 +49843,7 @@
         <v>45589</v>
       </c>
       <c r="E656" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F656" t="inlineStr">
         <is>
@@ -49916,7 +49916,7 @@
         <v>45546</v>
       </c>
       <c r="E657" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F657" t="inlineStr">
         <is>
@@ -49989,7 +49989,7 @@
         <v>45623</v>
       </c>
       <c r="E658" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F658" t="inlineStr">
         <is>
@@ -50062,7 +50062,7 @@
         <v>45838</v>
       </c>
       <c r="E659" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F659" t="inlineStr">
         <is>
@@ -50135,7 +50135,7 @@
         <v>44817</v>
       </c>
       <c r="E660" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F660" t="inlineStr">
         <is>
@@ -50208,7 +50208,7 @@
         <v>45257</v>
       </c>
       <c r="E661" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F661" t="inlineStr">
         <is>
@@ -50286,7 +50286,7 @@
         <v>45245</v>
       </c>
       <c r="E662" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F662" t="inlineStr">
         <is>
@@ -50359,7 +50359,7 @@
         <v>44964</v>
       </c>
       <c r="E663" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F663" t="inlineStr">
         <is>
@@ -50432,7 +50432,7 @@
         <v>45877</v>
       </c>
       <c r="E664" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F664" t="inlineStr">
         <is>
@@ -50505,7 +50505,7 @@
         <v>45880</v>
       </c>
       <c r="E665" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F665" t="inlineStr">
         <is>
@@ -50578,7 +50578,7 @@
         <v>45880</v>
       </c>
       <c r="E666" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F666" t="inlineStr">
         <is>
@@ -50651,7 +50651,7 @@
         <v>45880</v>
       </c>
       <c r="E667" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F667" t="inlineStr">
         <is>
@@ -50724,7 +50724,7 @@
         <v>45880</v>
       </c>
       <c r="E668" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F668" t="inlineStr">
         <is>
@@ -50797,7 +50797,7 @@
         <v>45614</v>
       </c>
       <c r="E669" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F669" t="inlineStr">
         <is>
@@ -50875,7 +50875,7 @@
         <v>44631</v>
       </c>
       <c r="E670" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F670" t="inlineStr">
         <is>
@@ -50948,7 +50948,7 @@
         <v>44743</v>
       </c>
       <c r="E671" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F671" t="inlineStr">
         <is>
@@ -51021,7 +51021,7 @@
         <v>45375</v>
       </c>
       <c r="E672" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F672" t="inlineStr">
         <is>
@@ -51094,7 +51094,7 @@
         <v>44488</v>
       </c>
       <c r="E673" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F673" t="inlineStr">
         <is>
@@ -51167,7 +51167,7 @@
         <v>45604</v>
       </c>
       <c r="E674" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F674" t="inlineStr">
         <is>
@@ -51240,7 +51240,7 @@
         <v>45356</v>
       </c>
       <c r="E675" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F675" t="inlineStr">
         <is>
@@ -51313,7 +51313,7 @@
         <v>44613</v>
       </c>
       <c r="E676" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F676" t="inlineStr">
         <is>
@@ -51386,7 +51386,7 @@
         <v>45349</v>
       </c>
       <c r="E677" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F677" t="inlineStr">
         <is>
@@ -51459,7 +51459,7 @@
         <v>44608</v>
       </c>
       <c r="E678" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F678" t="inlineStr">
         <is>
@@ -51532,7 +51532,7 @@
         <v>44631</v>
       </c>
       <c r="E679" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F679" t="inlineStr">
         <is>
@@ -51605,7 +51605,7 @@
         <v>44631</v>
       </c>
       <c r="E680" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F680" t="inlineStr">
         <is>
@@ -51678,7 +51678,7 @@
         <v>45744</v>
       </c>
       <c r="E681" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F681" t="inlineStr">
         <is>
@@ -51751,7 +51751,7 @@
         <v>45714</v>
       </c>
       <c r="E682" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F682" t="inlineStr">
         <is>
@@ -51824,7 +51824,7 @@
         <v>45715</v>
       </c>
       <c r="E683" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F683" t="inlineStr">
         <is>
@@ -51897,7 +51897,7 @@
         <v>45709</v>
       </c>
       <c r="E684" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F684" t="inlineStr">
         <is>
@@ -51970,7 +51970,7 @@
         <v>45714</v>
       </c>
       <c r="E685" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F685" t="inlineStr">
         <is>
@@ -52043,7 +52043,7 @@
         <v>45813</v>
       </c>
       <c r="E686" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F686" t="inlineStr">
         <is>
@@ -52116,7 +52116,7 @@
         <v>45813</v>
       </c>
       <c r="E687" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F687" t="inlineStr">
         <is>
@@ -52189,7 +52189,7 @@
         <v>45813</v>
       </c>
       <c r="E688" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F688" t="inlineStr">
         <is>
@@ -52262,7 +52262,7 @@
         <v>45820</v>
       </c>
       <c r="E689" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F689" t="inlineStr">
         <is>
@@ -52335,7 +52335,7 @@
         <v>45827</v>
       </c>
       <c r="E690" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F690" t="inlineStr">
         <is>
@@ -52408,7 +52408,7 @@
         <v>45845</v>
       </c>
       <c r="E691" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F691" t="inlineStr">
         <is>
@@ -52481,7 +52481,7 @@
         <v>45883</v>
       </c>
       <c r="E692" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F692" t="inlineStr">
         <is>
@@ -52554,7 +52554,7 @@
         <v>45915</v>
       </c>
       <c r="E693" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F693" t="inlineStr">
         <is>
@@ -52627,7 +52627,7 @@
         <v>46041</v>
       </c>
       <c r="E694" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F694" t="inlineStr">
         <is>
@@ -52700,7 +52700,7 @@
         <v>46133</v>
       </c>
       <c r="E695" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F695" t="inlineStr">
         <is>
@@ -52773,7 +52773,7 @@
         <v>46147</v>
       </c>
       <c r="E696" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F696" t="inlineStr">
         <is>
@@ -52846,7 +52846,7 @@
         <v>46211</v>
       </c>
       <c r="E697" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F697" t="inlineStr">
         <is>
@@ -52919,7 +52919,7 @@
         <v>46290</v>
       </c>
       <c r="E698" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F698" t="inlineStr">
         <is>
@@ -52992,7 +52992,7 @@
         <v>46253</v>
       </c>
       <c r="E699" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F699" t="inlineStr">
         <is>

--- a/Översikt HYLTE.xlsx
+++ b/Översikt HYLTE.xlsx
@@ -601,7 +601,7 @@
         <v>46090</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -718,7 +718,7 @@
         <v>45265</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -834,7 +834,7 @@
         <v>46066</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -945,7 +945,7 @@
         <v>44873</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1054,7 +1054,7 @@
         <v>45348</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1166,7 +1166,7 @@
         <v>45719</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1274,7 +1274,7 @@
         <v>45245</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1385,7 +1385,7 @@
         <v>46268</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1492,7 +1492,7 @@
         <v>45230</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1599,7 +1599,7 @@
         <v>45737</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1706,7 +1706,7 @@
         <v>46141</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1813,7 +1813,7 @@
         <v>46161</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1920,7 +1920,7 @@
         <v>44839</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2030,7 +2030,7 @@
         <v>46048</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2136,7 +2136,7 @@
         <v>45904</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2246,7 +2246,7 @@
         <v>46304</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2356,7 +2356,7 @@
         <v>45841</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2466,7 +2466,7 @@
         <v>45099</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2576,7 +2576,7 @@
         <v>46130</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2682,7 +2682,7 @@
         <v>44648</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2787,7 +2787,7 @@
         <v>44651</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2892,7 +2892,7 @@
         <v>44876</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2997,7 +2997,7 @@
         <v>45245</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3102,7 +3102,7 @@
         <v>45343</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3207,7 +3207,7 @@
         <v>45476</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3317,7 +3317,7 @@
         <v>45163</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3422,7 +3422,7 @@
         <v>45299</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3531,7 +3531,7 @@
         <v>45245</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3636,7 +3636,7 @@
         <v>45593</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3741,7 +3741,7 @@
         <v>45153</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3855,7 +3855,7 @@
         <v>45186</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3960,7 +3960,7 @@
         <v>45085</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4069,7 +4069,7 @@
         <v>45617</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4174,7 +4174,7 @@
         <v>45253</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4279,7 +4279,7 @@
         <v>45754</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4384,7 +4384,7 @@
         <v>46253</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4494,7 +4494,7 @@
         <v>44810</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4567,7 +4567,7 @@
         <v>44600</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4640,7 +4640,7 @@
         <v>44529</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4713,7 +4713,7 @@
         <v>44557</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4786,7 +4786,7 @@
         <v>44705</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4859,7 +4859,7 @@
         <v>44778</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4932,7 +4932,7 @@
         <v>44488</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5005,7 +5005,7 @@
         <v>44624</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5078,7 +5078,7 @@
         <v>44812</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5151,7 +5151,7 @@
         <v>44638</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5224,7 +5224,7 @@
         <v>44498</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5297,7 +5297,7 @@
         <v>44845</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5370,7 +5370,7 @@
         <v>44559</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5443,7 +5443,7 @@
         <v>44578</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5516,7 +5516,7 @@
         <v>44659</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5594,7 +5594,7 @@
         <v>44756</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5667,7 +5667,7 @@
         <v>44501</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5740,7 +5740,7 @@
         <v>44651</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5813,7 +5813,7 @@
         <v>44711</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5886,7 +5886,7 @@
         <v>44487</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5964,7 +5964,7 @@
         <v>44735</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6037,7 +6037,7 @@
         <v>44489</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6110,7 +6110,7 @@
         <v>44834</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6183,7 +6183,7 @@
         <v>44796</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6256,7 +6256,7 @@
         <v>44502</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6329,7 +6329,7 @@
         <v>44631</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6402,7 +6402,7 @@
         <v>44876</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6475,7 +6475,7 @@
         <v>44659</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6548,7 +6548,7 @@
         <v>44644</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6621,7 +6621,7 @@
         <v>44515</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6699,7 +6699,7 @@
         <v>44778</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6772,7 +6772,7 @@
         <v>44867</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6845,7 +6845,7 @@
         <v>44505</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6918,7 +6918,7 @@
         <v>44634</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6991,7 +6991,7 @@
         <v>44728</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7064,7 +7064,7 @@
         <v>44714</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7137,7 +7137,7 @@
         <v>44795</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7210,7 +7210,7 @@
         <v>44818</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7283,7 +7283,7 @@
         <v>44801</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7356,7 +7356,7 @@
         <v>44596</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7434,7 +7434,7 @@
         <v>44644</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7507,7 +7507,7 @@
         <v>44523</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7580,7 +7580,7 @@
         <v>44500</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7653,7 +7653,7 @@
         <v>44727</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7726,7 +7726,7 @@
         <v>44705</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7799,7 +7799,7 @@
         <v>44659</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7877,7 +7877,7 @@
         <v>44659</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7955,7 +7955,7 @@
         <v>44757</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8028,7 +8028,7 @@
         <v>44494</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8101,7 +8101,7 @@
         <v>44495</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8174,7 +8174,7 @@
         <v>45460</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8247,7 +8247,7 @@
         <v>44487</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8325,7 +8325,7 @@
         <v>45132</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8398,7 +8398,7 @@
         <v>44851</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8471,7 +8471,7 @@
         <v>44851</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8544,7 +8544,7 @@
         <v>45715</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8617,7 +8617,7 @@
         <v>44714</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8695,7 +8695,7 @@
         <v>45002</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8768,7 +8768,7 @@
         <v>45568</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8841,7 +8841,7 @@
         <v>45062</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8914,7 +8914,7 @@
         <v>44900</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8992,7 +8992,7 @@
         <v>45107</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -9065,7 +9065,7 @@
         <v>44958</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9138,7 +9138,7 @@
         <v>44559</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9211,7 +9211,7 @@
         <v>45211</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9284,7 +9284,7 @@
         <v>44899</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9357,7 +9357,7 @@
         <v>45548</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9430,7 +9430,7 @@
         <v>45258</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9503,7 +9503,7 @@
         <v>45229</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9576,7 +9576,7 @@
         <v>45589</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9649,7 +9649,7 @@
         <v>45254</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9722,7 +9722,7 @@
         <v>45254</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9795,7 +9795,7 @@
         <v>45098</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9873,7 +9873,7 @@
         <v>45254</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9946,7 +9946,7 @@
         <v>45254</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -10019,7 +10019,7 @@
         <v>44910</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -10092,7 +10092,7 @@
         <v>44823</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10165,7 +10165,7 @@
         <v>45104</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10238,7 +10238,7 @@
         <v>45684</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10311,7 +10311,7 @@
         <v>45539</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10384,7 +10384,7 @@
         <v>45538</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10457,7 +10457,7 @@
         <v>44868</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10530,7 +10530,7 @@
         <v>45600</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10603,7 +10603,7 @@
         <v>45352</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10676,7 +10676,7 @@
         <v>45352</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10749,7 +10749,7 @@
         <v>44719</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -10822,7 +10822,7 @@
         <v>44896</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10895,7 +10895,7 @@
         <v>45638</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10968,7 +10968,7 @@
         <v>45434</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -11041,7 +11041,7 @@
         <v>45163</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -11114,7 +11114,7 @@
         <v>45089</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11187,7 +11187,7 @@
         <v>45145</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11260,7 +11260,7 @@
         <v>45252</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11333,7 +11333,7 @@
         <v>45194</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11406,7 +11406,7 @@
         <v>44495</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11479,7 +11479,7 @@
         <v>44901</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11552,7 +11552,7 @@
         <v>45181</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11625,7 +11625,7 @@
         <v>45694</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11698,7 +11698,7 @@
         <v>45310</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -11771,7 +11771,7 @@
         <v>45441</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -11849,7 +11849,7 @@
         <v>45441</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -11922,7 +11922,7 @@
         <v>45229</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -11995,7 +11995,7 @@
         <v>44701</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -12073,7 +12073,7 @@
         <v>45527</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -12146,7 +12146,7 @@
         <v>44999</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12219,7 +12219,7 @@
         <v>45182</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12292,7 +12292,7 @@
         <v>44847</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12365,7 +12365,7 @@
         <v>44778</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12438,7 +12438,7 @@
         <v>45132</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -12511,7 +12511,7 @@
         <v>45173</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -12584,7 +12584,7 @@
         <v>45478</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -12657,7 +12657,7 @@
         <v>45019</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -12730,7 +12730,7 @@
         <v>45254</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -12803,7 +12803,7 @@
         <v>45331</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -12876,7 +12876,7 @@
         <v>45287</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -12949,7 +12949,7 @@
         <v>45817</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -13022,7 +13022,7 @@
         <v>45782</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -13095,7 +13095,7 @@
         <v>45673</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -13168,7 +13168,7 @@
         <v>45366</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13241,7 +13241,7 @@
         <v>46084</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13314,7 +13314,7 @@
         <v>45245</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13387,7 +13387,7 @@
         <v>45834</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -13460,7 +13460,7 @@
         <v>45485</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -13533,7 +13533,7 @@
         <v>45560</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -13606,7 +13606,7 @@
         <v>45436</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -13679,7 +13679,7 @@
         <v>44699</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -13752,7 +13752,7 @@
         <v>45790</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -13825,7 +13825,7 @@
         <v>45674</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -13898,7 +13898,7 @@
         <v>45748</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -13971,7 +13971,7 @@
         <v>45890</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -14044,7 +14044,7 @@
         <v>45891</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -14122,7 +14122,7 @@
         <v>45891</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -14200,7 +14200,7 @@
         <v>45531</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14273,7 +14273,7 @@
         <v>45775</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14346,7 +14346,7 @@
         <v>45840</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -14419,7 +14419,7 @@
         <v>44865</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -14492,7 +14492,7 @@
         <v>45897</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -14565,7 +14565,7 @@
         <v>45840</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -14643,7 +14643,7 @@
         <v>45848</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -14716,7 +14716,7 @@
         <v>45839</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -14789,7 +14789,7 @@
         <v>45898</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -14862,7 +14862,7 @@
         <v>45897</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -14935,7 +14935,7 @@
         <v>45617</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -15008,7 +15008,7 @@
         <v>45454</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -15081,7 +15081,7 @@
         <v>44701</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -15159,7 +15159,7 @@
         <v>45300</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -15232,7 +15232,7 @@
         <v>45905</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -15305,7 +15305,7 @@
         <v>45838</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -15378,7 +15378,7 @@
         <v>45456</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -15451,7 +15451,7 @@
         <v>45910</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -15524,7 +15524,7 @@
         <v>45910</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -15597,7 +15597,7 @@
         <v>45429</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -15670,7 +15670,7 @@
         <v>45405</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -15743,7 +15743,7 @@
         <v>44797</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -15816,7 +15816,7 @@
         <v>45035</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -15889,7 +15889,7 @@
         <v>45918</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -15962,7 +15962,7 @@
         <v>45259</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -16035,7 +16035,7 @@
         <v>45169</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -16108,7 +16108,7 @@
         <v>45104</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -16181,7 +16181,7 @@
         <v>45922</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -16254,7 +16254,7 @@
         <v>44900</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -16327,7 +16327,7 @@
         <v>45922</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -16400,7 +16400,7 @@
         <v>45922</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -16473,7 +16473,7 @@
         <v>45924</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -16546,7 +16546,7 @@
         <v>44974</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -16619,7 +16619,7 @@
         <v>45926</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -16692,7 +16692,7 @@
         <v>46148</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -16765,7 +16765,7 @@
         <v>45162</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -16838,7 +16838,7 @@
         <v>45926</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -16911,7 +16911,7 @@
         <v>45926</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -16984,7 +16984,7 @@
         <v>45929</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -17057,7 +17057,7 @@
         <v>44694</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -17130,7 +17130,7 @@
         <v>45502</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -17203,7 +17203,7 @@
         <v>44974</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -17276,7 +17276,7 @@
         <v>45091</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -17349,7 +17349,7 @@
         <v>45931</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -17422,7 +17422,7 @@
         <v>46153</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -17495,7 +17495,7 @@
         <v>45930</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -17568,7 +17568,7 @@
         <v>45931</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -17641,7 +17641,7 @@
         <v>46153</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -17714,7 +17714,7 @@
         <v>46153</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -17787,7 +17787,7 @@
         <v>46153</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -17860,7 +17860,7 @@
         <v>46153</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -17933,7 +17933,7 @@
         <v>45933</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -18006,7 +18006,7 @@
         <v>45933</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -18079,7 +18079,7 @@
         <v>45933</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -18152,7 +18152,7 @@
         <v>46153</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -18225,7 +18225,7 @@
         <v>46153</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -18298,7 +18298,7 @@
         <v>45936</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -18371,7 +18371,7 @@
         <v>45936</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -18444,7 +18444,7 @@
         <v>45936</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -18517,7 +18517,7 @@
         <v>45709</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -18590,7 +18590,7 @@
         <v>44926</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -18668,7 +18668,7 @@
         <v>45604</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -18741,7 +18741,7 @@
         <v>45097</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -18814,7 +18814,7 @@
         <v>45477</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -18887,7 +18887,7 @@
         <v>45938</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -18960,7 +18960,7 @@
         <v>45265</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -19033,7 +19033,7 @@
         <v>45937</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -19106,7 +19106,7 @@
         <v>45084</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -19179,7 +19179,7 @@
         <v>45944</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -19252,7 +19252,7 @@
         <v>44953</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -19325,7 +19325,7 @@
         <v>45019</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -19398,7 +19398,7 @@
         <v>45299</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -19471,7 +19471,7 @@
         <v>45645</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -19544,7 +19544,7 @@
         <v>45366</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -19622,7 +19622,7 @@
         <v>45957</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -19695,7 +19695,7 @@
         <v>46155</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -19768,7 +19768,7 @@
         <v>44903</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -19841,7 +19841,7 @@
         <v>45961</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -19914,7 +19914,7 @@
         <v>45922</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -19987,7 +19987,7 @@
         <v>45096</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -20060,7 +20060,7 @@
         <v>45167</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -20133,7 +20133,7 @@
         <v>46161</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -20211,7 +20211,7 @@
         <v>46161</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -20284,7 +20284,7 @@
         <v>45961</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -20357,7 +20357,7 @@
         <v>45751</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -20435,7 +20435,7 @@
         <v>45352</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -20508,7 +20508,7 @@
         <v>46161</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -20586,7 +20586,7 @@
         <v>45254</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -20659,7 +20659,7 @@
         <v>45254</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -20732,7 +20732,7 @@
         <v>46161</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -20805,7 +20805,7 @@
         <v>46161</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -20883,7 +20883,7 @@
         <v>45203</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -20956,7 +20956,7 @@
         <v>45972</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -21029,7 +21029,7 @@
         <v>45972</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -21102,7 +21102,7 @@
         <v>44750</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -21175,7 +21175,7 @@
         <v>45972</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -21248,7 +21248,7 @@
         <v>44714</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -21321,7 +21321,7 @@
         <v>45441</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -21394,7 +21394,7 @@
         <v>45441</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -21467,7 +21467,7 @@
         <v>45441</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -21540,7 +21540,7 @@
         <v>45377</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -21618,7 +21618,7 @@
         <v>45979</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -21691,7 +21691,7 @@
         <v>45170</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -21764,7 +21764,7 @@
         <v>45981</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -21837,7 +21837,7 @@
         <v>45981</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -21910,7 +21910,7 @@
         <v>44869</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -21983,7 +21983,7 @@
         <v>45754</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -22056,7 +22056,7 @@
         <v>45268</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -22129,7 +22129,7 @@
         <v>45441</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -22207,7 +22207,7 @@
         <v>45597</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -22280,7 +22280,7 @@
         <v>45092</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -22353,7 +22353,7 @@
         <v>45987</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -22426,7 +22426,7 @@
         <v>45989</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -22499,7 +22499,7 @@
         <v>45378</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -22572,7 +22572,7 @@
         <v>46169</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -22645,7 +22645,7 @@
         <v>45382</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -22718,7 +22718,7 @@
         <v>46169</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -22791,7 +22791,7 @@
         <v>46169</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -22864,7 +22864,7 @@
         <v>45995</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -22937,7 +22937,7 @@
         <v>45429</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -23010,7 +23010,7 @@
         <v>45371</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -23083,7 +23083,7 @@
         <v>45411</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -23156,7 +23156,7 @@
         <v>45558</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -23229,7 +23229,7 @@
         <v>44950</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -23302,7 +23302,7 @@
         <v>45246</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -23375,7 +23375,7 @@
         <v>45246</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -23448,7 +23448,7 @@
         <v>44697</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -23521,7 +23521,7 @@
         <v>46170</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -23594,7 +23594,7 @@
         <v>45926</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -23667,7 +23667,7 @@
         <v>45351</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -23740,7 +23740,7 @@
         <v>46171</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -23813,7 +23813,7 @@
         <v>45580</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -23886,7 +23886,7 @@
         <v>45159</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -23959,7 +23959,7 @@
         <v>45541</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -24032,7 +24032,7 @@
         <v>46174</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -24105,7 +24105,7 @@
         <v>44635</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -24183,7 +24183,7 @@
         <v>45462</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -24256,7 +24256,7 @@
         <v>44539</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -24329,7 +24329,7 @@
         <v>45042</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -24402,7 +24402,7 @@
         <v>46174</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -24475,7 +24475,7 @@
         <v>45352</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -24548,7 +24548,7 @@
         <v>46020</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -24621,7 +24621,7 @@
         <v>44970</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -24694,7 +24694,7 @@
         <v>45568</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -24767,7 +24767,7 @@
         <v>45145</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -24840,7 +24840,7 @@
         <v>44510</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -24913,7 +24913,7 @@
         <v>45624</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -24986,7 +24986,7 @@
         <v>45170</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -25059,7 +25059,7 @@
         <v>44965</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -25137,7 +25137,7 @@
         <v>46175</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -25210,7 +25210,7 @@
         <v>45257</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -25283,7 +25283,7 @@
         <v>46174</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -25356,7 +25356,7 @@
         <v>46174</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -25429,7 +25429,7 @@
         <v>46178</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -25502,7 +25502,7 @@
         <v>46178</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -25575,7 +25575,7 @@
         <v>45538</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -25648,7 +25648,7 @@
         <v>45456</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -25721,7 +25721,7 @@
         <v>46042</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -25794,7 +25794,7 @@
         <v>46042</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -25867,7 +25867,7 @@
         <v>46044</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -25940,7 +25940,7 @@
         <v>46044</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -26013,7 +26013,7 @@
         <v>46044</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -26086,7 +26086,7 @@
         <v>46044</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -26159,7 +26159,7 @@
         <v>46048</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -26232,7 +26232,7 @@
         <v>46049</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -26305,7 +26305,7 @@
         <v>46048</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -26378,7 +26378,7 @@
         <v>46048</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -26451,7 +26451,7 @@
         <v>46048</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -26524,7 +26524,7 @@
         <v>46048</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -26597,7 +26597,7 @@
         <v>46048</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -26670,7 +26670,7 @@
         <v>46048</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -26743,7 +26743,7 @@
         <v>46048</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -26816,7 +26816,7 @@
         <v>46048</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -26889,7 +26889,7 @@
         <v>46048</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -26962,7 +26962,7 @@
         <v>46048</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -27035,7 +27035,7 @@
         <v>46048</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -27108,7 +27108,7 @@
         <v>45182</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -27181,7 +27181,7 @@
         <v>44489</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -27254,7 +27254,7 @@
         <v>45456</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -27327,7 +27327,7 @@
         <v>46052</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -27400,7 +27400,7 @@
         <v>46183</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -27473,7 +27473,7 @@
         <v>46055</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -27546,7 +27546,7 @@
         <v>46052</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -27619,7 +27619,7 @@
         <v>45198</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -27692,7 +27692,7 @@
         <v>45752</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -27770,7 +27770,7 @@
         <v>44735</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -27843,7 +27843,7 @@
         <v>46057</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -27916,7 +27916,7 @@
         <v>46062</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -27989,7 +27989,7 @@
         <v>46062</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -28062,7 +28062,7 @@
         <v>46064</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -28135,7 +28135,7 @@
         <v>45153</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -28208,7 +28208,7 @@
         <v>46065</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -28281,7 +28281,7 @@
         <v>45568</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -28354,7 +28354,7 @@
         <v>46185</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -28427,7 +28427,7 @@
         <v>46070</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -28500,7 +28500,7 @@
         <v>44970</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -28573,7 +28573,7 @@
         <v>44970</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -28646,7 +28646,7 @@
         <v>44641</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -28719,7 +28719,7 @@
         <v>45342</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -28797,7 +28797,7 @@
         <v>45737</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -28870,7 +28870,7 @@
         <v>45483</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -28943,7 +28943,7 @@
         <v>45061</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -29016,7 +29016,7 @@
         <v>44893</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -29089,7 +29089,7 @@
         <v>46188</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -29162,7 +29162,7 @@
         <v>46188</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -29235,7 +29235,7 @@
         <v>46084</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -29308,7 +29308,7 @@
         <v>45084</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -29381,7 +29381,7 @@
         <v>46084</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -29454,7 +29454,7 @@
         <v>44900</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -29527,7 +29527,7 @@
         <v>46087</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -29600,7 +29600,7 @@
         <v>45572</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -29673,7 +29673,7 @@
         <v>45002</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -29746,7 +29746,7 @@
         <v>46093</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -29819,7 +29819,7 @@
         <v>46093</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -29892,7 +29892,7 @@
         <v>44847</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -29965,7 +29965,7 @@
         <v>46093</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -30038,7 +30038,7 @@
         <v>45432</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -30111,7 +30111,7 @@
         <v>46196</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -30184,7 +30184,7 @@
         <v>45677</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -30257,7 +30257,7 @@
         <v>46057</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -30330,7 +30330,7 @@
         <v>46057</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -30403,7 +30403,7 @@
         <v>45253</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -30476,7 +30476,7 @@
         <v>45253</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -30549,7 +30549,7 @@
         <v>46199</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -30622,7 +30622,7 @@
         <v>46111</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -30695,7 +30695,7 @@
         <v>46111</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -30768,7 +30768,7 @@
         <v>46111</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -30841,7 +30841,7 @@
         <v>45104</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -30914,7 +30914,7 @@
         <v>45715</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -30987,7 +30987,7 @@
         <v>45117</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -31060,7 +31060,7 @@
         <v>46120</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -31133,7 +31133,7 @@
         <v>45357</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -31206,7 +31206,7 @@
         <v>46120</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -31279,7 +31279,7 @@
         <v>45107</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -31352,7 +31352,7 @@
         <v>46122</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -31425,7 +31425,7 @@
         <v>46121</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -31498,7 +31498,7 @@
         <v>46121</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -31571,7 +31571,7 @@
         <v>46121</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -31644,7 +31644,7 @@
         <v>46122</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -31717,7 +31717,7 @@
         <v>46122</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -31790,7 +31790,7 @@
         <v>46121</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -31863,7 +31863,7 @@
         <v>46122</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -31936,7 +31936,7 @@
         <v>46121</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -32009,7 +32009,7 @@
         <v>46121</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -32082,7 +32082,7 @@
         <v>46121</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -32155,7 +32155,7 @@
         <v>46121</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -32228,7 +32228,7 @@
         <v>45267</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -32301,7 +32301,7 @@
         <v>46128</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -32374,7 +32374,7 @@
         <v>44726</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -32447,7 +32447,7 @@
         <v>45351</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -32520,7 +32520,7 @@
         <v>45426</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -32593,7 +32593,7 @@
         <v>44872</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -32666,7 +32666,7 @@
         <v>45456</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -32739,7 +32739,7 @@
         <v>45091</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -32812,7 +32812,7 @@
         <v>45989</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -32885,7 +32885,7 @@
         <v>45462</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -32958,7 +32958,7 @@
         <v>46209</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -33031,7 +33031,7 @@
         <v>45839</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -33104,7 +33104,7 @@
         <v>46206</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -33177,7 +33177,7 @@
         <v>45524</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -33250,7 +33250,7 @@
         <v>45114</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -33323,7 +33323,7 @@
         <v>45225</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -33396,7 +33396,7 @@
         <v>45246</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -33469,7 +33469,7 @@
         <v>45316</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -33547,7 +33547,7 @@
         <v>44601</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -33620,7 +33620,7 @@
         <v>44575</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -33693,7 +33693,7 @@
         <v>45170</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -33766,7 +33766,7 @@
         <v>45334</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -33839,7 +33839,7 @@
         <v>45169</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -33912,7 +33912,7 @@
         <v>44729</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -33985,7 +33985,7 @@
         <v>44796</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -34058,7 +34058,7 @@
         <v>44995</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -34131,7 +34131,7 @@
         <v>44951</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -34204,7 +34204,7 @@
         <v>45110</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -34277,7 +34277,7 @@
         <v>45432</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -34350,7 +34350,7 @@
         <v>46224</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -34428,7 +34428,7 @@
         <v>44530</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -34501,7 +34501,7 @@
         <v>44980</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -34574,7 +34574,7 @@
         <v>45350</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -34647,7 +34647,7 @@
         <v>45229</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -34720,7 +34720,7 @@
         <v>46273</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -34793,7 +34793,7 @@
         <v>46272</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -34866,7 +34866,7 @@
         <v>46272</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -34939,7 +34939,7 @@
         <v>45840</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -35017,7 +35017,7 @@
         <v>45245</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -35090,7 +35090,7 @@
         <v>46273</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -35163,7 +35163,7 @@
         <v>45531</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -35236,7 +35236,7 @@
         <v>45352</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -35309,7 +35309,7 @@
         <v>45208</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -35382,7 +35382,7 @@
         <v>45110</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -35455,7 +35455,7 @@
         <v>44756</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -35528,7 +35528,7 @@
         <v>45390</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -35601,7 +35601,7 @@
         <v>45238</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -35674,7 +35674,7 @@
         <v>46279</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -35747,7 +35747,7 @@
         <v>44866</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -35820,7 +35820,7 @@
         <v>46279</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -35893,7 +35893,7 @@
         <v>46279</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -35966,7 +35966,7 @@
         <v>46036</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -36039,7 +36039,7 @@
         <v>45406</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -36112,7 +36112,7 @@
         <v>45414</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -36185,7 +36185,7 @@
         <v>45229</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -36258,7 +36258,7 @@
         <v>44651</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -36331,7 +36331,7 @@
         <v>45092</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -36404,7 +36404,7 @@
         <v>45455</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -36477,7 +36477,7 @@
         <v>46281</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -36550,7 +36550,7 @@
         <v>45051</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -36623,7 +36623,7 @@
         <v>46282</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -36696,7 +36696,7 @@
         <v>45770</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -36769,7 +36769,7 @@
         <v>46241</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -36842,7 +36842,7 @@
         <v>46273</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -36915,7 +36915,7 @@
         <v>45671</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -36988,7 +36988,7 @@
         <v>46283</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -37061,7 +37061,7 @@
         <v>45939</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -37139,7 +37139,7 @@
         <v>44813</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -37212,7 +37212,7 @@
         <v>45162</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -37285,7 +37285,7 @@
         <v>45254</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -37358,7 +37358,7 @@
         <v>46286</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -37431,7 +37431,7 @@
         <v>46281</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -37504,7 +37504,7 @@
         <v>46283</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -37577,7 +37577,7 @@
         <v>46030</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -37650,7 +37650,7 @@
         <v>46281</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -37723,7 +37723,7 @@
         <v>46283</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -37796,7 +37796,7 @@
         <v>46286</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -37869,7 +37869,7 @@
         <v>44900</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -37942,7 +37942,7 @@
         <v>46224</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -38015,7 +38015,7 @@
         <v>44893</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -38088,7 +38088,7 @@
         <v>45327</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -38161,7 +38161,7 @@
         <v>45624</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -38234,7 +38234,7 @@
         <v>46247</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -38307,7 +38307,7 @@
         <v>46245</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -38380,7 +38380,7 @@
         <v>44712</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -38453,7 +38453,7 @@
         <v>44834</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -38526,7 +38526,7 @@
         <v>45400</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -38599,7 +38599,7 @@
         <v>45229</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -38672,7 +38672,7 @@
         <v>44967</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -38745,7 +38745,7 @@
         <v>46293</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -38818,7 +38818,7 @@
         <v>45544</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -38891,7 +38891,7 @@
         <v>46248</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -38964,7 +38964,7 @@
         <v>45715</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -39037,7 +39037,7 @@
         <v>46248</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -39110,7 +39110,7 @@
         <v>45700</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -39183,7 +39183,7 @@
         <v>46292</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -39256,7 +39256,7 @@
         <v>45316</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -39329,7 +39329,7 @@
         <v>45643</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -39402,7 +39402,7 @@
         <v>44900</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -39475,7 +39475,7 @@
         <v>45368</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -39553,7 +39553,7 @@
         <v>45371</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -39626,7 +39626,7 @@
         <v>45371</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -39699,7 +39699,7 @@
         <v>45254</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -39772,7 +39772,7 @@
         <v>46244</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -39845,7 +39845,7 @@
         <v>46295</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -39918,7 +39918,7 @@
         <v>45229</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -39991,7 +39991,7 @@
         <v>45035</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -40064,7 +40064,7 @@
         <v>45299</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -40137,7 +40137,7 @@
         <v>45176</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -40215,7 +40215,7 @@
         <v>45638</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -40288,7 +40288,7 @@
         <v>45588</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -40366,7 +40366,7 @@
         <v>46070</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -40439,7 +40439,7 @@
         <v>45876</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -40512,7 +40512,7 @@
         <v>45510</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -40585,7 +40585,7 @@
         <v>45559</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -40658,7 +40658,7 @@
         <v>46161</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -40736,7 +40736,7 @@
         <v>45783</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -40809,7 +40809,7 @@
         <v>45616</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -40882,7 +40882,7 @@
         <v>45483</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -40955,7 +40955,7 @@
         <v>45680</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -41028,7 +41028,7 @@
         <v>45616</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -41101,7 +41101,7 @@
         <v>46292</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -41174,7 +41174,7 @@
         <v>45225</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -41247,7 +41247,7 @@
         <v>45618</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -41320,7 +41320,7 @@
         <v>45726</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -41393,7 +41393,7 @@
         <v>45483</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -41466,7 +41466,7 @@
         <v>45589</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -41544,7 +41544,7 @@
         <v>45391</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -41617,7 +41617,7 @@
         <v>45786</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -41695,7 +41695,7 @@
         <v>46292</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -41768,7 +41768,7 @@
         <v>46292</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -41841,7 +41841,7 @@
         <v>46292</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -41914,7 +41914,7 @@
         <v>46292</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -41987,7 +41987,7 @@
         <v>46302</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -42060,7 +42060,7 @@
         <v>46302</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -42133,7 +42133,7 @@
         <v>45590</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -42206,7 +42206,7 @@
         <v>46294</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -42284,7 +42284,7 @@
         <v>45609</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -42357,7 +42357,7 @@
         <v>45743</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -42435,7 +42435,7 @@
         <v>46292</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -42508,7 +42508,7 @@
         <v>45743</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -42586,7 +42586,7 @@
         <v>45741</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -42659,7 +42659,7 @@
         <v>45793</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -42732,7 +42732,7 @@
         <v>45559</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -42805,7 +42805,7 @@
         <v>45681</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -42878,7 +42878,7 @@
         <v>46261</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -42951,7 +42951,7 @@
         <v>45743</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -43029,7 +43029,7 @@
         <v>46261</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -43102,7 +43102,7 @@
         <v>44851</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -43175,7 +43175,7 @@
         <v>46263</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -43248,7 +43248,7 @@
         <v>45806</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -43321,7 +43321,7 @@
         <v>45609</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -43394,7 +43394,7 @@
         <v>45812</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -43467,7 +43467,7 @@
         <v>46268</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -43540,7 +43540,7 @@
         <v>46268</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -43613,7 +43613,7 @@
         <v>45706</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -43686,7 +43686,7 @@
         <v>45694</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -43759,7 +43759,7 @@
         <v>45708</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -43832,7 +43832,7 @@
         <v>45597</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -43905,7 +43905,7 @@
         <v>45387</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -43978,7 +43978,7 @@
         <v>45730</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -44051,7 +44051,7 @@
         <v>45820</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -44124,7 +44124,7 @@
         <v>44900</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -44197,7 +44197,7 @@
         <v>45825</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -44270,7 +44270,7 @@
         <v>45548</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -44343,7 +44343,7 @@
         <v>46268</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -44416,7 +44416,7 @@
         <v>45831</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -44489,7 +44489,7 @@
         <v>45601</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -44562,7 +44562,7 @@
         <v>45835</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -44635,7 +44635,7 @@
         <v>45838</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -44708,7 +44708,7 @@
         <v>45836</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -44781,7 +44781,7 @@
         <v>45840</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -44854,7 +44854,7 @@
         <v>45840</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -44927,7 +44927,7 @@
         <v>45840</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -45000,7 +45000,7 @@
         <v>45800</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -45073,7 +45073,7 @@
         <v>45847</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -45146,7 +45146,7 @@
         <v>45847</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -45219,7 +45219,7 @@
         <v>45845</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -45292,7 +45292,7 @@
         <v>45845</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -45365,7 +45365,7 @@
         <v>45846</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -45443,7 +45443,7 @@
         <v>45846</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -45521,7 +45521,7 @@
         <v>45846</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -45599,7 +45599,7 @@
         <v>45803</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -45672,7 +45672,7 @@
         <v>45700</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -45745,7 +45745,7 @@
         <v>45700</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -45818,7 +45818,7 @@
         <v>45687</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -45891,7 +45891,7 @@
         <v>45190</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -45964,7 +45964,7 @@
         <v>45293</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -46037,7 +46037,7 @@
         <v>45392</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -46110,7 +46110,7 @@
         <v>45145</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -46183,7 +46183,7 @@
         <v>45623</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -46256,7 +46256,7 @@
         <v>44917</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -46329,7 +46329,7 @@
         <v>45190</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -46407,7 +46407,7 @@
         <v>45517</v>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -46480,7 +46480,7 @@
         <v>45545</v>
       </c>
       <c r="E610" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -46553,7 +46553,7 @@
         <v>45204</v>
       </c>
       <c r="E611" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
@@ -46626,7 +46626,7 @@
         <v>45395</v>
       </c>
       <c r="E612" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
@@ -46699,7 +46699,7 @@
         <v>45541</v>
       </c>
       <c r="E613" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
@@ -46772,7 +46772,7 @@
         <v>45677</v>
       </c>
       <c r="E614" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F614" t="inlineStr">
         <is>
@@ -46845,7 +46845,7 @@
         <v>45727</v>
       </c>
       <c r="E615" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F615" t="inlineStr">
         <is>
@@ -46918,7 +46918,7 @@
         <v>45252</v>
       </c>
       <c r="E616" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F616" t="inlineStr">
         <is>
@@ -46991,7 +46991,7 @@
         <v>45257</v>
       </c>
       <c r="E617" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F617" t="inlineStr">
         <is>
@@ -47064,7 +47064,7 @@
         <v>45309</v>
       </c>
       <c r="E618" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F618" t="inlineStr">
         <is>
@@ -47137,7 +47137,7 @@
         <v>45245</v>
       </c>
       <c r="E619" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F619" t="inlineStr">
         <is>
@@ -47210,7 +47210,7 @@
         <v>45288</v>
       </c>
       <c r="E620" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F620" t="inlineStr">
         <is>
@@ -47288,7 +47288,7 @@
         <v>44896</v>
       </c>
       <c r="E621" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F621" t="inlineStr">
         <is>
@@ -47361,7 +47361,7 @@
         <v>44592</v>
       </c>
       <c r="E622" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F622" t="inlineStr">
         <is>
@@ -47434,7 +47434,7 @@
         <v>45407</v>
       </c>
       <c r="E623" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F623" t="inlineStr">
         <is>
@@ -47507,7 +47507,7 @@
         <v>45589</v>
       </c>
       <c r="E624" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F624" t="inlineStr">
         <is>
@@ -47580,7 +47580,7 @@
         <v>45623</v>
       </c>
       <c r="E625" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F625" t="inlineStr">
         <is>
@@ -47653,7 +47653,7 @@
         <v>45769</v>
       </c>
       <c r="E626" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F626" t="inlineStr">
         <is>
@@ -47726,7 +47726,7 @@
         <v>45672</v>
       </c>
       <c r="E627" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F627" t="inlineStr">
         <is>
@@ -47799,7 +47799,7 @@
         <v>45672</v>
       </c>
       <c r="E628" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F628" t="inlineStr">
         <is>
@@ -47872,7 +47872,7 @@
         <v>45524</v>
       </c>
       <c r="E629" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F629" t="inlineStr">
         <is>
@@ -47945,7 +47945,7 @@
         <v>44508</v>
       </c>
       <c r="E630" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F630" t="inlineStr">
         <is>
@@ -48018,7 +48018,7 @@
         <v>44889</v>
       </c>
       <c r="E631" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F631" t="inlineStr">
         <is>
@@ -48091,7 +48091,7 @@
         <v>45199</v>
       </c>
       <c r="E632" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F632" t="inlineStr">
         <is>
@@ -48164,7 +48164,7 @@
         <v>44671</v>
       </c>
       <c r="E633" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F633" t="inlineStr">
         <is>
@@ -48237,7 +48237,7 @@
         <v>45176</v>
       </c>
       <c r="E634" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F634" t="inlineStr">
         <is>
@@ -48310,7 +48310,7 @@
         <v>45199</v>
       </c>
       <c r="E635" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F635" t="inlineStr">
         <is>
@@ -48383,7 +48383,7 @@
         <v>45372</v>
       </c>
       <c r="E636" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F636" t="inlineStr">
         <is>
@@ -48456,7 +48456,7 @@
         <v>44712</v>
       </c>
       <c r="E637" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F637" t="inlineStr">
         <is>
@@ -48529,7 +48529,7 @@
         <v>45395</v>
       </c>
       <c r="E638" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F638" t="inlineStr">
         <is>
@@ -48602,7 +48602,7 @@
         <v>44739</v>
       </c>
       <c r="E639" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F639" t="inlineStr">
         <is>
@@ -48675,7 +48675,7 @@
         <v>45230</v>
       </c>
       <c r="E640" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F640" t="inlineStr">
         <is>
@@ -48748,7 +48748,7 @@
         <v>45672</v>
       </c>
       <c r="E641" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F641" t="inlineStr">
         <is>
@@ -48821,7 +48821,7 @@
         <v>44701</v>
       </c>
       <c r="E642" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F642" t="inlineStr">
         <is>
@@ -48894,7 +48894,7 @@
         <v>45677</v>
       </c>
       <c r="E643" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F643" t="inlineStr">
         <is>
@@ -48967,7 +48967,7 @@
         <v>45361</v>
       </c>
       <c r="E644" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F644" t="inlineStr">
         <is>
@@ -49040,7 +49040,7 @@
         <v>45735</v>
       </c>
       <c r="E645" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F645" t="inlineStr">
         <is>
@@ -49113,7 +49113,7 @@
         <v>45610</v>
       </c>
       <c r="E646" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F646" t="inlineStr">
         <is>
@@ -49186,7 +49186,7 @@
         <v>45679</v>
       </c>
       <c r="E647" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F647" t="inlineStr">
         <is>
@@ -49259,7 +49259,7 @@
         <v>45735</v>
       </c>
       <c r="E648" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F648" t="inlineStr">
         <is>
@@ -49332,7 +49332,7 @@
         <v>45272</v>
       </c>
       <c r="E649" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F649" t="inlineStr">
         <is>
@@ -49405,7 +49405,7 @@
         <v>45309</v>
       </c>
       <c r="E650" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F650" t="inlineStr">
         <is>
@@ -49478,7 +49478,7 @@
         <v>45432</v>
       </c>
       <c r="E651" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F651" t="inlineStr">
         <is>
@@ -49551,7 +49551,7 @@
         <v>45293</v>
       </c>
       <c r="E652" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F652" t="inlineStr">
         <is>
@@ -49624,7 +49624,7 @@
         <v>44671</v>
       </c>
       <c r="E653" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F653" t="inlineStr">
         <is>
@@ -49697,7 +49697,7 @@
         <v>45131</v>
       </c>
       <c r="E654" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F654" t="inlineStr">
         <is>
@@ -49770,7 +49770,7 @@
         <v>45574</v>
       </c>
       <c r="E655" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F655" t="inlineStr">
         <is>
@@ -49843,7 +49843,7 @@
         <v>45589</v>
       </c>
       <c r="E656" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F656" t="inlineStr">
         <is>
@@ -49916,7 +49916,7 @@
         <v>45546</v>
       </c>
       <c r="E657" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F657" t="inlineStr">
         <is>
@@ -49989,7 +49989,7 @@
         <v>45623</v>
       </c>
       <c r="E658" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F658" t="inlineStr">
         <is>
@@ -50062,7 +50062,7 @@
         <v>45838</v>
       </c>
       <c r="E659" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F659" t="inlineStr">
         <is>
@@ -50135,7 +50135,7 @@
         <v>44817</v>
       </c>
       <c r="E660" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F660" t="inlineStr">
         <is>
@@ -50208,7 +50208,7 @@
         <v>45257</v>
       </c>
       <c r="E661" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F661" t="inlineStr">
         <is>
@@ -50286,7 +50286,7 @@
         <v>45245</v>
       </c>
       <c r="E662" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F662" t="inlineStr">
         <is>
@@ -50359,7 +50359,7 @@
         <v>44964</v>
       </c>
       <c r="E663" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F663" t="inlineStr">
         <is>
@@ -50432,7 +50432,7 @@
         <v>45877</v>
       </c>
       <c r="E664" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F664" t="inlineStr">
         <is>
@@ -50505,7 +50505,7 @@
         <v>45880</v>
       </c>
       <c r="E665" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F665" t="inlineStr">
         <is>
@@ -50578,7 +50578,7 @@
         <v>45880</v>
       </c>
       <c r="E666" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F666" t="inlineStr">
         <is>
@@ -50651,7 +50651,7 @@
         <v>45880</v>
       </c>
       <c r="E667" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F667" t="inlineStr">
         <is>
@@ -50724,7 +50724,7 @@
         <v>45880</v>
       </c>
       <c r="E668" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F668" t="inlineStr">
         <is>
@@ -50797,7 +50797,7 @@
         <v>45614</v>
       </c>
       <c r="E669" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F669" t="inlineStr">
         <is>
@@ -50875,7 +50875,7 @@
         <v>44631</v>
       </c>
       <c r="E670" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F670" t="inlineStr">
         <is>
@@ -50948,7 +50948,7 @@
         <v>44743</v>
       </c>
       <c r="E671" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F671" t="inlineStr">
         <is>
@@ -51021,7 +51021,7 @@
         <v>45375</v>
       </c>
       <c r="E672" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F672" t="inlineStr">
         <is>
@@ -51094,7 +51094,7 @@
         <v>44488</v>
       </c>
       <c r="E673" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F673" t="inlineStr">
         <is>
@@ -51167,7 +51167,7 @@
         <v>45604</v>
       </c>
       <c r="E674" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F674" t="inlineStr">
         <is>
@@ -51240,7 +51240,7 @@
         <v>45356</v>
       </c>
       <c r="E675" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F675" t="inlineStr">
         <is>
@@ -51313,7 +51313,7 @@
         <v>44613</v>
       </c>
       <c r="E676" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F676" t="inlineStr">
         <is>
@@ -51386,7 +51386,7 @@
         <v>45349</v>
       </c>
       <c r="E677" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F677" t="inlineStr">
         <is>
@@ -51459,7 +51459,7 @@
         <v>44608</v>
       </c>
       <c r="E678" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F678" t="inlineStr">
         <is>
@@ -51532,7 +51532,7 @@
         <v>44631</v>
       </c>
       <c r="E679" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F679" t="inlineStr">
         <is>
@@ -51605,7 +51605,7 @@
         <v>44631</v>
       </c>
       <c r="E680" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F680" t="inlineStr">
         <is>
@@ -51678,7 +51678,7 @@
         <v>45744</v>
       </c>
       <c r="E681" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F681" t="inlineStr">
         <is>
@@ -51751,7 +51751,7 @@
         <v>45714</v>
       </c>
       <c r="E682" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F682" t="inlineStr">
         <is>
@@ -51824,7 +51824,7 @@
         <v>45715</v>
       </c>
       <c r="E683" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F683" t="inlineStr">
         <is>
@@ -51897,7 +51897,7 @@
         <v>45709</v>
       </c>
       <c r="E684" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F684" t="inlineStr">
         <is>
@@ -51970,7 +51970,7 @@
         <v>45714</v>
       </c>
       <c r="E685" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F685" t="inlineStr">
         <is>
@@ -52043,7 +52043,7 @@
         <v>45813</v>
       </c>
       <c r="E686" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F686" t="inlineStr">
         <is>
@@ -52116,7 +52116,7 @@
         <v>45813</v>
       </c>
       <c r="E687" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F687" t="inlineStr">
         <is>
@@ -52189,7 +52189,7 @@
         <v>45813</v>
       </c>
       <c r="E688" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F688" t="inlineStr">
         <is>
@@ -52262,7 +52262,7 @@
         <v>45820</v>
       </c>
       <c r="E689" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F689" t="inlineStr">
         <is>
@@ -52335,7 +52335,7 @@
         <v>45827</v>
       </c>
       <c r="E690" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F690" t="inlineStr">
         <is>
@@ -52408,7 +52408,7 @@
         <v>45845</v>
       </c>
       <c r="E691" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F691" t="inlineStr">
         <is>
@@ -52481,7 +52481,7 @@
         <v>45883</v>
       </c>
       <c r="E692" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F692" t="inlineStr">
         <is>
@@ -52554,7 +52554,7 @@
         <v>45915</v>
       </c>
       <c r="E693" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F693" t="inlineStr">
         <is>
@@ -52627,7 +52627,7 @@
         <v>46041</v>
       </c>
       <c r="E694" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F694" t="inlineStr">
         <is>
@@ -52700,7 +52700,7 @@
         <v>46133</v>
       </c>
       <c r="E695" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F695" t="inlineStr">
         <is>
@@ -52773,7 +52773,7 @@
         <v>46147</v>
       </c>
       <c r="E696" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F696" t="inlineStr">
         <is>
@@ -52846,7 +52846,7 @@
         <v>46211</v>
       </c>
       <c r="E697" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F697" t="inlineStr">
         <is>
@@ -52919,7 +52919,7 @@
         <v>46290</v>
       </c>
       <c r="E698" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F698" t="inlineStr">
         <is>
@@ -52992,7 +52992,7 @@
         <v>46253</v>
       </c>
       <c r="E699" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F699" t="inlineStr">
         <is>

--- a/Översikt HYLTE.xlsx
+++ b/Översikt HYLTE.xlsx
@@ -601,7 +601,7 @@
         <v>46090</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -718,7 +718,7 @@
         <v>45265</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -834,7 +834,7 @@
         <v>46066</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -945,7 +945,7 @@
         <v>44873</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1054,7 +1054,7 @@
         <v>45348</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1166,7 +1166,7 @@
         <v>45719</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1274,7 +1274,7 @@
         <v>46268</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1381,7 +1381,7 @@
         <v>45245</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1492,7 +1492,7 @@
         <v>45230</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1599,7 +1599,7 @@
         <v>45737</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1706,7 +1706,7 @@
         <v>46141</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1813,7 +1813,7 @@
         <v>46161</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1920,7 +1920,7 @@
         <v>44839</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2030,7 +2030,7 @@
         <v>45904</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2140,7 +2140,7 @@
         <v>46048</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2246,7 +2246,7 @@
         <v>45841</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2356,7 +2356,7 @@
         <v>45099</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2466,7 +2466,7 @@
         <v>46304</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2576,7 +2576,7 @@
         <v>46130</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2682,7 +2682,7 @@
         <v>44648</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2787,7 +2787,7 @@
         <v>44651</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2892,7 +2892,7 @@
         <v>44876</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2997,7 +2997,7 @@
         <v>45186</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3102,7 +3102,7 @@
         <v>45299</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3211,7 +3211,7 @@
         <v>45245</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3316,7 +3316,7 @@
         <v>45593</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3421,7 +3421,7 @@
         <v>45245</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3526,7 +3526,7 @@
         <v>45617</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3631,7 +3631,7 @@
         <v>45153</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3745,7 +3745,7 @@
         <v>45163</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3850,7 +3850,7 @@
         <v>45343</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3955,7 +3955,7 @@
         <v>45476</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4065,7 +4065,7 @@
         <v>45085</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4174,7 +4174,7 @@
         <v>45253</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4279,7 +4279,7 @@
         <v>45754</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4384,7 +4384,7 @@
         <v>46253</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4494,7 +4494,7 @@
         <v>44810</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4567,7 +4567,7 @@
         <v>44600</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4640,7 +4640,7 @@
         <v>44529</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4713,7 +4713,7 @@
         <v>44557</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4786,7 +4786,7 @@
         <v>44705</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4859,7 +4859,7 @@
         <v>44778</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4932,7 +4932,7 @@
         <v>44624</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5005,7 +5005,7 @@
         <v>44812</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5078,7 +5078,7 @@
         <v>44638</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5151,7 +5151,7 @@
         <v>44498</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5224,7 +5224,7 @@
         <v>44845</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5297,7 +5297,7 @@
         <v>44559</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5370,7 +5370,7 @@
         <v>44659</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5448,7 +5448,7 @@
         <v>44578</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5521,7 +5521,7 @@
         <v>44756</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5594,7 +5594,7 @@
         <v>44501</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5667,7 +5667,7 @@
         <v>44651</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5740,7 +5740,7 @@
         <v>44711</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5813,7 +5813,7 @@
         <v>44735</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5886,7 +5886,7 @@
         <v>44834</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5959,7 +5959,7 @@
         <v>44796</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6032,7 +6032,7 @@
         <v>44502</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6105,7 +6105,7 @@
         <v>44631</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6178,7 +6178,7 @@
         <v>44876</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6251,7 +6251,7 @@
         <v>44659</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6324,7 +6324,7 @@
         <v>44644</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6397,7 +6397,7 @@
         <v>44515</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6475,7 +6475,7 @@
         <v>44778</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6548,7 +6548,7 @@
         <v>44867</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6621,7 +6621,7 @@
         <v>44505</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6694,7 +6694,7 @@
         <v>44634</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6767,7 +6767,7 @@
         <v>44728</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6840,7 +6840,7 @@
         <v>44714</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6913,7 +6913,7 @@
         <v>44795</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6986,7 +6986,7 @@
         <v>44818</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7059,7 +7059,7 @@
         <v>44801</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7132,7 +7132,7 @@
         <v>44596</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7210,7 +7210,7 @@
         <v>44644</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7283,7 +7283,7 @@
         <v>44523</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7356,7 +7356,7 @@
         <v>44500</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7429,7 +7429,7 @@
         <v>44727</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7502,7 +7502,7 @@
         <v>44705</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7575,7 +7575,7 @@
         <v>44659</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7653,7 +7653,7 @@
         <v>44659</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7731,7 +7731,7 @@
         <v>44757</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7804,7 +7804,7 @@
         <v>44494</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7877,7 +7877,7 @@
         <v>45834</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7950,7 +7950,7 @@
         <v>45840</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8023,7 +8023,7 @@
         <v>45436</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8096,7 +8096,7 @@
         <v>44495</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8169,7 +8169,7 @@
         <v>45132</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8242,7 +8242,7 @@
         <v>45246</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8315,7 +8315,7 @@
         <v>45246</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8388,7 +8388,7 @@
         <v>45673</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8461,7 +8461,7 @@
         <v>45426</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8534,7 +8534,7 @@
         <v>45042</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8607,7 +8607,7 @@
         <v>45327</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8680,7 +8680,7 @@
         <v>45890</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8753,7 +8753,7 @@
         <v>45748</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8826,7 +8826,7 @@
         <v>45371</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8899,7 +8899,7 @@
         <v>45891</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8977,7 +8977,7 @@
         <v>45891</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -9055,7 +9055,7 @@
         <v>45411</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9128,7 +9128,7 @@
         <v>45299</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9201,7 +9201,7 @@
         <v>45208</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9274,7 +9274,7 @@
         <v>45254</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9347,7 +9347,7 @@
         <v>45897</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9420,7 +9420,7 @@
         <v>45897</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9493,7 +9493,7 @@
         <v>45839</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9566,7 +9566,7 @@
         <v>45898</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9639,7 +9639,7 @@
         <v>44900</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9712,7 +9712,7 @@
         <v>44900</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9785,7 +9785,7 @@
         <v>45441</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9863,7 +9863,7 @@
         <v>44866</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9936,7 +9936,7 @@
         <v>45905</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -10009,7 +10009,7 @@
         <v>45624</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -10082,7 +10082,7 @@
         <v>45910</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10155,7 +10155,7 @@
         <v>46161</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10233,7 +10233,7 @@
         <v>46161</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10306,7 +10306,7 @@
         <v>45910</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10379,7 +10379,7 @@
         <v>45580</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10452,7 +10452,7 @@
         <v>45568</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10525,7 +10525,7 @@
         <v>46161</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10603,7 +10603,7 @@
         <v>45838</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10676,7 +10676,7 @@
         <v>46161</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10749,7 +10749,7 @@
         <v>46161</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -10827,7 +10827,7 @@
         <v>45918</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10900,7 +10900,7 @@
         <v>44714</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10978,7 +10978,7 @@
         <v>44813</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -11051,7 +11051,7 @@
         <v>45922</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -11124,7 +11124,7 @@
         <v>45163</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11197,7 +11197,7 @@
         <v>44851</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11270,7 +11270,7 @@
         <v>44851</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11343,7 +11343,7 @@
         <v>45922</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11416,7 +11416,7 @@
         <v>45035</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11489,7 +11489,7 @@
         <v>45922</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11562,7 +11562,7 @@
         <v>44726</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11635,7 +11635,7 @@
         <v>45331</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11708,7 +11708,7 @@
         <v>45924</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -11781,7 +11781,7 @@
         <v>45926</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -11854,7 +11854,7 @@
         <v>45926</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -11927,7 +11927,7 @@
         <v>45926</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -12000,7 +12000,7 @@
         <v>45019</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -12073,7 +12073,7 @@
         <v>46169</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -12146,7 +12146,7 @@
         <v>45350</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12219,7 +12219,7 @@
         <v>45929</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12292,7 +12292,7 @@
         <v>46169</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12365,7 +12365,7 @@
         <v>46169</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12438,7 +12438,7 @@
         <v>45434</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -12511,7 +12511,7 @@
         <v>44847</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -12584,7 +12584,7 @@
         <v>45254</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -12657,7 +12657,7 @@
         <v>45254</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -12730,7 +12730,7 @@
         <v>45931</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -12803,7 +12803,7 @@
         <v>45931</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -12876,7 +12876,7 @@
         <v>46171</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -12949,7 +12949,7 @@
         <v>46170</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -13022,7 +13022,7 @@
         <v>45930</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -13095,7 +13095,7 @@
         <v>44900</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -13168,7 +13168,7 @@
         <v>45357</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13241,7 +13241,7 @@
         <v>45429</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13314,7 +13314,7 @@
         <v>45933</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13387,7 +13387,7 @@
         <v>45936</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -13460,7 +13460,7 @@
         <v>45936</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -13533,7 +13533,7 @@
         <v>45933</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -13606,7 +13606,7 @@
         <v>45933</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -13679,7 +13679,7 @@
         <v>46174</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -13752,7 +13752,7 @@
         <v>45936</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -13825,7 +13825,7 @@
         <v>44872</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -13898,7 +13898,7 @@
         <v>45937</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -13971,7 +13971,7 @@
         <v>45390</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -14044,7 +14044,7 @@
         <v>45938</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -14117,7 +14117,7 @@
         <v>46175</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -14190,7 +14190,7 @@
         <v>46174</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14263,7 +14263,7 @@
         <v>45944</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14336,7 +14336,7 @@
         <v>46174</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -14409,7 +14409,7 @@
         <v>45002</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -14482,7 +14482,7 @@
         <v>45684</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -14555,7 +14555,7 @@
         <v>46178</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -14628,7 +14628,7 @@
         <v>46178</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -14701,7 +14701,7 @@
         <v>45441</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -14774,7 +14774,7 @@
         <v>45254</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -14847,7 +14847,7 @@
         <v>45254</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -14920,7 +14920,7 @@
         <v>45752</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -14998,7 +14998,7 @@
         <v>45378</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -15071,7 +15071,7 @@
         <v>45382</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -15144,7 +15144,7 @@
         <v>45061</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -15217,7 +15217,7 @@
         <v>45342</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -15295,7 +15295,7 @@
         <v>45477</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -15368,7 +15368,7 @@
         <v>45371</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -15441,7 +15441,7 @@
         <v>46174</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -15514,7 +15514,7 @@
         <v>45456</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -15587,7 +15587,7 @@
         <v>44953</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -15660,7 +15660,7 @@
         <v>45253</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -15733,7 +15733,7 @@
         <v>45624</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -15806,7 +15806,7 @@
         <v>45169</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -15879,7 +15879,7 @@
         <v>45229</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -15952,7 +15952,7 @@
         <v>45770</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -16025,7 +16025,7 @@
         <v>45674</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -16098,7 +16098,7 @@
         <v>45035</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -16171,7 +16171,7 @@
         <v>46183</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -16244,7 +16244,7 @@
         <v>44635</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -16322,7 +16322,7 @@
         <v>46185</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -16395,7 +16395,7 @@
         <v>45957</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -16468,7 +16468,7 @@
         <v>45700</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -16541,7 +16541,7 @@
         <v>45751</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -16619,7 +16619,7 @@
         <v>45961</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -16692,7 +16692,7 @@
         <v>45961</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -16765,7 +16765,7 @@
         <v>45084</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -16838,7 +16838,7 @@
         <v>46188</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -16911,7 +16911,7 @@
         <v>45229</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -16984,7 +16984,7 @@
         <v>45922</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -17057,7 +17057,7 @@
         <v>46188</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -17130,7 +17130,7 @@
         <v>45252</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -17203,7 +17203,7 @@
         <v>44750</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -17276,7 +17276,7 @@
         <v>45368</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -17354,7 +17354,7 @@
         <v>45972</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -17427,7 +17427,7 @@
         <v>45972</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -17500,7 +17500,7 @@
         <v>44893</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -17573,7 +17573,7 @@
         <v>45972</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -17646,7 +17646,7 @@
         <v>46196</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -17719,7 +17719,7 @@
         <v>45541</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -17792,7 +17792,7 @@
         <v>45527</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -17865,7 +17865,7 @@
         <v>45062</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -17938,7 +17938,7 @@
         <v>46199</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -18011,7 +18011,7 @@
         <v>45979</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -18084,7 +18084,7 @@
         <v>45371</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -18157,7 +18157,7 @@
         <v>44868</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -18230,7 +18230,7 @@
         <v>45981</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -18303,7 +18303,7 @@
         <v>45737</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -18376,7 +18376,7 @@
         <v>45258</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -18449,7 +18449,7 @@
         <v>45981</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -18522,7 +18522,7 @@
         <v>45485</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -18595,7 +18595,7 @@
         <v>45462</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -18668,7 +18668,7 @@
         <v>45987</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -18741,7 +18741,7 @@
         <v>45560</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -18814,7 +18814,7 @@
         <v>46209</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -18887,7 +18887,7 @@
         <v>45089</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -18960,7 +18960,7 @@
         <v>46206</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -19033,7 +19033,7 @@
         <v>45989</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -19106,7 +19106,7 @@
         <v>45300</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -19179,7 +19179,7 @@
         <v>45352</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -19252,7 +19252,7 @@
         <v>45995</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -19325,7 +19325,7 @@
         <v>45097</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -19398,7 +19398,7 @@
         <v>45377</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -19476,7 +19476,7 @@
         <v>45176</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -19554,7 +19554,7 @@
         <v>45638</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -19627,7 +19627,7 @@
         <v>46224</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -19705,7 +19705,7 @@
         <v>45478</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -19778,7 +19778,7 @@
         <v>45351</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -19851,7 +19851,7 @@
         <v>45588</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -19929,7 +19929,7 @@
         <v>45926</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -20002,7 +20002,7 @@
         <v>45840</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -20080,7 +20080,7 @@
         <v>45616</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -20153,7 +20153,7 @@
         <v>45391</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -20226,7 +20226,7 @@
         <v>45510</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -20299,7 +20299,7 @@
         <v>46279</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -20372,7 +20372,7 @@
         <v>46279</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -20445,7 +20445,7 @@
         <v>46279</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -20518,7 +20518,7 @@
         <v>46036</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -20591,7 +20591,7 @@
         <v>45783</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -20664,7 +20664,7 @@
         <v>45616</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -20737,7 +20737,7 @@
         <v>45786</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -20815,7 +20815,7 @@
         <v>45559</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -20888,7 +20888,7 @@
         <v>44539</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -20961,7 +20961,7 @@
         <v>45680</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -21034,7 +21034,7 @@
         <v>45225</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -21107,7 +21107,7 @@
         <v>45589</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -21185,7 +21185,7 @@
         <v>45618</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -21258,7 +21258,7 @@
         <v>45726</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -21331,7 +21331,7 @@
         <v>45741</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -21404,7 +21404,7 @@
         <v>46020</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -21477,7 +21477,7 @@
         <v>45483</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -21550,7 +21550,7 @@
         <v>45609</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -21623,7 +21623,7 @@
         <v>46282</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -21696,7 +21696,7 @@
         <v>45483</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -21769,7 +21769,7 @@
         <v>46281</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -21842,7 +21842,7 @@
         <v>45743</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -21920,7 +21920,7 @@
         <v>45939</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -21998,7 +21998,7 @@
         <v>45590</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -22071,7 +22071,7 @@
         <v>45743</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -22149,7 +22149,7 @@
         <v>46241</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -22222,7 +22222,7 @@
         <v>46286</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -22295,7 +22295,7 @@
         <v>45559</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -22368,7 +22368,7 @@
         <v>45681</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -22441,7 +22441,7 @@
         <v>46286</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -22514,7 +22514,7 @@
         <v>45743</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -22592,7 +22592,7 @@
         <v>44851</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -22665,7 +22665,7 @@
         <v>46042</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -22738,7 +22738,7 @@
         <v>46283</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -22811,7 +22811,7 @@
         <v>46042</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -22884,7 +22884,7 @@
         <v>45793</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -22957,7 +22957,7 @@
         <v>46283</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -23030,7 +23030,7 @@
         <v>46245</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -23103,7 +23103,7 @@
         <v>46044</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -23176,7 +23176,7 @@
         <v>46044</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -23249,7 +23249,7 @@
         <v>46044</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -23322,7 +23322,7 @@
         <v>46044</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -23395,7 +23395,7 @@
         <v>46283</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -23468,7 +23468,7 @@
         <v>46048</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -23541,7 +23541,7 @@
         <v>46048</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -23614,7 +23614,7 @@
         <v>46048</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -23687,7 +23687,7 @@
         <v>46048</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -23760,7 +23760,7 @@
         <v>46048</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -23833,7 +23833,7 @@
         <v>46048</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -23906,7 +23906,7 @@
         <v>45600</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -23979,7 +23979,7 @@
         <v>46048</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -24052,7 +24052,7 @@
         <v>46048</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -24125,7 +24125,7 @@
         <v>46048</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -24198,7 +24198,7 @@
         <v>46048</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -24271,7 +24271,7 @@
         <v>46048</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -24344,7 +24344,7 @@
         <v>46048</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -24417,7 +24417,7 @@
         <v>46030</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -24490,7 +24490,7 @@
         <v>46281</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -24563,7 +24563,7 @@
         <v>46281</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -24636,7 +24636,7 @@
         <v>46049</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -24709,7 +24709,7 @@
         <v>46052</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -24782,7 +24782,7 @@
         <v>46052</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -24855,7 +24855,7 @@
         <v>44495</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -24928,7 +24928,7 @@
         <v>46247</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -25001,7 +25001,7 @@
         <v>45806</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -25074,7 +25074,7 @@
         <v>46055</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -25147,7 +25147,7 @@
         <v>46224</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -25220,7 +25220,7 @@
         <v>45400</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -25293,7 +25293,7 @@
         <v>45609</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -25366,7 +25366,7 @@
         <v>46057</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -25439,7 +25439,7 @@
         <v>46062</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -25512,7 +25512,7 @@
         <v>45812</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -25585,7 +25585,7 @@
         <v>46062</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -25658,7 +25658,7 @@
         <v>46064</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -25731,7 +25731,7 @@
         <v>46293</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -25804,7 +25804,7 @@
         <v>44950</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -25877,7 +25877,7 @@
         <v>45730</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -25950,7 +25950,7 @@
         <v>45694</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -26023,7 +26023,7 @@
         <v>45597</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -26096,7 +26096,7 @@
         <v>45708</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -26169,7 +26169,7 @@
         <v>46065</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -26242,7 +26242,7 @@
         <v>45387</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -26315,7 +26315,7 @@
         <v>45299</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -26388,7 +26388,7 @@
         <v>46248</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -26461,7 +26461,7 @@
         <v>46292</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -26534,7 +26534,7 @@
         <v>46070</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -26607,7 +26607,7 @@
         <v>45706</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -26680,7 +26680,7 @@
         <v>45820</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -26753,7 +26753,7 @@
         <v>46248</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -26826,7 +26826,7 @@
         <v>44900</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -26899,7 +26899,7 @@
         <v>46295</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -26972,7 +26972,7 @@
         <v>45825</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -27045,7 +27045,7 @@
         <v>45548</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -27118,7 +27118,7 @@
         <v>45831</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -27191,7 +27191,7 @@
         <v>46084</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -27264,7 +27264,7 @@
         <v>46161</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -27342,7 +27342,7 @@
         <v>46084</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -27415,7 +27415,7 @@
         <v>46087</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -27488,7 +27488,7 @@
         <v>45601</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -27561,7 +27561,7 @@
         <v>46244</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -27634,7 +27634,7 @@
         <v>45835</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -27707,7 +27707,7 @@
         <v>45836</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -27780,7 +27780,7 @@
         <v>45838</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -27853,7 +27853,7 @@
         <v>45840</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -27926,7 +27926,7 @@
         <v>45840</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -27999,7 +27999,7 @@
         <v>45840</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -28072,7 +28072,7 @@
         <v>46070</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -28145,7 +28145,7 @@
         <v>46093</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -28218,7 +28218,7 @@
         <v>46093</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -28291,7 +28291,7 @@
         <v>46093</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -28364,7 +28364,7 @@
         <v>45876</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -28437,7 +28437,7 @@
         <v>45845</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -28510,7 +28510,7 @@
         <v>45845</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -28583,7 +28583,7 @@
         <v>45800</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -28656,7 +28656,7 @@
         <v>45846</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -28734,7 +28734,7 @@
         <v>45846</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -28812,7 +28812,7 @@
         <v>45846</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -28890,7 +28890,7 @@
         <v>45352</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -28963,7 +28963,7 @@
         <v>46057</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -29036,7 +29036,7 @@
         <v>46302</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -29109,7 +29109,7 @@
         <v>44865</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -29182,7 +29182,7 @@
         <v>45847</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -29255,7 +29255,7 @@
         <v>45847</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -29328,7 +29328,7 @@
         <v>45803</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -29401,7 +29401,7 @@
         <v>46057</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -29474,7 +29474,7 @@
         <v>46111</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -29547,7 +29547,7 @@
         <v>46111</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -29620,7 +29620,7 @@
         <v>46111</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -29693,7 +29693,7 @@
         <v>46302</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -29766,7 +29766,7 @@
         <v>45352</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -29839,7 +29839,7 @@
         <v>46261</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -29912,7 +29912,7 @@
         <v>45700</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -29985,7 +29985,7 @@
         <v>45700</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -30058,7 +30058,7 @@
         <v>45687</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -30131,7 +30131,7 @@
         <v>44834</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -30204,7 +30204,7 @@
         <v>46294</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -30282,7 +30282,7 @@
         <v>45838</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -30355,7 +30355,7 @@
         <v>46121</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -30428,7 +30428,7 @@
         <v>46120</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -30501,7 +30501,7 @@
         <v>46292</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -30574,7 +30574,7 @@
         <v>46292</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -30647,7 +30647,7 @@
         <v>46292</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -30720,7 +30720,7 @@
         <v>46292</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -30793,7 +30793,7 @@
         <v>46121</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -30866,7 +30866,7 @@
         <v>46121</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -30939,7 +30939,7 @@
         <v>45288</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -31017,7 +31017,7 @@
         <v>45309</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -31090,7 +31090,7 @@
         <v>45407</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -31163,7 +31163,7 @@
         <v>45677</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -31236,7 +31236,7 @@
         <v>46121</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -31309,7 +31309,7 @@
         <v>46121</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -31382,7 +31382,7 @@
         <v>46120</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -31455,7 +31455,7 @@
         <v>45257</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -31528,7 +31528,7 @@
         <v>45395</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -31601,7 +31601,7 @@
         <v>44671</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -31674,7 +31674,7 @@
         <v>45524</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -31747,7 +31747,7 @@
         <v>45272</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -31820,7 +31820,7 @@
         <v>46121</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -31893,7 +31893,7 @@
         <v>46121</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -31966,7 +31966,7 @@
         <v>45245</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -32039,7 +32039,7 @@
         <v>45679</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -32112,7 +32112,7 @@
         <v>45610</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -32185,7 +32185,7 @@
         <v>46122</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -32258,7 +32258,7 @@
         <v>45432</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -32331,7 +32331,7 @@
         <v>44712</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -32404,7 +32404,7 @@
         <v>45131</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -32477,7 +32477,7 @@
         <v>45176</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -32550,7 +32550,7 @@
         <v>45372</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -32623,7 +32623,7 @@
         <v>45361</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -32696,7 +32696,7 @@
         <v>45541</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -32769,7 +32769,7 @@
         <v>45257</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -32847,7 +32847,7 @@
         <v>45727</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -32920,7 +32920,7 @@
         <v>44917</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -32993,7 +32993,7 @@
         <v>46122</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -33066,7 +33066,7 @@
         <v>45735</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -33139,7 +33139,7 @@
         <v>45672</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -33212,7 +33212,7 @@
         <v>45204</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -33285,7 +33285,7 @@
         <v>45293</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -33358,7 +33358,7 @@
         <v>45245</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -33431,7 +33431,7 @@
         <v>44671</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -33504,7 +33504,7 @@
         <v>44896</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -33577,7 +33577,7 @@
         <v>44592</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -33650,7 +33650,7 @@
         <v>46292</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -33723,7 +33723,7 @@
         <v>45293</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -33796,7 +33796,7 @@
         <v>45623</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -33869,7 +33869,7 @@
         <v>45199</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -33942,7 +33942,7 @@
         <v>46122</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -34015,7 +34015,7 @@
         <v>45769</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -34088,7 +34088,7 @@
         <v>45392</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -34161,7 +34161,7 @@
         <v>46261</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -34234,7 +34234,7 @@
         <v>45395</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -34307,7 +34307,7 @@
         <v>45589</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -34380,7 +34380,7 @@
         <v>46122</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -34453,7 +34453,7 @@
         <v>45546</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -34526,7 +34526,7 @@
         <v>46121</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -34599,7 +34599,7 @@
         <v>44701</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -34672,7 +34672,7 @@
         <v>45145</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -34745,7 +34745,7 @@
         <v>45517</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -34818,7 +34818,7 @@
         <v>45230</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -34891,7 +34891,7 @@
         <v>45677</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -34964,7 +34964,7 @@
         <v>45672</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -35037,7 +35037,7 @@
         <v>45672</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -35110,7 +35110,7 @@
         <v>44964</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -35183,7 +35183,7 @@
         <v>45735</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -35256,7 +35256,7 @@
         <v>44739</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -35329,7 +35329,7 @@
         <v>45309</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -35402,7 +35402,7 @@
         <v>44508</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -35475,7 +35475,7 @@
         <v>45623</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -35548,7 +35548,7 @@
         <v>45252</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -35621,7 +35621,7 @@
         <v>45589</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -35694,7 +35694,7 @@
         <v>45190</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -35767,7 +35767,7 @@
         <v>44817</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -35840,7 +35840,7 @@
         <v>45574</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -35913,7 +35913,7 @@
         <v>45545</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -35986,7 +35986,7 @@
         <v>45199</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -36059,7 +36059,7 @@
         <v>45190</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -36137,7 +36137,7 @@
         <v>44889</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -36210,7 +36210,7 @@
         <v>45623</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -36283,7 +36283,7 @@
         <v>46292</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -36356,7 +36356,7 @@
         <v>45880</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -36429,7 +36429,7 @@
         <v>45880</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -36502,7 +36502,7 @@
         <v>46128</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -36575,7 +36575,7 @@
         <v>45877</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -36648,7 +36648,7 @@
         <v>45880</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -36721,7 +36721,7 @@
         <v>45880</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -36794,7 +36794,7 @@
         <v>46263</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -36867,7 +36867,7 @@
         <v>44896</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -36940,7 +36940,7 @@
         <v>45429</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -37013,7 +37013,7 @@
         <v>45790</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -37086,7 +37086,7 @@
         <v>45366</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -37159,7 +37159,7 @@
         <v>45538</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -37232,7 +37232,7 @@
         <v>45840</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -37310,7 +37310,7 @@
         <v>45671</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -37383,7 +37383,7 @@
         <v>45775</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -37456,7 +37456,7 @@
         <v>45782</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -37529,7 +37529,7 @@
         <v>46268</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -37602,7 +37602,7 @@
         <v>44699</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -37675,7 +37675,7 @@
         <v>45524</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -37748,7 +37748,7 @@
         <v>45558</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -37821,7 +37821,7 @@
         <v>46268</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -37894,7 +37894,7 @@
         <v>45989</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -37967,7 +37967,7 @@
         <v>46084</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -38040,7 +38040,7 @@
         <v>46268</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -38113,7 +38113,7 @@
         <v>46272</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -38186,7 +38186,7 @@
         <v>45531</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -38259,7 +38259,7 @@
         <v>45817</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -38332,7 +38332,7 @@
         <v>45839</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -38405,7 +38405,7 @@
         <v>46316</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -38478,7 +38478,7 @@
         <v>44719</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -38551,7 +38551,7 @@
         <v>45848</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -38624,7 +38624,7 @@
         <v>46272</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -38697,7 +38697,7 @@
         <v>46273</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -38770,7 +38770,7 @@
         <v>46273</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -38843,7 +38843,7 @@
         <v>46273</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -38916,7 +38916,7 @@
         <v>44701</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -38994,7 +38994,7 @@
         <v>45259</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -39067,7 +39067,7 @@
         <v>44714</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -39140,7 +39140,7 @@
         <v>46317</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -39218,7 +39218,7 @@
         <v>46317</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -39296,7 +39296,7 @@
         <v>46317</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -39374,7 +39374,7 @@
         <v>46317</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -39447,7 +39447,7 @@
         <v>45617</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -39520,7 +39520,7 @@
         <v>44974</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -39593,7 +39593,7 @@
         <v>46318</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -39666,7 +39666,7 @@
         <v>45229</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -39739,7 +39739,7 @@
         <v>45198</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -39812,7 +39812,7 @@
         <v>46317</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -39885,7 +39885,7 @@
         <v>44900</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -39958,7 +39958,7 @@
         <v>46148</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -40031,7 +40031,7 @@
         <v>45441</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -40104,7 +40104,7 @@
         <v>44926</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -40182,7 +40182,7 @@
         <v>44756</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -40255,7 +40255,7 @@
         <v>45162</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -40328,7 +40328,7 @@
         <v>45162</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -40401,7 +40401,7 @@
         <v>45268</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -40474,7 +40474,7 @@
         <v>44903</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -40547,7 +40547,7 @@
         <v>46153</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -40620,7 +40620,7 @@
         <v>44999</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -40693,7 +40693,7 @@
         <v>46153</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -40766,7 +40766,7 @@
         <v>46153</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -40839,7 +40839,7 @@
         <v>46153</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -40912,7 +40912,7 @@
         <v>45709</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -40985,7 +40985,7 @@
         <v>46153</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -41058,7 +41058,7 @@
         <v>46153</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -41131,7 +41131,7 @@
         <v>46153</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -41204,7 +41204,7 @@
         <v>46155</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -41277,7 +41277,7 @@
         <v>45254</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -41350,7 +41350,7 @@
         <v>45460</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -41423,7 +41423,7 @@
         <v>44965</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -41501,7 +41501,7 @@
         <v>44970</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -41574,7 +41574,7 @@
         <v>44970</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -41647,7 +41647,7 @@
         <v>45107</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -41720,7 +41720,7 @@
         <v>45456</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -41793,7 +41793,7 @@
         <v>45092</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -41866,7 +41866,7 @@
         <v>45229</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -41939,7 +41939,7 @@
         <v>45002</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -42012,7 +42012,7 @@
         <v>45107</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -42085,7 +42085,7 @@
         <v>45645</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -42158,7 +42158,7 @@
         <v>45145</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -42231,7 +42231,7 @@
         <v>45638</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -42304,7 +42304,7 @@
         <v>45568</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -42377,7 +42377,7 @@
         <v>44712</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -42450,7 +42450,7 @@
         <v>44729</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -42523,7 +42523,7 @@
         <v>45483</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -42596,7 +42596,7 @@
         <v>44980</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -42669,7 +42669,7 @@
         <v>45246</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -42742,7 +42742,7 @@
         <v>45715</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -42815,7 +42815,7 @@
         <v>45544</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -42888,7 +42888,7 @@
         <v>45229</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -42961,7 +42961,7 @@
         <v>45502</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -43034,7 +43034,7 @@
         <v>44910</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -43107,7 +43107,7 @@
         <v>45019</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -43180,7 +43180,7 @@
         <v>45257</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -43253,7 +43253,7 @@
         <v>45754</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -43326,7 +43326,7 @@
         <v>45091</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -43399,7 +43399,7 @@
         <v>44869</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -43472,7 +43472,7 @@
         <v>45096</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -43545,7 +43545,7 @@
         <v>44900</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -43623,7 +43623,7 @@
         <v>45104</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -43696,7 +43696,7 @@
         <v>45441</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -43769,7 +43769,7 @@
         <v>45441</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -43842,7 +43842,7 @@
         <v>45229</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -43915,7 +43915,7 @@
         <v>45110</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -43988,7 +43988,7 @@
         <v>45170</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -44061,7 +44061,7 @@
         <v>45310</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -44134,7 +44134,7 @@
         <v>45694</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -44207,7 +44207,7 @@
         <v>45406</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -44280,7 +44280,7 @@
         <v>44967</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -44353,7 +44353,7 @@
         <v>45110</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -44426,7 +44426,7 @@
         <v>45145</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -44499,7 +44499,7 @@
         <v>45117</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -44572,7 +44572,7 @@
         <v>45352</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -44645,7 +44645,7 @@
         <v>45405</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -44718,7 +44718,7 @@
         <v>44530</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -44791,7 +44791,7 @@
         <v>45104</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -44864,7 +44864,7 @@
         <v>45454</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -44937,7 +44937,7 @@
         <v>44601</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -45010,7 +45010,7 @@
         <v>44510</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -45083,7 +45083,7 @@
         <v>45182</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -45156,7 +45156,7 @@
         <v>45539</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -45229,7 +45229,7 @@
         <v>45253</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -45302,7 +45302,7 @@
         <v>45531</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -45375,7 +45375,7 @@
         <v>45715</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -45448,7 +45448,7 @@
         <v>45182</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -45521,7 +45521,7 @@
         <v>45414</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -45594,7 +45594,7 @@
         <v>45643</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -45667,7 +45667,7 @@
         <v>45114</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -45740,7 +45740,7 @@
         <v>44970</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -45813,7 +45813,7 @@
         <v>45538</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -45886,7 +45886,7 @@
         <v>45170</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -45959,7 +45959,7 @@
         <v>45462</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -46032,7 +46032,7 @@
         <v>45170</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -46105,7 +46105,7 @@
         <v>45604</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -46178,7 +46178,7 @@
         <v>45091</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -46251,7 +46251,7 @@
         <v>45597</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -46324,7 +46324,7 @@
         <v>44641</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -46397,7 +46397,7 @@
         <v>45432</v>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -46470,7 +46470,7 @@
         <v>45159</v>
       </c>
       <c r="E610" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -46543,7 +46543,7 @@
         <v>45456</v>
       </c>
       <c r="E611" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
@@ -46616,7 +46616,7 @@
         <v>45366</v>
       </c>
       <c r="E612" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
@@ -46694,7 +46694,7 @@
         <v>44697</v>
       </c>
       <c r="E613" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
@@ -46767,7 +46767,7 @@
         <v>45194</v>
       </c>
       <c r="E614" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F614" t="inlineStr">
         <is>
@@ -46840,7 +46840,7 @@
         <v>45203</v>
       </c>
       <c r="E615" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F615" t="inlineStr">
         <is>
@@ -46913,7 +46913,7 @@
         <v>45677</v>
       </c>
       <c r="E616" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F616" t="inlineStr">
         <is>
@@ -46986,7 +46986,7 @@
         <v>45132</v>
       </c>
       <c r="E617" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F617" t="inlineStr">
         <is>
@@ -47059,7 +47059,7 @@
         <v>45173</v>
       </c>
       <c r="E618" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F618" t="inlineStr">
         <is>
@@ -47132,7 +47132,7 @@
         <v>45153</v>
       </c>
       <c r="E619" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F619" t="inlineStr">
         <is>
@@ -47205,7 +47205,7 @@
         <v>45084</v>
       </c>
       <c r="E620" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F620" t="inlineStr">
         <is>
@@ -47278,7 +47278,7 @@
         <v>45254</v>
       </c>
       <c r="E621" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F621" t="inlineStr">
         <is>
@@ -47351,7 +47351,7 @@
         <v>45211</v>
       </c>
       <c r="E622" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F622" t="inlineStr">
         <is>
@@ -47424,7 +47424,7 @@
         <v>45568</v>
       </c>
       <c r="E623" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F623" t="inlineStr">
         <is>
@@ -47497,7 +47497,7 @@
         <v>45441</v>
       </c>
       <c r="E624" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F624" t="inlineStr">
         <is>
@@ -47575,7 +47575,7 @@
         <v>45456</v>
       </c>
       <c r="E625" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F625" t="inlineStr">
         <is>
@@ -47648,7 +47648,7 @@
         <v>45225</v>
       </c>
       <c r="E626" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F626" t="inlineStr">
         <is>
@@ -47721,7 +47721,7 @@
         <v>45181</v>
       </c>
       <c r="E627" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F627" t="inlineStr">
         <is>
@@ -47794,7 +47794,7 @@
         <v>44823</v>
       </c>
       <c r="E628" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F628" t="inlineStr">
         <is>
@@ -47867,7 +47867,7 @@
         <v>45238</v>
       </c>
       <c r="E629" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F629" t="inlineStr">
         <is>
@@ -47940,7 +47940,7 @@
         <v>45287</v>
       </c>
       <c r="E630" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F630" t="inlineStr">
         <is>
@@ -48013,7 +48013,7 @@
         <v>44701</v>
       </c>
       <c r="E631" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F631" t="inlineStr">
         <is>
@@ -48091,7 +48091,7 @@
         <v>44735</v>
       </c>
       <c r="E632" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F632" t="inlineStr">
         <is>
@@ -48164,7 +48164,7 @@
         <v>44651</v>
       </c>
       <c r="E633" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F633" t="inlineStr">
         <is>
@@ -48237,7 +48237,7 @@
         <v>45169</v>
       </c>
       <c r="E634" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F634" t="inlineStr">
         <is>
@@ -48310,7 +48310,7 @@
         <v>45316</v>
       </c>
       <c r="E635" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F635" t="inlineStr">
         <is>
@@ -48388,7 +48388,7 @@
         <v>45167</v>
       </c>
       <c r="E636" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F636" t="inlineStr">
         <is>
@@ -48461,7 +48461,7 @@
         <v>45254</v>
       </c>
       <c r="E637" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F637" t="inlineStr">
         <is>
@@ -48534,7 +48534,7 @@
         <v>45254</v>
       </c>
       <c r="E638" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F638" t="inlineStr">
         <is>
@@ -48607,7 +48607,7 @@
         <v>45245</v>
       </c>
       <c r="E639" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F639" t="inlineStr">
         <is>
@@ -48680,7 +48680,7 @@
         <v>44778</v>
       </c>
       <c r="E640" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F640" t="inlineStr">
         <is>
@@ -48753,7 +48753,7 @@
         <v>44847</v>
       </c>
       <c r="E641" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F641" t="inlineStr">
         <is>
@@ -48826,7 +48826,7 @@
         <v>44694</v>
       </c>
       <c r="E642" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F642" t="inlineStr">
         <is>
@@ -48899,7 +48899,7 @@
         <v>45245</v>
       </c>
       <c r="E643" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F643" t="inlineStr">
         <is>
@@ -48972,7 +48972,7 @@
         <v>45092</v>
       </c>
       <c r="E644" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F644" t="inlineStr">
         <is>
@@ -49045,7 +49045,7 @@
         <v>45051</v>
       </c>
       <c r="E645" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F645" t="inlineStr">
         <is>
@@ -49118,7 +49118,7 @@
         <v>45098</v>
       </c>
       <c r="E646" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F646" t="inlineStr">
         <is>
@@ -49196,7 +49196,7 @@
         <v>45351</v>
       </c>
       <c r="E647" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F647" t="inlineStr">
         <is>
@@ -49269,7 +49269,7 @@
         <v>44797</v>
       </c>
       <c r="E648" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F648" t="inlineStr">
         <is>
@@ -49342,7 +49342,7 @@
         <v>45267</v>
       </c>
       <c r="E649" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F649" t="inlineStr">
         <is>
@@ -49415,7 +49415,7 @@
         <v>44974</v>
       </c>
       <c r="E650" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F650" t="inlineStr">
         <is>
@@ -49488,7 +49488,7 @@
         <v>44559</v>
       </c>
       <c r="E651" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F651" t="inlineStr">
         <is>
@@ -49561,7 +49561,7 @@
         <v>44893</v>
       </c>
       <c r="E652" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F652" t="inlineStr">
         <is>
@@ -49634,7 +49634,7 @@
         <v>45455</v>
       </c>
       <c r="E653" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F653" t="inlineStr">
         <is>
@@ -49707,7 +49707,7 @@
         <v>45104</v>
       </c>
       <c r="E654" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F654" t="inlineStr">
         <is>
@@ -49780,7 +49780,7 @@
         <v>45334</v>
       </c>
       <c r="E655" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F655" t="inlineStr">
         <is>
@@ -49853,7 +49853,7 @@
         <v>45352</v>
       </c>
       <c r="E656" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F656" t="inlineStr">
         <is>
@@ -49926,7 +49926,7 @@
         <v>45715</v>
       </c>
       <c r="E657" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F657" t="inlineStr">
         <is>
@@ -49999,7 +49999,7 @@
         <v>45316</v>
       </c>
       <c r="E658" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F658" t="inlineStr">
         <is>
@@ -50072,7 +50072,7 @@
         <v>44796</v>
       </c>
       <c r="E659" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F659" t="inlineStr">
         <is>
@@ -50145,7 +50145,7 @@
         <v>44901</v>
       </c>
       <c r="E660" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F660" t="inlineStr">
         <is>
@@ -50218,7 +50218,7 @@
         <v>45589</v>
       </c>
       <c r="E661" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F661" t="inlineStr">
         <is>
@@ -50291,7 +50291,7 @@
         <v>44899</v>
       </c>
       <c r="E662" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F662" t="inlineStr">
         <is>
@@ -50364,7 +50364,7 @@
         <v>44995</v>
       </c>
       <c r="E663" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F663" t="inlineStr">
         <is>
@@ -50437,7 +50437,7 @@
         <v>45548</v>
       </c>
       <c r="E664" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F664" t="inlineStr">
         <is>
@@ -50510,7 +50510,7 @@
         <v>44958</v>
       </c>
       <c r="E665" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F665" t="inlineStr">
         <is>
@@ -50583,7 +50583,7 @@
         <v>44575</v>
       </c>
       <c r="E666" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F666" t="inlineStr">
         <is>
@@ -50656,7 +50656,7 @@
         <v>45572</v>
       </c>
       <c r="E667" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F667" t="inlineStr">
         <is>
@@ -50729,7 +50729,7 @@
         <v>44951</v>
       </c>
       <c r="E668" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F668" t="inlineStr">
         <is>
@@ -50802,7 +50802,7 @@
         <v>45265</v>
       </c>
       <c r="E669" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F669" t="inlineStr">
         <is>
@@ -50875,7 +50875,7 @@
         <v>45432</v>
       </c>
       <c r="E670" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F670" t="inlineStr">
         <is>
@@ -50948,7 +50948,7 @@
         <v>44631</v>
       </c>
       <c r="E671" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F671" t="inlineStr">
         <is>
@@ -51021,7 +51021,7 @@
         <v>44613</v>
       </c>
       <c r="E672" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F672" t="inlineStr">
         <is>
@@ -51094,7 +51094,7 @@
         <v>44608</v>
       </c>
       <c r="E673" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F673" t="inlineStr">
         <is>
@@ -51167,7 +51167,7 @@
         <v>44631</v>
       </c>
       <c r="E674" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F674" t="inlineStr">
         <is>
@@ -51240,7 +51240,7 @@
         <v>44631</v>
       </c>
       <c r="E675" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F675" t="inlineStr">
         <is>
@@ -51313,7 +51313,7 @@
         <v>45614</v>
       </c>
       <c r="E676" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F676" t="inlineStr">
         <is>
@@ -51391,7 +51391,7 @@
         <v>44743</v>
       </c>
       <c r="E677" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F677" t="inlineStr">
         <is>
@@ -51464,7 +51464,7 @@
         <v>45375</v>
       </c>
       <c r="E678" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F678" t="inlineStr">
         <is>
@@ -51537,7 +51537,7 @@
         <v>45604</v>
       </c>
       <c r="E679" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F679" t="inlineStr">
         <is>
@@ -51610,7 +51610,7 @@
         <v>45356</v>
       </c>
       <c r="E680" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F680" t="inlineStr">
         <is>
@@ -51683,7 +51683,7 @@
         <v>45349</v>
       </c>
       <c r="E681" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F681" t="inlineStr">
         <is>
@@ -51756,7 +51756,7 @@
         <v>45744</v>
       </c>
       <c r="E682" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F682" t="inlineStr">
         <is>
@@ -51829,7 +51829,7 @@
         <v>45714</v>
       </c>
       <c r="E683" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F683" t="inlineStr">
         <is>
@@ -51902,7 +51902,7 @@
         <v>45715</v>
       </c>
       <c r="E684" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F684" t="inlineStr">
         <is>
@@ -51975,7 +51975,7 @@
         <v>45709</v>
       </c>
       <c r="E685" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F685" t="inlineStr">
         <is>
@@ -52048,7 +52048,7 @@
         <v>45714</v>
       </c>
       <c r="E686" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F686" t="inlineStr">
         <is>
@@ -52121,7 +52121,7 @@
         <v>45813</v>
       </c>
       <c r="E687" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F687" t="inlineStr">
         <is>
@@ -52194,7 +52194,7 @@
         <v>45813</v>
       </c>
       <c r="E688" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F688" t="inlineStr">
         <is>
@@ -52267,7 +52267,7 @@
         <v>45813</v>
       </c>
       <c r="E689" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F689" t="inlineStr">
         <is>
@@ -52340,7 +52340,7 @@
         <v>45820</v>
       </c>
       <c r="E690" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F690" t="inlineStr">
         <is>
@@ -52413,7 +52413,7 @@
         <v>45827</v>
       </c>
       <c r="E691" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F691" t="inlineStr">
         <is>
@@ -52486,7 +52486,7 @@
         <v>45845</v>
       </c>
       <c r="E692" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F692" t="inlineStr">
         <is>
@@ -52559,7 +52559,7 @@
         <v>45883</v>
       </c>
       <c r="E693" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F693" t="inlineStr">
         <is>
@@ -52632,7 +52632,7 @@
         <v>45915</v>
       </c>
       <c r="E694" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F694" t="inlineStr">
         <is>
@@ -52705,7 +52705,7 @@
         <v>46041</v>
       </c>
       <c r="E695" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F695" t="inlineStr">
         <is>
@@ -52778,7 +52778,7 @@
         <v>46133</v>
       </c>
       <c r="E696" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F696" t="inlineStr">
         <is>
@@ -52851,7 +52851,7 @@
         <v>46147</v>
       </c>
       <c r="E697" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F697" t="inlineStr">
         <is>
@@ -52924,7 +52924,7 @@
         <v>46211</v>
       </c>
       <c r="E698" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F698" t="inlineStr">
         <is>
@@ -52997,7 +52997,7 @@
         <v>46290</v>
       </c>
       <c r="E699" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F699" t="inlineStr">
         <is>
@@ -53070,7 +53070,7 @@
         <v>46253</v>
       </c>
       <c r="E700" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F700" t="inlineStr">
         <is>

--- a/Översikt HYLTE.xlsx
+++ b/Översikt HYLTE.xlsx
@@ -601,7 +601,7 @@
         <v>46090</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -718,7 +718,7 @@
         <v>45265</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -834,7 +834,7 @@
         <v>46066</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -945,7 +945,7 @@
         <v>44873</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1054,7 +1054,7 @@
         <v>45348</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1166,7 +1166,7 @@
         <v>45719</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1274,7 +1274,7 @@
         <v>46268</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1381,7 +1381,7 @@
         <v>45245</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1492,7 +1492,7 @@
         <v>45230</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1599,7 +1599,7 @@
         <v>45737</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1706,7 +1706,7 @@
         <v>46141</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1813,7 +1813,7 @@
         <v>46161</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1920,7 +1920,7 @@
         <v>44839</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2030,7 +2030,7 @@
         <v>45904</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2140,7 +2140,7 @@
         <v>46048</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2246,7 +2246,7 @@
         <v>45841</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2356,7 +2356,7 @@
         <v>45099</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2466,7 +2466,7 @@
         <v>46304</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2576,7 +2576,7 @@
         <v>46130</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2682,7 +2682,7 @@
         <v>44648</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2787,7 +2787,7 @@
         <v>44651</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2892,7 +2892,7 @@
         <v>44876</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2997,7 +2997,7 @@
         <v>45186</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3102,7 +3102,7 @@
         <v>45299</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3211,7 +3211,7 @@
         <v>45245</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3316,7 +3316,7 @@
         <v>45593</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3421,7 +3421,7 @@
         <v>45245</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3526,7 +3526,7 @@
         <v>45617</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3631,7 +3631,7 @@
         <v>45153</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3745,7 +3745,7 @@
         <v>45163</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3850,7 +3850,7 @@
         <v>45343</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3955,7 +3955,7 @@
         <v>45476</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4065,7 +4065,7 @@
         <v>45085</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4174,7 +4174,7 @@
         <v>45253</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4279,7 +4279,7 @@
         <v>45754</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4384,7 +4384,7 @@
         <v>46253</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4494,7 +4494,7 @@
         <v>44810</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4567,7 +4567,7 @@
         <v>44600</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4640,7 +4640,7 @@
         <v>44529</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4713,7 +4713,7 @@
         <v>44557</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4786,7 +4786,7 @@
         <v>44705</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4859,7 +4859,7 @@
         <v>44778</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4932,7 +4932,7 @@
         <v>44624</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5005,7 +5005,7 @@
         <v>44812</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5078,7 +5078,7 @@
         <v>44638</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5151,7 +5151,7 @@
         <v>44498</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5224,7 +5224,7 @@
         <v>44845</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5297,7 +5297,7 @@
         <v>44559</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5370,7 +5370,7 @@
         <v>44659</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5448,7 +5448,7 @@
         <v>44578</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5521,7 +5521,7 @@
         <v>44756</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5594,7 +5594,7 @@
         <v>44501</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5667,7 +5667,7 @@
         <v>44651</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5740,7 +5740,7 @@
         <v>44711</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5813,7 +5813,7 @@
         <v>44735</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5886,7 +5886,7 @@
         <v>44834</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5959,7 +5959,7 @@
         <v>44796</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6032,7 +6032,7 @@
         <v>44502</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6105,7 +6105,7 @@
         <v>44631</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6178,7 +6178,7 @@
         <v>44876</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6251,7 +6251,7 @@
         <v>44659</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6324,7 +6324,7 @@
         <v>44644</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6397,7 +6397,7 @@
         <v>44515</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6475,7 +6475,7 @@
         <v>44778</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6548,7 +6548,7 @@
         <v>44867</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6621,7 +6621,7 @@
         <v>44505</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6694,7 +6694,7 @@
         <v>44634</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6767,7 +6767,7 @@
         <v>44728</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6840,7 +6840,7 @@
         <v>44714</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6913,7 +6913,7 @@
         <v>44795</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6986,7 +6986,7 @@
         <v>44818</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7059,7 +7059,7 @@
         <v>44801</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7132,7 +7132,7 @@
         <v>44596</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7210,7 +7210,7 @@
         <v>44644</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7283,7 +7283,7 @@
         <v>44523</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7356,7 +7356,7 @@
         <v>44500</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7429,7 +7429,7 @@
         <v>44727</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7502,7 +7502,7 @@
         <v>44705</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7575,7 +7575,7 @@
         <v>44659</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7653,7 +7653,7 @@
         <v>44659</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7731,7 +7731,7 @@
         <v>44757</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7804,7 +7804,7 @@
         <v>44494</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7877,7 +7877,7 @@
         <v>45834</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7950,7 +7950,7 @@
         <v>45840</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8023,7 +8023,7 @@
         <v>45436</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8096,7 +8096,7 @@
         <v>44495</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8169,7 +8169,7 @@
         <v>45132</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8242,7 +8242,7 @@
         <v>45246</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8315,7 +8315,7 @@
         <v>45246</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8388,7 +8388,7 @@
         <v>45673</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8461,7 +8461,7 @@
         <v>45426</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8534,7 +8534,7 @@
         <v>45042</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8607,7 +8607,7 @@
         <v>45327</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8680,7 +8680,7 @@
         <v>45890</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8753,7 +8753,7 @@
         <v>45748</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8826,7 +8826,7 @@
         <v>45371</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8899,7 +8899,7 @@
         <v>45891</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8977,7 +8977,7 @@
         <v>45891</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -9055,7 +9055,7 @@
         <v>45411</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9128,7 +9128,7 @@
         <v>45299</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9201,7 +9201,7 @@
         <v>45208</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9274,7 +9274,7 @@
         <v>45254</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9347,7 +9347,7 @@
         <v>45897</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9420,7 +9420,7 @@
         <v>45897</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9493,7 +9493,7 @@
         <v>45839</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9566,7 +9566,7 @@
         <v>45898</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9639,7 +9639,7 @@
         <v>44900</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9712,7 +9712,7 @@
         <v>44900</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9785,7 +9785,7 @@
         <v>45441</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9863,7 +9863,7 @@
         <v>44866</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9936,7 +9936,7 @@
         <v>45905</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -10009,7 +10009,7 @@
         <v>45624</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -10082,7 +10082,7 @@
         <v>45910</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10155,7 +10155,7 @@
         <v>46161</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10233,7 +10233,7 @@
         <v>46161</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10306,7 +10306,7 @@
         <v>45910</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10379,7 +10379,7 @@
         <v>45580</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10452,7 +10452,7 @@
         <v>45568</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10525,7 +10525,7 @@
         <v>46161</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10603,7 +10603,7 @@
         <v>45838</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10676,7 +10676,7 @@
         <v>46161</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10749,7 +10749,7 @@
         <v>46161</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -10827,7 +10827,7 @@
         <v>45918</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10900,7 +10900,7 @@
         <v>44714</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10978,7 +10978,7 @@
         <v>44813</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -11051,7 +11051,7 @@
         <v>45922</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -11124,7 +11124,7 @@
         <v>45163</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11197,7 +11197,7 @@
         <v>44851</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11270,7 +11270,7 @@
         <v>44851</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11343,7 +11343,7 @@
         <v>45922</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11416,7 +11416,7 @@
         <v>45035</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11489,7 +11489,7 @@
         <v>45922</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11562,7 +11562,7 @@
         <v>44726</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11635,7 +11635,7 @@
         <v>45331</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11708,7 +11708,7 @@
         <v>45924</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -11781,7 +11781,7 @@
         <v>45926</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -11854,7 +11854,7 @@
         <v>45926</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -11927,7 +11927,7 @@
         <v>45926</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -12000,7 +12000,7 @@
         <v>45019</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -12073,7 +12073,7 @@
         <v>46169</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -12146,7 +12146,7 @@
         <v>45350</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12219,7 +12219,7 @@
         <v>45929</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12292,7 +12292,7 @@
         <v>46169</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12365,7 +12365,7 @@
         <v>46169</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12438,7 +12438,7 @@
         <v>45434</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -12511,7 +12511,7 @@
         <v>44847</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -12584,7 +12584,7 @@
         <v>45254</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -12657,7 +12657,7 @@
         <v>45254</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -12730,7 +12730,7 @@
         <v>45931</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -12803,7 +12803,7 @@
         <v>45931</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -12876,7 +12876,7 @@
         <v>46171</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -12949,7 +12949,7 @@
         <v>46170</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -13022,7 +13022,7 @@
         <v>45930</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -13095,7 +13095,7 @@
         <v>44900</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -13168,7 +13168,7 @@
         <v>45357</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13241,7 +13241,7 @@
         <v>45429</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13314,7 +13314,7 @@
         <v>45933</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13387,7 +13387,7 @@
         <v>45936</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -13460,7 +13460,7 @@
         <v>45936</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -13533,7 +13533,7 @@
         <v>45933</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -13606,7 +13606,7 @@
         <v>45933</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -13679,7 +13679,7 @@
         <v>46174</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -13752,7 +13752,7 @@
         <v>45936</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -13825,7 +13825,7 @@
         <v>44872</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -13898,7 +13898,7 @@
         <v>45937</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -13971,7 +13971,7 @@
         <v>45390</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -14044,7 +14044,7 @@
         <v>45938</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -14117,7 +14117,7 @@
         <v>46175</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -14190,7 +14190,7 @@
         <v>46174</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14263,7 +14263,7 @@
         <v>45944</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14336,7 +14336,7 @@
         <v>46174</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -14409,7 +14409,7 @@
         <v>45002</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -14482,7 +14482,7 @@
         <v>45684</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -14555,7 +14555,7 @@
         <v>46178</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -14628,7 +14628,7 @@
         <v>46178</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -14701,7 +14701,7 @@
         <v>45441</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -14774,7 +14774,7 @@
         <v>45254</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -14847,7 +14847,7 @@
         <v>45254</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -14920,7 +14920,7 @@
         <v>45752</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -14998,7 +14998,7 @@
         <v>45378</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -15071,7 +15071,7 @@
         <v>45382</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -15144,7 +15144,7 @@
         <v>45061</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -15217,7 +15217,7 @@
         <v>45342</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -15295,7 +15295,7 @@
         <v>45477</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -15368,7 +15368,7 @@
         <v>45371</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -15441,7 +15441,7 @@
         <v>46174</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -15514,7 +15514,7 @@
         <v>45456</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -15587,7 +15587,7 @@
         <v>44953</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -15660,7 +15660,7 @@
         <v>45253</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -15733,7 +15733,7 @@
         <v>45624</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -15806,7 +15806,7 @@
         <v>45169</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -15879,7 +15879,7 @@
         <v>45229</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -15952,7 +15952,7 @@
         <v>45770</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -16025,7 +16025,7 @@
         <v>45674</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -16098,7 +16098,7 @@
         <v>45035</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -16171,7 +16171,7 @@
         <v>46183</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -16244,7 +16244,7 @@
         <v>44635</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -16322,7 +16322,7 @@
         <v>46185</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -16395,7 +16395,7 @@
         <v>45957</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -16468,7 +16468,7 @@
         <v>45700</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -16541,7 +16541,7 @@
         <v>45751</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -16619,7 +16619,7 @@
         <v>45961</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -16692,7 +16692,7 @@
         <v>45961</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -16765,7 +16765,7 @@
         <v>45084</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -16838,7 +16838,7 @@
         <v>46188</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -16911,7 +16911,7 @@
         <v>45229</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -16984,7 +16984,7 @@
         <v>45922</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -17057,7 +17057,7 @@
         <v>46188</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -17130,7 +17130,7 @@
         <v>45252</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -17203,7 +17203,7 @@
         <v>44750</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -17276,7 +17276,7 @@
         <v>45368</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -17354,7 +17354,7 @@
         <v>45972</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -17427,7 +17427,7 @@
         <v>45972</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -17500,7 +17500,7 @@
         <v>44893</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -17573,7 +17573,7 @@
         <v>45972</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -17646,7 +17646,7 @@
         <v>46196</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -17719,7 +17719,7 @@
         <v>45541</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -17792,7 +17792,7 @@
         <v>45527</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -17865,7 +17865,7 @@
         <v>45062</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -17938,7 +17938,7 @@
         <v>46199</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -18011,7 +18011,7 @@
         <v>45979</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -18084,7 +18084,7 @@
         <v>45371</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -18157,7 +18157,7 @@
         <v>44868</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -18230,7 +18230,7 @@
         <v>45981</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -18303,7 +18303,7 @@
         <v>45737</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -18376,7 +18376,7 @@
         <v>45258</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -18449,7 +18449,7 @@
         <v>45981</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -18522,7 +18522,7 @@
         <v>45485</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -18595,7 +18595,7 @@
         <v>45462</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -18668,7 +18668,7 @@
         <v>45987</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -18741,7 +18741,7 @@
         <v>45560</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -18814,7 +18814,7 @@
         <v>46209</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -18887,7 +18887,7 @@
         <v>45089</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -18960,7 +18960,7 @@
         <v>46206</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -19033,7 +19033,7 @@
         <v>45989</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -19106,7 +19106,7 @@
         <v>45300</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -19179,7 +19179,7 @@
         <v>45352</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -19252,7 +19252,7 @@
         <v>45995</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -19325,7 +19325,7 @@
         <v>45097</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -19398,7 +19398,7 @@
         <v>45377</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -19476,7 +19476,7 @@
         <v>45176</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -19554,7 +19554,7 @@
         <v>45638</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -19627,7 +19627,7 @@
         <v>46224</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -19705,7 +19705,7 @@
         <v>45478</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -19778,7 +19778,7 @@
         <v>45351</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -19851,7 +19851,7 @@
         <v>45588</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -19929,7 +19929,7 @@
         <v>45926</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -20002,7 +20002,7 @@
         <v>45840</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -20080,7 +20080,7 @@
         <v>45616</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -20153,7 +20153,7 @@
         <v>45391</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -20226,7 +20226,7 @@
         <v>45510</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -20299,7 +20299,7 @@
         <v>46279</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -20372,7 +20372,7 @@
         <v>46279</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -20445,7 +20445,7 @@
         <v>46279</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -20518,7 +20518,7 @@
         <v>46036</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -20591,7 +20591,7 @@
         <v>45783</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -20664,7 +20664,7 @@
         <v>45616</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -20737,7 +20737,7 @@
         <v>45786</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -20815,7 +20815,7 @@
         <v>45559</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -20888,7 +20888,7 @@
         <v>44539</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -20961,7 +20961,7 @@
         <v>45680</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -21034,7 +21034,7 @@
         <v>45225</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -21107,7 +21107,7 @@
         <v>45589</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -21185,7 +21185,7 @@
         <v>45618</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -21258,7 +21258,7 @@
         <v>45726</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -21331,7 +21331,7 @@
         <v>45741</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -21404,7 +21404,7 @@
         <v>46020</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -21477,7 +21477,7 @@
         <v>45483</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -21550,7 +21550,7 @@
         <v>45609</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -21623,7 +21623,7 @@
         <v>46282</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -21696,7 +21696,7 @@
         <v>45483</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -21769,7 +21769,7 @@
         <v>46281</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -21842,7 +21842,7 @@
         <v>45743</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -21920,7 +21920,7 @@
         <v>45939</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -21998,7 +21998,7 @@
         <v>45590</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -22071,7 +22071,7 @@
         <v>45743</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -22149,7 +22149,7 @@
         <v>46241</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -22222,7 +22222,7 @@
         <v>46286</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -22295,7 +22295,7 @@
         <v>45559</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -22368,7 +22368,7 @@
         <v>45681</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -22441,7 +22441,7 @@
         <v>46286</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -22514,7 +22514,7 @@
         <v>45743</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -22592,7 +22592,7 @@
         <v>44851</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -22665,7 +22665,7 @@
         <v>46042</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -22738,7 +22738,7 @@
         <v>46283</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -22811,7 +22811,7 @@
         <v>46042</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -22884,7 +22884,7 @@
         <v>45793</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -22957,7 +22957,7 @@
         <v>46283</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -23030,7 +23030,7 @@
         <v>46245</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -23103,7 +23103,7 @@
         <v>46044</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -23176,7 +23176,7 @@
         <v>46044</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -23249,7 +23249,7 @@
         <v>46044</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -23322,7 +23322,7 @@
         <v>46044</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -23395,7 +23395,7 @@
         <v>46283</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -23468,7 +23468,7 @@
         <v>46048</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -23541,7 +23541,7 @@
         <v>46048</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -23614,7 +23614,7 @@
         <v>46048</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -23687,7 +23687,7 @@
         <v>46048</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -23760,7 +23760,7 @@
         <v>46048</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -23833,7 +23833,7 @@
         <v>46048</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -23906,7 +23906,7 @@
         <v>45600</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -23979,7 +23979,7 @@
         <v>46048</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -24052,7 +24052,7 @@
         <v>46048</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -24125,7 +24125,7 @@
         <v>46048</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -24198,7 +24198,7 @@
         <v>46048</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -24271,7 +24271,7 @@
         <v>46048</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -24344,7 +24344,7 @@
         <v>46048</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -24417,7 +24417,7 @@
         <v>46030</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -24490,7 +24490,7 @@
         <v>46281</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -24563,7 +24563,7 @@
         <v>46281</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -24636,7 +24636,7 @@
         <v>46049</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -24709,7 +24709,7 @@
         <v>46052</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -24782,7 +24782,7 @@
         <v>46052</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -24855,7 +24855,7 @@
         <v>44495</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -24928,7 +24928,7 @@
         <v>46247</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -25001,7 +25001,7 @@
         <v>45806</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -25074,7 +25074,7 @@
         <v>46055</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -25147,7 +25147,7 @@
         <v>46224</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -25220,7 +25220,7 @@
         <v>45400</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -25293,7 +25293,7 @@
         <v>45609</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -25366,7 +25366,7 @@
         <v>46057</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -25439,7 +25439,7 @@
         <v>46062</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -25512,7 +25512,7 @@
         <v>45812</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -25585,7 +25585,7 @@
         <v>46062</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -25658,7 +25658,7 @@
         <v>46064</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -25731,7 +25731,7 @@
         <v>46293</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -25804,7 +25804,7 @@
         <v>44950</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -25877,7 +25877,7 @@
         <v>45730</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -25950,7 +25950,7 @@
         <v>45694</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -26023,7 +26023,7 @@
         <v>45597</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -26096,7 +26096,7 @@
         <v>45708</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -26169,7 +26169,7 @@
         <v>46065</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -26242,7 +26242,7 @@
         <v>45387</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -26315,7 +26315,7 @@
         <v>45299</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -26388,7 +26388,7 @@
         <v>46248</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -26461,7 +26461,7 @@
         <v>46292</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -26534,7 +26534,7 @@
         <v>46070</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -26607,7 +26607,7 @@
         <v>45706</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -26680,7 +26680,7 @@
         <v>45820</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -26753,7 +26753,7 @@
         <v>46248</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -26826,7 +26826,7 @@
         <v>44900</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -26899,7 +26899,7 @@
         <v>46295</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -26972,7 +26972,7 @@
         <v>45825</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -27045,7 +27045,7 @@
         <v>45548</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -27118,7 +27118,7 @@
         <v>45831</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -27191,7 +27191,7 @@
         <v>46084</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -27264,7 +27264,7 @@
         <v>46161</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -27342,7 +27342,7 @@
         <v>46084</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -27415,7 +27415,7 @@
         <v>46087</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -27488,7 +27488,7 @@
         <v>45601</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -27561,7 +27561,7 @@
         <v>46244</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -27634,7 +27634,7 @@
         <v>45835</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -27707,7 +27707,7 @@
         <v>45836</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -27780,7 +27780,7 @@
         <v>45838</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -27853,7 +27853,7 @@
         <v>45840</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -27926,7 +27926,7 @@
         <v>45840</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -27999,7 +27999,7 @@
         <v>45840</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -28072,7 +28072,7 @@
         <v>46070</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -28145,7 +28145,7 @@
         <v>46093</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -28218,7 +28218,7 @@
         <v>46093</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -28291,7 +28291,7 @@
         <v>46093</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -28364,7 +28364,7 @@
         <v>45876</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -28437,7 +28437,7 @@
         <v>45845</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -28510,7 +28510,7 @@
         <v>45845</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -28583,7 +28583,7 @@
         <v>45800</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -28656,7 +28656,7 @@
         <v>45846</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -28734,7 +28734,7 @@
         <v>45846</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -28812,7 +28812,7 @@
         <v>45846</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -28890,7 +28890,7 @@
         <v>45352</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -28963,7 +28963,7 @@
         <v>46057</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -29036,7 +29036,7 @@
         <v>46302</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -29109,7 +29109,7 @@
         <v>44865</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -29182,7 +29182,7 @@
         <v>45847</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -29255,7 +29255,7 @@
         <v>45847</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -29328,7 +29328,7 @@
         <v>45803</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -29401,7 +29401,7 @@
         <v>46057</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -29474,7 +29474,7 @@
         <v>46111</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -29547,7 +29547,7 @@
         <v>46111</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -29620,7 +29620,7 @@
         <v>46111</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -29693,7 +29693,7 @@
         <v>46302</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -29766,7 +29766,7 @@
         <v>45352</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -29839,7 +29839,7 @@
         <v>46261</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -29912,7 +29912,7 @@
         <v>45700</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -29985,7 +29985,7 @@
         <v>45700</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -30058,7 +30058,7 @@
         <v>45687</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -30131,7 +30131,7 @@
         <v>44834</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -30204,7 +30204,7 @@
         <v>46294</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -30282,7 +30282,7 @@
         <v>45838</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -30355,7 +30355,7 @@
         <v>46121</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -30428,7 +30428,7 @@
         <v>46120</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -30501,7 +30501,7 @@
         <v>46292</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -30574,7 +30574,7 @@
         <v>46292</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -30647,7 +30647,7 @@
         <v>46292</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -30720,7 +30720,7 @@
         <v>46292</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -30793,7 +30793,7 @@
         <v>46121</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -30866,7 +30866,7 @@
         <v>46121</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -30939,7 +30939,7 @@
         <v>45288</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -31017,7 +31017,7 @@
         <v>45309</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -31090,7 +31090,7 @@
         <v>45407</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -31163,7 +31163,7 @@
         <v>45677</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -31236,7 +31236,7 @@
         <v>46121</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -31309,7 +31309,7 @@
         <v>46121</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -31382,7 +31382,7 @@
         <v>46120</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -31455,7 +31455,7 @@
         <v>45257</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -31528,7 +31528,7 @@
         <v>45395</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -31601,7 +31601,7 @@
         <v>44671</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -31674,7 +31674,7 @@
         <v>45524</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -31747,7 +31747,7 @@
         <v>45272</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -31820,7 +31820,7 @@
         <v>46121</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -31893,7 +31893,7 @@
         <v>46121</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -31966,7 +31966,7 @@
         <v>45245</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -32039,7 +32039,7 @@
         <v>45679</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -32112,7 +32112,7 @@
         <v>45610</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -32185,7 +32185,7 @@
         <v>46122</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -32258,7 +32258,7 @@
         <v>45432</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -32331,7 +32331,7 @@
         <v>44712</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -32404,7 +32404,7 @@
         <v>45131</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -32477,7 +32477,7 @@
         <v>45176</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -32550,7 +32550,7 @@
         <v>45372</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -32623,7 +32623,7 @@
         <v>45361</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -32696,7 +32696,7 @@
         <v>45541</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -32769,7 +32769,7 @@
         <v>45257</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -32847,7 +32847,7 @@
         <v>45727</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -32920,7 +32920,7 @@
         <v>44917</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -32993,7 +32993,7 @@
         <v>46122</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -33066,7 +33066,7 @@
         <v>45735</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -33139,7 +33139,7 @@
         <v>45672</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -33212,7 +33212,7 @@
         <v>45204</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -33285,7 +33285,7 @@
         <v>45293</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -33358,7 +33358,7 @@
         <v>45245</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -33431,7 +33431,7 @@
         <v>44671</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -33504,7 +33504,7 @@
         <v>44896</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -33577,7 +33577,7 @@
         <v>44592</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -33650,7 +33650,7 @@
         <v>46292</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -33723,7 +33723,7 @@
         <v>45293</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -33796,7 +33796,7 @@
         <v>45623</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -33869,7 +33869,7 @@
         <v>45199</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -33942,7 +33942,7 @@
         <v>46122</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -34015,7 +34015,7 @@
         <v>45769</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -34088,7 +34088,7 @@
         <v>45392</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -34161,7 +34161,7 @@
         <v>46261</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -34234,7 +34234,7 @@
         <v>45395</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -34307,7 +34307,7 @@
         <v>45589</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -34380,7 +34380,7 @@
         <v>46122</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -34453,7 +34453,7 @@
         <v>45546</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -34526,7 +34526,7 @@
         <v>46121</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -34599,7 +34599,7 @@
         <v>44701</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -34672,7 +34672,7 @@
         <v>45145</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -34745,7 +34745,7 @@
         <v>45517</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -34818,7 +34818,7 @@
         <v>45230</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -34891,7 +34891,7 @@
         <v>45677</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -34964,7 +34964,7 @@
         <v>45672</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -35037,7 +35037,7 @@
         <v>45672</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -35110,7 +35110,7 @@
         <v>44964</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -35183,7 +35183,7 @@
         <v>45735</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -35256,7 +35256,7 @@
         <v>44739</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -35329,7 +35329,7 @@
         <v>45309</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -35402,7 +35402,7 @@
         <v>44508</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -35475,7 +35475,7 @@
         <v>45623</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -35548,7 +35548,7 @@
         <v>45252</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -35621,7 +35621,7 @@
         <v>45589</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -35694,7 +35694,7 @@
         <v>45190</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -35767,7 +35767,7 @@
         <v>44817</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -35840,7 +35840,7 @@
         <v>45574</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -35913,7 +35913,7 @@
         <v>45545</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -35986,7 +35986,7 @@
         <v>45199</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -36059,7 +36059,7 @@
         <v>45190</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -36137,7 +36137,7 @@
         <v>44889</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -36210,7 +36210,7 @@
         <v>45623</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -36283,7 +36283,7 @@
         <v>46292</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -36356,7 +36356,7 @@
         <v>45880</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -36429,7 +36429,7 @@
         <v>45880</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -36502,7 +36502,7 @@
         <v>46128</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -36575,7 +36575,7 @@
         <v>45877</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -36648,7 +36648,7 @@
         <v>45880</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -36721,7 +36721,7 @@
         <v>45880</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -36794,7 +36794,7 @@
         <v>46263</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -36867,7 +36867,7 @@
         <v>44896</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -36940,7 +36940,7 @@
         <v>45429</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -37013,7 +37013,7 @@
         <v>45790</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -37086,7 +37086,7 @@
         <v>45366</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -37159,7 +37159,7 @@
         <v>45538</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -37232,7 +37232,7 @@
         <v>45840</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -37310,7 +37310,7 @@
         <v>45671</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -37383,7 +37383,7 @@
         <v>45775</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -37456,7 +37456,7 @@
         <v>45782</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -37529,7 +37529,7 @@
         <v>46268</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -37602,7 +37602,7 @@
         <v>44699</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -37675,7 +37675,7 @@
         <v>45524</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -37748,7 +37748,7 @@
         <v>45558</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -37821,7 +37821,7 @@
         <v>46268</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -37894,7 +37894,7 @@
         <v>45989</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -37967,7 +37967,7 @@
         <v>46084</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -38040,7 +38040,7 @@
         <v>46268</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -38113,7 +38113,7 @@
         <v>46272</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -38186,7 +38186,7 @@
         <v>45531</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -38259,7 +38259,7 @@
         <v>45817</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -38332,7 +38332,7 @@
         <v>45839</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -38405,7 +38405,7 @@
         <v>46316</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -38478,7 +38478,7 @@
         <v>44719</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -38551,7 +38551,7 @@
         <v>45848</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -38624,7 +38624,7 @@
         <v>46272</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -38697,7 +38697,7 @@
         <v>46273</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -38770,7 +38770,7 @@
         <v>46273</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -38843,7 +38843,7 @@
         <v>46273</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -38916,7 +38916,7 @@
         <v>44701</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -38994,7 +38994,7 @@
         <v>45259</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -39067,7 +39067,7 @@
         <v>44714</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -39140,7 +39140,7 @@
         <v>46317</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -39218,7 +39218,7 @@
         <v>46317</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -39296,7 +39296,7 @@
         <v>46317</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -39374,7 +39374,7 @@
         <v>46317</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -39447,7 +39447,7 @@
         <v>45617</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -39520,7 +39520,7 @@
         <v>44974</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -39593,7 +39593,7 @@
         <v>46318</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -39666,7 +39666,7 @@
         <v>45229</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -39739,7 +39739,7 @@
         <v>45198</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -39812,7 +39812,7 @@
         <v>46317</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -39885,7 +39885,7 @@
         <v>44900</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -39958,7 +39958,7 @@
         <v>46148</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -40031,7 +40031,7 @@
         <v>45441</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -40104,7 +40104,7 @@
         <v>44926</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -40182,7 +40182,7 @@
         <v>44756</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -40255,7 +40255,7 @@
         <v>45162</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -40328,7 +40328,7 @@
         <v>45162</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -40401,7 +40401,7 @@
         <v>45268</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -40474,7 +40474,7 @@
         <v>44903</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -40547,7 +40547,7 @@
         <v>46153</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -40620,7 +40620,7 @@
         <v>44999</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -40693,7 +40693,7 @@
         <v>46153</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -40766,7 +40766,7 @@
         <v>46153</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -40839,7 +40839,7 @@
         <v>46153</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -40912,7 +40912,7 @@
         <v>45709</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -40985,7 +40985,7 @@
         <v>46153</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -41058,7 +41058,7 @@
         <v>46153</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -41131,7 +41131,7 @@
         <v>46153</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -41204,7 +41204,7 @@
         <v>46155</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -41277,7 +41277,7 @@
         <v>45254</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -41350,7 +41350,7 @@
         <v>45460</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -41423,7 +41423,7 @@
         <v>44965</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -41501,7 +41501,7 @@
         <v>44970</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -41574,7 +41574,7 @@
         <v>44970</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -41647,7 +41647,7 @@
         <v>45107</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -41720,7 +41720,7 @@
         <v>45456</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -41793,7 +41793,7 @@
         <v>45092</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -41866,7 +41866,7 @@
         <v>45229</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -41939,7 +41939,7 @@
         <v>45002</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -42012,7 +42012,7 @@
         <v>45107</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -42085,7 +42085,7 @@
         <v>45645</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -42158,7 +42158,7 @@
         <v>45145</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -42231,7 +42231,7 @@
         <v>45638</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -42304,7 +42304,7 @@
         <v>45568</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -42377,7 +42377,7 @@
         <v>44712</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -42450,7 +42450,7 @@
         <v>44729</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -42523,7 +42523,7 @@
         <v>45483</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -42596,7 +42596,7 @@
         <v>44980</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -42669,7 +42669,7 @@
         <v>45246</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -42742,7 +42742,7 @@
         <v>45715</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -42815,7 +42815,7 @@
         <v>45544</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -42888,7 +42888,7 @@
         <v>45229</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -42961,7 +42961,7 @@
         <v>45502</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -43034,7 +43034,7 @@
         <v>44910</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -43107,7 +43107,7 @@
         <v>45019</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -43180,7 +43180,7 @@
         <v>45257</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -43253,7 +43253,7 @@
         <v>45754</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -43326,7 +43326,7 @@
         <v>45091</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -43399,7 +43399,7 @@
         <v>44869</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -43472,7 +43472,7 @@
         <v>45096</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -43545,7 +43545,7 @@
         <v>44900</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -43623,7 +43623,7 @@
         <v>45104</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -43696,7 +43696,7 @@
         <v>45441</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -43769,7 +43769,7 @@
         <v>45441</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -43842,7 +43842,7 @@
         <v>45229</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -43915,7 +43915,7 @@
         <v>45110</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -43988,7 +43988,7 @@
         <v>45170</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -44061,7 +44061,7 @@
         <v>45310</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -44134,7 +44134,7 @@
         <v>45694</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -44207,7 +44207,7 @@
         <v>45406</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -44280,7 +44280,7 @@
         <v>44967</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -44353,7 +44353,7 @@
         <v>45110</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -44426,7 +44426,7 @@
         <v>45145</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -44499,7 +44499,7 @@
         <v>45117</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -44572,7 +44572,7 @@
         <v>45352</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -44645,7 +44645,7 @@
         <v>45405</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -44718,7 +44718,7 @@
         <v>44530</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -44791,7 +44791,7 @@
         <v>45104</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -44864,7 +44864,7 @@
         <v>45454</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -44937,7 +44937,7 @@
         <v>44601</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -45010,7 +45010,7 @@
         <v>44510</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -45083,7 +45083,7 @@
         <v>45182</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -45156,7 +45156,7 @@
         <v>45539</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -45229,7 +45229,7 @@
         <v>45253</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -45302,7 +45302,7 @@
         <v>45531</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -45375,7 +45375,7 @@
         <v>45715</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -45448,7 +45448,7 @@
         <v>45182</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -45521,7 +45521,7 @@
         <v>45414</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -45594,7 +45594,7 @@
         <v>45643</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -45667,7 +45667,7 @@
         <v>45114</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -45740,7 +45740,7 @@
         <v>44970</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -45813,7 +45813,7 @@
         <v>45538</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -45886,7 +45886,7 @@
         <v>45170</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -45959,7 +45959,7 @@
         <v>45462</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -46032,7 +46032,7 @@
         <v>45170</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -46105,7 +46105,7 @@
         <v>45604</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -46178,7 +46178,7 @@
         <v>45091</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -46251,7 +46251,7 @@
         <v>45597</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -46324,7 +46324,7 @@
         <v>44641</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -46397,7 +46397,7 @@
         <v>45432</v>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -46470,7 +46470,7 @@
         <v>45159</v>
       </c>
       <c r="E610" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -46543,7 +46543,7 @@
         <v>45456</v>
       </c>
       <c r="E611" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
@@ -46616,7 +46616,7 @@
         <v>45366</v>
       </c>
       <c r="E612" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
@@ -46694,7 +46694,7 @@
         <v>44697</v>
       </c>
       <c r="E613" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
@@ -46767,7 +46767,7 @@
         <v>45194</v>
       </c>
       <c r="E614" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F614" t="inlineStr">
         <is>
@@ -46840,7 +46840,7 @@
         <v>45203</v>
       </c>
       <c r="E615" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F615" t="inlineStr">
         <is>
@@ -46913,7 +46913,7 @@
         <v>45677</v>
       </c>
       <c r="E616" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F616" t="inlineStr">
         <is>
@@ -46986,7 +46986,7 @@
         <v>45132</v>
       </c>
       <c r="E617" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F617" t="inlineStr">
         <is>
@@ -47059,7 +47059,7 @@
         <v>45173</v>
       </c>
       <c r="E618" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F618" t="inlineStr">
         <is>
@@ -47132,7 +47132,7 @@
         <v>45153</v>
       </c>
       <c r="E619" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F619" t="inlineStr">
         <is>
@@ -47205,7 +47205,7 @@
         <v>45084</v>
       </c>
       <c r="E620" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F620" t="inlineStr">
         <is>
@@ -47278,7 +47278,7 @@
         <v>45254</v>
       </c>
       <c r="E621" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F621" t="inlineStr">
         <is>
@@ -47351,7 +47351,7 @@
         <v>45211</v>
       </c>
       <c r="E622" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F622" t="inlineStr">
         <is>
@@ -47424,7 +47424,7 @@
         <v>45568</v>
       </c>
       <c r="E623" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F623" t="inlineStr">
         <is>
@@ -47497,7 +47497,7 @@
         <v>45441</v>
       </c>
       <c r="E624" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F624" t="inlineStr">
         <is>
@@ -47575,7 +47575,7 @@
         <v>45456</v>
       </c>
       <c r="E625" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F625" t="inlineStr">
         <is>
@@ -47648,7 +47648,7 @@
         <v>45225</v>
       </c>
       <c r="E626" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F626" t="inlineStr">
         <is>
@@ -47721,7 +47721,7 @@
         <v>45181</v>
       </c>
       <c r="E627" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F627" t="inlineStr">
         <is>
@@ -47794,7 +47794,7 @@
         <v>44823</v>
       </c>
       <c r="E628" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F628" t="inlineStr">
         <is>
@@ -47867,7 +47867,7 @@
         <v>45238</v>
       </c>
       <c r="E629" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F629" t="inlineStr">
         <is>
@@ -47940,7 +47940,7 @@
         <v>45287</v>
       </c>
       <c r="E630" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F630" t="inlineStr">
         <is>
@@ -48013,7 +48013,7 @@
         <v>44701</v>
       </c>
       <c r="E631" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F631" t="inlineStr">
         <is>
@@ -48091,7 +48091,7 @@
         <v>44735</v>
       </c>
       <c r="E632" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F632" t="inlineStr">
         <is>
@@ -48164,7 +48164,7 @@
         <v>44651</v>
       </c>
       <c r="E633" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F633" t="inlineStr">
         <is>
@@ -48237,7 +48237,7 @@
         <v>45169</v>
       </c>
       <c r="E634" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F634" t="inlineStr">
         <is>
@@ -48310,7 +48310,7 @@
         <v>45316</v>
       </c>
       <c r="E635" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F635" t="inlineStr">
         <is>
@@ -48388,7 +48388,7 @@
         <v>45167</v>
       </c>
       <c r="E636" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F636" t="inlineStr">
         <is>
@@ -48461,7 +48461,7 @@
         <v>45254</v>
       </c>
       <c r="E637" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F637" t="inlineStr">
         <is>
@@ -48534,7 +48534,7 @@
         <v>45254</v>
       </c>
       <c r="E638" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F638" t="inlineStr">
         <is>
@@ -48607,7 +48607,7 @@
         <v>45245</v>
       </c>
       <c r="E639" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F639" t="inlineStr">
         <is>
@@ -48680,7 +48680,7 @@
         <v>44778</v>
       </c>
       <c r="E640" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F640" t="inlineStr">
         <is>
@@ -48753,7 +48753,7 @@
         <v>44847</v>
       </c>
       <c r="E641" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F641" t="inlineStr">
         <is>
@@ -48826,7 +48826,7 @@
         <v>44694</v>
       </c>
       <c r="E642" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F642" t="inlineStr">
         <is>
@@ -48899,7 +48899,7 @@
         <v>45245</v>
       </c>
       <c r="E643" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F643" t="inlineStr">
         <is>
@@ -48972,7 +48972,7 @@
         <v>45092</v>
       </c>
       <c r="E644" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F644" t="inlineStr">
         <is>
@@ -49045,7 +49045,7 @@
         <v>45051</v>
       </c>
       <c r="E645" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F645" t="inlineStr">
         <is>
@@ -49118,7 +49118,7 @@
         <v>45098</v>
       </c>
       <c r="E646" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F646" t="inlineStr">
         <is>
@@ -49196,7 +49196,7 @@
         <v>45351</v>
       </c>
       <c r="E647" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F647" t="inlineStr">
         <is>
@@ -49269,7 +49269,7 @@
         <v>44797</v>
       </c>
       <c r="E648" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F648" t="inlineStr">
         <is>
@@ -49342,7 +49342,7 @@
         <v>45267</v>
       </c>
       <c r="E649" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F649" t="inlineStr">
         <is>
@@ -49415,7 +49415,7 @@
         <v>44974</v>
       </c>
       <c r="E650" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F650" t="inlineStr">
         <is>
@@ -49488,7 +49488,7 @@
         <v>44559</v>
       </c>
       <c r="E651" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F651" t="inlineStr">
         <is>
@@ -49561,7 +49561,7 @@
         <v>44893</v>
       </c>
       <c r="E652" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F652" t="inlineStr">
         <is>
@@ -49634,7 +49634,7 @@
         <v>45455</v>
       </c>
       <c r="E653" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F653" t="inlineStr">
         <is>
@@ -49707,7 +49707,7 @@
         <v>45104</v>
       </c>
       <c r="E654" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F654" t="inlineStr">
         <is>
@@ -49780,7 +49780,7 @@
         <v>45334</v>
       </c>
       <c r="E655" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F655" t="inlineStr">
         <is>
@@ -49853,7 +49853,7 @@
         <v>45352</v>
       </c>
       <c r="E656" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F656" t="inlineStr">
         <is>
@@ -49926,7 +49926,7 @@
         <v>45715</v>
       </c>
       <c r="E657" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F657" t="inlineStr">
         <is>
@@ -49999,7 +49999,7 @@
         <v>45316</v>
       </c>
       <c r="E658" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F658" t="inlineStr">
         <is>
@@ -50072,7 +50072,7 @@
         <v>44796</v>
       </c>
       <c r="E659" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F659" t="inlineStr">
         <is>
@@ -50145,7 +50145,7 @@
         <v>44901</v>
       </c>
       <c r="E660" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F660" t="inlineStr">
         <is>
@@ -50218,7 +50218,7 @@
         <v>45589</v>
       </c>
       <c r="E661" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F661" t="inlineStr">
         <is>
@@ -50291,7 +50291,7 @@
         <v>44899</v>
       </c>
       <c r="E662" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F662" t="inlineStr">
         <is>
@@ -50364,7 +50364,7 @@
         <v>44995</v>
       </c>
       <c r="E663" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F663" t="inlineStr">
         <is>
@@ -50437,7 +50437,7 @@
         <v>45548</v>
       </c>
       <c r="E664" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F664" t="inlineStr">
         <is>
@@ -50510,7 +50510,7 @@
         <v>44958</v>
       </c>
       <c r="E665" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F665" t="inlineStr">
         <is>
@@ -50583,7 +50583,7 @@
         <v>44575</v>
       </c>
       <c r="E666" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F666" t="inlineStr">
         <is>
@@ -50656,7 +50656,7 @@
         <v>45572</v>
       </c>
       <c r="E667" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F667" t="inlineStr">
         <is>
@@ -50729,7 +50729,7 @@
         <v>44951</v>
       </c>
       <c r="E668" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F668" t="inlineStr">
         <is>
@@ -50802,7 +50802,7 @@
         <v>45265</v>
       </c>
       <c r="E669" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F669" t="inlineStr">
         <is>
@@ -50875,7 +50875,7 @@
         <v>45432</v>
       </c>
       <c r="E670" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F670" t="inlineStr">
         <is>
@@ -50948,7 +50948,7 @@
         <v>44631</v>
       </c>
       <c r="E671" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F671" t="inlineStr">
         <is>
@@ -51021,7 +51021,7 @@
         <v>44613</v>
       </c>
       <c r="E672" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F672" t="inlineStr">
         <is>
@@ -51094,7 +51094,7 @@
         <v>44608</v>
       </c>
       <c r="E673" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F673" t="inlineStr">
         <is>
@@ -51167,7 +51167,7 @@
         <v>44631</v>
       </c>
       <c r="E674" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F674" t="inlineStr">
         <is>
@@ -51240,7 +51240,7 @@
         <v>44631</v>
       </c>
       <c r="E675" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F675" t="inlineStr">
         <is>
@@ -51313,7 +51313,7 @@
         <v>45614</v>
       </c>
       <c r="E676" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F676" t="inlineStr">
         <is>
@@ -51391,7 +51391,7 @@
         <v>44743</v>
       </c>
       <c r="E677" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F677" t="inlineStr">
         <is>
@@ -51464,7 +51464,7 @@
         <v>45375</v>
       </c>
       <c r="E678" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F678" t="inlineStr">
         <is>
@@ -51537,7 +51537,7 @@
         <v>45604</v>
       </c>
       <c r="E679" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F679" t="inlineStr">
         <is>
@@ -51610,7 +51610,7 @@
         <v>45356</v>
       </c>
       <c r="E680" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F680" t="inlineStr">
         <is>
@@ -51683,7 +51683,7 @@
         <v>45349</v>
       </c>
       <c r="E681" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F681" t="inlineStr">
         <is>
@@ -51756,7 +51756,7 @@
         <v>45744</v>
       </c>
       <c r="E682" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F682" t="inlineStr">
         <is>
@@ -51829,7 +51829,7 @@
         <v>45714</v>
       </c>
       <c r="E683" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F683" t="inlineStr">
         <is>
@@ -51902,7 +51902,7 @@
         <v>45715</v>
       </c>
       <c r="E684" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F684" t="inlineStr">
         <is>
@@ -51975,7 +51975,7 @@
         <v>45709</v>
       </c>
       <c r="E685" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F685" t="inlineStr">
         <is>
@@ -52048,7 +52048,7 @@
         <v>45714</v>
       </c>
       <c r="E686" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F686" t="inlineStr">
         <is>
@@ -52121,7 +52121,7 @@
         <v>45813</v>
       </c>
       <c r="E687" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F687" t="inlineStr">
         <is>
@@ -52194,7 +52194,7 @@
         <v>45813</v>
       </c>
       <c r="E688" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F688" t="inlineStr">
         <is>
@@ -52267,7 +52267,7 @@
         <v>45813</v>
       </c>
       <c r="E689" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F689" t="inlineStr">
         <is>
@@ -52340,7 +52340,7 @@
         <v>45820</v>
       </c>
       <c r="E690" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F690" t="inlineStr">
         <is>
@@ -52413,7 +52413,7 @@
         <v>45827</v>
       </c>
       <c r="E691" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F691" t="inlineStr">
         <is>
@@ -52486,7 +52486,7 @@
         <v>45845</v>
       </c>
       <c r="E692" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F692" t="inlineStr">
         <is>
@@ -52559,7 +52559,7 @@
         <v>45883</v>
       </c>
       <c r="E693" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F693" t="inlineStr">
         <is>
@@ -52632,7 +52632,7 @@
         <v>45915</v>
       </c>
       <c r="E694" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F694" t="inlineStr">
         <is>
@@ -52705,7 +52705,7 @@
         <v>46041</v>
       </c>
       <c r="E695" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F695" t="inlineStr">
         <is>
@@ -52778,7 +52778,7 @@
         <v>46133</v>
       </c>
       <c r="E696" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F696" t="inlineStr">
         <is>
@@ -52851,7 +52851,7 @@
         <v>46147</v>
       </c>
       <c r="E697" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F697" t="inlineStr">
         <is>
@@ -52924,7 +52924,7 @@
         <v>46211</v>
       </c>
       <c r="E698" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F698" t="inlineStr">
         <is>
@@ -52997,7 +52997,7 @@
         <v>46290</v>
       </c>
       <c r="E699" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F699" t="inlineStr">
         <is>
@@ -53070,7 +53070,7 @@
         <v>46253</v>
       </c>
       <c r="E700" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F700" t="inlineStr">
         <is>
